--- a/pendencias-condicionantes-2026-10-23.xlsx
+++ b/pendencias-condicionantes-2026-10-23.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="346">
   <si>
     <t xml:space="preserve">Condicionantes ambientais – pendências</t>
   </si>
@@ -59,10 +59,7 @@
     <t xml:space="preserve">Renovação da licença</t>
   </si>
   <si>
-    <t xml:space="preserve">IBAMA – Certificado de Regularidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBAMA – TCFA em aberto</t>
+    <t xml:space="preserve">IBAMA – Certificado de Regularidade / TCFA</t>
   </si>
   <si>
     <t xml:space="preserve">Publicação da concessão</t>
@@ -188,7 +185,7 @@
     <t xml:space="preserve">Documento na pasta: Certificado de Regularidade (CTF/APP) emitido em 18/08/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitir novo Certificado de Regularidade (CTF/APP) no site do IBAMA (vale 3 meses) e arquivar na pasta.</t>
+    <t xml:space="preserve">Conferir se a TCFA (boletos trimestrais) está paga e emitir novo Certificado de Regularidade (CTF/APP) no site do IBAMA (vale 3 meses); arquivar na pasta.</t>
   </si>
   <si>
     <t xml:space="preserve">Documento na pasta: AVCB nº 65529 emitido em 18/11/2025</t>
@@ -413,10 +410,7 @@
     <t xml:space="preserve">2025-250825/TEC/RLO-0982</t>
   </si>
   <si>
-    <t xml:space="preserve">Documento na pasta: 6 boletos TCFA em aberto na pasta: 2022/3 a 2023/4, todos com vencimento em 31/01/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conferir o pagamento dos boletos TCFA em aberto (2022/3 a 2023/4); se não pagos, emitir 2ª via ou parcelamento no IBAMA.</t>
+    <t xml:space="preserve">Documento na pasta: Sem certificado na pasta; 6 boletos TCFA em aberto (2022/3 a 2023/4), todos vencidos em 31/01/2024</t>
   </si>
   <si>
     <t xml:space="preserve">Documento na pasta: AVCB emitido em 05/08/2025</t>
@@ -1729,7 +1723,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -1801,7 +1795,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A7,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A7,Pendências!$J$2:$J$135,"Sem data")</f>
@@ -1813,7 +1807,7 @@
       </c>
       <c r="E7" s="7" t="n">
         <f aca="false">SUM(B7:D7)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1822,7 +1816,7 @@
       </c>
       <c r="B8" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A8,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A8,Pendências!$J$2:$J$135,"Sem data")</f>
@@ -1834,7 +1828,7 @@
       </c>
       <c r="E8" s="7" t="n">
         <f aca="false">SUM(B8:D8)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1843,7 +1837,7 @@
       </c>
       <c r="B9" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A9,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C9" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A9,Pendências!$J$2:$J$135,"Sem data")</f>
@@ -1851,11 +1845,11 @@
       </c>
       <c r="D9" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A9,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
         <f aca="false">SUM(B9:D9)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1864,19 +1858,19 @@
       </c>
       <c r="B10" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A10,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A10,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A10,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="7" t="n">
         <f aca="false">SUM(B10:D10)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1885,19 +1879,19 @@
       </c>
       <c r="B11" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A11,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C11" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A11,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D11" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A11,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" s="7" t="n">
         <f aca="false">SUM(B11:D11)</f>
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1906,7 +1900,7 @@
       </c>
       <c r="B12" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A12,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C12" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A12,Pendências!$J$2:$J$135,"Sem data")</f>
@@ -1914,11 +1908,11 @@
       </c>
       <c r="D12" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A12,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
         <f aca="false">SUM(B12:D12)</f>
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1927,19 +1921,19 @@
       </c>
       <c r="B13" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A13,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="C13" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A13,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D13" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A13,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E13" s="7" t="n">
         <f aca="false">SUM(B13:D13)</f>
-        <v>44</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1952,15 +1946,15 @@
       </c>
       <c r="C14" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A14,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A14,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
         <f aca="false">SUM(B14:D14)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1969,11 +1963,11 @@
       </c>
       <c r="B15" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A15,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A15,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A15,Pendências!$J$2:$J$135,"Vence em breve")</f>
@@ -1994,7 +1988,7 @@
       </c>
       <c r="C16" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A16,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A16,Pendências!$J$2:$J$135,"Vence em breve")</f>
@@ -2002,54 +1996,42 @@
       </c>
       <c r="E16" s="7" t="n">
         <f aca="false">SUM(B16:D16)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A17,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A17,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>3</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A17,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <f aca="false">SUM(B17:D17)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+      <c r="B17" s="8" t="n">
+        <f aca="false">SUM(B6:B16)</f>
+        <v>92</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <f aca="false">SUM(C6:C16)</f>
+        <v>31</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <f aca="false">SUM(D6:D16)</f>
+        <v>11</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <f aca="false">SUM(E6:E16)</f>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="8" t="n">
-        <f aca="false">SUM(B6:B17)</f>
-        <v>92</v>
-      </c>
-      <c r="C18" s="8" t="n">
-        <f aca="false">SUM(C6:C17)</f>
-        <v>31</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <f aca="false">SUM(D6:D17)</f>
-        <v>11</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <f aca="false">SUM(E6:E17)</f>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="6" t="n">
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$135,A20)</f>
         <v>134</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2058,7 +2040,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">COUNTIF(Pendências!$P$2:$P$135,A21)</f>
-        <v>134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2088,18 +2070,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="B25" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$135,A25)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2142,58 +2115,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>34</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>35</v>
       </c>
       <c r="H1" s="9" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,19 +2174,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D2" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>50</v>
       </c>
       <c r="G2" s="12" t="n">
         <v>46505</v>
@@ -2223,7 +2196,7 @@
       </c>
       <c r="I2" s="10"/>
       <c r="J2" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K2" s="12" t="n">
         <v>46344</v>
@@ -2233,14 +2206,14 @@
         <v>26</v>
       </c>
       <c r="M2" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="N2" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="O2" s="14"/>
       <c r="P2" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q2" s="15"/>
       <c r="R2" s="14"/>
@@ -2250,31 +2223,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="F3" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>50</v>
       </c>
       <c r="G3" s="12" t="n">
         <v>46505</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I3" s="10" t="n">
         <v>4</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K3" s="12" t="n">
         <v>46344</v>
@@ -2284,14 +2257,14 @@
         <v>26</v>
       </c>
       <c r="M3" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="N3" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="O3" s="14"/>
       <c r="P3" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q3" s="15"/>
       <c r="R3" s="14"/>
@@ -2301,31 +2274,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>50</v>
       </c>
       <c r="G4" s="12" t="n">
         <v>46505</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I4" s="10" t="n">
         <v>13</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K4" s="12" t="n">
         <v>46281</v>
@@ -2335,14 +2308,14 @@
         <v>-37</v>
       </c>
       <c r="M4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="O4" s="14"/>
       <c r="P4" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q4" s="15"/>
       <c r="R4" s="14"/>
@@ -2352,31 +2325,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="E5" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="F5" s="10" t="s">
         <v>62</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>63</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>47374</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K5" s="12" t="n">
         <v>45995</v>
@@ -2386,14 +2359,14 @@
         <v>-323</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q5" s="15"/>
       <c r="R5" s="14"/>
@@ -2403,31 +2376,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="F6" s="10" t="s">
         <v>62</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>63</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>47374</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>16</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K6" s="12" t="n">
         <v>46281</v>
@@ -2437,14 +2410,14 @@
         <v>-37</v>
       </c>
       <c r="M6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N6" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="N6" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="O6" s="14"/>
       <c r="P6" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q6" s="15"/>
       <c r="R6" s="14"/>
@@ -2454,31 +2427,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="E7" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="F7" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>68</v>
       </c>
       <c r="G7" s="12" t="n">
         <v>47584</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K7" s="12" t="n">
         <v>46309</v>
@@ -2488,14 +2461,14 @@
         <v>-9</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q7" s="15"/>
       <c r="R7" s="14"/>
@@ -2505,31 +2478,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>68</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>47584</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>17</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K8" s="12" t="n">
         <v>46281</v>
@@ -2539,14 +2512,14 @@
         <v>-37</v>
       </c>
       <c r="M8" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="N8" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q8" s="15"/>
       <c r="R8" s="14"/>
@@ -2556,25 +2529,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="E9" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="F9" s="10" t="s">
         <v>72</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>73</v>
       </c>
       <c r="G9" s="12" t="n">
         <v>46546</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>14</v>
@@ -2588,14 +2561,14 @@
         <v/>
       </c>
       <c r="M9" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O9" s="14"/>
       <c r="P9" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q9" s="15"/>
       <c r="R9" s="14"/>
@@ -2605,31 +2578,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="D10" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="F10" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>79</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>46764</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>21</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K10" s="12" t="n">
         <v>46101</v>
@@ -2639,14 +2612,14 @@
         <v>-217</v>
       </c>
       <c r="M10" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N10" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="N10" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q10" s="15"/>
       <c r="R10" s="14"/>
@@ -2656,31 +2629,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="D11" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="E11" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="F11" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>79</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>46764</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>19</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>46181</v>
@@ -2690,14 +2663,14 @@
         <v>-137</v>
       </c>
       <c r="M11" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="N11" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="N11" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q11" s="15"/>
       <c r="R11" s="14"/>
@@ -2707,31 +2680,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C12" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="E12" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="F12" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>79</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>46764</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>46150</v>
@@ -2741,14 +2714,14 @@
         <v>-168</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O12" s="14"/>
       <c r="P12" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q12" s="15"/>
       <c r="R12" s="14"/>
@@ -2758,31 +2731,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C13" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="E13" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="F13" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>79</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>46764</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>16</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>46282</v>
@@ -2792,14 +2765,14 @@
         <v>-36</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O13" s="14"/>
       <c r="P13" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q13" s="15"/>
       <c r="R13" s="14"/>
@@ -2809,25 +2782,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="E14" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="F14" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>79</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>46764</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>15</v>
@@ -2841,14 +2814,14 @@
         <v/>
       </c>
       <c r="M14" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O14" s="14"/>
       <c r="P14" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q14" s="15"/>
       <c r="R14" s="14"/>
@@ -2858,31 +2831,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="D15" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="E15" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="F15" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>79</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>46764</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>15</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>46042</v>
@@ -2892,14 +2865,14 @@
         <v>-276</v>
       </c>
       <c r="M15" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="N15" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="O15" s="14"/>
       <c r="P15" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q15" s="15"/>
       <c r="R15" s="14"/>
@@ -2909,25 +2882,25 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="E16" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="F16" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>79</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>46764</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>8</v>
@@ -2941,14 +2914,14 @@
         <v/>
       </c>
       <c r="M16" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O16" s="14"/>
       <c r="P16" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q16" s="15"/>
       <c r="R16" s="14"/>
@@ -2958,19 +2931,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C17" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="F17" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>46374</v>
@@ -2982,7 +2955,7 @@
         <v>21</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>46254</v>
@@ -2992,14 +2965,14 @@
         <v>-64</v>
       </c>
       <c r="M17" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="N17" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="N17" s="10" t="s">
-        <v>95</v>
       </c>
       <c r="O17" s="14"/>
       <c r="P17" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q17" s="15"/>
       <c r="R17" s="14"/>
@@ -3009,19 +2982,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C18" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="E18" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="F18" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>46374</v>
@@ -3031,7 +3004,7 @@
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>46303</v>
@@ -3041,14 +3014,14 @@
         <v>-15</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O18" s="14"/>
       <c r="P18" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q18" s="15"/>
       <c r="R18" s="14"/>
@@ -3058,25 +3031,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="E19" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="F19" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>46374</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>5</v>
@@ -3090,14 +3063,14 @@
         <v/>
       </c>
       <c r="M19" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O19" s="14"/>
       <c r="P19" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q19" s="15"/>
       <c r="R19" s="14"/>
@@ -3107,25 +3080,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C20" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="E20" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="F20" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>46374</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>17</v>
@@ -3139,14 +3112,14 @@
         <v/>
       </c>
       <c r="M20" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O20" s="14"/>
       <c r="P20" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q20" s="15"/>
       <c r="R20" s="14"/>
@@ -3156,25 +3129,25 @@
         <v>20</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C21" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="E21" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="F21" s="10" t="s">
         <v>99</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>100</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>48100</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>16</v>
@@ -3188,14 +3161,14 @@
         <v/>
       </c>
       <c r="M21" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O21" s="14"/>
       <c r="P21" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q21" s="15"/>
       <c r="R21" s="14"/>
@@ -3205,19 +3178,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C22" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="E22" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="F22" s="10" t="s">
         <v>103</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>104</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>44080</v>
@@ -3229,7 +3202,7 @@
         <v>24</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>43960</v>
@@ -3239,14 +3212,14 @@
         <v>-2358</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O22" s="14"/>
       <c r="P22" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q22" s="15"/>
       <c r="R22" s="14"/>
@@ -3256,19 +3229,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C23" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="E23" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="F23" s="10" t="s">
         <v>103</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>104</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>44080</v>
@@ -3278,7 +3251,7 @@
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>46346</v>
@@ -3288,14 +3261,14 @@
         <v>28</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O23" s="14"/>
       <c r="P23" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q23" s="15"/>
       <c r="R23" s="14"/>
@@ -3305,25 +3278,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C24" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="E24" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="F24" s="10" t="s">
         <v>103</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>104</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>44080</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>5</v>
@@ -3337,14 +3310,14 @@
         <v/>
       </c>
       <c r="M24" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O24" s="14"/>
       <c r="P24" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q24" s="15"/>
       <c r="R24" s="14"/>
@@ -3354,25 +3327,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="E25" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="F25" s="10" t="s">
         <v>103</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>104</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>44080</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>15</v>
@@ -3386,14 +3359,14 @@
         <v/>
       </c>
       <c r="M25" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O25" s="14"/>
       <c r="P25" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q25" s="15"/>
       <c r="R25" s="14"/>
@@ -3403,25 +3376,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C26" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="E26" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="F26" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>110</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>46595</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>5</v>
@@ -3435,14 +3408,14 @@
         <v/>
       </c>
       <c r="M26" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O26" s="14"/>
       <c r="P26" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q26" s="15"/>
       <c r="R26" s="14"/>
@@ -3452,25 +3425,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C27" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="E27" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="F27" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>110</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>46595</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>15</v>
@@ -3484,14 +3457,14 @@
         <v/>
       </c>
       <c r="M27" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O27" s="14"/>
       <c r="P27" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q27" s="15"/>
       <c r="R27" s="14"/>
@@ -3501,31 +3474,31 @@
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C28" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="E28" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="F28" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>19</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>46034</v>
@@ -3535,14 +3508,14 @@
         <v>-284</v>
       </c>
       <c r="M28" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N28" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="N28" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="O28" s="14"/>
       <c r="P28" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q28" s="15"/>
       <c r="R28" s="14"/>
@@ -3552,31 +3525,31 @@
         <v>28</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C29" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="E29" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="F29" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>17</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>46114</v>
@@ -3586,14 +3559,14 @@
         <v>-204</v>
       </c>
       <c r="M29" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="N29" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="N29" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="O29" s="14"/>
       <c r="P29" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q29" s="15"/>
       <c r="R29" s="14"/>
@@ -3603,31 +3576,31 @@
         <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C30" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="E30" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="F30" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>15</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>46281</v>
@@ -3637,14 +3610,14 @@
         <v>-37</v>
       </c>
       <c r="M30" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N30" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="N30" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="O30" s="14"/>
       <c r="P30" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q30" s="15"/>
       <c r="R30" s="14"/>
@@ -3654,25 +3627,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C31" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="E31" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="F31" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>8</v>
@@ -3686,14 +3659,14 @@
         <v/>
       </c>
       <c r="M31" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O31" s="14"/>
       <c r="P31" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q31" s="15"/>
       <c r="R31" s="14"/>
@@ -3703,25 +3676,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="E32" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="F32" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>14</v>
@@ -3735,14 +3708,14 @@
         <v/>
       </c>
       <c r="M32" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N32" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O32" s="14"/>
       <c r="P32" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q32" s="15"/>
       <c r="R32" s="14"/>
@@ -3752,25 +3725,25 @@
         <v>32</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C33" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="E33" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="F33" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>8</v>
@@ -3784,14 +3757,14 @@
         <v/>
       </c>
       <c r="M33" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O33" s="14"/>
       <c r="P33" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q33" s="15"/>
       <c r="R33" s="14"/>
@@ -3801,31 +3774,31 @@
         <v>33</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C34" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="E34" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="F34" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>47766</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>4</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>45995</v>
@@ -3835,14 +3808,14 @@
         <v>-323</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N34" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O34" s="14"/>
       <c r="P34" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q34" s="15"/>
       <c r="R34" s="14"/>
@@ -3852,31 +3825,31 @@
         <v>34</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C35" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="E35" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="F35" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>122</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>47037</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>46225</v>
@@ -3886,14 +3859,14 @@
         <v>-93</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O35" s="14"/>
       <c r="P35" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q35" s="15"/>
       <c r="R35" s="14"/>
@@ -3903,31 +3876,31 @@
         <v>35</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C36" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D36" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="E36" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="F36" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>122</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>47037</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>15</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>46282</v>
@@ -3937,46 +3910,46 @@
         <v>-36</v>
       </c>
       <c r="M36" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N36" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O36" s="14"/>
       <c r="P36" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q36" s="15"/>
       <c r="R36" s="14"/>
     </row>
-    <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C37" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="E37" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="F37" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>48208</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>45322</v>
@@ -3986,14 +3959,14 @@
         <v>-996</v>
       </c>
       <c r="M37" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="O37" s="14"/>
       <c r="P37" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q37" s="15"/>
       <c r="R37" s="14"/>
@@ -4003,31 +3976,31 @@
         <v>37</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C38" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="E38" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="F38" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>48208</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>46239</v>
@@ -4037,14 +4010,14 @@
         <v>-79</v>
       </c>
       <c r="M38" s="10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N38" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O38" s="14"/>
       <c r="P38" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q38" s="15"/>
       <c r="R38" s="14"/>
@@ -4054,31 +4027,31 @@
         <v>38</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C39" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="E39" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="F39" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>48208</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>10</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>46282</v>
@@ -4088,14 +4061,14 @@
         <v>-36</v>
       </c>
       <c r="M39" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O39" s="14"/>
       <c r="P39" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q39" s="15"/>
       <c r="R39" s="14"/>
@@ -4105,25 +4078,25 @@
         <v>39</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D40" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="E40" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="F40" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="F40" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>48208</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>11</v>
@@ -4137,14 +4110,14 @@
         <v/>
       </c>
       <c r="M40" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N40" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="O40" s="14"/>
       <c r="P40" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q40" s="15"/>
       <c r="R40" s="14"/>
@@ -4154,31 +4127,31 @@
         <v>40</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C41" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="E41" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="F41" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>47333</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>14</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>46282</v>
@@ -4188,14 +4161,14 @@
         <v>-36</v>
       </c>
       <c r="M41" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O41" s="14"/>
       <c r="P41" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q41" s="15"/>
       <c r="R41" s="14"/>
@@ -4205,31 +4178,31 @@
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C42" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F42" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>48394</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>22</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>46212</v>
@@ -4239,14 +4212,14 @@
         <v>-106</v>
       </c>
       <c r="M42" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N42" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="N42" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="O42" s="14"/>
       <c r="P42" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q42" s="15"/>
       <c r="R42" s="14"/>
@@ -4256,31 +4229,31 @@
         <v>42</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C43" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F43" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>48394</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>19</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>46292</v>
@@ -4290,14 +4263,14 @@
         <v>-26</v>
       </c>
       <c r="M43" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="N43" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="N43" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="O43" s="14"/>
       <c r="P43" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q43" s="15"/>
       <c r="R43" s="14"/>
@@ -4307,31 +4280,31 @@
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C44" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F44" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>48394</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>46323</v>
@@ -4341,14 +4314,14 @@
         <v>5</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N44" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O44" s="14"/>
       <c r="P44" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q44" s="15"/>
       <c r="R44" s="14"/>
@@ -4358,31 +4331,31 @@
         <v>44</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C45" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F45" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>48394</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>15</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>46282</v>
@@ -4392,14 +4365,14 @@
         <v>-36</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O45" s="14"/>
       <c r="P45" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q45" s="15"/>
       <c r="R45" s="14"/>
@@ -4409,31 +4382,31 @@
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C46" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F46" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F46" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>48394</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>14</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>44478</v>
@@ -4443,14 +4416,14 @@
         <v>-1840</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N46" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O46" s="14"/>
       <c r="P46" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q46" s="15"/>
       <c r="R46" s="14"/>
@@ -4460,25 +4433,25 @@
         <v>46</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F47" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>48394</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>14</v>
@@ -4492,14 +4465,14 @@
         <v/>
       </c>
       <c r="M47" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O47" s="14"/>
       <c r="P47" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q47" s="15"/>
       <c r="R47" s="14"/>
@@ -4509,25 +4482,25 @@
         <v>47</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F48" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>48394</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>8</v>
@@ -4541,14 +4514,14 @@
         <v/>
       </c>
       <c r="M48" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N48" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O48" s="14"/>
       <c r="P48" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q48" s="15"/>
       <c r="R48" s="14"/>
@@ -4558,19 +4531,19 @@
         <v>48</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C49" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="E49" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="F49" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="F49" s="10" t="s">
-        <v>144</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>47129</v>
@@ -4580,7 +4553,7 @@
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>46273</v>
@@ -4590,14 +4563,14 @@
         <v>-45</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O49" s="14"/>
       <c r="P49" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q49" s="15"/>
       <c r="R49" s="14"/>
@@ -4607,25 +4580,25 @@
         <v>49</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C50" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="E50" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="F50" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>144</v>
       </c>
       <c r="G50" s="12" t="n">
         <v>47129</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>5</v>
@@ -4639,14 +4612,14 @@
         <v/>
       </c>
       <c r="M50" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N50" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O50" s="14"/>
       <c r="P50" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q50" s="15"/>
       <c r="R50" s="14"/>
@@ -4656,31 +4629,31 @@
         <v>50</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C51" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="E51" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="F51" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>144</v>
       </c>
       <c r="G51" s="12" t="n">
         <v>47129</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>17</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>46282</v>
@@ -4690,14 +4663,14 @@
         <v>-36</v>
       </c>
       <c r="M51" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O51" s="14"/>
       <c r="P51" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q51" s="15"/>
       <c r="R51" s="14"/>
@@ -4707,31 +4680,31 @@
         <v>51</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C52" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="E52" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="F52" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>144</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>47129</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>8</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>46337</v>
@@ -4741,14 +4714,14 @@
         <v>19</v>
       </c>
       <c r="M52" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N52" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O52" s="14"/>
       <c r="P52" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q52" s="15"/>
       <c r="R52" s="14"/>
@@ -4758,31 +4731,31 @@
         <v>52</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C53" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F53" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>46872</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>15</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>46281</v>
@@ -4792,14 +4765,14 @@
         <v>-37</v>
       </c>
       <c r="M53" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N53" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="N53" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="O53" s="14"/>
       <c r="P53" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q53" s="15"/>
       <c r="R53" s="14"/>
@@ -4809,19 +4782,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C54" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E54" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="F54" s="10" t="s">
         <v>151</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="F54" s="10" t="s">
-        <v>153</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>46374</v>
@@ -4833,7 +4806,7 @@
         <v>20</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>46254</v>
@@ -4843,14 +4816,14 @@
         <v>-64</v>
       </c>
       <c r="M54" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="N54" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="N54" s="10" t="s">
-        <v>95</v>
       </c>
       <c r="O54" s="14"/>
       <c r="P54" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q54" s="15"/>
       <c r="R54" s="14"/>
@@ -4860,25 +4833,25 @@
         <v>54</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C55" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E55" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="F55" s="10" t="s">
         <v>151</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>153</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>46374</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I55" s="10" t="n">
         <v>5</v>
@@ -4892,14 +4865,14 @@
         <v/>
       </c>
       <c r="M55" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O55" s="14"/>
       <c r="P55" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q55" s="15"/>
       <c r="R55" s="14"/>
@@ -4909,31 +4882,31 @@
         <v>55</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C56" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E56" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="F56" s="10" t="s">
         <v>151</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="F56" s="10" t="s">
-        <v>153</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>46374</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I56" s="10" t="n">
         <v>15</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K56" s="12" t="n">
         <v>46282</v>
@@ -4943,14 +4916,14 @@
         <v>-36</v>
       </c>
       <c r="M56" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N56" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O56" s="14"/>
       <c r="P56" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q56" s="15"/>
       <c r="R56" s="14"/>
@@ -4960,29 +4933,29 @@
         <v>56</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C57" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E57" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="D57" s="10" t="s">
+      <c r="F57" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>157</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>46911</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K57" s="12" t="n">
         <v>46282</v>
@@ -4992,14 +4965,14 @@
         <v>-36</v>
       </c>
       <c r="M57" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O57" s="14"/>
       <c r="P57" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q57" s="15"/>
       <c r="R57" s="14"/>
@@ -5009,25 +4982,25 @@
         <v>57</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C58" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="E58" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="F58" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="F58" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="G58" s="12" t="n">
         <v>46875</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" s="10" t="s">
@@ -5039,14 +5012,14 @@
         <v/>
       </c>
       <c r="M58" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N58" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O58" s="14"/>
       <c r="P58" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q58" s="15"/>
       <c r="R58" s="14"/>
@@ -5056,29 +5029,29 @@
         <v>58</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C59" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="E59" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="D59" s="10" t="s">
+      <c r="F59" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="F59" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="G59" s="12" t="n">
         <v>46875</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K59" s="12" t="n">
         <v>46282</v>
@@ -5088,14 +5061,14 @@
         <v>-36</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O59" s="14"/>
       <c r="P59" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q59" s="15"/>
       <c r="R59" s="14"/>
@@ -5105,31 +5078,31 @@
         <v>59</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C60" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E60" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="F60" s="10" t="s">
         <v>163</v>
-      </c>
-      <c r="E60" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="F60" s="10" t="s">
-        <v>165</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>47952</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I60" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K60" s="12" t="n">
         <v>45898</v>
@@ -5139,14 +5112,14 @@
         <v>-420</v>
       </c>
       <c r="M60" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N60" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O60" s="14"/>
       <c r="P60" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q60" s="15"/>
       <c r="R60" s="14"/>
@@ -5156,31 +5129,31 @@
         <v>60</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C61" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E61" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="D61" s="10" t="s">
+      <c r="F61" s="10" t="s">
         <v>163</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="F61" s="10" t="s">
-        <v>165</v>
       </c>
       <c r="G61" s="12" t="n">
         <v>47952</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I61" s="10" t="n">
         <v>17</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K61" s="12" t="n">
         <v>46281</v>
@@ -5190,14 +5163,14 @@
         <v>-37</v>
       </c>
       <c r="M61" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N61" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="N61" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="O61" s="14"/>
       <c r="P61" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q61" s="15"/>
       <c r="R61" s="14"/>
@@ -5207,31 +5180,31 @@
         <v>61</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C62" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="E62" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="F62" s="10" t="s">
         <v>168</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="F62" s="10" t="s">
-        <v>170</v>
       </c>
       <c r="G62" s="12" t="n">
         <v>46990</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I62" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K62" s="12" t="n">
         <v>46163</v>
@@ -5241,14 +5214,14 @@
         <v>-155</v>
       </c>
       <c r="M62" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N62" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O62" s="14"/>
       <c r="P62" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q62" s="15"/>
       <c r="R62" s="14"/>
@@ -5258,31 +5231,31 @@
         <v>62</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C63" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="E63" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="F63" s="10" t="s">
         <v>168</v>
-      </c>
-      <c r="E63" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="F63" s="10" t="s">
-        <v>170</v>
       </c>
       <c r="G63" s="12" t="n">
         <v>46990</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I63" s="10" t="n">
         <v>16</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K63" s="12" t="n">
         <v>46281</v>
@@ -5292,14 +5265,14 @@
         <v>-37</v>
       </c>
       <c r="M63" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N63" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="N63" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="O63" s="14"/>
       <c r="P63" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q63" s="15"/>
       <c r="R63" s="14"/>
@@ -5309,19 +5282,19 @@
         <v>63</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C64" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F64" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F64" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="G64" s="12" t="n">
         <v>47087</v>
@@ -5331,7 +5304,7 @@
       </c>
       <c r="I64" s="10"/>
       <c r="J64" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K64" s="12" t="n">
         <v>46274</v>
@@ -5341,14 +5314,14 @@
         <v>-44</v>
       </c>
       <c r="M64" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N64" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O64" s="14"/>
       <c r="P64" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q64" s="15"/>
       <c r="R64" s="14"/>
@@ -5358,31 +5331,31 @@
         <v>64</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C65" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F65" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="D65" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F65" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="G65" s="12" t="n">
         <v>47087</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I65" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K65" s="12" t="n">
         <v>45997</v>
@@ -5392,14 +5365,14 @@
         <v>-321</v>
       </c>
       <c r="M65" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O65" s="14"/>
       <c r="P65" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q65" s="15"/>
       <c r="R65" s="14"/>
@@ -5409,31 +5382,31 @@
         <v>65</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C66" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F66" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F66" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="G66" s="12" t="n">
         <v>47087</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I66" s="10" t="n">
         <v>16</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K66" s="12" t="n">
         <v>46281</v>
@@ -5443,14 +5416,14 @@
         <v>-37</v>
       </c>
       <c r="M66" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N66" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="N66" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="O66" s="14"/>
       <c r="P66" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q66" s="15"/>
       <c r="R66" s="14"/>
@@ -5460,19 +5433,19 @@
         <v>66</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C67" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F67" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E67" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F67" s="10" t="s">
-        <v>179</v>
       </c>
       <c r="G67" s="12" t="n">
         <v>47854</v>
@@ -5482,7 +5455,7 @@
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K67" s="12" t="n">
         <v>46316</v>
@@ -5492,14 +5465,14 @@
         <v>-2</v>
       </c>
       <c r="M67" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O67" s="14"/>
       <c r="P67" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q67" s="15"/>
       <c r="R67" s="14"/>
@@ -5509,31 +5482,31 @@
         <v>67</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C68" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F68" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F68" s="10" t="s">
-        <v>179</v>
       </c>
       <c r="G68" s="12" t="n">
         <v>47854</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I68" s="10" t="n">
         <v>18</v>
       </c>
       <c r="J68" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K68" s="12" t="n">
         <v>46281</v>
@@ -5543,14 +5516,14 @@
         <v>-37</v>
       </c>
       <c r="M68" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N68" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="N68" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="O68" s="14"/>
       <c r="P68" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q68" s="15"/>
       <c r="R68" s="14"/>
@@ -5560,19 +5533,19 @@
         <v>68</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C69" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E69" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="D69" s="10" t="s">
+      <c r="F69" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="F69" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="G69" s="12" t="n">
         <v>46031</v>
@@ -5584,7 +5557,7 @@
         <v>19</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K69" s="12" t="n">
         <v>45911</v>
@@ -5594,14 +5567,14 @@
         <v>-407</v>
       </c>
       <c r="M69" s="10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O69" s="14"/>
       <c r="P69" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q69" s="15"/>
       <c r="R69" s="14"/>
@@ -5611,19 +5584,19 @@
         <v>69</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C70" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E70" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="D70" s="10" t="s">
+      <c r="F70" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="F70" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>46031</v>
@@ -5633,7 +5606,7 @@
       </c>
       <c r="I70" s="10"/>
       <c r="J70" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K70" s="12" t="n">
         <v>45659</v>
@@ -5643,14 +5616,14 @@
         <v>-659</v>
       </c>
       <c r="M70" s="10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="N70" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O70" s="14"/>
       <c r="P70" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q70" s="15"/>
       <c r="R70" s="14"/>
@@ -5660,31 +5633,31 @@
         <v>70</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C71" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E71" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="D71" s="10" t="s">
+      <c r="F71" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="F71" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I71" s="10" t="n">
         <v>14</v>
       </c>
       <c r="J71" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K71" s="12" t="n">
         <v>46083</v>
@@ -5694,14 +5667,14 @@
         <v>-235</v>
       </c>
       <c r="M71" s="10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="O71" s="14"/>
       <c r="P71" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q71" s="15"/>
       <c r="R71" s="14"/>
@@ -5711,31 +5684,31 @@
         <v>71</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C72" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E72" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="D72" s="10" t="s">
+      <c r="F72" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="E72" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="F72" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="G72" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I72" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K72" s="12" t="n">
         <v>45514</v>
@@ -5745,14 +5718,14 @@
         <v>-804</v>
       </c>
       <c r="M72" s="10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N72" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O72" s="14"/>
       <c r="P72" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q72" s="15"/>
       <c r="R72" s="14"/>
@@ -5762,31 +5735,31 @@
         <v>72</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C73" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E73" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="D73" s="10" t="s">
+      <c r="F73" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="F73" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="G73" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I73" s="10" t="n">
         <v>15</v>
       </c>
       <c r="J73" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K73" s="12" t="n">
         <v>45356</v>
@@ -5796,14 +5769,14 @@
         <v>-962</v>
       </c>
       <c r="M73" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O73" s="14"/>
       <c r="P73" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q73" s="15"/>
       <c r="R73" s="14"/>
@@ -5813,25 +5786,25 @@
         <v>73</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C74" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E74" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="F74" s="10" t="s">
         <v>192</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="F74" s="10" t="s">
-        <v>194</v>
       </c>
       <c r="G74" s="12" t="n">
         <v>46729</v>
       </c>
       <c r="H74" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I74" s="10" t="n">
         <v>15</v>
@@ -5845,14 +5818,14 @@
         <v/>
       </c>
       <c r="M74" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N74" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O74" s="14"/>
       <c r="P74" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q74" s="15"/>
       <c r="R74" s="14"/>
@@ -5862,19 +5835,19 @@
         <v>74</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C75" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F75" s="10" t="s">
         <v>195</v>
-      </c>
-      <c r="D75" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="F75" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>48171</v>
@@ -5884,7 +5857,7 @@
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K75" s="12" t="n">
         <v>46272</v>
@@ -5894,14 +5867,14 @@
         <v>-46</v>
       </c>
       <c r="M75" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O75" s="14"/>
       <c r="P75" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q75" s="15"/>
       <c r="R75" s="14"/>
@@ -5911,31 +5884,31 @@
         <v>75</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C76" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F76" s="10" t="s">
         <v>195</v>
-      </c>
-      <c r="D76" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="F76" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="G76" s="12" t="n">
         <v>48171</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I76" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J76" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K76" s="12" t="n">
         <v>46309</v>
@@ -5945,14 +5918,14 @@
         <v>-9</v>
       </c>
       <c r="M76" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N76" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O76" s="14"/>
       <c r="P76" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q76" s="15"/>
       <c r="R76" s="14"/>
@@ -5962,31 +5935,31 @@
         <v>76</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C77" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F77" s="10" t="s">
         <v>195</v>
-      </c>
-      <c r="D77" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="F77" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="G77" s="12" t="n">
         <v>48171</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I77" s="10" t="n">
         <v>15</v>
       </c>
       <c r="J77" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K77" s="12" t="n">
         <v>46281</v>
@@ -5996,14 +5969,14 @@
         <v>-37</v>
       </c>
       <c r="M77" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N77" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="N77" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="O77" s="14"/>
       <c r="P77" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q77" s="15"/>
       <c r="R77" s="14"/>
@@ -6013,19 +5986,19 @@
         <v>77</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C78" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="E78" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="D78" s="10" t="s">
+      <c r="F78" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="F78" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="G78" s="12" t="n">
         <v>46288</v>
@@ -6037,7 +6010,7 @@
         <v>18</v>
       </c>
       <c r="J78" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K78" s="12" t="n">
         <v>46168</v>
@@ -6047,14 +6020,14 @@
         <v>-150</v>
       </c>
       <c r="M78" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N78" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O78" s="14"/>
       <c r="P78" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q78" s="15"/>
       <c r="R78" s="14"/>
@@ -6064,31 +6037,31 @@
         <v>78</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C79" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="E79" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="D79" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="E79" s="10" t="s">
-        <v>202</v>
-      </c>
       <c r="F79" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G79" s="12" t="n">
         <v>48005</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I79" s="10" t="n">
         <v>12</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K79" s="12" t="n">
         <v>46163</v>
@@ -6098,14 +6071,14 @@
         <v>-155</v>
       </c>
       <c r="M79" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N79" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="N79" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="O79" s="14"/>
       <c r="P79" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q79" s="15"/>
       <c r="R79" s="14"/>
@@ -6115,25 +6088,25 @@
         <v>79</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C80" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="E80" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="D80" s="10" t="s">
+      <c r="F80" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="F80" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="G80" s="12" t="n">
         <v>46288</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I80" s="10" t="n">
         <v>4</v>
@@ -6147,14 +6120,14 @@
         <v/>
       </c>
       <c r="M80" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N80" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O80" s="14"/>
       <c r="P80" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q80" s="15"/>
       <c r="R80" s="14"/>
@@ -6164,31 +6137,31 @@
         <v>80</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C81" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="E81" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="D81" s="10" t="s">
+      <c r="F81" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="F81" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="G81" s="12" t="n">
         <v>46288</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I81" s="10" t="n">
         <v>14</v>
       </c>
       <c r="J81" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K81" s="12" t="n">
         <v>46283</v>
@@ -6198,14 +6171,14 @@
         <v>-35</v>
       </c>
       <c r="M81" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O81" s="14"/>
       <c r="P81" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q81" s="15"/>
       <c r="R81" s="14"/>
@@ -6215,31 +6188,31 @@
         <v>81</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C82" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="E82" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="D82" s="10" t="s">
+      <c r="F82" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F82" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="G82" s="12" t="n">
         <v>46798</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I82" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K82" s="12" t="n">
         <v>46323</v>
@@ -6249,14 +6222,14 @@
         <v>5</v>
       </c>
       <c r="M82" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N82" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O82" s="14"/>
       <c r="P82" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q82" s="15"/>
       <c r="R82" s="14"/>
@@ -6266,31 +6239,31 @@
         <v>82</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C83" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="E83" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="D83" s="10" t="s">
+      <c r="F83" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F83" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>46798</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I83" s="10" t="n">
         <v>16</v>
       </c>
       <c r="J83" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K83" s="12" t="n">
         <v>46281</v>
@@ -6300,14 +6273,14 @@
         <v>-37</v>
       </c>
       <c r="M83" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N83" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="N83" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="O83" s="14"/>
       <c r="P83" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q83" s="15"/>
       <c r="R83" s="14"/>
@@ -6317,25 +6290,25 @@
         <v>83</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C84" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="E84" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="D84" s="10" t="s">
+      <c r="F84" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F84" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>46798</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I84" s="10" t="n">
         <v>15</v>
@@ -6349,14 +6322,14 @@
         <v/>
       </c>
       <c r="M84" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N84" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="O84" s="14"/>
       <c r="P84" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q84" s="15"/>
       <c r="R84" s="14"/>
@@ -6366,31 +6339,31 @@
         <v>84</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C85" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E85" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="D85" s="10" t="s">
+      <c r="F85" s="10" t="s">
         <v>213</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="F85" s="10" t="s">
-        <v>215</v>
       </c>
       <c r="G85" s="12" t="n">
         <v>47004</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I85" s="10" t="n">
         <v>16</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K85" s="12" t="n">
         <v>46280</v>
@@ -6400,14 +6373,14 @@
         <v>-38</v>
       </c>
       <c r="M85" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O85" s="14"/>
       <c r="P85" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q85" s="15"/>
       <c r="R85" s="14"/>
@@ -6417,31 +6390,31 @@
         <v>85</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C86" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E86" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="D86" s="10" t="s">
+      <c r="F86" s="10" t="s">
         <v>213</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="F86" s="10" t="s">
-        <v>215</v>
       </c>
       <c r="G86" s="12" t="n">
         <v>47004</v>
       </c>
       <c r="H86" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I86" s="10" t="n">
         <v>15</v>
       </c>
       <c r="J86" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K86" s="12" t="n">
         <v>46344</v>
@@ -6451,14 +6424,14 @@
         <v>26</v>
       </c>
       <c r="M86" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N86" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O86" s="14"/>
       <c r="P86" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q86" s="15"/>
       <c r="R86" s="14"/>
@@ -6468,19 +6441,19 @@
         <v>86</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C87" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="F87" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="D87" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="F87" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="G87" s="12" t="n">
         <v>46046</v>
@@ -6492,7 +6465,7 @@
         <v>20</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K87" s="12" t="n">
         <v>45926</v>
@@ -6502,14 +6475,14 @@
         <v>-392</v>
       </c>
       <c r="M87" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O87" s="14"/>
       <c r="P87" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q87" s="15"/>
       <c r="R87" s="14"/>
@@ -6519,19 +6492,19 @@
         <v>87</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C88" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="F88" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="D88" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="F88" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="G88" s="12" t="n">
         <v>46046</v>
@@ -6541,7 +6514,7 @@
       </c>
       <c r="I88" s="10"/>
       <c r="J88" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K88" s="12" t="n">
         <v>45823</v>
@@ -6551,14 +6524,14 @@
         <v>-495</v>
       </c>
       <c r="M88" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N88" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O88" s="14"/>
       <c r="P88" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q88" s="15"/>
       <c r="R88" s="14"/>
@@ -6568,31 +6541,31 @@
         <v>88</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C89" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="F89" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="D89" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="F89" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="G89" s="12" t="n">
         <v>46046</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I89" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K89" s="12" t="n">
         <v>46058</v>
@@ -6602,14 +6575,14 @@
         <v>-260</v>
       </c>
       <c r="M89" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O89" s="14"/>
       <c r="P89" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q89" s="15"/>
       <c r="R89" s="14"/>
@@ -6619,31 +6592,31 @@
         <v>89</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C90" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="F90" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="D90" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="F90" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="G90" s="12" t="n">
         <v>46046</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I90" s="10" t="n">
         <v>15</v>
       </c>
       <c r="J90" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K90" s="12" t="n">
         <v>46281</v>
@@ -6653,14 +6626,14 @@
         <v>-37</v>
       </c>
       <c r="M90" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N90" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="N90" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="O90" s="14"/>
       <c r="P90" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q90" s="15"/>
       <c r="R90" s="14"/>
@@ -6670,31 +6643,31 @@
         <v>90</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C91" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="F91" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="D91" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E91" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="F91" s="10" t="s">
-        <v>226</v>
       </c>
       <c r="G91" s="12" t="n">
         <v>46970</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I91" s="10" t="n">
         <v>15</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K91" s="12" t="n">
         <v>46281</v>
@@ -6704,14 +6677,14 @@
         <v>-37</v>
       </c>
       <c r="M91" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N91" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="N91" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="O91" s="14"/>
       <c r="P91" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q91" s="15"/>
       <c r="R91" s="14"/>
@@ -6721,19 +6694,19 @@
         <v>91</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C92" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E92" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="D92" s="10" t="s">
+      <c r="F92" s="10" t="s">
         <v>228</v>
-      </c>
-      <c r="E92" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="F92" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="G92" s="12" t="n">
         <v>46505</v>
@@ -6743,7 +6716,7 @@
       </c>
       <c r="I92" s="10"/>
       <c r="J92" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K92" s="12" t="n">
         <v>46319</v>
@@ -6753,14 +6726,14 @@
         <v>1</v>
       </c>
       <c r="M92" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N92" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O92" s="14"/>
       <c r="P92" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q92" s="15"/>
       <c r="R92" s="14"/>
@@ -6770,31 +6743,31 @@
         <v>92</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C93" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E93" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="D93" s="10" t="s">
+      <c r="F93" s="10" t="s">
         <v>228</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="F93" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="G93" s="12" t="n">
         <v>46505</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I93" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K93" s="12" t="n">
         <v>45891</v>
@@ -6804,14 +6777,14 @@
         <v>-427</v>
       </c>
       <c r="M93" s="10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O93" s="14"/>
       <c r="P93" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q93" s="15"/>
       <c r="R93" s="14"/>
@@ -6821,31 +6794,31 @@
         <v>93</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C94" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E94" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="D94" s="10" t="s">
+      <c r="F94" s="10" t="s">
         <v>228</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="F94" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="G94" s="12" t="n">
         <v>46505</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I94" s="10" t="n">
         <v>15</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K94" s="12" t="n">
         <v>46282</v>
@@ -6855,14 +6828,14 @@
         <v>-36</v>
       </c>
       <c r="M94" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N94" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O94" s="14"/>
       <c r="P94" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q94" s="15"/>
       <c r="R94" s="14"/>
@@ -6872,19 +6845,19 @@
         <v>94</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C95" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="E95" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="D95" s="10" t="s">
+      <c r="F95" s="10" t="s">
         <v>234</v>
-      </c>
-      <c r="E95" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="F95" s="10" t="s">
-        <v>236</v>
       </c>
       <c r="G95" s="12" t="n">
         <v>46346</v>
@@ -6894,7 +6867,7 @@
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K95" s="12" t="n">
         <v>46226</v>
@@ -6904,14 +6877,14 @@
         <v>-92</v>
       </c>
       <c r="M95" s="10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O95" s="14"/>
       <c r="P95" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q95" s="15"/>
       <c r="R95" s="14"/>
@@ -6921,29 +6894,29 @@
         <v>95</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C96" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="E96" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="D96" s="10" t="s">
+      <c r="F96" s="10" t="s">
         <v>234</v>
-      </c>
-      <c r="E96" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="F96" s="10" t="s">
-        <v>236</v>
       </c>
       <c r="G96" s="12" t="n">
         <v>46346</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I96" s="10"/>
       <c r="J96" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K96" s="12" t="n">
         <v>46282</v>
@@ -6953,14 +6926,14 @@
         <v>-36</v>
       </c>
       <c r="M96" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N96" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O96" s="14"/>
       <c r="P96" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q96" s="15"/>
       <c r="R96" s="14"/>
@@ -6970,19 +6943,19 @@
         <v>96</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C97" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D97" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F97" s="10" t="s">
         <v>238</v>
-      </c>
-      <c r="D97" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E97" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="F97" s="10" t="s">
-        <v>240</v>
       </c>
       <c r="G97" s="12" t="n">
         <v>46373</v>
@@ -6994,7 +6967,7 @@
         <v>22</v>
       </c>
       <c r="J97" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K97" s="12" t="n">
         <v>46253</v>
@@ -7004,14 +6977,14 @@
         <v>-65</v>
       </c>
       <c r="M97" s="10" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O97" s="14"/>
       <c r="P97" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q97" s="15"/>
       <c r="R97" s="14"/>
@@ -7021,31 +6994,31 @@
         <v>97</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C98" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D98" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F98" s="10" t="s">
         <v>238</v>
-      </c>
-      <c r="D98" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="F98" s="10" t="s">
-        <v>240</v>
       </c>
       <c r="G98" s="12" t="n">
         <v>46373</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I98" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J98" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K98" s="12" t="n">
         <v>45192</v>
@@ -7055,14 +7028,14 @@
         <v>-1126</v>
       </c>
       <c r="M98" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="N98" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O98" s="14"/>
       <c r="P98" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q98" s="15"/>
       <c r="R98" s="14"/>
@@ -7072,31 +7045,31 @@
         <v>98</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C99" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D99" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F99" s="10" t="s">
         <v>238</v>
-      </c>
-      <c r="D99" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="F99" s="10" t="s">
-        <v>240</v>
       </c>
       <c r="G99" s="12" t="n">
         <v>46373</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I99" s="10" t="n">
         <v>16</v>
       </c>
       <c r="J99" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K99" s="12" t="n">
         <v>45262</v>
@@ -7106,14 +7079,14 @@
         <v>-1056</v>
       </c>
       <c r="M99" s="10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O99" s="14"/>
       <c r="P99" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q99" s="15"/>
       <c r="R99" s="14"/>
@@ -7123,31 +7096,31 @@
         <v>99</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C100" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="D100" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="E100" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="D100" s="10" t="s">
+      <c r="F100" s="10" t="s">
         <v>245</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="F100" s="10" t="s">
-        <v>247</v>
       </c>
       <c r="G100" s="12" t="n">
         <v>48010</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I100" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J100" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K100" s="12" t="n">
         <v>46127</v>
@@ -7157,14 +7130,14 @@
         <v>-191</v>
       </c>
       <c r="M100" s="10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="N100" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O100" s="14"/>
       <c r="P100" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q100" s="15"/>
       <c r="R100" s="14"/>
@@ -7174,31 +7147,31 @@
         <v>100</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C101" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="D101" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="E101" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="D101" s="10" t="s">
+      <c r="F101" s="10" t="s">
         <v>245</v>
-      </c>
-      <c r="E101" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="F101" s="10" t="s">
-        <v>247</v>
       </c>
       <c r="G101" s="12" t="n">
         <v>48010</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I101" s="10" t="n">
         <v>15</v>
       </c>
       <c r="J101" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K101" s="12" t="n">
         <v>46280</v>
@@ -7208,14 +7181,14 @@
         <v>-38</v>
       </c>
       <c r="M101" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O101" s="14"/>
       <c r="P101" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q101" s="15"/>
       <c r="R101" s="14"/>
@@ -7225,19 +7198,19 @@
         <v>101</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C102" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="D102" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="E102" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="D102" s="10" t="s">
+      <c r="F102" s="10" t="s">
         <v>250</v>
-      </c>
-      <c r="E102" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="F102" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="G102" s="12" t="n">
         <v>46043</v>
@@ -7249,7 +7222,7 @@
         <v>21</v>
       </c>
       <c r="J102" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K102" s="12" t="n">
         <v>45923</v>
@@ -7259,14 +7232,14 @@
         <v>-395</v>
       </c>
       <c r="M102" s="10" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="N102" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O102" s="14"/>
       <c r="P102" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q102" s="15"/>
       <c r="R102" s="14"/>
@@ -7276,31 +7249,31 @@
         <v>102</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C103" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="D103" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="E103" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="D103" s="10" t="s">
+      <c r="F103" s="10" t="s">
         <v>250</v>
-      </c>
-      <c r="E103" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="F103" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="G103" s="12" t="n">
         <v>46043</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I103" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J103" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K103" s="12" t="n">
         <v>46113</v>
@@ -7310,14 +7283,14 @@
         <v>-205</v>
       </c>
       <c r="M103" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O103" s="14"/>
       <c r="P103" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q103" s="15"/>
       <c r="R103" s="14"/>
@@ -7327,31 +7300,31 @@
         <v>103</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C104" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="D104" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="E104" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="D104" s="10" t="s">
+      <c r="F104" s="10" t="s">
         <v>250</v>
-      </c>
-      <c r="E104" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="F104" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="G104" s="12" t="n">
         <v>46043</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I104" s="10" t="n">
         <v>17</v>
       </c>
       <c r="J104" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K104" s="12" t="n">
         <v>45351</v>
@@ -7361,14 +7334,14 @@
         <v>-967</v>
       </c>
       <c r="M104" s="10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="N104" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O104" s="14"/>
       <c r="P104" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q104" s="15"/>
       <c r="R104" s="14"/>
@@ -7378,19 +7351,19 @@
         <v>104</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C105" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D105" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F105" s="10" t="s">
         <v>256</v>
-      </c>
-      <c r="D105" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="E105" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="F105" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="G105" s="12" t="n">
         <v>46408</v>
@@ -7402,7 +7375,7 @@
         <v>19</v>
       </c>
       <c r="J105" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K105" s="12" t="n">
         <v>46288</v>
@@ -7412,14 +7385,14 @@
         <v>-30</v>
       </c>
       <c r="M105" s="10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O105" s="14"/>
       <c r="P105" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q105" s="15"/>
       <c r="R105" s="14"/>
@@ -7429,31 +7402,31 @@
         <v>105</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C106" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D106" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F106" s="10" t="s">
         <v>256</v>
-      </c>
-      <c r="D106" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="E106" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="F106" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="G106" s="12" t="n">
         <v>46408</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I106" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K106" s="12" t="n">
         <v>46113</v>
@@ -7463,14 +7436,14 @@
         <v>-205</v>
       </c>
       <c r="M106" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N106" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O106" s="14"/>
       <c r="P106" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q106" s="15"/>
       <c r="R106" s="14"/>
@@ -7480,31 +7453,31 @@
         <v>106</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C107" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F107" s="10" t="s">
         <v>256</v>
-      </c>
-      <c r="D107" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="F107" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="G107" s="12" t="n">
         <v>46408</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I107" s="10" t="n">
         <v>15</v>
       </c>
       <c r="J107" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K107" s="12" t="n">
         <v>46282</v>
@@ -7514,14 +7487,14 @@
         <v>-36</v>
       </c>
       <c r="M107" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O107" s="14"/>
       <c r="P107" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q107" s="15"/>
       <c r="R107" s="14"/>
@@ -7531,25 +7504,25 @@
         <v>107</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C108" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="D108" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="F108" s="10" t="s">
         <v>260</v>
-      </c>
-      <c r="D108" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E108" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="F108" s="10" t="s">
-        <v>262</v>
       </c>
       <c r="G108" s="12" t="n">
         <v>47310</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I108" s="10" t="n">
         <v>9</v>
@@ -7563,14 +7536,14 @@
         <v/>
       </c>
       <c r="M108" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N108" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="O108" s="14"/>
       <c r="P108" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q108" s="15"/>
       <c r="R108" s="14"/>
@@ -7580,25 +7553,25 @@
         <v>108</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C109" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="D109" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="F109" s="10" t="s">
         <v>260</v>
-      </c>
-      <c r="D109" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E109" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="F109" s="10" t="s">
-        <v>262</v>
       </c>
       <c r="G109" s="12" t="n">
         <v>47310</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I109" s="10" t="n">
         <v>5</v>
@@ -7612,14 +7585,14 @@
         <v/>
       </c>
       <c r="M109" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O109" s="14"/>
       <c r="P109" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q109" s="15"/>
       <c r="R109" s="14"/>
@@ -7629,31 +7602,31 @@
         <v>109</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C110" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="D110" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="F110" s="10" t="s">
         <v>260</v>
-      </c>
-      <c r="D110" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="F110" s="10" t="s">
-        <v>262</v>
       </c>
       <c r="G110" s="12" t="n">
         <v>47310</v>
       </c>
       <c r="H110" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I110" s="10" t="n">
         <v>16</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K110" s="12" t="n">
         <v>46043</v>
@@ -7663,14 +7636,14 @@
         <v>-275</v>
       </c>
       <c r="M110" s="10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N110" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O110" s="14"/>
       <c r="P110" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q110" s="15"/>
       <c r="R110" s="14"/>
@@ -7680,31 +7653,31 @@
         <v>110</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C111" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="D111" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="F111" s="10" t="s">
         <v>264</v>
-      </c>
-      <c r="D111" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="E111" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="F111" s="10" t="s">
-        <v>266</v>
       </c>
       <c r="G111" s="12" t="n">
         <v>46658</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I111" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J111" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K111" s="12" t="n">
         <v>46107</v>
@@ -7714,14 +7687,14 @@
         <v>-211</v>
       </c>
       <c r="M111" s="10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O111" s="14"/>
       <c r="P111" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q111" s="15"/>
       <c r="R111" s="14"/>
@@ -7731,31 +7704,31 @@
         <v>111</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C112" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="D112" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="F112" s="10" t="s">
         <v>264</v>
-      </c>
-      <c r="D112" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="E112" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="F112" s="10" t="s">
-        <v>266</v>
       </c>
       <c r="G112" s="12" t="n">
         <v>46658</v>
       </c>
       <c r="H112" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I112" s="10" t="n">
         <v>18</v>
       </c>
       <c r="J112" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K112" s="12" t="n">
         <v>46280</v>
@@ -7765,14 +7738,14 @@
         <v>-38</v>
       </c>
       <c r="M112" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N112" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O112" s="14"/>
       <c r="P112" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q112" s="15"/>
       <c r="R112" s="14"/>
@@ -7782,25 +7755,25 @@
         <v>112</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C113" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="D113" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E113" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="F113" s="10" t="s">
         <v>264</v>
-      </c>
-      <c r="D113" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="E113" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="F113" s="10" t="s">
-        <v>266</v>
       </c>
       <c r="G113" s="12" t="n">
         <v>46658</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I113" s="10" t="n">
         <v>17</v>
@@ -7814,14 +7787,14 @@
         <v/>
       </c>
       <c r="M113" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="O113" s="14"/>
       <c r="P113" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q113" s="15"/>
       <c r="R113" s="14"/>
@@ -7831,31 +7804,31 @@
         <v>113</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C114" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D114" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="E114" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="D114" s="10" t="s">
+      <c r="F114" s="10" t="s">
         <v>269</v>
-      </c>
-      <c r="E114" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="F114" s="10" t="s">
-        <v>271</v>
       </c>
       <c r="G114" s="12" t="n">
         <v>47016</v>
       </c>
       <c r="H114" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I114" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K114" s="12" t="n">
         <v>46113</v>
@@ -7865,14 +7838,14 @@
         <v>-205</v>
       </c>
       <c r="M114" s="10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="N114" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O114" s="14"/>
       <c r="P114" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q114" s="15"/>
       <c r="R114" s="14"/>
@@ -7882,31 +7855,31 @@
         <v>114</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C115" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D115" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="E115" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="D115" s="10" t="s">
+      <c r="F115" s="10" t="s">
         <v>269</v>
-      </c>
-      <c r="E115" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="F115" s="10" t="s">
-        <v>271</v>
       </c>
       <c r="G115" s="12" t="n">
         <v>47016</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I115" s="10" t="n">
         <v>16</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K115" s="12" t="n">
         <v>45519</v>
@@ -7916,14 +7889,14 @@
         <v>-799</v>
       </c>
       <c r="M115" s="10" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O115" s="14"/>
       <c r="P115" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q115" s="15"/>
       <c r="R115" s="14"/>
@@ -7933,31 +7906,31 @@
         <v>115</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C116" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D116" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="E116" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="D116" s="10" t="s">
+      <c r="F116" s="10" t="s">
         <v>269</v>
-      </c>
-      <c r="E116" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="F116" s="10" t="s">
-        <v>271</v>
       </c>
       <c r="G116" s="12" t="n">
         <v>47016</v>
       </c>
       <c r="H116" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I116" s="10" t="n">
         <v>15</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K116" s="12" t="n">
         <v>46339</v>
@@ -7967,14 +7940,14 @@
         <v>21</v>
       </c>
       <c r="M116" s="10" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N116" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O116" s="14"/>
       <c r="P116" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q116" s="15"/>
       <c r="R116" s="14"/>
@@ -7984,19 +7957,19 @@
         <v>116</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C117" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="D117" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="E117" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="D117" s="10" t="s">
+      <c r="F117" s="10" t="s">
         <v>276</v>
-      </c>
-      <c r="E117" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="F117" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="G117" s="12" t="n">
         <v>46332</v>
@@ -8008,7 +7981,7 @@
         <v>19</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K117" s="12" t="n">
         <v>46212</v>
@@ -8018,14 +7991,14 @@
         <v>-106</v>
       </c>
       <c r="M117" s="10" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O117" s="14"/>
       <c r="P117" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q117" s="15"/>
       <c r="R117" s="14"/>
@@ -8035,31 +8008,31 @@
         <v>117</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C118" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="D118" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="E118" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="D118" s="10" t="s">
+      <c r="F118" s="10" t="s">
         <v>276</v>
-      </c>
-      <c r="E118" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="F118" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="G118" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H118" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I118" s="10" t="n">
         <v>18</v>
       </c>
       <c r="J118" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K118" s="12" t="n">
         <v>46248</v>
@@ -8069,14 +8042,14 @@
         <v>-70</v>
       </c>
       <c r="M118" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N118" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="N118" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="O118" s="14"/>
       <c r="P118" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q118" s="15"/>
       <c r="R118" s="14"/>
@@ -8086,31 +8059,31 @@
         <v>118</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C119" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="D119" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="E119" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="D119" s="10" t="s">
+      <c r="F119" s="10" t="s">
         <v>276</v>
-      </c>
-      <c r="E119" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="F119" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="G119" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I119" s="10" t="n">
         <v>16</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K119" s="12" t="n">
         <v>46328</v>
@@ -8120,14 +8093,14 @@
         <v>10</v>
       </c>
       <c r="M119" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="N119" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="N119" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="O119" s="14"/>
       <c r="P119" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q119" s="15"/>
       <c r="R119" s="14"/>
@@ -8137,31 +8110,31 @@
         <v>119</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C120" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="D120" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="E120" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="D120" s="10" t="s">
+      <c r="F120" s="10" t="s">
         <v>276</v>
-      </c>
-      <c r="E120" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="F120" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="G120" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H120" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I120" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J120" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K120" s="12" t="n">
         <v>46259</v>
@@ -8171,14 +8144,14 @@
         <v>-59</v>
       </c>
       <c r="M120" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="N120" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O120" s="14"/>
       <c r="P120" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q120" s="15"/>
       <c r="R120" s="14"/>
@@ -8188,31 +8161,31 @@
         <v>120</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C121" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="D121" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="E121" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="D121" s="10" t="s">
+      <c r="F121" s="10" t="s">
         <v>276</v>
-      </c>
-      <c r="E121" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="F121" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="G121" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I121" s="10" t="n">
         <v>14</v>
       </c>
       <c r="J121" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K121" s="12" t="n">
         <v>46280</v>
@@ -8222,14 +8195,14 @@
         <v>-38</v>
       </c>
       <c r="M121" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O121" s="14"/>
       <c r="P121" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q121" s="15"/>
       <c r="R121" s="14"/>
@@ -8239,25 +8212,25 @@
         <v>121</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C122" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="D122" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="E122" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="D122" s="10" t="s">
+      <c r="F122" s="10" t="s">
         <v>276</v>
-      </c>
-      <c r="E122" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="F122" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="G122" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H122" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I122" s="10" t="n">
         <v>13</v>
@@ -8271,14 +8244,14 @@
         <v/>
       </c>
       <c r="M122" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N122" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O122" s="14"/>
       <c r="P122" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q122" s="15"/>
       <c r="R122" s="14"/>
@@ -8288,31 +8261,31 @@
         <v>122</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C123" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="D123" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="E123" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D123" s="10" t="s">
+      <c r="F123" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="E123" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="F123" s="10" t="s">
-        <v>284</v>
       </c>
       <c r="G123" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I123" s="10" t="n">
         <v>20</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K123" s="12" t="n">
         <v>46034</v>
@@ -8322,14 +8295,14 @@
         <v>-284</v>
       </c>
       <c r="M123" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N123" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="N123" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="O123" s="14"/>
       <c r="P123" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q123" s="15"/>
       <c r="R123" s="14"/>
@@ -8339,31 +8312,31 @@
         <v>123</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C124" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="D124" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="E124" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D124" s="10" t="s">
+      <c r="F124" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="E124" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="F124" s="10" t="s">
-        <v>284</v>
       </c>
       <c r="G124" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H124" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I124" s="10" t="n">
         <v>18</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K124" s="12" t="n">
         <v>46114</v>
@@ -8373,14 +8346,14 @@
         <v>-204</v>
       </c>
       <c r="M124" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="N124" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="N124" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="O124" s="14"/>
       <c r="P124" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q124" s="15"/>
       <c r="R124" s="14"/>
@@ -8390,31 +8363,31 @@
         <v>124</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C125" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="D125" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="E125" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D125" s="10" t="s">
+      <c r="F125" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="E125" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="F125" s="10" t="s">
-        <v>284</v>
       </c>
       <c r="G125" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I125" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K125" s="12" t="n">
         <v>46276</v>
@@ -8424,14 +8397,14 @@
         <v>-42</v>
       </c>
       <c r="M125" s="10" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O125" s="14"/>
       <c r="P125" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q125" s="15"/>
       <c r="R125" s="14"/>
@@ -8441,25 +8414,25 @@
         <v>125</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C126" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="D126" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="E126" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D126" s="10" t="s">
+      <c r="F126" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="E126" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="F126" s="10" t="s">
-        <v>284</v>
       </c>
       <c r="G126" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H126" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I126" s="10" t="n">
         <v>15</v>
@@ -8473,14 +8446,14 @@
         <v/>
       </c>
       <c r="M126" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N126" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O126" s="14"/>
       <c r="P126" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q126" s="15"/>
       <c r="R126" s="14"/>
@@ -8490,25 +8463,25 @@
         <v>126</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C127" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="D127" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="E127" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D127" s="10" t="s">
+      <c r="F127" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="E127" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="F127" s="10" t="s">
-        <v>284</v>
       </c>
       <c r="G127" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I127" s="10" t="n">
         <v>14</v>
@@ -8522,14 +8495,14 @@
         <v/>
       </c>
       <c r="M127" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O127" s="14"/>
       <c r="P127" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q127" s="15"/>
       <c r="R127" s="14"/>
@@ -8539,25 +8512,25 @@
         <v>127</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C128" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="D128" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="E128" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D128" s="10" t="s">
+      <c r="F128" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="E128" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="F128" s="10" t="s">
-        <v>284</v>
       </c>
       <c r="G128" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H128" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I128" s="10" t="n">
         <v>14</v>
@@ -8571,14 +8544,14 @@
         <v/>
       </c>
       <c r="M128" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N128" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O128" s="14"/>
       <c r="P128" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q128" s="15"/>
       <c r="R128" s="14"/>
@@ -8588,25 +8561,25 @@
         <v>128</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C129" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="D129" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="E129" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D129" s="10" t="s">
+      <c r="F129" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="E129" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="F129" s="10" t="s">
-        <v>284</v>
       </c>
       <c r="G129" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I129" s="10" t="n">
         <v>8</v>
@@ -8620,14 +8593,14 @@
         <v/>
       </c>
       <c r="M129" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O129" s="14"/>
       <c r="P129" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q129" s="15"/>
       <c r="R129" s="14"/>
@@ -8637,19 +8610,19 @@
         <v>129</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C130" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="D130" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E130" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="F130" s="10" t="s">
         <v>286</v>
-      </c>
-      <c r="D130" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="E130" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="F130" s="10" t="s">
-        <v>288</v>
       </c>
       <c r="G130" s="12" t="n">
         <v>47697</v>
@@ -8659,7 +8632,7 @@
       </c>
       <c r="I130" s="10"/>
       <c r="J130" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K130" s="12" t="n">
         <v>46344</v>
@@ -8669,14 +8642,14 @@
         <v>26</v>
       </c>
       <c r="M130" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="N130" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="N130" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="O130" s="14"/>
       <c r="P130" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q130" s="15"/>
       <c r="R130" s="14"/>
@@ -8686,31 +8659,31 @@
         <v>130</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C131" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="D131" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E131" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="F131" s="10" t="s">
         <v>286</v>
-      </c>
-      <c r="D131" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="E131" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="F131" s="10" t="s">
-        <v>288</v>
       </c>
       <c r="G131" s="12" t="n">
         <v>47697</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I131" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K131" s="12" t="n">
         <v>46127</v>
@@ -8720,14 +8693,14 @@
         <v>-191</v>
       </c>
       <c r="M131" s="10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O131" s="14"/>
       <c r="P131" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q131" s="15"/>
       <c r="R131" s="14"/>
@@ -8737,31 +8710,31 @@
         <v>131</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C132" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="D132" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="F132" s="10" t="s">
         <v>286</v>
-      </c>
-      <c r="D132" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="E132" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="F132" s="10" t="s">
-        <v>288</v>
       </c>
       <c r="G132" s="12" t="n">
         <v>47697</v>
       </c>
       <c r="H132" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I132" s="10" t="n">
         <v>17</v>
       </c>
       <c r="J132" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K132" s="12" t="n">
         <v>46282</v>
@@ -8771,14 +8744,14 @@
         <v>-36</v>
       </c>
       <c r="M132" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N132" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O132" s="14"/>
       <c r="P132" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q132" s="15"/>
       <c r="R132" s="14"/>
@@ -8788,19 +8761,19 @@
         <v>132</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C133" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="D133" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="E133" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="D133" s="10" t="s">
+      <c r="F133" s="10" t="s">
         <v>290</v>
-      </c>
-      <c r="E133" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="F133" s="10" t="s">
-        <v>292</v>
       </c>
       <c r="G133" s="12" t="n">
         <v>46244</v>
@@ -8812,7 +8785,7 @@
         <v>21</v>
       </c>
       <c r="J133" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K133" s="12" t="n">
         <v>46124</v>
@@ -8822,14 +8795,14 @@
         <v>-194</v>
       </c>
       <c r="M133" s="10" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O133" s="14"/>
       <c r="P133" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q133" s="15"/>
       <c r="R133" s="14"/>
@@ -8839,31 +8812,31 @@
         <v>133</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C134" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="D134" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="E134" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="D134" s="10" t="s">
+      <c r="F134" s="10" t="s">
         <v>290</v>
-      </c>
-      <c r="E134" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="F134" s="10" t="s">
-        <v>292</v>
       </c>
       <c r="G134" s="12" t="n">
         <v>46244</v>
       </c>
       <c r="H134" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I134" s="10" t="n">
         <v>5</v>
       </c>
       <c r="J134" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K134" s="12" t="n">
         <v>46276</v>
@@ -8873,14 +8846,14 @@
         <v>-42</v>
       </c>
       <c r="M134" s="10" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="N134" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O134" s="14"/>
       <c r="P134" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q134" s="15"/>
       <c r="R134" s="14"/>
@@ -8890,25 +8863,25 @@
         <v>134</v>
       </c>
       <c r="B135" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C135" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="D135" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="E135" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="D135" s="10" t="s">
+      <c r="F135" s="10" t="s">
         <v>290</v>
-      </c>
-      <c r="E135" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="F135" s="10" t="s">
-        <v>292</v>
       </c>
       <c r="G135" s="12" t="n">
         <v>46244</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I135" s="10" t="n">
         <v>15</v>
@@ -8922,14 +8895,14 @@
         <v/>
       </c>
       <c r="M135" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O135" s="14"/>
       <c r="P135" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q135" s="15"/>
       <c r="R135" s="14"/>
@@ -8991,7 +8964,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>5</v>
@@ -9006,12 +8979,12 @@
         <v>8</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A2,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9036,7 +9009,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A3,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9061,7 +9034,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A4,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9086,7 +9059,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A5,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9111,7 +9084,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A6,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9136,7 +9109,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A7,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9161,7 +9134,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B8" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A8,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9186,7 +9159,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B9" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A9,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9211,7 +9184,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B10" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A10,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9236,7 +9209,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A11,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9261,7 +9234,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B12" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A12,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9286,7 +9259,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B13" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A13,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9311,7 +9284,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B14" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A14,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9336,7 +9309,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B15" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A15,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9361,7 +9334,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B16" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A16,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9386,7 +9359,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B17" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A17,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9411,7 +9384,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B18" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A18,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9436,7 +9409,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B19" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A19,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9461,7 +9434,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B20" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A20,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9486,7 +9459,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A21,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9511,7 +9484,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B22" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A22,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9536,7 +9509,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B23" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A23,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9561,7 +9534,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B24" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A24,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9586,7 +9559,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B25" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A25,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9611,7 +9584,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B26" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A26,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9636,7 +9609,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B27" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A27,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9661,7 +9634,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B28" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A28,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9686,7 +9659,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B29" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A29,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9711,7 +9684,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B30" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A30,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9736,7 +9709,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B31" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A31,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9761,7 +9734,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B32" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A32,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9786,7 +9759,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B33" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A33,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9811,7 +9784,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B34" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A34,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9836,7 +9809,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B35" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A35,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9861,7 +9834,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B36" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A36,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9886,7 +9859,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B37" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A37,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9911,7 +9884,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B38" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A38,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9936,7 +9909,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B39" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A39,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9961,7 +9934,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B40" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A40,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -9986,7 +9959,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B41" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A41,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -10011,7 +9984,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B42" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A42,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -10036,7 +10009,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B43" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A43,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -10061,7 +10034,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B44" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A44,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -10086,7 +10059,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B45" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A45,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -10111,7 +10084,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B46" s="6" t="n">
         <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A46,Pendências!$J$2:$J$135,"Vencida")</f>
@@ -10163,228 +10136,228 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D1" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>42</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="C2" s="17" t="s">
         <v>295</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>296</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="C3" s="17" t="s">
         <v>298</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>299</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="C4" s="17" t="s">
         <v>301</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>302</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>304</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>305</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>307</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="C7" s="17" t="s">
         <v>310</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="C8" s="17" t="s">
         <v>313</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>316</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>319</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>322</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="C13" s="17" t="s">
         <v>327</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>328</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>330</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="C15" s="17" t="s">
         <v>333</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>334</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="C16" s="17" t="s">
         <v>336</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>337</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>339</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>340</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>

--- a/pendencias-condicionantes-2026-10-23.xlsx
+++ b/pendencias-condicionantes-2026-10-23.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Licenças que faltam" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Pendências!$A$1:$R$135</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Por empresa'!$A$1:$F$46</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Pendências!$A$1:$R$137</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Por empresa'!$A$1:$F$47</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="347">
   <si>
     <t xml:space="preserve">Condicionantes ambientais – pendências</t>
   </si>
@@ -236,6 +236,24 @@
     <t xml:space="preserve">Documento na pasta: AVCB nº 65330 emitido em 14/10/2025</t>
   </si>
   <si>
+    <t xml:space="preserve">Auto Posto Pais &amp; Filhos Ltda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coronel João Pessoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.479.953/0001-51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-158126/TEC/RLO-0023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documento na pasta: AVCB nº 61155 emitido em 24/04/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documento na pasta: Coleta em 17/06/2026 → +3 meses</t>
+  </si>
+  <si>
     <t xml:space="preserve">Auto Posto Santo Expedito Eireli</t>
   </si>
   <si>
@@ -281,9 +299,6 @@
     <t xml:space="preserve">Documento na pasta: AVCB emitido em 08/05/2025</t>
   </si>
   <si>
-    <t xml:space="preserve">Documento na pasta: Coleta em 17/06/2026 → +3 meses</t>
-  </si>
-  <si>
     <t xml:space="preserve">Conferir verificação anual das bombas (IPEM/INMETRO); se vencida, solicitar vistoria e guardar os certificados.</t>
   </si>
   <si>
@@ -707,9 +722,6 @@
     <t xml:space="preserve">Posto Central Sao Sebastiao Ltda</t>
   </si>
   <si>
-    <t xml:space="preserve">Coronel João Pessoa</t>
-  </si>
-  <si>
     <t xml:space="preserve">12.203.201/0001-75</t>
   </si>
   <si>
@@ -906,15 +918,6 @@
   </si>
   <si>
     <t xml:space="preserve">Prioridade alta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto Posto Pais e Filhos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.479.953/0001-51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pasta 20 tem AVCB, ANP e TOG, mas não tem a licença do IDEMA</t>
   </si>
   <si>
     <t xml:space="preserve">Gás Coronel (Maria S N Gomes)</t>
@@ -1773,15 +1776,15 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A6,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A6,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>12</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A6,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A6,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A6,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A6,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
@@ -1794,15 +1797,15 @@
         <v>10</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A7,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A7,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>8</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A7,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A7,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A7,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A7,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>4</v>
       </c>
       <c r="E7" s="7" t="n">
@@ -1815,15 +1818,15 @@
         <v>11</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A8,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A8,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>6</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A8,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A8,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A8,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A8,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
@@ -1836,15 +1839,15 @@
         <v>12</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A9,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A9,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>4</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A9,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A9,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A9,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A9,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
@@ -1857,15 +1860,15 @@
         <v>13</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A10,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A10,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A10,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A10,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A10,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A10,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E10" s="7" t="n">
@@ -1878,20 +1881,20 @@
         <v>14</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A11,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>23</v>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A11,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>24</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A11,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A11,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>8</v>
       </c>
       <c r="D11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A11,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A11,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>3</v>
       </c>
       <c r="E11" s="7" t="n">
         <f aca="false">SUM(B11:D11)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1899,20 +1902,20 @@
         <v>15</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A12,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>36</v>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A12,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>37</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A12,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A12,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>8</v>
       </c>
       <c r="D12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A12,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A12,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
         <f aca="false">SUM(B12:D12)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1920,15 +1923,15 @@
         <v>16</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A13,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A13,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A13,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A13,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>4</v>
       </c>
       <c r="D13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A13,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A13,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>3</v>
       </c>
       <c r="E13" s="7" t="n">
@@ -1941,15 +1944,15 @@
         <v>17</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A14,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A14,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A14,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A14,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A14,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A14,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
@@ -1962,15 +1965,15 @@
         <v>18</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A15,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A15,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A15,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A15,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>4</v>
       </c>
       <c r="D15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A15,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A15,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
@@ -1983,15 +1986,15 @@
         <v>19</v>
       </c>
       <c r="B16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A16,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A16,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A16,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A16,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>3</v>
       </c>
       <c r="D16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$135,$A16,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A16,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
@@ -2005,7 +2008,7 @@
       </c>
       <c r="B17" s="8" t="n">
         <f aca="false">SUM(B6:B16)</f>
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C17" s="8" t="n">
         <f aca="false">SUM(C6:C16)</f>
@@ -2017,7 +2020,7 @@
       </c>
       <c r="E17" s="8" t="n">
         <f aca="false">SUM(E6:E16)</f>
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2030,8 +2033,8 @@
         <v>22</v>
       </c>
       <c r="B20" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$135,A20)</f>
-        <v>134</v>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$137,A20)</f>
+        <v>136</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2039,7 +2042,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$135,A21)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$137,A21)</f>
         <v>0</v>
       </c>
     </row>
@@ -2048,7 +2051,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$135,A22)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$137,A22)</f>
         <v>0</v>
       </c>
     </row>
@@ -2057,7 +2060,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$135,A23)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$137,A23)</f>
         <v>0</v>
       </c>
     </row>
@@ -2066,7 +2069,7 @@
         <v>26</v>
       </c>
       <c r="B24" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$135,A24)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$137,A24)</f>
         <v>0</v>
       </c>
     </row>
@@ -2091,7 +2094,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R135"/>
+  <dimension ref="A1:R137"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2524,12 +2527,12 @@
       <c r="Q8" s="15"/>
       <c r="R8" s="14"/>
     </row>
-    <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>69</v>
@@ -2544,27 +2547,29 @@
         <v>72</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>46546</v>
+        <v>46721</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K9" s="12"/>
-      <c r="L9" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>46136</v>
+      </c>
+      <c r="L9" s="13" t="n">
         <f aca="false">IF(K9="","",K9-Resumo!$B$3)</f>
-        <v/>
+        <v>-182</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>73</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O9" s="14"/>
       <c r="P9" s="14" t="s">
@@ -2578,44 +2583,44 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>46764</v>
+        <v>46721</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K10" s="12" t="n">
-        <v>46101</v>
+        <v>46282</v>
       </c>
       <c r="L10" s="13" t="n">
         <f aca="false">IF(K10="","",K10-Resumo!$B$3)</f>
-        <v>-217</v>
+        <v>-36</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="14" t="s">
@@ -2624,12 +2629,12 @@
       <c r="Q10" s="15"/>
       <c r="R10" s="14"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>75</v>
@@ -2644,29 +2649,27 @@
         <v>78</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>46764</v>
+        <v>46546</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <v>46181</v>
-      </c>
-      <c r="L11" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" s="12"/>
+      <c r="L11" s="13" t="str">
         <f aca="false">IF(K11="","",K11-Resumo!$B$3)</f>
-        <v>-137</v>
+        <v/>
       </c>
       <c r="M11" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="14" t="s">
@@ -2675,49 +2678,49 @@
       <c r="Q11" s="15"/>
       <c r="R11" s="14"/>
     </row>
-    <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>46764</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J12" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>46150</v>
+        <v>46101</v>
       </c>
       <c r="L12" s="13" t="n">
         <f aca="false">IF(K12="","",K12-Resumo!$B$3)</f>
-        <v>-168</v>
+        <v>-217</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="O12" s="14"/>
       <c r="P12" s="14" t="s">
@@ -2726,49 +2729,49 @@
       <c r="Q12" s="15"/>
       <c r="R12" s="14"/>
     </row>
-    <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>46764</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J13" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>46282</v>
+        <v>46181</v>
       </c>
       <c r="L13" s="13" t="n">
         <f aca="false">IF(K13="","",K13-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-137</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="O13" s="14"/>
       <c r="P13" s="14" t="s">
@@ -2777,47 +2780,49 @@
       <c r="Q13" s="15"/>
       <c r="R13" s="14"/>
     </row>
-    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>46764</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K14" s="12"/>
-      <c r="L14" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>46150</v>
+      </c>
+      <c r="L14" s="13" t="n">
         <f aca="false">IF(K14="","",K14-Resumo!$B$3)</f>
-        <v/>
+        <v>-168</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="O14" s="14"/>
       <c r="P14" s="14" t="s">
@@ -2831,44 +2836,44 @@
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>46764</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>46042</v>
+        <v>46282</v>
       </c>
       <c r="L15" s="13" t="n">
         <f aca="false">IF(K15="","",K15-Resumo!$B$3)</f>
-        <v>-276</v>
+        <v>-36</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="O15" s="14"/>
       <c r="P15" s="14" t="s">
@@ -2885,25 +2890,25 @@
         <v>45</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>46764</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>6</v>
@@ -2914,10 +2919,10 @@
         <v/>
       </c>
       <c r="M16" s="10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O16" s="14"/>
       <c r="P16" s="14" t="s">
@@ -2931,44 +2936,44 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>46374</v>
+        <v>46764</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>46254</v>
+        <v>46042</v>
       </c>
       <c r="L17" s="13" t="n">
         <f aca="false">IF(K17="","",K17-Resumo!$B$3)</f>
-        <v>-64</v>
+        <v>-276</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O17" s="14"/>
       <c r="P17" s="14" t="s">
@@ -2982,42 +2987,42 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>46374</v>
+        <v>46764</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I18" s="10"/>
+        <v>18</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>8</v>
+      </c>
       <c r="J18" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>46303</v>
-      </c>
-      <c r="L18" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" s="12"/>
+      <c r="L18" s="13" t="str">
         <f aca="false">IF(K18="","",K18-Resumo!$B$3)</f>
-        <v>-15</v>
+        <v/>
       </c>
       <c r="M18" s="10" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="O18" s="14"/>
       <c r="P18" s="14" t="s">
@@ -3026,47 +3031,49 @@
       <c r="Q18" s="15"/>
       <c r="R18" s="14"/>
     </row>
-    <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>46374</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K19" s="12"/>
-      <c r="L19" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K19" s="12" t="n">
+        <v>46254</v>
+      </c>
+      <c r="L19" s="13" t="n">
         <f aca="false">IF(K19="","",K19-Resumo!$B$3)</f>
-        <v/>
+        <v>-64</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O19" s="14"/>
       <c r="P19" s="14" t="s">
@@ -3080,42 +3087,42 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>46374</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="10" t="n">
-        <v>17</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I20" s="10"/>
       <c r="J20" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K20" s="12"/>
-      <c r="L20" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L20" s="13" t="n">
         <f aca="false">IF(K20="","",K20-Resumo!$B$3)</f>
-        <v/>
+        <v>-15</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O20" s="14"/>
       <c r="P20" s="14" t="s">
@@ -3124,7 +3131,7 @@
       <c r="Q20" s="15"/>
       <c r="R20" s="14"/>
     </row>
-    <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="n">
         <v>20</v>
       </c>
@@ -3132,25 +3139,25 @@
         <v>45</v>
       </c>
       <c r="C21" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="F21" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="E21" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="G21" s="12" t="n">
-        <v>48100</v>
+        <v>46374</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>6</v>
@@ -3161,10 +3168,10 @@
         <v/>
       </c>
       <c r="M21" s="10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O21" s="14"/>
       <c r="P21" s="14" t="s">
@@ -3178,44 +3185,42 @@
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>44080</v>
+        <v>46374</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>43960</v>
-      </c>
-      <c r="L22" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K22" s="12"/>
+      <c r="L22" s="13" t="str">
         <f aca="false">IF(K22="","",K22-Resumo!$B$3)</f>
-        <v>-2358</v>
+        <v/>
       </c>
       <c r="M22" s="10" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="O22" s="14"/>
       <c r="P22" s="14" t="s">
@@ -3232,39 +3237,39 @@
         <v>45</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>44080</v>
+        <v>48100</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I23" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>16</v>
+      </c>
       <c r="J23" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>46346</v>
-      </c>
-      <c r="L23" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K23" s="12"/>
+      <c r="L23" s="13" t="str">
         <f aca="false">IF(K23="","",K23-Resumo!$B$3)</f>
-        <v>28</v>
+        <v/>
       </c>
       <c r="M23" s="10" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O23" s="14"/>
       <c r="P23" s="14" t="s">
@@ -3273,47 +3278,49 @@
       <c r="Q23" s="15"/>
       <c r="R23" s="14"/>
     </row>
-    <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>44080</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K24" s="12"/>
-      <c r="L24" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K24" s="12" t="n">
+        <v>43960</v>
+      </c>
+      <c r="L24" s="13" t="n">
         <f aca="false">IF(K24="","",K24-Resumo!$B$3)</f>
-        <v/>
+        <v>-2358</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O24" s="14"/>
       <c r="P24" s="14" t="s">
@@ -3330,39 +3337,39 @@
         <v>45</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>44080</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="10" t="n">
-        <v>15</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I25" s="10"/>
       <c r="J25" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K25" s="12"/>
-      <c r="L25" s="13" t="str">
+        <v>50</v>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>46346</v>
+      </c>
+      <c r="L25" s="13" t="n">
         <f aca="false">IF(K25="","",K25-Resumo!$B$3)</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O25" s="14"/>
       <c r="P25" s="14" t="s">
@@ -3379,19 +3386,19 @@
         <v>45</v>
       </c>
       <c r="C26" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="E26" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="F26" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="F26" s="10" t="s">
-        <v>109</v>
-      </c>
       <c r="G26" s="12" t="n">
-        <v>46595</v>
+        <v>44080</v>
       </c>
       <c r="H26" s="10" t="s">
         <v>14</v>
@@ -3408,7 +3415,7 @@
         <v/>
       </c>
       <c r="M26" s="10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="N26" s="10" t="s">
         <v>54</v>
@@ -3428,19 +3435,19 @@
         <v>45</v>
       </c>
       <c r="C27" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="E27" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="F27" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>109</v>
-      </c>
       <c r="G27" s="12" t="n">
-        <v>46595</v>
+        <v>44080</v>
       </c>
       <c r="H27" s="10" t="s">
         <v>15</v>
@@ -3457,7 +3464,7 @@
         <v/>
       </c>
       <c r="M27" s="10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="N27" s="10" t="s">
         <v>58</v>
@@ -3469,49 +3476,47 @@
       <c r="Q27" s="15"/>
       <c r="R27" s="14"/>
     </row>
-    <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>48215</v>
+        <v>46595</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>46034</v>
-      </c>
-      <c r="L28" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K28" s="12"/>
+      <c r="L28" s="13" t="str">
         <f aca="false">IF(K28="","",K28-Resumo!$B$3)</f>
-        <v>-284</v>
+        <v/>
       </c>
       <c r="M28" s="10" t="s">
         <v>79</v>
       </c>
       <c r="N28" s="10" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="O28" s="14"/>
       <c r="P28" s="14" t="s">
@@ -3525,44 +3530,42 @@
         <v>28</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>48215</v>
+        <v>46595</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>46114</v>
-      </c>
-      <c r="L29" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" s="12"/>
+      <c r="L29" s="13" t="str">
         <f aca="false">IF(K29="","",K29-Resumo!$B$3)</f>
-        <v>-204</v>
+        <v/>
       </c>
       <c r="M29" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="O29" s="14"/>
       <c r="P29" s="14" t="s">
@@ -3576,44 +3579,44 @@
         <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J30" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>46281</v>
+        <v>46034</v>
       </c>
       <c r="L30" s="13" t="n">
         <f aca="false">IF(K30="","",K30-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-284</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="N30" s="10" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="O30" s="14"/>
       <c r="P30" s="14" t="s">
@@ -3627,42 +3630,44 @@
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K31" s="12"/>
-      <c r="L31" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K31" s="12" t="n">
+        <v>46114</v>
+      </c>
+      <c r="L31" s="13" t="n">
         <f aca="false">IF(K31="","",K31-Resumo!$B$3)</f>
-        <v/>
+        <v>-204</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="O31" s="14"/>
       <c r="P31" s="14" t="s">
@@ -3676,42 +3681,44 @@
         <v>31</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K32" s="12"/>
-      <c r="L32" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K32" s="12" t="n">
+        <v>46281</v>
+      </c>
+      <c r="L32" s="13" t="n">
         <f aca="false">IF(K32="","",K32-Resumo!$B$3)</f>
-        <v/>
+        <v>-37</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="N32" s="10" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="O32" s="14"/>
       <c r="P32" s="14" t="s">
@@ -3728,22 +3735,22 @@
         <v>45</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>8</v>
@@ -3757,10 +3764,10 @@
         <v/>
       </c>
       <c r="M33" s="10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O33" s="14"/>
       <c r="P33" s="14" t="s">
@@ -3769,49 +3776,47 @@
       <c r="Q33" s="15"/>
       <c r="R33" s="14"/>
     </row>
-    <row r="34" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>47766</v>
+        <v>48215</v>
       </c>
       <c r="H34" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="I34" s="10" t="n">
-        <v>4</v>
-      </c>
       <c r="J34" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K34" s="12" t="n">
-        <v>45995</v>
-      </c>
-      <c r="L34" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K34" s="12"/>
+      <c r="L34" s="13" t="str">
         <f aca="false">IF(K34="","",K34-Resumo!$B$3)</f>
-        <v>-323</v>
+        <v/>
       </c>
       <c r="M34" s="10" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="N34" s="10" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="O34" s="14"/>
       <c r="P34" s="14" t="s">
@@ -3820,49 +3825,47 @@
       <c r="Q34" s="15"/>
       <c r="R34" s="14"/>
     </row>
-    <row r="35" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C35" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F35" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>121</v>
-      </c>
       <c r="G35" s="12" t="n">
-        <v>47037</v>
+        <v>48215</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K35" s="12" t="n">
-        <v>46225</v>
-      </c>
-      <c r="L35" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K35" s="12"/>
+      <c r="L35" s="13" t="str">
         <f aca="false">IF(K35="","",K35-Resumo!$B$3)</f>
-        <v>-93</v>
+        <v/>
       </c>
       <c r="M35" s="10" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="O35" s="14"/>
       <c r="P35" s="14" t="s">
@@ -3871,7 +3874,7 @@
       <c r="Q35" s="15"/>
       <c r="R35" s="14"/>
     </row>
-    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="n">
         <v>35</v>
       </c>
@@ -3879,41 +3882,41 @@
         <v>55</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>47037</v>
+        <v>47766</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J36" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>46282</v>
+        <v>45995</v>
       </c>
       <c r="L36" s="13" t="n">
         <f aca="false">IF(K36="","",K36-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-323</v>
       </c>
       <c r="M36" s="10" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="N36" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O36" s="14"/>
       <c r="P36" s="14" t="s">
@@ -3927,7 +3930,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>123</v>
@@ -3942,27 +3945,29 @@
         <v>126</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>48208</v>
+        <v>47037</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I37" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I37" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J37" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>45322</v>
+        <v>46225</v>
       </c>
       <c r="L37" s="13" t="n">
         <f aca="false">IF(K37="","",K37-Resumo!$B$3)</f>
-        <v>-996</v>
+        <v>-93</v>
       </c>
       <c r="M37" s="10" t="s">
         <v>127</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O37" s="14"/>
       <c r="P37" s="14" t="s">
@@ -3971,7 +3976,7 @@
       <c r="Q37" s="15"/>
       <c r="R37" s="14"/>
     </row>
-    <row r="38" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="n">
         <v>37</v>
       </c>
@@ -3991,29 +3996,29 @@
         <v>126</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>48208</v>
+        <v>47037</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J38" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>46239</v>
+        <v>46282</v>
       </c>
       <c r="L38" s="13" t="n">
         <f aca="false">IF(K38="","",K38-Resumo!$B$3)</f>
-        <v>-79</v>
+        <v>-36</v>
       </c>
       <c r="M38" s="10" t="s">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="N38" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O38" s="14"/>
       <c r="P38" s="14" t="s">
@@ -4022,49 +4027,47 @@
       <c r="Q38" s="15"/>
       <c r="R38" s="14"/>
     </row>
-    <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>48208</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" s="10" t="n">
         <v>10</v>
       </c>
+      <c r="I39" s="10"/>
       <c r="J39" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>46282</v>
+        <v>45322</v>
       </c>
       <c r="L39" s="13" t="n">
         <f aca="false">IF(K39="","",K39-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-996</v>
       </c>
       <c r="M39" s="10" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O39" s="14"/>
       <c r="P39" s="14" t="s">
@@ -4073,47 +4076,49 @@
       <c r="Q39" s="15"/>
       <c r="R39" s="14"/>
     </row>
-    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>48208</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K40" s="12"/>
-      <c r="L40" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K40" s="12" t="n">
+        <v>46239</v>
+      </c>
+      <c r="L40" s="13" t="n">
         <f aca="false">IF(K40="","",K40-Resumo!$B$3)</f>
-        <v/>
+        <v>-79</v>
       </c>
       <c r="M40" s="10" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="N40" s="10" t="s">
-        <v>129</v>
+        <v>54</v>
       </c>
       <c r="O40" s="14"/>
       <c r="P40" s="14" t="s">
@@ -4130,25 +4135,25 @@
         <v>55</v>
       </c>
       <c r="C41" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E41" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="F41" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="E41" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>133</v>
-      </c>
       <c r="G41" s="12" t="n">
-        <v>47333</v>
+        <v>48208</v>
       </c>
       <c r="H41" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J41" s="10" t="s">
         <v>56</v>
@@ -4161,7 +4166,7 @@
         <v>-36</v>
       </c>
       <c r="M41" s="10" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="N41" s="10" t="s">
         <v>58</v>
@@ -4178,44 +4183,42 @@
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>48394</v>
+        <v>48208</v>
       </c>
       <c r="H42" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="I42" s="10" t="n">
-        <v>22</v>
-      </c>
       <c r="J42" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K42" s="12" t="n">
-        <v>46212</v>
-      </c>
-      <c r="L42" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K42" s="12"/>
+      <c r="L42" s="13" t="str">
         <f aca="false">IF(K42="","",K42-Resumo!$B$3)</f>
-        <v>-106</v>
+        <v/>
       </c>
       <c r="M42" s="10" t="s">
         <v>79</v>
       </c>
       <c r="N42" s="10" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="O42" s="14"/>
       <c r="P42" s="14" t="s">
@@ -4224,49 +4227,49 @@
       <c r="Q42" s="15"/>
       <c r="R42" s="14"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>48394</v>
+        <v>47333</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J43" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>46292</v>
+        <v>46282</v>
       </c>
       <c r="L43" s="13" t="n">
         <f aca="false">IF(K43="","",K43-Resumo!$B$3)</f>
-        <v>-26</v>
+        <v>-36</v>
       </c>
       <c r="M43" s="10" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="O43" s="14"/>
       <c r="P43" s="14" t="s">
@@ -4275,49 +4278,49 @@
       <c r="Q43" s="15"/>
       <c r="R43" s="14"/>
     </row>
-    <row r="44" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>48394</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>46323</v>
+        <v>46212</v>
       </c>
       <c r="L44" s="13" t="n">
         <f aca="false">IF(K44="","",K44-Resumo!$B$3)</f>
-        <v>5</v>
+        <v>-106</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="N44" s="10" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="O44" s="14"/>
       <c r="P44" s="14" t="s">
@@ -4326,49 +4329,49 @@
       <c r="Q44" s="15"/>
       <c r="R44" s="14"/>
     </row>
-    <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>48394</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J45" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>46282</v>
+        <v>46292</v>
       </c>
       <c r="L45" s="13" t="n">
         <f aca="false">IF(K45="","",K45-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-26</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="O45" s="14"/>
       <c r="P45" s="14" t="s">
@@ -4377,49 +4380,49 @@
       <c r="Q45" s="15"/>
       <c r="R45" s="14"/>
     </row>
-    <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>48394</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>44478</v>
+        <v>46323</v>
       </c>
       <c r="L46" s="13" t="n">
         <f aca="false">IF(K46="","",K46-Resumo!$B$3)</f>
-        <v>-1840</v>
+        <v>5</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="N46" s="10" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="O46" s="14"/>
       <c r="P46" s="14" t="s">
@@ -4433,42 +4436,44 @@
         <v>46</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>48394</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K47" s="12"/>
-      <c r="L47" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K47" s="12" t="n">
+        <v>46282</v>
+      </c>
+      <c r="L47" s="13" t="n">
         <f aca="false">IF(K47="","",K47-Resumo!$B$3)</f>
-        <v/>
+        <v>-36</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="O47" s="14"/>
       <c r="P47" s="14" t="s">
@@ -4482,42 +4487,44 @@
         <v>47</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>48394</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K48" s="12"/>
-      <c r="L48" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K48" s="12" t="n">
+        <v>44478</v>
+      </c>
+      <c r="L48" s="13" t="n">
         <f aca="false">IF(K48="","",K48-Resumo!$B$3)</f>
-        <v/>
+        <v>-1840</v>
       </c>
       <c r="M48" s="10" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="N48" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O48" s="14"/>
       <c r="P48" s="14" t="s">
@@ -4531,42 +4538,42 @@
         <v>48</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>139</v>
       </c>
       <c r="D49" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E49" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="F49" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>142</v>
-      </c>
       <c r="G49" s="12" t="n">
-        <v>47129</v>
+        <v>48394</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I49" s="10"/>
+        <v>17</v>
+      </c>
+      <c r="I49" s="10" t="n">
+        <v>14</v>
+      </c>
       <c r="J49" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K49" s="12" t="n">
-        <v>46273</v>
-      </c>
-      <c r="L49" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K49" s="12"/>
+      <c r="L49" s="13" t="str">
         <f aca="false">IF(K49="","",K49-Resumo!$B$3)</f>
-        <v>-45</v>
+        <v/>
       </c>
       <c r="M49" s="10" t="s">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="O49" s="14"/>
       <c r="P49" s="14" t="s">
@@ -4575,7 +4582,7 @@
       <c r="Q49" s="15"/>
       <c r="R49" s="14"/>
     </row>
-    <row r="50" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="n">
         <v>49</v>
       </c>
@@ -4586,22 +4593,22 @@
         <v>139</v>
       </c>
       <c r="D50" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E50" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="F50" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="F50" s="10" t="s">
-        <v>142</v>
-      </c>
       <c r="G50" s="12" t="n">
-        <v>47129</v>
+        <v>48394</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J50" s="10" t="s">
         <v>6</v>
@@ -4612,10 +4619,10 @@
         <v/>
       </c>
       <c r="M50" s="10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="N50" s="10" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="O50" s="14"/>
       <c r="P50" s="14" t="s">
@@ -4629,44 +4636,42 @@
         <v>50</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G51" s="12" t="n">
         <v>47129</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I51" s="10" t="n">
-        <v>17</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I51" s="10"/>
       <c r="J51" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>46282</v>
+        <v>46273</v>
       </c>
       <c r="L51" s="13" t="n">
         <f aca="false">IF(K51="","",K51-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-45</v>
       </c>
       <c r="M51" s="10" t="s">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O51" s="14"/>
       <c r="P51" s="14" t="s">
@@ -4675,7 +4680,7 @@
       <c r="Q51" s="15"/>
       <c r="R51" s="14"/>
     </row>
-    <row r="52" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="n">
         <v>51</v>
       </c>
@@ -4683,41 +4688,39 @@
         <v>45</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>47129</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K52" s="12" t="n">
-        <v>46337</v>
-      </c>
-      <c r="L52" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K52" s="12"/>
+      <c r="L52" s="13" t="str">
         <f aca="false">IF(K52="","",K52-Resumo!$B$3)</f>
-        <v>19</v>
+        <v/>
       </c>
       <c r="M52" s="10" t="s">
-        <v>144</v>
+        <v>79</v>
       </c>
       <c r="N52" s="10" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="O52" s="14"/>
       <c r="P52" s="14" t="s">
@@ -4734,10 +4737,10 @@
         <v>55</v>
       </c>
       <c r="C53" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D53" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>90</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>146</v>
@@ -4746,26 +4749,26 @@
         <v>147</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>46872</v>
+        <v>47129</v>
       </c>
       <c r="H53" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J53" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="L53" s="13" t="n">
         <f aca="false">IF(K53="","",K53-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-36</v>
       </c>
       <c r="M53" s="10" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="N53" s="10" t="s">
         <v>58</v>
@@ -4782,44 +4785,44 @@
         <v>53</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>46374</v>
+        <v>47129</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>46254</v>
+        <v>46337</v>
       </c>
       <c r="L54" s="13" t="n">
         <f aca="false">IF(K54="","",K54-Resumo!$B$3)</f>
-        <v>-64</v>
+        <v>19</v>
       </c>
       <c r="M54" s="10" t="s">
-        <v>93</v>
+        <v>149</v>
       </c>
       <c r="N54" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O54" s="14"/>
       <c r="P54" s="14" t="s">
@@ -4828,47 +4831,49 @@
       <c r="Q54" s="15"/>
       <c r="R54" s="14"/>
     </row>
-    <row r="55" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>46374</v>
+        <v>46872</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K55" s="12"/>
-      <c r="L55" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K55" s="12" t="n">
+        <v>46281</v>
+      </c>
+      <c r="L55" s="13" t="n">
         <f aca="false">IF(K55="","",K55-Resumo!$B$3)</f>
-        <v/>
+        <v>-37</v>
       </c>
       <c r="M55" s="10" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O55" s="14"/>
       <c r="P55" s="14" t="s">
@@ -4885,41 +4890,41 @@
         <v>55</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>46374</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J56" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L56" s="13" t="n">
         <f aca="false">IF(K56="","",K56-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-64</v>
       </c>
       <c r="M56" s="10" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="N56" s="10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O56" s="14"/>
       <c r="P56" s="14" t="s">
@@ -4928,47 +4933,47 @@
       <c r="Q56" s="15"/>
       <c r="R56" s="14"/>
     </row>
-    <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>46911</v>
+        <v>46374</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I57" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I57" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J57" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K57" s="12" t="n">
-        <v>46282</v>
-      </c>
-      <c r="L57" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K57" s="12"/>
+      <c r="L57" s="13" t="str">
         <f aca="false">IF(K57="","",K57-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v/>
       </c>
       <c r="M57" s="10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O57" s="14"/>
       <c r="P57" s="14" t="s">
@@ -4977,45 +4982,49 @@
       <c r="Q57" s="15"/>
       <c r="R57" s="14"/>
     </row>
-    <row r="58" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C58" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F58" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="D58" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="F58" s="10" t="s">
-        <v>159</v>
-      </c>
       <c r="G58" s="12" t="n">
-        <v>46875</v>
+        <v>46374</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I58" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="I58" s="10" t="n">
+        <v>15</v>
+      </c>
       <c r="J58" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K58" s="12"/>
-      <c r="L58" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K58" s="12" t="n">
+        <v>46282</v>
+      </c>
+      <c r="L58" s="13" t="n">
         <f aca="false">IF(K58="","",K58-Resumo!$B$3)</f>
-        <v/>
+        <v>-36</v>
       </c>
       <c r="M58" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N58" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O58" s="14"/>
       <c r="P58" s="14" t="s">
@@ -5032,19 +5041,19 @@
         <v>55</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>46875</v>
+        <v>46911</v>
       </c>
       <c r="H59" s="10" t="s">
         <v>15</v>
@@ -5061,7 +5070,7 @@
         <v>-36</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="N59" s="10" t="s">
         <v>58</v>
@@ -5078,41 +5087,37 @@
         <v>59</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>47952</v>
+        <v>46875</v>
       </c>
       <c r="H60" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I60" s="10" t="n">
-        <v>5</v>
-      </c>
+      <c r="I60" s="10"/>
       <c r="J60" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K60" s="12" t="n">
-        <v>45898</v>
-      </c>
-      <c r="L60" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K60" s="12"/>
+      <c r="L60" s="13" t="str">
         <f aca="false">IF(K60="","",K60-Resumo!$B$3)</f>
-        <v>-420</v>
+        <v/>
       </c>
       <c r="M60" s="10" t="s">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="N60" s="10" t="s">
         <v>54</v>
@@ -5132,38 +5137,36 @@
         <v>55</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>47952</v>
+        <v>46875</v>
       </c>
       <c r="H61" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I61" s="10" t="n">
-        <v>17</v>
-      </c>
+      <c r="I61" s="10"/>
       <c r="J61" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="L61" s="13" t="n">
         <f aca="false">IF(K61="","",K61-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-36</v>
       </c>
       <c r="M61" s="10" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="N61" s="10" t="s">
         <v>58</v>
@@ -5195,7 +5198,7 @@
         <v>168</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>46990</v>
+        <v>47952</v>
       </c>
       <c r="H62" s="10" t="s">
         <v>14</v>
@@ -5207,11 +5210,11 @@
         <v>56</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>46163</v>
+        <v>45898</v>
       </c>
       <c r="L62" s="13" t="n">
         <f aca="false">IF(K62="","",K62-Resumo!$B$3)</f>
-        <v>-155</v>
+        <v>-420</v>
       </c>
       <c r="M62" s="10" t="s">
         <v>169</v>
@@ -5246,13 +5249,13 @@
         <v>168</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>46990</v>
+        <v>47952</v>
       </c>
       <c r="H63" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J63" s="10" t="s">
         <v>56</v>
@@ -5277,47 +5280,49 @@
       <c r="Q63" s="15"/>
       <c r="R63" s="14"/>
     </row>
-    <row r="64" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>170</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>90</v>
+        <v>171</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>47087</v>
+        <v>46990</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I64" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I64" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J64" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>46274</v>
+        <v>46163</v>
       </c>
       <c r="L64" s="13" t="n">
         <f aca="false">IF(K64="","",K64-Resumo!$B$3)</f>
-        <v>-44</v>
+        <v>-155</v>
       </c>
       <c r="M64" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N64" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O64" s="14"/>
       <c r="P64" s="14" t="s">
@@ -5326,7 +5331,7 @@
       <c r="Q64" s="15"/>
       <c r="R64" s="14"/>
     </row>
-    <row r="65" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="n">
         <v>64</v>
       </c>
@@ -5337,38 +5342,38 @@
         <v>170</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>90</v>
+        <v>171</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>47087</v>
+        <v>46990</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I65" s="10" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J65" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>45997</v>
+        <v>46281</v>
       </c>
       <c r="L65" s="13" t="n">
         <f aca="false">IF(K65="","",K65-Resumo!$B$3)</f>
-        <v>-321</v>
+        <v>-37</v>
       </c>
       <c r="M65" s="10" t="s">
-        <v>174</v>
+        <v>57</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O65" s="14"/>
       <c r="P65" s="14" t="s">
@@ -5382,44 +5387,42 @@
         <v>65</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="G66" s="12" t="n">
         <v>47087</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I66" s="10" t="n">
-        <v>16</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I66" s="10"/>
       <c r="J66" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="L66" s="13" t="n">
         <f aca="false">IF(K66="","",K66-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-44</v>
       </c>
       <c r="M66" s="10" t="s">
-        <v>57</v>
+        <v>178</v>
       </c>
       <c r="N66" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O66" s="14"/>
       <c r="P66" s="14" t="s">
@@ -5428,18 +5431,18 @@
       <c r="Q66" s="15"/>
       <c r="R66" s="14"/>
     </row>
-    <row r="67" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>175</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>176</v>
@@ -5448,27 +5451,29 @@
         <v>177</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>47854</v>
+        <v>47087</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I67" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I67" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J67" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>46316</v>
+        <v>45997</v>
       </c>
       <c r="L67" s="13" t="n">
         <f aca="false">IF(K67="","",K67-Resumo!$B$3)</f>
-        <v>-2</v>
+        <v>-321</v>
       </c>
       <c r="M67" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O67" s="14"/>
       <c r="P67" s="14" t="s">
@@ -5488,7 +5493,7 @@
         <v>175</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>176</v>
@@ -5497,13 +5502,13 @@
         <v>177</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>47854</v>
+        <v>47087</v>
       </c>
       <c r="H68" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J68" s="10" t="s">
         <v>56</v>
@@ -5533,13 +5538,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>181</v>
@@ -5548,29 +5553,27 @@
         <v>182</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>46031</v>
+        <v>47854</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="I69" s="10" t="n">
-        <v>19</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I69" s="10"/>
       <c r="J69" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>45911</v>
+        <v>46316</v>
       </c>
       <c r="L69" s="13" t="n">
         <f aca="false">IF(K69="","",K69-Resumo!$B$3)</f>
-        <v>-407</v>
+        <v>-2</v>
       </c>
       <c r="M69" s="10" t="s">
         <v>183</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="O69" s="14"/>
       <c r="P69" s="14" t="s">
@@ -5579,18 +5582,18 @@
       <c r="Q69" s="15"/>
       <c r="R69" s="14"/>
     </row>
-    <row r="70" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>181</v>
@@ -5599,27 +5602,29 @@
         <v>182</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>46031</v>
+        <v>47854</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I70" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="I70" s="10" t="n">
+        <v>18</v>
+      </c>
       <c r="J70" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>45659</v>
+        <v>46281</v>
       </c>
       <c r="L70" s="13" t="n">
         <f aca="false">IF(K70="","",K70-Resumo!$B$3)</f>
-        <v>-659</v>
+        <v>-37</v>
       </c>
       <c r="M70" s="10" t="s">
-        <v>184</v>
+        <v>57</v>
       </c>
       <c r="N70" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O70" s="14"/>
       <c r="P70" s="14" t="s">
@@ -5633,44 +5638,44 @@
         <v>70</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I71" s="10" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J71" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>46083</v>
+        <v>45911</v>
       </c>
       <c r="L71" s="13" t="n">
         <f aca="false">IF(K71="","",K71-Resumo!$B$3)</f>
-        <v>-235</v>
+        <v>-407</v>
       </c>
       <c r="M71" s="10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>186</v>
+        <v>99</v>
       </c>
       <c r="O71" s="14"/>
       <c r="P71" s="14" t="s">
@@ -5684,44 +5689,42 @@
         <v>71</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G72" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I72" s="10" t="n">
-        <v>5</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I72" s="10"/>
       <c r="J72" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>45514</v>
+        <v>45659</v>
       </c>
       <c r="L72" s="13" t="n">
         <f aca="false">IF(K72="","",K72-Resumo!$B$3)</f>
-        <v>-804</v>
+        <v>-659</v>
       </c>
       <c r="M72" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="N72" s="10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O72" s="14"/>
       <c r="P72" s="14" t="s">
@@ -5735,44 +5738,44 @@
         <v>72</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G73" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I73" s="10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J73" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>45356</v>
+        <v>46083</v>
       </c>
       <c r="L73" s="13" t="n">
         <f aca="false">IF(K73="","",K73-Resumo!$B$3)</f>
-        <v>-962</v>
+        <v>-235</v>
       </c>
       <c r="M73" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>58</v>
+        <v>191</v>
       </c>
       <c r="O73" s="14"/>
       <c r="P73" s="14" t="s">
@@ -5781,47 +5784,49 @@
       <c r="Q73" s="15"/>
       <c r="R73" s="14"/>
     </row>
-    <row r="74" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="n">
         <v>73</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F74" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>46031</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I74" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J74" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K74" s="12" t="n">
+        <v>45514</v>
+      </c>
+      <c r="L74" s="13" t="n">
+        <f aca="false">IF(K74="","",K74-Resumo!$B$3)</f>
+        <v>-804</v>
+      </c>
+      <c r="M74" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="G74" s="12" t="n">
-        <v>46729</v>
-      </c>
-      <c r="H74" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I74" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="J74" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K74" s="12"/>
-      <c r="L74" s="13" t="str">
-        <f aca="false">IF(K74="","",K74-Resumo!$B$3)</f>
-        <v/>
-      </c>
-      <c r="M74" s="10" t="s">
-        <v>73</v>
-      </c>
       <c r="N74" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O74" s="14"/>
       <c r="P74" s="14" t="s">
@@ -5835,42 +5840,44 @@
         <v>74</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>65</v>
+        <v>185</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>48171</v>
+        <v>46031</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I75" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="I75" s="10" t="n">
+        <v>15</v>
+      </c>
       <c r="J75" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>46272</v>
+        <v>45356</v>
       </c>
       <c r="L75" s="13" t="n">
         <f aca="false">IF(K75="","",K75-Resumo!$B$3)</f>
-        <v>-46</v>
+        <v>-962</v>
       </c>
       <c r="M75" s="10" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O75" s="14"/>
       <c r="P75" s="14" t="s">
@@ -5879,49 +5886,47 @@
       <c r="Q75" s="15"/>
       <c r="R75" s="14"/>
     </row>
-    <row r="76" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>48171</v>
+        <v>46729</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I76" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J76" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K76" s="12" t="n">
-        <v>46309</v>
-      </c>
-      <c r="L76" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K76" s="12"/>
+      <c r="L76" s="13" t="str">
         <f aca="false">IF(K76="","",K76-Resumo!$B$3)</f>
-        <v>-9</v>
+        <v/>
       </c>
       <c r="M76" s="10" t="s">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="N76" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O76" s="14"/>
       <c r="P76" s="14" t="s">
@@ -5935,44 +5940,42 @@
         <v>76</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>65</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G77" s="12" t="n">
         <v>48171</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I77" s="10" t="n">
-        <v>15</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I77" s="10"/>
       <c r="J77" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>46281</v>
+        <v>46272</v>
       </c>
       <c r="L77" s="13" t="n">
         <f aca="false">IF(K77="","",K77-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-46</v>
       </c>
       <c r="M77" s="10" t="s">
-        <v>57</v>
+        <v>201</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O77" s="14"/>
       <c r="P77" s="14" t="s">
@@ -5981,7 +5984,7 @@
       <c r="Q77" s="15"/>
       <c r="R77" s="14"/>
     </row>
-    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="n">
         <v>77</v>
       </c>
@@ -5992,38 +5995,38 @@
         <v>198</v>
       </c>
       <c r="D78" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E78" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E78" s="10" t="s">
+      <c r="F78" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F78" s="10" t="s">
-        <v>201</v>
-      </c>
       <c r="G78" s="12" t="n">
-        <v>46288</v>
+        <v>48171</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I78" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J78" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>46168</v>
+        <v>46309</v>
       </c>
       <c r="L78" s="13" t="n">
         <f aca="false">IF(K78="","",K78-Resumo!$B$3)</f>
-        <v>-150</v>
+        <v>-9</v>
       </c>
       <c r="M78" s="10" t="s">
         <v>202</v>
       </c>
       <c r="N78" s="10" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="O78" s="14"/>
       <c r="P78" s="14" t="s">
@@ -6037,44 +6040,44 @@
         <v>78</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C79" s="10" t="s">
         <v>198</v>
       </c>
       <c r="D79" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E79" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E79" s="10" t="s">
+      <c r="F79" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F79" s="10" t="s">
-        <v>203</v>
-      </c>
       <c r="G79" s="12" t="n">
-        <v>48005</v>
+        <v>48171</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I79" s="10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J79" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>46163</v>
+        <v>46281</v>
       </c>
       <c r="L79" s="13" t="n">
         <f aca="false">IF(K79="","",K79-Resumo!$B$3)</f>
-        <v>-155</v>
+        <v>-37</v>
       </c>
       <c r="M79" s="10" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="O79" s="14"/>
       <c r="P79" s="14" t="s">
@@ -6083,47 +6086,49 @@
       <c r="Q79" s="15"/>
       <c r="R79" s="14"/>
     </row>
-    <row r="80" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="10" t="n">
         <v>79</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G80" s="12" t="n">
         <v>46288</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I80" s="10" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K80" s="12"/>
-      <c r="L80" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K80" s="12" t="n">
+        <v>46168</v>
+      </c>
+      <c r="L80" s="13" t="n">
         <f aca="false">IF(K80="","",K80-Resumo!$B$3)</f>
-        <v/>
+        <v>-150</v>
       </c>
       <c r="M80" s="10" t="s">
-        <v>73</v>
+        <v>207</v>
       </c>
       <c r="N80" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O80" s="14"/>
       <c r="P80" s="14" t="s">
@@ -6137,44 +6142,44 @@
         <v>80</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>46288</v>
+        <v>48005</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I81" s="10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J81" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>46283</v>
+        <v>46163</v>
       </c>
       <c r="L81" s="13" t="n">
         <f aca="false">IF(K81="","",K81-Resumo!$B$3)</f>
-        <v>-35</v>
+        <v>-155</v>
       </c>
       <c r="M81" s="10" t="s">
-        <v>204</v>
+        <v>85</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="O81" s="14"/>
       <c r="P81" s="14" t="s">
@@ -6188,41 +6193,39 @@
         <v>81</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C82" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="E82" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="D82" s="10" t="s">
+      <c r="F82" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="E82" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="F82" s="10" t="s">
-        <v>208</v>
-      </c>
       <c r="G82" s="12" t="n">
-        <v>46798</v>
+        <v>46288</v>
       </c>
       <c r="H82" s="10" t="s">
         <v>14</v>
       </c>
       <c r="I82" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>46323</v>
-      </c>
-      <c r="L82" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K82" s="12"/>
+      <c r="L82" s="13" t="str">
         <f aca="false">IF(K82="","",K82-Resumo!$B$3)</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="M82" s="10" t="s">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="N82" s="10" t="s">
         <v>54</v>
@@ -6242,38 +6245,38 @@
         <v>55</v>
       </c>
       <c r="C83" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="E83" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="D83" s="10" t="s">
+      <c r="F83" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="E83" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="F83" s="10" t="s">
-        <v>208</v>
-      </c>
       <c r="G83" s="12" t="n">
-        <v>46798</v>
+        <v>46288</v>
       </c>
       <c r="H83" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J83" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="L83" s="13" t="n">
         <f aca="false">IF(K83="","",K83-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-35</v>
       </c>
       <c r="M83" s="10" t="s">
-        <v>57</v>
+        <v>209</v>
       </c>
       <c r="N83" s="10" t="s">
         <v>58</v>
@@ -6285,47 +6288,49 @@
       <c r="Q83" s="15"/>
       <c r="R83" s="14"/>
     </row>
-    <row r="84" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>46798</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I84" s="10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K84" s="12"/>
-      <c r="L84" s="13" t="str">
+        <v>50</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>46323</v>
+      </c>
+      <c r="L84" s="13" t="n">
         <f aca="false">IF(K84="","",K84-Resumo!$B$3)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M84" s="10" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="N84" s="10" t="s">
-        <v>129</v>
+        <v>54</v>
       </c>
       <c r="O84" s="14"/>
       <c r="P84" s="14" t="s">
@@ -6354,7 +6359,7 @@
         <v>213</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>47004</v>
+        <v>46798</v>
       </c>
       <c r="H85" s="10" t="s">
         <v>15</v>
@@ -6366,14 +6371,14 @@
         <v>56</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="L85" s="13" t="n">
         <f aca="false">IF(K85="","",K85-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="M85" s="10" t="s">
-        <v>214</v>
+        <v>57</v>
       </c>
       <c r="N85" s="10" t="s">
         <v>58</v>
@@ -6405,29 +6410,27 @@
         <v>213</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>47004</v>
+        <v>46798</v>
       </c>
       <c r="H86" s="10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I86" s="10" t="n">
         <v>15</v>
       </c>
       <c r="J86" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K86" s="12" t="n">
-        <v>46344</v>
-      </c>
-      <c r="L86" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K86" s="12"/>
+      <c r="L86" s="13" t="str">
         <f aca="false">IF(K86="","",K86-Resumo!$B$3)</f>
-        <v>26</v>
+        <v/>
       </c>
       <c r="M86" s="10" t="s">
-        <v>215</v>
+        <v>79</v>
       </c>
       <c r="N86" s="10" t="s">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="O86" s="14"/>
       <c r="P86" s="14" t="s">
@@ -6444,10 +6447,10 @@
         <v>55</v>
       </c>
       <c r="C87" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D87" s="10" t="s">
         <v>216</v>
-      </c>
-      <c r="D87" s="10" t="s">
-        <v>47</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>217</v>
@@ -6456,29 +6459,29 @@
         <v>218</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>46046</v>
+        <v>47004</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I87" s="10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J87" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>45926</v>
+        <v>46280</v>
       </c>
       <c r="L87" s="13" t="n">
         <f aca="false">IF(K87="","",K87-Resumo!$B$3)</f>
-        <v>-392</v>
+        <v>-38</v>
       </c>
       <c r="M87" s="10" t="s">
         <v>219</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="O87" s="14"/>
       <c r="P87" s="14" t="s">
@@ -6492,13 +6495,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="C88" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D88" s="10" t="s">
         <v>216</v>
-      </c>
-      <c r="D88" s="10" t="s">
-        <v>47</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>217</v>
@@ -6507,27 +6510,29 @@
         <v>218</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>46046</v>
+        <v>47004</v>
       </c>
       <c r="H88" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I88" s="10"/>
+        <v>16</v>
+      </c>
+      <c r="I88" s="10" t="n">
+        <v>15</v>
+      </c>
       <c r="J88" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>45823</v>
+        <v>46344</v>
       </c>
       <c r="L88" s="13" t="n">
         <f aca="false">IF(K88="","",K88-Resumo!$B$3)</f>
-        <v>-495</v>
+        <v>26</v>
       </c>
       <c r="M88" s="10" t="s">
         <v>220</v>
       </c>
       <c r="N88" s="10" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="O88" s="14"/>
       <c r="P88" s="14" t="s">
@@ -6536,7 +6541,7 @@
       <c r="Q88" s="15"/>
       <c r="R88" s="14"/>
     </row>
-    <row r="89" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="n">
         <v>88</v>
       </c>
@@ -6544,41 +6549,41 @@
         <v>55</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>47</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="G89" s="12" t="n">
         <v>46046</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I89" s="10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J89" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>46058</v>
+        <v>45926</v>
       </c>
       <c r="L89" s="13" t="n">
         <f aca="false">IF(K89="","",K89-Resumo!$B$3)</f>
-        <v>-260</v>
+        <v>-392</v>
       </c>
       <c r="M89" s="10" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O89" s="14"/>
       <c r="P89" s="14" t="s">
@@ -6592,44 +6597,42 @@
         <v>89</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D90" s="10" t="s">
         <v>47</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="G90" s="12" t="n">
         <v>46046</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I90" s="10" t="n">
-        <v>15</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I90" s="10"/>
       <c r="J90" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K90" s="12" t="n">
-        <v>46281</v>
+        <v>45823</v>
       </c>
       <c r="L90" s="13" t="n">
         <f aca="false">IF(K90="","",K90-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-495</v>
       </c>
       <c r="M90" s="10" t="s">
-        <v>57</v>
+        <v>225</v>
       </c>
       <c r="N90" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O90" s="14"/>
       <c r="P90" s="14" t="s">
@@ -6638,7 +6641,7 @@
       <c r="Q90" s="15"/>
       <c r="R90" s="14"/>
     </row>
-    <row r="91" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="n">
         <v>90</v>
       </c>
@@ -6646,41 +6649,41 @@
         <v>55</v>
       </c>
       <c r="C91" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E91" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="D91" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E91" s="10" t="s">
+      <c r="F91" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="F91" s="10" t="s">
-        <v>224</v>
-      </c>
       <c r="G91" s="12" t="n">
-        <v>46970</v>
+        <v>46046</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I91" s="10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J91" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>46281</v>
+        <v>46058</v>
       </c>
       <c r="L91" s="13" t="n">
         <f aca="false">IF(K91="","",K91-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-260</v>
       </c>
       <c r="M91" s="10" t="s">
-        <v>57</v>
+        <v>226</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O91" s="14"/>
       <c r="P91" s="14" t="s">
@@ -6697,39 +6700,41 @@
         <v>55</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>226</v>
+        <v>47</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>46505</v>
+        <v>46046</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I92" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="I92" s="10" t="n">
+        <v>15</v>
+      </c>
       <c r="J92" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K92" s="12" t="n">
-        <v>46319</v>
+        <v>46281</v>
       </c>
       <c r="L92" s="13" t="n">
         <f aca="false">IF(K92="","",K92-Resumo!$B$3)</f>
-        <v>1</v>
+        <v>-37</v>
       </c>
       <c r="M92" s="10" t="s">
-        <v>229</v>
+        <v>57</v>
       </c>
       <c r="N92" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O92" s="14"/>
       <c r="P92" s="14" t="s">
@@ -6738,7 +6743,7 @@
       <c r="Q92" s="15"/>
       <c r="R92" s="14"/>
     </row>
-    <row r="93" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="n">
         <v>92</v>
       </c>
@@ -6746,41 +6751,41 @@
         <v>55</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>46505</v>
+        <v>46970</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I93" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J93" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>45891</v>
+        <v>46281</v>
       </c>
       <c r="L93" s="13" t="n">
         <f aca="false">IF(K93="","",K93-Resumo!$B$3)</f>
-        <v>-427</v>
+        <v>-37</v>
       </c>
       <c r="M93" s="10" t="s">
-        <v>230</v>
+        <v>57</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O93" s="14"/>
       <c r="P93" s="14" t="s">
@@ -6797,41 +6802,39 @@
         <v>55</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>226</v>
+        <v>70</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="G94" s="12" t="n">
         <v>46505</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I94" s="10" t="n">
-        <v>15</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I94" s="10"/>
       <c r="J94" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K94" s="12" t="n">
-        <v>46282</v>
+        <v>46319</v>
       </c>
       <c r="L94" s="13" t="n">
         <f aca="false">IF(K94="","",K94-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>1</v>
       </c>
       <c r="M94" s="10" t="s">
-        <v>84</v>
+        <v>233</v>
       </c>
       <c r="N94" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O94" s="14"/>
       <c r="P94" s="14" t="s">
@@ -6840,7 +6843,7 @@
       <c r="Q94" s="15"/>
       <c r="R94" s="14"/>
     </row>
-    <row r="95" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="10" t="n">
         <v>94</v>
       </c>
@@ -6848,39 +6851,41 @@
         <v>55</v>
       </c>
       <c r="C95" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E95" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="D95" s="10" t="s">
+      <c r="F95" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="E95" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="F95" s="10" t="s">
-        <v>234</v>
-      </c>
       <c r="G95" s="12" t="n">
-        <v>46346</v>
+        <v>46505</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="I95" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I95" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J95" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>46226</v>
+        <v>45891</v>
       </c>
       <c r="L95" s="13" t="n">
         <f aca="false">IF(K95="","",K95-Resumo!$B$3)</f>
-        <v>-92</v>
+        <v>-427</v>
       </c>
       <c r="M95" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="O95" s="14"/>
       <c r="P95" s="14" t="s">
@@ -6897,24 +6902,26 @@
         <v>55</v>
       </c>
       <c r="C96" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E96" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="D96" s="10" t="s">
+      <c r="F96" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="E96" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="F96" s="10" t="s">
-        <v>234</v>
-      </c>
       <c r="G96" s="12" t="n">
-        <v>46346</v>
+        <v>46505</v>
       </c>
       <c r="H96" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I96" s="10"/>
+      <c r="I96" s="10" t="n">
+        <v>15</v>
+      </c>
       <c r="J96" s="10" t="s">
         <v>56</v>
       </c>
@@ -6926,7 +6933,7 @@
         <v>-36</v>
       </c>
       <c r="M96" s="10" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="N96" s="10" t="s">
         <v>58</v>
@@ -6946,10 +6953,10 @@
         <v>55</v>
       </c>
       <c r="C97" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D97" s="10" t="s">
         <v>236</v>
-      </c>
-      <c r="D97" s="10" t="s">
-        <v>65</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>237</v>
@@ -6958,29 +6965,27 @@
         <v>238</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>46373</v>
+        <v>46346</v>
       </c>
       <c r="H97" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I97" s="10" t="n">
-        <v>22</v>
-      </c>
+      <c r="I97" s="10"/>
       <c r="J97" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>46253</v>
+        <v>46226</v>
       </c>
       <c r="L97" s="13" t="n">
         <f aca="false">IF(K97="","",K97-Resumo!$B$3)</f>
-        <v>-65</v>
+        <v>-92</v>
       </c>
       <c r="M97" s="10" t="s">
         <v>239</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="O97" s="14"/>
       <c r="P97" s="14" t="s">
@@ -6989,7 +6994,7 @@
       <c r="Q97" s="15"/>
       <c r="R97" s="14"/>
     </row>
-    <row r="98" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="n">
         <v>97</v>
       </c>
@@ -6997,10 +7002,10 @@
         <v>55</v>
       </c>
       <c r="C98" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D98" s="10" t="s">
         <v>236</v>
-      </c>
-      <c r="D98" s="10" t="s">
-        <v>65</v>
       </c>
       <c r="E98" s="10" t="s">
         <v>237</v>
@@ -7009,29 +7014,27 @@
         <v>238</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>46373</v>
+        <v>46346</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I98" s="10" t="n">
-        <v>5</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I98" s="10"/>
       <c r="J98" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K98" s="12" t="n">
-        <v>45192</v>
+        <v>46282</v>
       </c>
       <c r="L98" s="13" t="n">
         <f aca="false">IF(K98="","",K98-Resumo!$B$3)</f>
-        <v>-1126</v>
+        <v>-36</v>
       </c>
       <c r="M98" s="10" t="s">
-        <v>240</v>
+        <v>74</v>
       </c>
       <c r="N98" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O98" s="14"/>
       <c r="P98" s="14" t="s">
@@ -7048,41 +7051,41 @@
         <v>55</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>65</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="G99" s="12" t="n">
         <v>46373</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I99" s="10" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J99" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>45262</v>
+        <v>46253</v>
       </c>
       <c r="L99" s="13" t="n">
         <f aca="false">IF(K99="","",K99-Resumo!$B$3)</f>
-        <v>-1056</v>
+        <v>-65</v>
       </c>
       <c r="M99" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O99" s="14"/>
       <c r="P99" s="14" t="s">
@@ -7099,19 +7102,19 @@
         <v>55</v>
       </c>
       <c r="C100" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="D100" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="F100" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="D100" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="F100" s="10" t="s">
-        <v>245</v>
-      </c>
       <c r="G100" s="12" t="n">
-        <v>48010</v>
+        <v>46373</v>
       </c>
       <c r="H100" s="10" t="s">
         <v>14</v>
@@ -7123,14 +7126,14 @@
         <v>56</v>
       </c>
       <c r="K100" s="12" t="n">
-        <v>46127</v>
+        <v>45192</v>
       </c>
       <c r="L100" s="13" t="n">
         <f aca="false">IF(K100="","",K100-Resumo!$B$3)</f>
-        <v>-191</v>
+        <v>-1126</v>
       </c>
       <c r="M100" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="N100" s="10" t="s">
         <v>54</v>
@@ -7150,38 +7153,38 @@
         <v>55</v>
       </c>
       <c r="C101" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="D101" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="F101" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="D101" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="E101" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="F101" s="10" t="s">
-        <v>245</v>
-      </c>
       <c r="G101" s="12" t="n">
-        <v>48010</v>
+        <v>46373</v>
       </c>
       <c r="H101" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J101" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>46280</v>
+        <v>45262</v>
       </c>
       <c r="L101" s="13" t="n">
         <f aca="false">IF(K101="","",K101-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>-1056</v>
       </c>
       <c r="M101" s="10" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="N101" s="10" t="s">
         <v>58</v>
@@ -7193,7 +7196,7 @@
       <c r="Q101" s="15"/>
       <c r="R101" s="14"/>
     </row>
-    <row r="102" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="10" t="n">
         <v>101</v>
       </c>
@@ -7201,41 +7204,41 @@
         <v>55</v>
       </c>
       <c r="C102" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D102" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="D102" s="10" t="s">
+      <c r="E102" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="E102" s="10" t="s">
+      <c r="F102" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="F102" s="10" t="s">
-        <v>250</v>
-      </c>
       <c r="G102" s="12" t="n">
-        <v>46043</v>
+        <v>48010</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I102" s="10" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="J102" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K102" s="12" t="n">
-        <v>45923</v>
+        <v>46127</v>
       </c>
       <c r="L102" s="13" t="n">
         <f aca="false">IF(K102="","",K102-Resumo!$B$3)</f>
-        <v>-395</v>
+        <v>-191</v>
       </c>
       <c r="M102" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N102" s="10" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="O102" s="14"/>
       <c r="P102" s="14" t="s">
@@ -7244,7 +7247,7 @@
       <c r="Q102" s="15"/>
       <c r="R102" s="14"/>
     </row>
-    <row r="103" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="10" t="n">
         <v>102</v>
       </c>
@@ -7252,41 +7255,41 @@
         <v>55</v>
       </c>
       <c r="C103" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D103" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="D103" s="10" t="s">
+      <c r="E103" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="E103" s="10" t="s">
+      <c r="F103" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="F103" s="10" t="s">
-        <v>250</v>
-      </c>
       <c r="G103" s="12" t="n">
-        <v>46043</v>
+        <v>48010</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I103" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J103" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>46113</v>
+        <v>46280</v>
       </c>
       <c r="L103" s="13" t="n">
         <f aca="false">IF(K103="","",K103-Resumo!$B$3)</f>
-        <v>-205</v>
+        <v>-38</v>
       </c>
       <c r="M103" s="10" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O103" s="14"/>
       <c r="P103" s="14" t="s">
@@ -7303,41 +7306,41 @@
         <v>55</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="G104" s="12" t="n">
         <v>46043</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I104" s="10" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J104" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K104" s="12" t="n">
-        <v>45351</v>
+        <v>45923</v>
       </c>
       <c r="L104" s="13" t="n">
         <f aca="false">IF(K104="","",K104-Resumo!$B$3)</f>
-        <v>-967</v>
+        <v>-395</v>
       </c>
       <c r="M104" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N104" s="10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O104" s="14"/>
       <c r="P104" s="14" t="s">
@@ -7346,7 +7349,7 @@
       <c r="Q104" s="15"/>
       <c r="R104" s="14"/>
     </row>
-    <row r="105" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="10" t="n">
         <v>104</v>
       </c>
@@ -7354,41 +7357,41 @@
         <v>55</v>
       </c>
       <c r="C105" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="D105" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F105" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="D105" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="E105" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="F105" s="10" t="s">
-        <v>256</v>
-      </c>
       <c r="G105" s="12" t="n">
-        <v>46408</v>
+        <v>46043</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I105" s="10" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J105" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>46288</v>
+        <v>46113</v>
       </c>
       <c r="L105" s="13" t="n">
         <f aca="false">IF(K105="","",K105-Resumo!$B$3)</f>
-        <v>-30</v>
+        <v>-205</v>
       </c>
       <c r="M105" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="O105" s="14"/>
       <c r="P105" s="14" t="s">
@@ -7397,7 +7400,7 @@
       <c r="Q105" s="15"/>
       <c r="R105" s="14"/>
     </row>
-    <row r="106" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="10" t="n">
         <v>105</v>
       </c>
@@ -7405,41 +7408,41 @@
         <v>55</v>
       </c>
       <c r="C106" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="D106" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F106" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="D106" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="E106" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="F106" s="10" t="s">
-        <v>256</v>
-      </c>
       <c r="G106" s="12" t="n">
-        <v>46408</v>
+        <v>46043</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I106" s="10" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J106" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K106" s="12" t="n">
-        <v>46113</v>
+        <v>45351</v>
       </c>
       <c r="L106" s="13" t="n">
         <f aca="false">IF(K106="","",K106-Resumo!$B$3)</f>
-        <v>-205</v>
+        <v>-967</v>
       </c>
       <c r="M106" s="10" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="N106" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O106" s="14"/>
       <c r="P106" s="14" t="s">
@@ -7456,41 +7459,41 @@
         <v>55</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="G107" s="12" t="n">
         <v>46408</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I107" s="10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J107" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="L107" s="13" t="n">
         <f aca="false">IF(K107="","",K107-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-30</v>
       </c>
       <c r="M107" s="10" t="s">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O107" s="14"/>
       <c r="P107" s="14" t="s">
@@ -7499,18 +7502,18 @@
       <c r="Q107" s="15"/>
       <c r="R107" s="14"/>
     </row>
-    <row r="108" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="10" t="n">
         <v>107</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C108" s="10" t="s">
         <v>258</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>90</v>
+        <v>195</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>259</v>
@@ -7519,27 +7522,29 @@
         <v>260</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>47310</v>
+        <v>46408</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I108" s="10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K108" s="12"/>
-      <c r="L108" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K108" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="L108" s="13" t="n">
         <f aca="false">IF(K108="","",K108-Resumo!$B$3)</f>
-        <v/>
+        <v>-205</v>
       </c>
       <c r="M108" s="10" t="s">
-        <v>73</v>
+        <v>256</v>
       </c>
       <c r="N108" s="10" t="s">
-        <v>186</v>
+        <v>54</v>
       </c>
       <c r="O108" s="14"/>
       <c r="P108" s="14" t="s">
@@ -7548,18 +7553,18 @@
       <c r="Q108" s="15"/>
       <c r="R108" s="14"/>
     </row>
-    <row r="109" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="10" t="n">
         <v>108</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C109" s="10" t="s">
         <v>258</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>90</v>
+        <v>195</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>259</v>
@@ -7568,27 +7573,29 @@
         <v>260</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>47310</v>
+        <v>46408</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I109" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K109" s="12"/>
-      <c r="L109" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K109" s="12" t="n">
+        <v>46282</v>
+      </c>
+      <c r="L109" s="13" t="n">
         <f aca="false">IF(K109="","",K109-Resumo!$B$3)</f>
-        <v/>
+        <v>-36</v>
       </c>
       <c r="M109" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O109" s="14"/>
       <c r="P109" s="14" t="s">
@@ -7602,44 +7609,42 @@
         <v>109</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F110" s="10" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G110" s="12" t="n">
         <v>47310</v>
       </c>
       <c r="H110" s="10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I110" s="10" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K110" s="12" t="n">
-        <v>46043</v>
-      </c>
-      <c r="L110" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K110" s="12"/>
+      <c r="L110" s="13" t="str">
         <f aca="false">IF(K110="","",K110-Resumo!$B$3)</f>
-        <v>-275</v>
+        <v/>
       </c>
       <c r="M110" s="10" t="s">
-        <v>261</v>
+        <v>79</v>
       </c>
       <c r="N110" s="10" t="s">
-        <v>58</v>
+        <v>191</v>
       </c>
       <c r="O110" s="14"/>
       <c r="P110" s="14" t="s">
@@ -7653,13 +7658,13 @@
         <v>110</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C111" s="10" t="s">
         <v>262</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>263</v>
@@ -7668,7 +7673,7 @@
         <v>264</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>46658</v>
+        <v>47310</v>
       </c>
       <c r="H111" s="10" t="s">
         <v>14</v>
@@ -7677,17 +7682,15 @@
         <v>5</v>
       </c>
       <c r="J111" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K111" s="12" t="n">
-        <v>46107</v>
-      </c>
-      <c r="L111" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K111" s="12"/>
+      <c r="L111" s="13" t="str">
         <f aca="false">IF(K111="","",K111-Resumo!$B$3)</f>
-        <v>-211</v>
+        <v/>
       </c>
       <c r="M111" s="10" t="s">
-        <v>265</v>
+        <v>79</v>
       </c>
       <c r="N111" s="10" t="s">
         <v>54</v>
@@ -7710,7 +7713,7 @@
         <v>262</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>263</v>
@@ -7719,26 +7722,26 @@
         <v>264</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>46658</v>
+        <v>47310</v>
       </c>
       <c r="H112" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J112" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K112" s="12" t="n">
-        <v>46280</v>
+        <v>46043</v>
       </c>
       <c r="L112" s="13" t="n">
         <f aca="false">IF(K112="","",K112-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>-275</v>
       </c>
       <c r="M112" s="10" t="s">
-        <v>214</v>
+        <v>265</v>
       </c>
       <c r="N112" s="10" t="s">
         <v>58</v>
@@ -7750,47 +7753,49 @@
       <c r="Q112" s="15"/>
       <c r="R112" s="14"/>
     </row>
-    <row r="113" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="10" t="n">
         <v>112</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G113" s="12" t="n">
         <v>46658</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I113" s="10" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K113" s="12"/>
-      <c r="L113" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K113" s="12" t="n">
+        <v>46107</v>
+      </c>
+      <c r="L113" s="13" t="n">
         <f aca="false">IF(K113="","",K113-Resumo!$B$3)</f>
-        <v/>
+        <v>-211</v>
       </c>
       <c r="M113" s="10" t="s">
-        <v>73</v>
+        <v>269</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>129</v>
+        <v>54</v>
       </c>
       <c r="O113" s="14"/>
       <c r="P113" s="14" t="s">
@@ -7799,7 +7804,7 @@
       <c r="Q113" s="15"/>
       <c r="R113" s="14"/>
     </row>
-    <row r="114" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="10" t="n">
         <v>113</v>
       </c>
@@ -7810,38 +7815,38 @@
         <v>266</v>
       </c>
       <c r="D114" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E114" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="E114" s="10" t="s">
+      <c r="F114" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="F114" s="10" t="s">
-        <v>269</v>
-      </c>
       <c r="G114" s="12" t="n">
-        <v>47016</v>
+        <v>46658</v>
       </c>
       <c r="H114" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I114" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J114" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K114" s="12" t="n">
-        <v>46113</v>
+        <v>46280</v>
       </c>
       <c r="L114" s="13" t="n">
         <f aca="false">IF(K114="","",K114-Resumo!$B$3)</f>
-        <v>-205</v>
+        <v>-38</v>
       </c>
       <c r="M114" s="10" t="s">
-        <v>270</v>
+        <v>219</v>
       </c>
       <c r="N114" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O114" s="14"/>
       <c r="P114" s="14" t="s">
@@ -7855,44 +7860,42 @@
         <v>114</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C115" s="10" t="s">
         <v>266</v>
       </c>
       <c r="D115" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E115" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="E115" s="10" t="s">
+      <c r="F115" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="F115" s="10" t="s">
-        <v>269</v>
-      </c>
       <c r="G115" s="12" t="n">
-        <v>47016</v>
+        <v>46658</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I115" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K115" s="12" t="n">
-        <v>45519</v>
-      </c>
-      <c r="L115" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K115" s="12"/>
+      <c r="L115" s="13" t="str">
         <f aca="false">IF(K115="","",K115-Resumo!$B$3)</f>
-        <v>-799</v>
+        <v/>
       </c>
       <c r="M115" s="10" t="s">
-        <v>271</v>
+        <v>79</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="O115" s="14"/>
       <c r="P115" s="14" t="s">
@@ -7901,49 +7904,49 @@
       <c r="Q115" s="15"/>
       <c r="R115" s="14"/>
     </row>
-    <row r="116" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="10" t="n">
         <v>115</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E116" s="10" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F116" s="10" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G116" s="12" t="n">
         <v>47016</v>
       </c>
       <c r="H116" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I116" s="10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K116" s="12" t="n">
-        <v>46339</v>
+        <v>46113</v>
       </c>
       <c r="L116" s="13" t="n">
         <f aca="false">IF(K116="","",K116-Resumo!$B$3)</f>
-        <v>21</v>
+        <v>-205</v>
       </c>
       <c r="M116" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N116" s="10" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="O116" s="14"/>
       <c r="P116" s="14" t="s">
@@ -7960,41 +7963,41 @@
         <v>55</v>
       </c>
       <c r="C117" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="D117" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E117" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F117" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="D117" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="E117" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="F117" s="10" t="s">
-        <v>276</v>
-      </c>
       <c r="G117" s="12" t="n">
-        <v>46332</v>
+        <v>47016</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I117" s="10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J117" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>46212</v>
+        <v>45519</v>
       </c>
       <c r="L117" s="13" t="n">
         <f aca="false">IF(K117="","",K117-Resumo!$B$3)</f>
-        <v>-106</v>
+        <v>-799</v>
       </c>
       <c r="M117" s="10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="O117" s="14"/>
       <c r="P117" s="14" t="s">
@@ -8008,44 +8011,44 @@
         <v>117</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="C118" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="D118" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F118" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="D118" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="E118" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="F118" s="10" t="s">
-        <v>276</v>
-      </c>
       <c r="G118" s="12" t="n">
-        <v>46332</v>
+        <v>47016</v>
       </c>
       <c r="H118" s="10" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I118" s="10" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J118" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K118" s="12" t="n">
-        <v>46248</v>
+        <v>46339</v>
       </c>
       <c r="L118" s="13" t="n">
         <f aca="false">IF(K118="","",K118-Resumo!$B$3)</f>
-        <v>-70</v>
+        <v>21</v>
       </c>
       <c r="M118" s="10" t="s">
-        <v>79</v>
+        <v>276</v>
       </c>
       <c r="N118" s="10" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O118" s="14"/>
       <c r="P118" s="14" t="s">
@@ -8054,7 +8057,7 @@
       <c r="Q118" s="15"/>
       <c r="R118" s="14"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="10" t="n">
         <v>118</v>
       </c>
@@ -8062,41 +8065,41 @@
         <v>55</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G119" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I119" s="10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>46328</v>
+        <v>46212</v>
       </c>
       <c r="L119" s="13" t="n">
         <f aca="false">IF(K119="","",K119-Resumo!$B$3)</f>
-        <v>10</v>
+        <v>-106</v>
       </c>
       <c r="M119" s="10" t="s">
-        <v>81</v>
+        <v>281</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="O119" s="14"/>
       <c r="P119" s="14" t="s">
@@ -8105,49 +8108,49 @@
       <c r="Q119" s="15"/>
       <c r="R119" s="14"/>
     </row>
-    <row r="120" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="10" t="n">
         <v>119</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F120" s="10" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G120" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H120" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I120" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J120" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K120" s="12" t="n">
-        <v>46259</v>
+        <v>46248</v>
       </c>
       <c r="L120" s="13" t="n">
         <f aca="false">IF(K120="","",K120-Resumo!$B$3)</f>
-        <v>-59</v>
+        <v>-70</v>
       </c>
       <c r="M120" s="10" t="s">
-        <v>278</v>
+        <v>85</v>
       </c>
       <c r="N120" s="10" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="O120" s="14"/>
       <c r="P120" s="14" t="s">
@@ -8156,7 +8159,7 @@
       <c r="Q120" s="15"/>
       <c r="R120" s="14"/>
     </row>
-    <row r="121" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="10" t="n">
         <v>120</v>
       </c>
@@ -8164,41 +8167,41 @@
         <v>55</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G121" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I121" s="10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J121" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>46280</v>
+        <v>46328</v>
       </c>
       <c r="L121" s="13" t="n">
         <f aca="false">IF(K121="","",K121-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>10</v>
       </c>
       <c r="M121" s="10" t="s">
-        <v>214</v>
+        <v>87</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="O121" s="14"/>
       <c r="P121" s="14" t="s">
@@ -8207,47 +8210,49 @@
       <c r="Q121" s="15"/>
       <c r="R121" s="14"/>
     </row>
-    <row r="122" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="10" t="n">
         <v>121</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G122" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H122" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I122" s="10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J122" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K122" s="12"/>
-      <c r="L122" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K122" s="12" t="n">
+        <v>46259</v>
+      </c>
+      <c r="L122" s="13" t="n">
         <f aca="false">IF(K122="","",K122-Resumo!$B$3)</f>
-        <v/>
+        <v>-59</v>
       </c>
       <c r="M122" s="10" t="s">
-        <v>73</v>
+        <v>282</v>
       </c>
       <c r="N122" s="10" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="O122" s="14"/>
       <c r="P122" s="14" t="s">
@@ -8261,44 +8266,44 @@
         <v>122</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C123" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D123" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="E123" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="D123" s="10" t="s">
+      <c r="F123" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="E123" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="F123" s="10" t="s">
-        <v>282</v>
-      </c>
       <c r="G123" s="12" t="n">
-        <v>48215</v>
+        <v>46332</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I123" s="10" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J123" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>46034</v>
+        <v>46280</v>
       </c>
       <c r="L123" s="13" t="n">
         <f aca="false">IF(K123="","",K123-Resumo!$B$3)</f>
-        <v>-284</v>
+        <v>-38</v>
       </c>
       <c r="M123" s="10" t="s">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="O123" s="14"/>
       <c r="P123" s="14" t="s">
@@ -8307,49 +8312,47 @@
       <c r="Q123" s="15"/>
       <c r="R123" s="14"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="10" t="n">
         <v>123</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="C124" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D124" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="E124" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="D124" s="10" t="s">
+      <c r="F124" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="E124" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="F124" s="10" t="s">
-        <v>282</v>
-      </c>
       <c r="G124" s="12" t="n">
-        <v>48215</v>
+        <v>46332</v>
       </c>
       <c r="H124" s="10" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I124" s="10" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K124" s="12" t="n">
-        <v>46114</v>
-      </c>
-      <c r="L124" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K124" s="12"/>
+      <c r="L124" s="13" t="str">
         <f aca="false">IF(K124="","",K124-Resumo!$B$3)</f>
-        <v>-204</v>
+        <v/>
       </c>
       <c r="M124" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N124" s="10" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="O124" s="14"/>
       <c r="P124" s="14" t="s">
@@ -8358,49 +8361,49 @@
       <c r="Q124" s="15"/>
       <c r="R124" s="14"/>
     </row>
-    <row r="125" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="10" t="n">
         <v>124</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G125" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I125" s="10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J125" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>46276</v>
+        <v>46034</v>
       </c>
       <c r="L125" s="13" t="n">
         <f aca="false">IF(K125="","",K125-Resumo!$B$3)</f>
-        <v>-42</v>
+        <v>-284</v>
       </c>
       <c r="M125" s="10" t="s">
-        <v>283</v>
+        <v>85</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="O125" s="14"/>
       <c r="P125" s="14" t="s">
@@ -8409,47 +8412,49 @@
       <c r="Q125" s="15"/>
       <c r="R125" s="14"/>
     </row>
-    <row r="126" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="10" t="n">
         <v>125</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F126" s="10" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G126" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H126" s="10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I126" s="10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J126" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K126" s="12"/>
-      <c r="L126" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K126" s="12" t="n">
+        <v>46114</v>
+      </c>
+      <c r="L126" s="13" t="n">
         <f aca="false">IF(K126="","",K126-Resumo!$B$3)</f>
-        <v/>
+        <v>-204</v>
       </c>
       <c r="M126" s="10" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="N126" s="10" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="O126" s="14"/>
       <c r="P126" s="14" t="s">
@@ -8458,47 +8463,49 @@
       <c r="Q126" s="15"/>
       <c r="R126" s="14"/>
     </row>
-    <row r="127" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="10" t="n">
         <v>126</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G127" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I127" s="10" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K127" s="12"/>
-      <c r="L127" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K127" s="12" t="n">
+        <v>46276</v>
+      </c>
+      <c r="L127" s="13" t="n">
         <f aca="false">IF(K127="","",K127-Resumo!$B$3)</f>
-        <v/>
+        <v>-42</v>
       </c>
       <c r="M127" s="10" t="s">
-        <v>73</v>
+        <v>287</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="O127" s="14"/>
       <c r="P127" s="14" t="s">
@@ -8515,25 +8522,25 @@
         <v>45</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E128" s="10" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G128" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H128" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I128" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J128" s="10" t="s">
         <v>6</v>
@@ -8544,10 +8551,10 @@
         <v/>
       </c>
       <c r="M128" s="10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="N128" s="10" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="O128" s="14"/>
       <c r="P128" s="14" t="s">
@@ -8564,25 +8571,25 @@
         <v>45</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G129" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I129" s="10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J129" s="10" t="s">
         <v>6</v>
@@ -8593,10 +8600,10 @@
         <v/>
       </c>
       <c r="M129" s="10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O129" s="14"/>
       <c r="P129" s="14" t="s">
@@ -8613,10 +8620,10 @@
         <v>45</v>
       </c>
       <c r="C130" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D130" s="10" t="s">
         <v>284</v>
-      </c>
-      <c r="D130" s="10" t="s">
-        <v>180</v>
       </c>
       <c r="E130" s="10" t="s">
         <v>285</v>
@@ -8625,27 +8632,27 @@
         <v>286</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>47697</v>
+        <v>48215</v>
       </c>
       <c r="H130" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I130" s="10"/>
+        <v>17</v>
+      </c>
+      <c r="I130" s="10" t="n">
+        <v>14</v>
+      </c>
       <c r="J130" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K130" s="12" t="n">
-        <v>46344</v>
-      </c>
-      <c r="L130" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K130" s="12"/>
+      <c r="L130" s="13" t="str">
         <f aca="false">IF(K130="","",K130-Resumo!$B$3)</f>
-        <v>26</v>
+        <v/>
       </c>
       <c r="M130" s="10" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="N130" s="10" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="O130" s="14"/>
       <c r="P130" s="14" t="s">
@@ -8654,18 +8661,18 @@
       <c r="Q130" s="15"/>
       <c r="R130" s="14"/>
     </row>
-    <row r="131" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="10" t="n">
         <v>130</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C131" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D131" s="10" t="s">
         <v>284</v>
-      </c>
-      <c r="D131" s="10" t="s">
-        <v>180</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>285</v>
@@ -8674,29 +8681,27 @@
         <v>286</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>47697</v>
+        <v>48215</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I131" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K131" s="12" t="n">
-        <v>46127</v>
-      </c>
-      <c r="L131" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K131" s="12"/>
+      <c r="L131" s="13" t="str">
         <f aca="false">IF(K131="","",K131-Resumo!$B$3)</f>
-        <v>-191</v>
+        <v/>
       </c>
       <c r="M131" s="10" t="s">
-        <v>246</v>
+        <v>79</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="O131" s="14"/>
       <c r="P131" s="14" t="s">
@@ -8710,44 +8715,42 @@
         <v>131</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="G132" s="12" t="n">
         <v>47697</v>
       </c>
       <c r="H132" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I132" s="10" t="n">
-        <v>17</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I132" s="10"/>
       <c r="J132" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K132" s="12" t="n">
-        <v>46282</v>
+        <v>46344</v>
       </c>
       <c r="L132" s="13" t="n">
         <f aca="false">IF(K132="","",K132-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>26</v>
       </c>
       <c r="M132" s="10" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="N132" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O132" s="14"/>
       <c r="P132" s="14" t="s">
@@ -8756,7 +8759,7 @@
       <c r="Q132" s="15"/>
       <c r="R132" s="14"/>
     </row>
-    <row r="133" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="10" t="n">
         <v>132</v>
       </c>
@@ -8764,10 +8767,10 @@
         <v>55</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>288</v>
+        <v>185</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>289</v>
@@ -8776,29 +8779,29 @@
         <v>290</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>46244</v>
+        <v>47697</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I133" s="10" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="J133" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>46124</v>
+        <v>46127</v>
       </c>
       <c r="L133" s="13" t="n">
         <f aca="false">IF(K133="","",K133-Resumo!$B$3)</f>
-        <v>-194</v>
+        <v>-191</v>
       </c>
       <c r="M133" s="10" t="s">
-        <v>291</v>
+        <v>250</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="O133" s="14"/>
       <c r="P133" s="14" t="s">
@@ -8807,7 +8810,7 @@
       <c r="Q133" s="15"/>
       <c r="R133" s="14"/>
     </row>
-    <row r="134" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="10" t="n">
         <v>133</v>
       </c>
@@ -8815,10 +8818,10 @@
         <v>55</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>288</v>
+        <v>185</v>
       </c>
       <c r="E134" s="10" t="s">
         <v>289</v>
@@ -8827,29 +8830,29 @@
         <v>290</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>46244</v>
+        <v>47697</v>
       </c>
       <c r="H134" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I134" s="10" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J134" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K134" s="12" t="n">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="L134" s="13" t="n">
         <f aca="false">IF(K134="","",K134-Resumo!$B$3)</f>
-        <v>-42</v>
+        <v>-36</v>
       </c>
       <c r="M134" s="10" t="s">
-        <v>283</v>
+        <v>74</v>
       </c>
       <c r="N134" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O134" s="14"/>
       <c r="P134" s="14" t="s">
@@ -8863,42 +8866,44 @@
         <v>134</v>
       </c>
       <c r="B135" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G135" s="12" t="n">
         <v>46244</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I135" s="10" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J135" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K135" s="12"/>
-      <c r="L135" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K135" s="12" t="n">
+        <v>46124</v>
+      </c>
+      <c r="L135" s="13" t="n">
         <f aca="false">IF(K135="","",K135-Resumo!$B$3)</f>
-        <v/>
+        <v>-194</v>
       </c>
       <c r="M135" s="10" t="s">
-        <v>73</v>
+        <v>295</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O135" s="14"/>
       <c r="P135" s="14" t="s">
@@ -8907,9 +8912,109 @@
       <c r="Q135" s="15"/>
       <c r="R135" s="14"/>
     </row>
+    <row r="136" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="10" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C136" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="D136" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="F136" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H136" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I136" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J136" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K136" s="12" t="n">
+        <v>46276</v>
+      </c>
+      <c r="L136" s="13" t="n">
+        <f aca="false">IF(K136="","",K136-Resumo!$B$3)</f>
+        <v>-42</v>
+      </c>
+      <c r="M136" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="N136" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="O136" s="14"/>
+      <c r="P136" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q136" s="15"/>
+      <c r="R136" s="14"/>
+    </row>
+    <row r="137" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="10" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C137" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="D137" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="E137" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="F137" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H137" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I137" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="J137" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K137" s="12"/>
+      <c r="L137" s="13" t="str">
+        <f aca="false">IF(K137="","",K137-Resumo!$B$3)</f>
+        <v/>
+      </c>
+      <c r="M137" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N137" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O137" s="14"/>
+      <c r="P137" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q137" s="15"/>
+      <c r="R137" s="14"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R135"/>
-  <conditionalFormatting sqref="J2:J135">
+  <autoFilter ref="A1:R137"/>
+  <conditionalFormatting sqref="J2:J137">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$J2="Vencida"</formula>
     </cfRule>
@@ -8920,12 +9025,12 @@
       <formula>$J2="Sem data"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B135">
+  <conditionalFormatting sqref="B2:B137">
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>$B2="Alta"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P135">
+  <conditionalFormatting sqref="P2:P137">
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>$P2="Resolvido"</formula>
     </cfRule>
@@ -8934,7 +9039,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P135" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P137" type="list">
       <formula1>"A fazer,Em andamento,Aguardando cliente,Resolvido,Já estava em dia"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8955,7 +9060,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -8979,7 +9084,7 @@
         <v>8</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8987,15 +9092,15 @@
         <v>46</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A2,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A2,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A2,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A2,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A2,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A2,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>2</v>
       </c>
       <c r="E2" s="7" t="n">
@@ -9003,7 +9108,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A2,Pendências!$B$2:$B$135,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A2,Pendências!$B$2:$B$137,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9012,15 +9117,15 @@
         <v>59</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A3,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A3,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A3,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A3,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A3,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A3,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E3" s="7" t="n">
@@ -9028,7 +9133,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A3,Pendências!$B$2:$B$135,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A3,Pendências!$B$2:$B$137,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9037,15 +9142,15 @@
         <v>64</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A4,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A4,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A4,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A4,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A4,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A4,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
@@ -9053,7 +9158,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A4,Pendências!$B$2:$B$135,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A4,Pendências!$B$2:$B$137,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9062,24 +9167,24 @@
         <v>69</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A5,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A5,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>2</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A5,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
-      <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A5,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A5,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A5,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
         <f aca="false">SUM(B5:D5)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A5,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A5,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9087,199 +9192,199 @@
         <v>75</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A6,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A6,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>0</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A6,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A6,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A6,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A6,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
         <f aca="false">SUM(B6:D6)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A6,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A6,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A7,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A7,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>5</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A7,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>2</v>
       </c>
-      <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A7,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>2</v>
-      </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A7,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A7,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
         <f aca="false">SUM(B7:D7)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A7,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A7,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A8,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A8,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A8,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A8,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A8,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A8,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
         <f aca="false">SUM(B8:D8)</f>
+        <v>4</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A8,Pendências!$B$2:$B$137,"Alta")</f>
         <v>1</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A8,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A9,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A9,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A9,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>1</v>
       </c>
-      <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A9,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>2</v>
-      </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A9,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A9,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
         <f aca="false">SUM(B9:D9)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A9,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A9,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A10,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A10,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A10,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A10,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A10,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A10,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E10" s="7" t="n">
         <f aca="false">SUM(B10:D10)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A10,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A10,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A11,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A11,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>0</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A11,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A11,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>2</v>
       </c>
       <c r="D11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A11,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A11,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E11" s="7" t="n">
         <f aca="false">SUM(B11:D11)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A11,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A11,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A12,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A12,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A12,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A12,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A12,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A12,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
         <f aca="false">SUM(B12:D12)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A12,Pendências!$B$2:$B$135,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A12,Pendências!$B$2:$B$137,"Alta")</f>
         <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A13,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A13,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A13,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A13,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A13,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A13,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
         <f aca="false">SUM(B13:D13)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A13,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A13,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9287,74 +9392,74 @@
         <v>123</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A14,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A14,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A14,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A14,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A14,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A14,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
         <f aca="false">SUM(B14:D14)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A14,Pendências!$B$2:$B$135,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A14,Pendências!$B$2:$B$137,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A15,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A15,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>3</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A15,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>1</v>
       </c>
-      <c r="C15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A15,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>0</v>
-      </c>
       <c r="D15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A15,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A15,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
         <f aca="false">SUM(B15:D15)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A15,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A15,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A16,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A16,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A16,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A16,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A16,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A16,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
         <f aca="false">SUM(B16:D16)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A16,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A16,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9362,140 +9467,140 @@
         <v>139</v>
       </c>
       <c r="B17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A17,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A17,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>4</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A17,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>2</v>
       </c>
-      <c r="C17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A17,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A17,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A17,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
         <f aca="false">SUM(B17:D17)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A17,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A17,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A18,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A18,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>2</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A18,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>1</v>
       </c>
-      <c r="C18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A18,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>0</v>
-      </c>
       <c r="D18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A18,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A18,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
         <f aca="false">SUM(B18:D18)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A18,Pendências!$B$2:$B$135,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A18,Pendências!$B$2:$B$137,"Alta")</f>
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A19,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A19,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A19,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A19,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A19,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A19,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
         <f aca="false">SUM(B19:D19)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A19,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A19,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A20,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A20,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>2</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A20,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>1</v>
       </c>
-      <c r="C20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A20,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>0</v>
-      </c>
       <c r="D20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A20,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A20,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E20" s="7" t="n">
         <f aca="false">SUM(B20:D20)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A20,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A20,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A21,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A21,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A21,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A21,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A21,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A21,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
         <f aca="false">SUM(B21:D21)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A21,Pendências!$B$2:$B$135,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A21,Pendências!$B$2:$B$137,"Alta")</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A22,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A22,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A22,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A22,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A22,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A22,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E22" s="7" t="n">
@@ -9503,8 +9608,8 @@
         <v>2</v>
       </c>
       <c r="F22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A22,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A22,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9512,15 +9617,15 @@
         <v>165</v>
       </c>
       <c r="B23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A23,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A23,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A23,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A23,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A23,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A23,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
@@ -9528,7 +9633,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A23,Pendências!$B$2:$B$135,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A23,Pendências!$B$2:$B$137,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9537,23 +9642,23 @@
         <v>170</v>
       </c>
       <c r="B24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A24,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A24,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A24,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A24,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A24,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A24,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E24" s="7" t="n">
         <f aca="false">SUM(B24:D24)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A24,Pendências!$B$2:$B$135,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A24,Pendências!$B$2:$B$137,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9562,99 +9667,99 @@
         <v>175</v>
       </c>
       <c r="B25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A25,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A25,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A25,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A25,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A25,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A25,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
         <f aca="false">SUM(B25:D25)</f>
+        <v>3</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A25,Pendências!$B$2:$B$137,"Alta")</f>
         <v>2</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A25,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A26,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A26,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A26,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A26,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A26,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A26,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E26" s="7" t="n">
         <f aca="false">SUM(B26:D26)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A26,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A26,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A27,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A27,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>5</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A27,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
-      <c r="C27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A27,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A27,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A27,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
         <f aca="false">SUM(B27:D27)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A27,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A27,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A28,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A28,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>0</v>
       </c>
       <c r="C28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A28,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A28,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A28,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A28,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E28" s="7" t="n">
         <f aca="false">SUM(B28:D28)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A28,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A28,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9662,48 +9767,48 @@
         <v>198</v>
       </c>
       <c r="B29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A29,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A29,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A29,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A29,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A29,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A29,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
         <f aca="false">SUM(B29:D29)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A29,Pendências!$B$2:$B$135,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A29,Pendências!$B$2:$B$137,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A30,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A30,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>3</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A30,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>1</v>
       </c>
-      <c r="C30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A30,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A30,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A30,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <v>0</v>
       </c>
       <c r="E30" s="7" t="n">
         <f aca="false">SUM(B30:D30)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A30,Pendências!$B$2:$B$135,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A30,Pendências!$B$2:$B$137,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9712,215 +9817,215 @@
         <v>210</v>
       </c>
       <c r="B31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A31,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A31,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A31,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A31,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A31,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A31,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E31" s="7" t="n">
         <f aca="false">SUM(B31:D31)</f>
+        <v>3</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A31,Pendências!$B$2:$B$137,"Alta")</f>
         <v>2</v>
-      </c>
-      <c r="F31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A31,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A32,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A32,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A32,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A32,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A32,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A32,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E32" s="7" t="n">
         <f aca="false">SUM(B32:D32)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A32,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A32,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A33,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A33,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>4</v>
       </c>
       <c r="C33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A33,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A33,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A33,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A33,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
         <f aca="false">SUM(B33:D33)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A33,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A33,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A34,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A34,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A34,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A34,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A34,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A34,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <v>0</v>
       </c>
       <c r="E34" s="7" t="n">
         <f aca="false">SUM(B34:D34)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A34,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A34,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A35,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A35,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A35,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A35,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A35,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A35,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E35" s="7" t="n">
         <f aca="false">SUM(B35:D35)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A35,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A35,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A36,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A36,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A36,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A36,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A36,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A36,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E36" s="7" t="n">
         <f aca="false">SUM(B36:D36)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A36,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A36,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A37,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A37,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A37,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A37,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A37,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A37,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E37" s="7" t="n">
         <f aca="false">SUM(B37:D37)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A37,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A37,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A38,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A38,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A38,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A38,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A38,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A38,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E38" s="7" t="n">
         <f aca="false">SUM(B38:D38)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A38,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A38,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A39,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A39,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A39,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A39,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A39,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A39,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
@@ -9928,7 +10033,7 @@
         <v>3</v>
       </c>
       <c r="F39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A39,Pendências!$B$2:$B$135,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A39,Pendências!$B$2:$B$137,"Alta")</f>
         <v>3</v>
       </c>
     </row>
@@ -9937,15 +10042,15 @@
         <v>258</v>
       </c>
       <c r="B40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A40,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A40,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A40,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A40,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A40,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A40,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E40" s="7" t="n">
@@ -9953,8 +10058,8 @@
         <v>3</v>
       </c>
       <c r="F40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A40,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A40,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9962,15 +10067,15 @@
         <v>262</v>
       </c>
       <c r="B41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A41,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A41,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>1</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A41,Pendências!$J$2:$J$137,"Sem data")</f>
         <v>2</v>
       </c>
-      <c r="C41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A41,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A41,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A41,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E41" s="7" t="n">
@@ -9978,8 +10083,8 @@
         <v>3</v>
       </c>
       <c r="F41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A41,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A41,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9987,128 +10092,153 @@
         <v>266</v>
       </c>
       <c r="B42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A42,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A42,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A42,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A42,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>1</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A42,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
-      </c>
-      <c r="D42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A42,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>1</v>
       </c>
       <c r="E42" s="7" t="n">
         <f aca="false">SUM(B42:D42)</f>
         <v>3</v>
       </c>
       <c r="F42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A42,Pendências!$B$2:$B$135,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A42,Pendências!$B$2:$B$137,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A43,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A43,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A43,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A43,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A43,Pendências!$J$2:$J$135,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A43,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E43" s="7" t="n">
         <f aca="false">SUM(B43:D43)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A43,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A43,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A44,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A44,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>4</v>
       </c>
       <c r="C44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A44,Pendências!$J$2:$J$135,"Sem data")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A44,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A44,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A44,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E44" s="7" t="n">
         <f aca="false">SUM(B44:D44)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A44,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A44,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A45,Pendências!$J$2:$J$135,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A45,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A45,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A45,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>4</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A45,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>0</v>
-      </c>
-      <c r="D45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A45,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>1</v>
       </c>
       <c r="E45" s="7" t="n">
         <f aca="false">SUM(B45:D45)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A45,Pendências!$B$2:$B$135,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A45,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A46,Pendências!$J$2:$J$135,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A46,Pendências!$J$2:$J$137,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A46,Pendências!$J$2:$J$135,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A46,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A46,Pendências!$J$2:$J$137,"Vence em breve")</f>
         <v>1</v>
-      </c>
-      <c r="D46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A46,Pendências!$J$2:$J$135,"Vence em breve")</f>
-        <v>0</v>
       </c>
       <c r="E46" s="7" t="n">
         <f aca="false">SUM(B46:D46)</f>
         <v>3</v>
       </c>
       <c r="F46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$135,$A46,Pendências!$B$2:$B$135,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A46,Pendências!$B$2:$B$137,"Alta")</f>
         <v>2</v>
       </c>
     </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="B47" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A47,Pendências!$J$2:$J$137,"Vencida")</f>
+        <v>2</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A47,Pendências!$J$2:$J$137,"Sem data")</f>
+        <v>1</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A47,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <v>0</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <f aca="false">SUM(B47:D47)</f>
+        <v>3</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A47,Pendências!$B$2:$B$137,"Alta")</f>
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F46"/>
+  <autoFilter ref="A1:F47"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -10125,7 +10255,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -10153,211 +10283,200 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>338</v>
+        <v>107</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>102</v>
+        <v>316</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
-        <v>344</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/pendencias-condicionantes-2026-10-23.xlsx
+++ b/pendencias-condicionantes-2026-10-23.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Licenças que faltam" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Pendências!$A$1:$R$137</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Por empresa'!$A$1:$F$47</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Pendências!$A$1:$R$140</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Por empresa'!$A$1:$F$48</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="348">
   <si>
     <t xml:space="preserve">Condicionantes ambientais – pendências</t>
   </si>
@@ -398,6 +398,18 @@
     <t xml:space="preserve">2024-219372/TEC/LO-0637</t>
   </si>
   <si>
+    <t xml:space="preserve">Coronel Gas Ltda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.720.210/0001-67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-191048/TEC/LS-0057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documento na pasta: AVCB nº 65101 emitido em 28/10/2025</t>
+  </si>
+  <si>
     <t xml:space="preserve">Damiana Maria De Jesus Dantas Varejista</t>
   </si>
   <si>
@@ -918,15 +930,6 @@
   </si>
   <si>
     <t xml:space="preserve">Prioridade alta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gás Coronel (Maria S N Gomes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.720.210/0001-67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pasta 23 sem licença; AVCB é de revenda de GLP (confirmar se é gás)</t>
   </si>
   <si>
     <t xml:space="preserve">G J Santos de Oliveira – Areia Branca</t>
@@ -1776,15 +1779,15 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A6,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A6,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>12</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A6,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A6,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A6,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A6,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
@@ -1797,15 +1800,15 @@
         <v>10</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A7,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A7,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>8</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A7,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A7,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A7,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A7,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>4</v>
       </c>
       <c r="E7" s="7" t="n">
@@ -1818,20 +1821,20 @@
         <v>11</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A8,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>6</v>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A8,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>7</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A8,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A8,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A8,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A8,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
         <f aca="false">SUM(B8:D8)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1839,20 +1842,20 @@
         <v>12</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A9,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A9,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>5</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A9,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A9,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A9,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A9,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
         <f aca="false">SUM(B9:D9)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1860,15 +1863,15 @@
         <v>13</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A10,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A10,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A10,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A10,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A10,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A10,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E10" s="7" t="n">
@@ -1881,20 +1884,20 @@
         <v>14</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A11,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A11,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>24</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A11,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A11,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>8</v>
       </c>
       <c r="D11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A11,Pendências!$J$2:$J$137,"Vence em breve")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A11,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <v>4</v>
       </c>
       <c r="E11" s="7" t="n">
         <f aca="false">SUM(B11:D11)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1902,15 +1905,15 @@
         <v>15</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A12,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A12,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>37</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A12,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A12,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>8</v>
       </c>
       <c r="D12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A12,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A12,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
@@ -1923,15 +1926,15 @@
         <v>16</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A13,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A13,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A13,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A13,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>4</v>
       </c>
       <c r="D13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A13,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A13,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>3</v>
       </c>
       <c r="E13" s="7" t="n">
@@ -1944,15 +1947,15 @@
         <v>17</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A14,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A14,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A14,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A14,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A14,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A14,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
@@ -1965,15 +1968,15 @@
         <v>18</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A15,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A15,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A15,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A15,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>4</v>
       </c>
       <c r="D15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A15,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A15,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
@@ -1986,15 +1989,15 @@
         <v>19</v>
       </c>
       <c r="B16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A16,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A16,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A16,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A16,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>3</v>
       </c>
       <c r="D16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$137,$A16,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A16,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
@@ -2008,7 +2011,7 @@
       </c>
       <c r="B17" s="8" t="n">
         <f aca="false">SUM(B6:B16)</f>
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C17" s="8" t="n">
         <f aca="false">SUM(C6:C16)</f>
@@ -2016,11 +2019,11 @@
       </c>
       <c r="D17" s="8" t="n">
         <f aca="false">SUM(D6:D16)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" s="8" t="n">
         <f aca="false">SUM(E6:E16)</f>
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,8 +2036,8 @@
         <v>22</v>
       </c>
       <c r="B20" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$137,A20)</f>
-        <v>136</v>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$140,A20)</f>
+        <v>139</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2042,7 +2045,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$137,A21)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$140,A21)</f>
         <v>0</v>
       </c>
     </row>
@@ -2051,7 +2054,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$137,A22)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$140,A22)</f>
         <v>0</v>
       </c>
     </row>
@@ -2060,7 +2063,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$137,A23)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$140,A23)</f>
         <v>0</v>
       </c>
     </row>
@@ -2069,7 +2072,7 @@
         <v>26</v>
       </c>
       <c r="B24" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$137,A24)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$140,A24)</f>
         <v>0</v>
       </c>
     </row>
@@ -2094,7 +2097,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R137"/>
+  <dimension ref="A1:R140"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3925,49 +3928,49 @@
       <c r="Q36" s="15"/>
       <c r="R36" s="14"/>
     </row>
-    <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>123</v>
       </c>
       <c r="D37" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E37" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="F37" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="F37" s="10" t="s">
-        <v>126</v>
-      </c>
       <c r="G37" s="12" t="n">
-        <v>47037</v>
+        <v>47193</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J37" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>46225</v>
+        <v>46131</v>
       </c>
       <c r="L37" s="13" t="n">
         <f aca="false">IF(K37="","",K37-Resumo!$B$3)</f>
-        <v>-93</v>
+        <v>-187</v>
       </c>
       <c r="M37" s="10" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="O37" s="14"/>
       <c r="P37" s="14" t="s">
@@ -3981,44 +3984,44 @@
         <v>37</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>123</v>
       </c>
       <c r="D38" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E38" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="F38" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="F38" s="10" t="s">
-        <v>126</v>
-      </c>
       <c r="G38" s="12" t="n">
-        <v>47037</v>
+        <v>47193</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J38" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>46282</v>
+        <v>46211</v>
       </c>
       <c r="L38" s="13" t="n">
         <f aca="false">IF(K38="","",K38-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-107</v>
       </c>
       <c r="M38" s="10" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N38" s="10" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="O38" s="14"/>
       <c r="P38" s="14" t="s">
@@ -4032,42 +4035,44 @@
         <v>38</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>48208</v>
+        <v>47193</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I39" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I39" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J39" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>45322</v>
+        <v>46323</v>
       </c>
       <c r="L39" s="13" t="n">
         <f aca="false">IF(K39="","",K39-Resumo!$B$3)</f>
-        <v>-996</v>
+        <v>5</v>
       </c>
       <c r="M39" s="10" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O39" s="14"/>
       <c r="P39" s="14" t="s">
@@ -4084,19 +4089,19 @@
         <v>55</v>
       </c>
       <c r="C40" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D40" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="E40" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="F40" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="F40" s="10" t="s">
-        <v>131</v>
-      </c>
       <c r="G40" s="12" t="n">
-        <v>48208</v>
+        <v>47037</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>14</v>
@@ -4108,14 +4113,14 @@
         <v>56</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>46239</v>
+        <v>46225</v>
       </c>
       <c r="L40" s="13" t="n">
         <f aca="false">IF(K40="","",K40-Resumo!$B$3)</f>
-        <v>-79</v>
+        <v>-93</v>
       </c>
       <c r="M40" s="10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N40" s="10" t="s">
         <v>54</v>
@@ -4135,25 +4140,25 @@
         <v>55</v>
       </c>
       <c r="C41" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D41" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="E41" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="F41" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>131</v>
-      </c>
       <c r="G41" s="12" t="n">
-        <v>48208</v>
+        <v>47037</v>
       </c>
       <c r="H41" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J41" s="10" t="s">
         <v>56</v>
@@ -4178,47 +4183,47 @@
       <c r="Q41" s="15"/>
       <c r="R41" s="14"/>
     </row>
-    <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>48208</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="I42" s="10" t="n">
-        <v>11</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I42" s="10"/>
       <c r="J42" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K42" s="12"/>
-      <c r="L42" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K42" s="12" t="n">
+        <v>45322</v>
+      </c>
+      <c r="L42" s="13" t="n">
         <f aca="false">IF(K42="","",K42-Resumo!$B$3)</f>
-        <v/>
+        <v>-996</v>
       </c>
       <c r="M42" s="10" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="N42" s="10" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="O42" s="14"/>
       <c r="P42" s="14" t="s">
@@ -4227,7 +4232,7 @@
       <c r="Q42" s="15"/>
       <c r="R42" s="14"/>
     </row>
-    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="n">
         <v>42</v>
       </c>
@@ -4235,41 +4240,41 @@
         <v>55</v>
       </c>
       <c r="C43" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F43" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="D43" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>138</v>
-      </c>
       <c r="G43" s="12" t="n">
-        <v>47333</v>
+        <v>48208</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J43" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>46282</v>
+        <v>46239</v>
       </c>
       <c r="L43" s="13" t="n">
         <f aca="false">IF(K43="","",K43-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-79</v>
       </c>
       <c r="M43" s="10" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O43" s="14"/>
       <c r="P43" s="14" t="s">
@@ -4283,44 +4288,44 @@
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>48394</v>
+        <v>48208</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J44" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>46212</v>
+        <v>46282</v>
       </c>
       <c r="L44" s="13" t="n">
         <f aca="false">IF(K44="","",K44-Resumo!$B$3)</f>
-        <v>-106</v>
+        <v>-36</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="N44" s="10" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="O44" s="14"/>
       <c r="P44" s="14" t="s">
@@ -4329,49 +4334,47 @@
       <c r="Q44" s="15"/>
       <c r="R44" s="14"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>48394</v>
+        <v>48208</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K45" s="12" t="n">
-        <v>46292</v>
-      </c>
-      <c r="L45" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K45" s="12"/>
+      <c r="L45" s="13" t="str">
         <f aca="false">IF(K45="","",K45-Resumo!$B$3)</f>
-        <v>-26</v>
+        <v/>
       </c>
       <c r="M45" s="10" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="O45" s="14"/>
       <c r="P45" s="14" t="s">
@@ -4380,7 +4383,7 @@
       <c r="Q45" s="15"/>
       <c r="R45" s="14"/>
     </row>
-    <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="n">
         <v>45</v>
       </c>
@@ -4391,38 +4394,38 @@
         <v>139</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>48394</v>
+        <v>47333</v>
       </c>
       <c r="H46" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="I46" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="J46" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>46323</v>
+        <v>46282</v>
       </c>
       <c r="L46" s="13" t="n">
         <f aca="false">IF(K46="","",K46-Resumo!$B$3)</f>
-        <v>5</v>
+        <v>-36</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>142</v>
+        <v>74</v>
       </c>
       <c r="N46" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O46" s="14"/>
       <c r="P46" s="14" t="s">
@@ -4436,44 +4439,44 @@
         <v>46</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>48394</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J47" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>46282</v>
+        <v>46212</v>
       </c>
       <c r="L47" s="13" t="n">
         <f aca="false">IF(K47="","",K47-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-106</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="O47" s="14"/>
       <c r="P47" s="14" t="s">
@@ -4482,7 +4485,7 @@
       <c r="Q47" s="15"/>
       <c r="R47" s="14"/>
     </row>
-    <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="n">
         <v>47</v>
       </c>
@@ -4490,41 +4493,41 @@
         <v>80</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>48394</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J48" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>44478</v>
+        <v>46292</v>
       </c>
       <c r="L48" s="13" t="n">
         <f aca="false">IF(K48="","",K48-Resumo!$B$3)</f>
-        <v>-1840</v>
+        <v>-26</v>
       </c>
       <c r="M48" s="10" t="s">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="N48" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O48" s="14"/>
       <c r="P48" s="14" t="s">
@@ -4533,47 +4536,49 @@
       <c r="Q48" s="15"/>
       <c r="R48" s="14"/>
     </row>
-    <row r="49" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>48394</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K49" s="12"/>
-      <c r="L49" s="13" t="str">
+        <v>50</v>
+      </c>
+      <c r="K49" s="12" t="n">
+        <v>46323</v>
+      </c>
+      <c r="L49" s="13" t="n">
         <f aca="false">IF(K49="","",K49-Resumo!$B$3)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="O49" s="14"/>
       <c r="P49" s="14" t="s">
@@ -4587,42 +4592,44 @@
         <v>49</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G50" s="12" t="n">
         <v>48394</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K50" s="12"/>
-      <c r="L50" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K50" s="12" t="n">
+        <v>46282</v>
+      </c>
+      <c r="L50" s="13" t="n">
         <f aca="false">IF(K50="","",K50-Resumo!$B$3)</f>
-        <v/>
+        <v>-36</v>
       </c>
       <c r="M50" s="10" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="N50" s="10" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="O50" s="14"/>
       <c r="P50" s="14" t="s">
@@ -4639,39 +4646,41 @@
         <v>80</v>
       </c>
       <c r="C51" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="E51" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="F51" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="E51" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>147</v>
-      </c>
       <c r="G51" s="12" t="n">
-        <v>47129</v>
+        <v>48394</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I51" s="10"/>
+        <v>16</v>
+      </c>
+      <c r="I51" s="10" t="n">
+        <v>14</v>
+      </c>
       <c r="J51" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>46273</v>
+        <v>44478</v>
       </c>
       <c r="L51" s="13" t="n">
         <f aca="false">IF(K51="","",K51-Resumo!$B$3)</f>
-        <v>-45</v>
+        <v>-1840</v>
       </c>
       <c r="M51" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="O51" s="14"/>
       <c r="P51" s="14" t="s">
@@ -4680,7 +4689,7 @@
       <c r="Q51" s="15"/>
       <c r="R51" s="14"/>
     </row>
-    <row r="52" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="n">
         <v>51</v>
       </c>
@@ -4688,25 +4697,25 @@
         <v>45</v>
       </c>
       <c r="C52" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="E52" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="F52" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="E52" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>147</v>
-      </c>
       <c r="G52" s="12" t="n">
-        <v>47129</v>
+        <v>48394</v>
       </c>
       <c r="H52" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I52" s="10" t="n">
         <v>14</v>
-      </c>
-      <c r="I52" s="10" t="n">
-        <v>5</v>
       </c>
       <c r="J52" s="10" t="s">
         <v>6</v>
@@ -4720,7 +4729,7 @@
         <v>79</v>
       </c>
       <c r="N52" s="10" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="O52" s="14"/>
       <c r="P52" s="14" t="s">
@@ -4734,44 +4743,42 @@
         <v>52</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C53" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="E53" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="F53" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="E53" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>147</v>
-      </c>
       <c r="G53" s="12" t="n">
-        <v>47129</v>
+        <v>48394</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K53" s="12" t="n">
-        <v>46282</v>
-      </c>
-      <c r="L53" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K53" s="12"/>
+      <c r="L53" s="13" t="str">
         <f aca="false">IF(K53="","",K53-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v/>
       </c>
       <c r="M53" s="10" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="O53" s="14"/>
       <c r="P53" s="14" t="s">
@@ -4785,44 +4792,42 @@
         <v>53</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>47129</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I54" s="10" t="n">
-        <v>8</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I54" s="10"/>
       <c r="J54" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>46337</v>
+        <v>46273</v>
       </c>
       <c r="L54" s="13" t="n">
         <f aca="false">IF(K54="","",K54-Resumo!$B$3)</f>
-        <v>19</v>
+        <v>-45</v>
       </c>
       <c r="M54" s="10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="N54" s="10" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="O54" s="14"/>
       <c r="P54" s="14" t="s">
@@ -4831,49 +4836,47 @@
       <c r="Q54" s="15"/>
       <c r="R54" s="14"/>
     </row>
-    <row r="55" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C55" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E55" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="D55" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E55" s="10" t="s">
+      <c r="F55" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>152</v>
-      </c>
       <c r="G55" s="12" t="n">
-        <v>46872</v>
+        <v>47129</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K55" s="12" t="n">
-        <v>46281</v>
-      </c>
-      <c r="L55" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K55" s="12"/>
+      <c r="L55" s="13" t="str">
         <f aca="false">IF(K55="","",K55-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v/>
       </c>
       <c r="M55" s="10" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O55" s="14"/>
       <c r="P55" s="14" t="s">
@@ -4890,41 +4893,41 @@
         <v>55</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>46374</v>
+        <v>47129</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J56" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>46254</v>
+        <v>46282</v>
       </c>
       <c r="L56" s="13" t="n">
         <f aca="false">IF(K56="","",K56-Resumo!$B$3)</f>
-        <v>-64</v>
+        <v>-36</v>
       </c>
       <c r="M56" s="10" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="N56" s="10" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="O56" s="14"/>
       <c r="P56" s="14" t="s">
@@ -4933,7 +4936,7 @@
       <c r="Q56" s="15"/>
       <c r="R56" s="14"/>
     </row>
-    <row r="57" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="n">
         <v>56</v>
       </c>
@@ -4941,39 +4944,41 @@
         <v>45</v>
       </c>
       <c r="C57" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>47129</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J57" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K57" s="12" t="n">
+        <v>46337</v>
+      </c>
+      <c r="L57" s="13" t="n">
+        <f aca="false">IF(K57="","",K57-Resumo!$B$3)</f>
+        <v>19</v>
+      </c>
+      <c r="M57" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="D57" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="G57" s="12" t="n">
-        <v>46374</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I57" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="J57" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K57" s="12"/>
-      <c r="L57" s="13" t="str">
-        <f aca="false">IF(K57="","",K57-Resumo!$B$3)</f>
-        <v/>
-      </c>
-      <c r="M57" s="10" t="s">
-        <v>79</v>
-      </c>
       <c r="N57" s="10" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="O57" s="14"/>
       <c r="P57" s="14" t="s">
@@ -4990,10 +4995,10 @@
         <v>55</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>155</v>
@@ -5002,7 +5007,7 @@
         <v>156</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>46374</v>
+        <v>46872</v>
       </c>
       <c r="H58" s="10" t="s">
         <v>15</v>
@@ -5014,14 +5019,14 @@
         <v>56</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="L58" s="13" t="n">
         <f aca="false">IF(K58="","",K58-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="M58" s="10" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="N58" s="10" t="s">
         <v>58</v>
@@ -5053,27 +5058,29 @@
         <v>160</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>46911</v>
+        <v>46374</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I59" s="10"/>
+        <v>9</v>
+      </c>
+      <c r="I59" s="10" t="n">
+        <v>20</v>
+      </c>
       <c r="J59" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L59" s="13" t="n">
         <f aca="false">IF(K59="","",K59-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-64</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O59" s="14"/>
       <c r="P59" s="14" t="s">
@@ -5090,24 +5097,26 @@
         <v>45</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>46875</v>
+        <v>46374</v>
       </c>
       <c r="H60" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I60" s="10"/>
+      <c r="I60" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J60" s="10" t="s">
         <v>6</v>
       </c>
@@ -5137,24 +5146,26 @@
         <v>55</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>46875</v>
+        <v>46374</v>
       </c>
       <c r="H61" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I61" s="10"/>
+      <c r="I61" s="10" t="n">
+        <v>15</v>
+      </c>
       <c r="J61" s="10" t="s">
         <v>56</v>
       </c>
@@ -5178,7 +5189,7 @@
       <c r="Q61" s="15"/>
       <c r="R61" s="14"/>
     </row>
-    <row r="62" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="n">
         <v>61</v>
       </c>
@@ -5186,41 +5197,39 @@
         <v>55</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>47952</v>
+        <v>46911</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I62" s="10" t="n">
-        <v>5</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I62" s="10"/>
       <c r="J62" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>45898</v>
+        <v>46282</v>
       </c>
       <c r="L62" s="13" t="n">
         <f aca="false">IF(K62="","",K62-Resumo!$B$3)</f>
-        <v>-420</v>
+        <v>-36</v>
       </c>
       <c r="M62" s="10" t="s">
-        <v>169</v>
+        <v>74</v>
       </c>
       <c r="N62" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O62" s="14"/>
       <c r="P62" s="14" t="s">
@@ -5229,12 +5238,12 @@
       <c r="Q62" s="15"/>
       <c r="R62" s="14"/>
     </row>
-    <row r="63" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>165</v>
@@ -5249,29 +5258,25 @@
         <v>168</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>47952</v>
+        <v>46875</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I63" s="10" t="n">
-        <v>17</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I63" s="10"/>
       <c r="J63" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K63" s="12" t="n">
-        <v>46281</v>
-      </c>
-      <c r="L63" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K63" s="12"/>
+      <c r="L63" s="13" t="str">
         <f aca="false">IF(K63="","",K63-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v/>
       </c>
       <c r="M63" s="10" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O63" s="14"/>
       <c r="P63" s="14" t="s">
@@ -5280,7 +5285,7 @@
       <c r="Q63" s="15"/>
       <c r="R63" s="14"/>
     </row>
-    <row r="64" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="n">
         <v>63</v>
       </c>
@@ -5288,41 +5293,39 @@
         <v>55</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>46990</v>
+        <v>46875</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I64" s="10" t="n">
-        <v>5</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I64" s="10"/>
       <c r="J64" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>46163</v>
+        <v>46282</v>
       </c>
       <c r="L64" s="13" t="n">
         <f aca="false">IF(K64="","",K64-Resumo!$B$3)</f>
-        <v>-155</v>
+        <v>-36</v>
       </c>
       <c r="M64" s="10" t="s">
-        <v>174</v>
+        <v>74</v>
       </c>
       <c r="N64" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O64" s="14"/>
       <c r="P64" s="14" t="s">
@@ -5331,7 +5334,7 @@
       <c r="Q64" s="15"/>
       <c r="R64" s="14"/>
     </row>
-    <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="n">
         <v>64</v>
       </c>
@@ -5339,41 +5342,41 @@
         <v>55</v>
       </c>
       <c r="C65" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D65" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="D65" s="10" t="s">
+      <c r="E65" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="E65" s="10" t="s">
+      <c r="F65" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="F65" s="10" t="s">
-        <v>173</v>
-      </c>
       <c r="G65" s="12" t="n">
-        <v>46990</v>
+        <v>47952</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I65" s="10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J65" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>46281</v>
+        <v>45898</v>
       </c>
       <c r="L65" s="13" t="n">
         <f aca="false">IF(K65="","",K65-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-420</v>
       </c>
       <c r="M65" s="10" t="s">
-        <v>57</v>
+        <v>173</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O65" s="14"/>
       <c r="P65" s="14" t="s">
@@ -5387,42 +5390,44 @@
         <v>65</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>47087</v>
+        <v>47952</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I66" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="I66" s="10" t="n">
+        <v>17</v>
+      </c>
       <c r="J66" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="L66" s="13" t="n">
         <f aca="false">IF(K66="","",K66-Resumo!$B$3)</f>
-        <v>-44</v>
+        <v>-37</v>
       </c>
       <c r="M66" s="10" t="s">
-        <v>178</v>
+        <v>57</v>
       </c>
       <c r="N66" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O66" s="14"/>
       <c r="P66" s="14" t="s">
@@ -5439,10 +5444,10 @@
         <v>55</v>
       </c>
       <c r="C67" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="D67" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>95</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>176</v>
@@ -5451,7 +5456,7 @@
         <v>177</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>47087</v>
+        <v>46990</v>
       </c>
       <c r="H67" s="10" t="s">
         <v>14</v>
@@ -5463,14 +5468,14 @@
         <v>56</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>45997</v>
+        <v>46163</v>
       </c>
       <c r="L67" s="13" t="n">
         <f aca="false">IF(K67="","",K67-Resumo!$B$3)</f>
-        <v>-321</v>
+        <v>-155</v>
       </c>
       <c r="M67" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N67" s="10" t="s">
         <v>54</v>
@@ -5490,10 +5495,10 @@
         <v>55</v>
       </c>
       <c r="C68" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="D68" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>95</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>176</v>
@@ -5502,7 +5507,7 @@
         <v>177</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>47087</v>
+        <v>46990</v>
       </c>
       <c r="H68" s="10" t="s">
         <v>15</v>
@@ -5541,19 +5546,19 @@
         <v>80</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>95</v>
       </c>
       <c r="E69" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="F69" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="F69" s="10" t="s">
-        <v>182</v>
-      </c>
       <c r="G69" s="12" t="n">
-        <v>47854</v>
+        <v>47087</v>
       </c>
       <c r="H69" s="10" t="s">
         <v>10</v>
@@ -5563,14 +5568,14 @@
         <v>56</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>46316</v>
+        <v>46274</v>
       </c>
       <c r="L69" s="13" t="n">
         <f aca="false">IF(K69="","",K69-Resumo!$B$3)</f>
-        <v>-2</v>
+        <v>-44</v>
       </c>
       <c r="M69" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N69" s="10" t="s">
         <v>52</v>
@@ -5582,7 +5587,7 @@
       <c r="Q69" s="15"/>
       <c r="R69" s="14"/>
     </row>
-    <row r="70" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="n">
         <v>69</v>
       </c>
@@ -5590,41 +5595,41 @@
         <v>55</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>95</v>
       </c>
       <c r="E70" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="F70" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="F70" s="10" t="s">
-        <v>182</v>
-      </c>
       <c r="G70" s="12" t="n">
-        <v>47854</v>
+        <v>47087</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I70" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J70" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>46281</v>
+        <v>45997</v>
       </c>
       <c r="L70" s="13" t="n">
         <f aca="false">IF(K70="","",K70-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-321</v>
       </c>
       <c r="M70" s="10" t="s">
-        <v>57</v>
+        <v>183</v>
       </c>
       <c r="N70" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O70" s="14"/>
       <c r="P70" s="14" t="s">
@@ -5641,41 +5646,41 @@
         <v>55</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>185</v>
+        <v>95</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>46031</v>
+        <v>47087</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I71" s="10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J71" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>45911</v>
+        <v>46281</v>
       </c>
       <c r="L71" s="13" t="n">
         <f aca="false">IF(K71="","",K71-Resumo!$B$3)</f>
-        <v>-407</v>
+        <v>-37</v>
       </c>
       <c r="M71" s="10" t="s">
-        <v>188</v>
+        <v>57</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="O71" s="14"/>
       <c r="P71" s="14" t="s">
@@ -5684,7 +5689,7 @@
       <c r="Q71" s="15"/>
       <c r="R71" s="14"/>
     </row>
-    <row r="72" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="n">
         <v>71</v>
       </c>
@@ -5695,16 +5700,16 @@
         <v>184</v>
       </c>
       <c r="D72" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E72" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="E72" s="10" t="s">
+      <c r="F72" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="F72" s="10" t="s">
-        <v>187</v>
-      </c>
       <c r="G72" s="12" t="n">
-        <v>46031</v>
+        <v>47854</v>
       </c>
       <c r="H72" s="10" t="s">
         <v>10</v>
@@ -5714,14 +5719,14 @@
         <v>56</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>45659</v>
+        <v>46316</v>
       </c>
       <c r="L72" s="13" t="n">
         <f aca="false">IF(K72="","",K72-Resumo!$B$3)</f>
-        <v>-659</v>
+        <v>-2</v>
       </c>
       <c r="M72" s="10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N72" s="10" t="s">
         <v>52</v>
@@ -5738,44 +5743,44 @@
         <v>72</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>184</v>
       </c>
       <c r="D73" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E73" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="E73" s="10" t="s">
+      <c r="F73" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="F73" s="10" t="s">
-        <v>187</v>
-      </c>
       <c r="G73" s="12" t="n">
-        <v>46031</v>
+        <v>47854</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I73" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J73" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>46083</v>
+        <v>46281</v>
       </c>
       <c r="L73" s="13" t="n">
         <f aca="false">IF(K73="","",K73-Resumo!$B$3)</f>
-        <v>-235</v>
+        <v>-37</v>
       </c>
       <c r="M73" s="10" t="s">
-        <v>190</v>
+        <v>57</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>191</v>
+        <v>58</v>
       </c>
       <c r="O73" s="14"/>
       <c r="P73" s="14" t="s">
@@ -5784,7 +5789,7 @@
       <c r="Q73" s="15"/>
       <c r="R73" s="14"/>
     </row>
-    <row r="74" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="n">
         <v>73</v>
       </c>
@@ -5792,41 +5797,41 @@
         <v>55</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G74" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="H74" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I74" s="10" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J74" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>45514</v>
+        <v>45911</v>
       </c>
       <c r="L74" s="13" t="n">
         <f aca="false">IF(K74="","",K74-Resumo!$B$3)</f>
-        <v>-804</v>
+        <v>-407</v>
       </c>
       <c r="M74" s="10" t="s">
         <v>192</v>
       </c>
       <c r="N74" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O74" s="14"/>
       <c r="P74" s="14" t="s">
@@ -5835,49 +5840,47 @@
       <c r="Q74" s="15"/>
       <c r="R74" s="14"/>
     </row>
-    <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I75" s="10" t="n">
-        <v>15</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I75" s="10"/>
       <c r="J75" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>45356</v>
+        <v>45659</v>
       </c>
       <c r="L75" s="13" t="n">
         <f aca="false">IF(K75="","",K75-Resumo!$B$3)</f>
-        <v>-962</v>
+        <v>-659</v>
       </c>
       <c r="M75" s="10" t="s">
         <v>193</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O75" s="14"/>
       <c r="P75" s="14" t="s">
@@ -5891,42 +5894,44 @@
         <v>75</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C76" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>46031</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I76" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="J76" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K76" s="12" t="n">
+        <v>46083</v>
+      </c>
+      <c r="L76" s="13" t="n">
+        <f aca="false">IF(K76="","",K76-Resumo!$B$3)</f>
+        <v>-235</v>
+      </c>
+      <c r="M76" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="N76" s="10" t="s">
         <v>195</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="F76" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="G76" s="12" t="n">
-        <v>46729</v>
-      </c>
-      <c r="H76" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I76" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="J76" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K76" s="12"/>
-      <c r="L76" s="13" t="str">
-        <f aca="false">IF(K76="","",K76-Resumo!$B$3)</f>
-        <v/>
-      </c>
-      <c r="M76" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="N76" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="O76" s="14"/>
       <c r="P76" s="14" t="s">
@@ -5935,47 +5940,49 @@
       <c r="Q76" s="15"/>
       <c r="R76" s="14"/>
     </row>
-    <row r="77" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>65</v>
+        <v>189</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>48171</v>
+        <v>46031</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I77" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I77" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J77" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>46272</v>
+        <v>45514</v>
       </c>
       <c r="L77" s="13" t="n">
         <f aca="false">IF(K77="","",K77-Resumo!$B$3)</f>
-        <v>-46</v>
+        <v>-804</v>
       </c>
       <c r="M77" s="10" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O77" s="14"/>
       <c r="P77" s="14" t="s">
@@ -5984,7 +5991,7 @@
       <c r="Q77" s="15"/>
       <c r="R77" s="14"/>
     </row>
-    <row r="78" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="n">
         <v>77</v>
       </c>
@@ -5992,41 +5999,41 @@
         <v>55</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>65</v>
+        <v>189</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>48171</v>
+        <v>46031</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I78" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J78" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>46309</v>
+        <v>45356</v>
       </c>
       <c r="L78" s="13" t="n">
         <f aca="false">IF(K78="","",K78-Resumo!$B$3)</f>
-        <v>-9</v>
+        <v>-962</v>
       </c>
       <c r="M78" s="10" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="N78" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O78" s="14"/>
       <c r="P78" s="14" t="s">
@@ -6040,22 +6047,22 @@
         <v>78</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C79" s="10" t="s">
         <v>198</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>65</v>
+        <v>199</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>48171</v>
+        <v>46729</v>
       </c>
       <c r="H79" s="10" t="s">
         <v>15</v>
@@ -6064,17 +6071,15 @@
         <v>15</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K79" s="12" t="n">
-        <v>46281</v>
-      </c>
-      <c r="L79" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K79" s="12"/>
+      <c r="L79" s="13" t="str">
         <f aca="false">IF(K79="","",K79-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v/>
       </c>
       <c r="M79" s="10" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="N79" s="10" t="s">
         <v>58</v>
@@ -6091,44 +6096,42 @@
         <v>79</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C80" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E80" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="D80" s="10" t="s">
+      <c r="F80" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="E80" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="F80" s="10" t="s">
-        <v>206</v>
-      </c>
       <c r="G80" s="12" t="n">
-        <v>46288</v>
+        <v>48171</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="I80" s="10" t="n">
-        <v>18</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I80" s="10"/>
       <c r="J80" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>46168</v>
+        <v>46272</v>
       </c>
       <c r="L80" s="13" t="n">
         <f aca="false">IF(K80="","",K80-Resumo!$B$3)</f>
-        <v>-150</v>
+        <v>-46</v>
       </c>
       <c r="M80" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="N80" s="10" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="O80" s="14"/>
       <c r="P80" s="14" t="s">
@@ -6137,49 +6140,49 @@
       <c r="Q80" s="15"/>
       <c r="R80" s="14"/>
     </row>
-    <row r="81" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C81" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E81" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="D81" s="10" t="s">
+      <c r="F81" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="E81" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="F81" s="10" t="s">
-        <v>208</v>
-      </c>
       <c r="G81" s="12" t="n">
-        <v>48005</v>
+        <v>48171</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I81" s="10" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J81" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>46163</v>
+        <v>46309</v>
       </c>
       <c r="L81" s="13" t="n">
         <f aca="false">IF(K81="","",K81-Resumo!$B$3)</f>
-        <v>-155</v>
+        <v>-9</v>
       </c>
       <c r="M81" s="10" t="s">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="O81" s="14"/>
       <c r="P81" s="14" t="s">
@@ -6188,47 +6191,49 @@
       <c r="Q81" s="15"/>
       <c r="R81" s="14"/>
     </row>
-    <row r="82" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C82" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E82" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="D82" s="10" t="s">
+      <c r="F82" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="E82" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="F82" s="10" t="s">
-        <v>206</v>
-      </c>
       <c r="G82" s="12" t="n">
-        <v>46288</v>
+        <v>48171</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I82" s="10" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K82" s="12"/>
-      <c r="L82" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K82" s="12" t="n">
+        <v>46281</v>
+      </c>
+      <c r="L82" s="13" t="n">
         <f aca="false">IF(K82="","",K82-Resumo!$B$3)</f>
-        <v/>
+        <v>-37</v>
       </c>
       <c r="M82" s="10" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="N82" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O82" s="14"/>
       <c r="P82" s="14" t="s">
@@ -6245,41 +6250,41 @@
         <v>55</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>46288</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I83" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J83" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>46283</v>
+        <v>46168</v>
       </c>
       <c r="L83" s="13" t="n">
         <f aca="false">IF(K83="","",K83-Resumo!$B$3)</f>
-        <v>-35</v>
+        <v>-150</v>
       </c>
       <c r="M83" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O83" s="14"/>
       <c r="P83" s="14" t="s">
@@ -6288,49 +6293,49 @@
       <c r="Q83" s="15"/>
       <c r="R83" s="14"/>
     </row>
-    <row r="84" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E84" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="F84" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="F84" s="10" t="s">
-        <v>213</v>
-      </c>
       <c r="G84" s="12" t="n">
-        <v>46798</v>
+        <v>48005</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I84" s="10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>46323</v>
+        <v>46163</v>
       </c>
       <c r="L84" s="13" t="n">
         <f aca="false">IF(K84="","",K84-Resumo!$B$3)</f>
-        <v>5</v>
+        <v>-155</v>
       </c>
       <c r="M84" s="10" t="s">
-        <v>214</v>
+        <v>85</v>
       </c>
       <c r="N84" s="10" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="O84" s="14"/>
       <c r="P84" s="14" t="s">
@@ -6339,49 +6344,47 @@
       <c r="Q84" s="15"/>
       <c r="R84" s="14"/>
     </row>
-    <row r="85" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C85" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="F85" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="D85" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="F85" s="10" t="s">
-        <v>213</v>
-      </c>
       <c r="G85" s="12" t="n">
-        <v>46798</v>
+        <v>46288</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I85" s="10" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K85" s="12" t="n">
-        <v>46281</v>
-      </c>
-      <c r="L85" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K85" s="12"/>
+      <c r="L85" s="13" t="str">
         <f aca="false">IF(K85="","",K85-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v/>
       </c>
       <c r="M85" s="10" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O85" s="14"/>
       <c r="P85" s="14" t="s">
@@ -6395,42 +6398,44 @@
         <v>85</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C86" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="F86" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="D86" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="F86" s="10" t="s">
+      <c r="G86" s="12" t="n">
+        <v>46288</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I86" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="J86" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K86" s="12" t="n">
+        <v>46283</v>
+      </c>
+      <c r="L86" s="13" t="n">
+        <f aca="false">IF(K86="","",K86-Resumo!$B$3)</f>
+        <v>-35</v>
+      </c>
+      <c r="M86" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="G86" s="12" t="n">
-        <v>46798</v>
-      </c>
-      <c r="H86" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="I86" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="J86" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K86" s="12"/>
-      <c r="L86" s="13" t="str">
-        <f aca="false">IF(K86="","",K86-Resumo!$B$3)</f>
-        <v/>
-      </c>
-      <c r="M86" s="10" t="s">
-        <v>79</v>
-      </c>
       <c r="N86" s="10" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="O86" s="14"/>
       <c r="P86" s="14" t="s">
@@ -6439,7 +6444,7 @@
       <c r="Q86" s="15"/>
       <c r="R86" s="14"/>
     </row>
-    <row r="87" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="n">
         <v>86</v>
       </c>
@@ -6447,41 +6452,41 @@
         <v>55</v>
       </c>
       <c r="C87" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D87" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="D87" s="10" t="s">
+      <c r="E87" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="E87" s="10" t="s">
+      <c r="F87" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="F87" s="10" t="s">
-        <v>218</v>
-      </c>
       <c r="G87" s="12" t="n">
-        <v>47004</v>
+        <v>46798</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I87" s="10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>46280</v>
+        <v>46323</v>
       </c>
       <c r="L87" s="13" t="n">
         <f aca="false">IF(K87="","",K87-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>5</v>
       </c>
       <c r="M87" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O87" s="14"/>
       <c r="P87" s="14" t="s">
@@ -6495,44 +6500,44 @@
         <v>87</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C88" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D88" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="D88" s="10" t="s">
+      <c r="E88" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="E88" s="10" t="s">
+      <c r="F88" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="F88" s="10" t="s">
-        <v>218</v>
-      </c>
       <c r="G88" s="12" t="n">
-        <v>47004</v>
+        <v>46798</v>
       </c>
       <c r="H88" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="I88" s="10" t="n">
-        <v>15</v>
-      </c>
       <c r="J88" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>46344</v>
+        <v>46281</v>
       </c>
       <c r="L88" s="13" t="n">
         <f aca="false">IF(K88="","",K88-Resumo!$B$3)</f>
-        <v>26</v>
+        <v>-37</v>
       </c>
       <c r="M88" s="10" t="s">
-        <v>220</v>
+        <v>57</v>
       </c>
       <c r="N88" s="10" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="O88" s="14"/>
       <c r="P88" s="14" t="s">
@@ -6546,44 +6551,42 @@
         <v>88</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>47</v>
+        <v>215</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>46046</v>
+        <v>46798</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I89" s="10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K89" s="12" t="n">
-        <v>45926</v>
-      </c>
-      <c r="L89" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K89" s="12"/>
+      <c r="L89" s="13" t="str">
         <f aca="false">IF(K89="","",K89-Resumo!$B$3)</f>
-        <v>-392</v>
+        <v/>
       </c>
       <c r="M89" s="10" t="s">
-        <v>224</v>
+        <v>79</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="O89" s="14"/>
       <c r="P89" s="14" t="s">
@@ -6597,42 +6600,44 @@
         <v>89</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C90" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="E90" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="D90" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E90" s="10" t="s">
+      <c r="F90" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="F90" s="10" t="s">
-        <v>223</v>
-      </c>
       <c r="G90" s="12" t="n">
-        <v>46046</v>
+        <v>47004</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I90" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="I90" s="10" t="n">
+        <v>16</v>
+      </c>
       <c r="J90" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K90" s="12" t="n">
-        <v>45823</v>
+        <v>46280</v>
       </c>
       <c r="L90" s="13" t="n">
         <f aca="false">IF(K90="","",K90-Resumo!$B$3)</f>
-        <v>-495</v>
+        <v>-38</v>
       </c>
       <c r="M90" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N90" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O90" s="14"/>
       <c r="P90" s="14" t="s">
@@ -6641,49 +6646,49 @@
       <c r="Q90" s="15"/>
       <c r="R90" s="14"/>
     </row>
-    <row r="91" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="n">
         <v>90</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C91" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="E91" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="D91" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E91" s="10" t="s">
+      <c r="F91" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="F91" s="10" t="s">
-        <v>223</v>
-      </c>
       <c r="G91" s="12" t="n">
-        <v>46046</v>
+        <v>47004</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I91" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>46058</v>
+        <v>46344</v>
       </c>
       <c r="L91" s="13" t="n">
         <f aca="false">IF(K91="","",K91-Resumo!$B$3)</f>
-        <v>-260</v>
+        <v>26</v>
       </c>
       <c r="M91" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="O91" s="14"/>
       <c r="P91" s="14" t="s">
@@ -6700,41 +6705,41 @@
         <v>55</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>47</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G92" s="12" t="n">
         <v>46046</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I92" s="10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J92" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K92" s="12" t="n">
-        <v>46281</v>
+        <v>45926</v>
       </c>
       <c r="L92" s="13" t="n">
         <f aca="false">IF(K92="","",K92-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-392</v>
       </c>
       <c r="M92" s="10" t="s">
-        <v>57</v>
+        <v>228</v>
       </c>
       <c r="N92" s="10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O92" s="14"/>
       <c r="P92" s="14" t="s">
@@ -6748,44 +6753,42 @@
         <v>92</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C93" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="F93" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="D93" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="F93" s="10" t="s">
-        <v>229</v>
-      </c>
       <c r="G93" s="12" t="n">
-        <v>46970</v>
+        <v>46046</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I93" s="10" t="n">
-        <v>15</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I93" s="10"/>
       <c r="J93" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>46281</v>
+        <v>45823</v>
       </c>
       <c r="L93" s="13" t="n">
         <f aca="false">IF(K93="","",K93-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-495</v>
       </c>
       <c r="M93" s="10" t="s">
-        <v>57</v>
+        <v>229</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O93" s="14"/>
       <c r="P93" s="14" t="s">
@@ -6794,7 +6797,7 @@
       <c r="Q93" s="15"/>
       <c r="R93" s="14"/>
     </row>
-    <row r="94" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="n">
         <v>93</v>
       </c>
@@ -6802,39 +6805,41 @@
         <v>55</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>46505</v>
+        <v>46046</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I94" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I94" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J94" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K94" s="12" t="n">
-        <v>46319</v>
+        <v>46058</v>
       </c>
       <c r="L94" s="13" t="n">
         <f aca="false">IF(K94="","",K94-Resumo!$B$3)</f>
-        <v>1</v>
+        <v>-260</v>
       </c>
       <c r="M94" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N94" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O94" s="14"/>
       <c r="P94" s="14" t="s">
@@ -6843,7 +6848,7 @@
       <c r="Q94" s="15"/>
       <c r="R94" s="14"/>
     </row>
-    <row r="95" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="10" t="n">
         <v>94</v>
       </c>
@@ -6851,41 +6856,41 @@
         <v>55</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>46505</v>
+        <v>46046</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I95" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J95" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>45891</v>
+        <v>46281</v>
       </c>
       <c r="L95" s="13" t="n">
         <f aca="false">IF(K95="","",K95-Resumo!$B$3)</f>
-        <v>-427</v>
+        <v>-37</v>
       </c>
       <c r="M95" s="10" t="s">
-        <v>234</v>
+        <v>57</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O95" s="14"/>
       <c r="P95" s="14" t="s">
@@ -6902,19 +6907,19 @@
         <v>55</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>46505</v>
+        <v>46970</v>
       </c>
       <c r="H96" s="10" t="s">
         <v>15</v>
@@ -6926,14 +6931,14 @@
         <v>56</v>
       </c>
       <c r="K96" s="12" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="L96" s="13" t="n">
         <f aca="false">IF(K96="","",K96-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="M96" s="10" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="N96" s="10" t="s">
         <v>58</v>
@@ -6953,39 +6958,39 @@
         <v>55</v>
       </c>
       <c r="C97" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="D97" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E97" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="D97" s="10" t="s">
+      <c r="F97" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="E97" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="F97" s="10" t="s">
-        <v>238</v>
-      </c>
       <c r="G97" s="12" t="n">
-        <v>46346</v>
+        <v>46505</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>46226</v>
+        <v>46319</v>
       </c>
       <c r="L97" s="13" t="n">
         <f aca="false">IF(K97="","",K97-Resumo!$B$3)</f>
-        <v>-92</v>
+        <v>1</v>
       </c>
       <c r="M97" s="10" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="O97" s="14"/>
       <c r="P97" s="14" t="s">
@@ -6994,7 +6999,7 @@
       <c r="Q97" s="15"/>
       <c r="R97" s="14"/>
     </row>
-    <row r="98" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="n">
         <v>97</v>
       </c>
@@ -7002,39 +7007,41 @@
         <v>55</v>
       </c>
       <c r="C98" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="D98" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E98" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="D98" s="10" t="s">
+      <c r="F98" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="E98" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="F98" s="10" t="s">
-        <v>238</v>
-      </c>
       <c r="G98" s="12" t="n">
-        <v>46346</v>
+        <v>46505</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I98" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I98" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J98" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K98" s="12" t="n">
-        <v>46282</v>
+        <v>45891</v>
       </c>
       <c r="L98" s="13" t="n">
         <f aca="false">IF(K98="","",K98-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-427</v>
       </c>
       <c r="M98" s="10" t="s">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="N98" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O98" s="14"/>
       <c r="P98" s="14" t="s">
@@ -7051,41 +7058,41 @@
         <v>55</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>46373</v>
+        <v>46505</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I99" s="10" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J99" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>46253</v>
+        <v>46282</v>
       </c>
       <c r="L99" s="13" t="n">
         <f aca="false">IF(K99="","",K99-Resumo!$B$3)</f>
-        <v>-65</v>
+        <v>-36</v>
       </c>
       <c r="M99" s="10" t="s">
-        <v>243</v>
+        <v>74</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="O99" s="14"/>
       <c r="P99" s="14" t="s">
@@ -7094,7 +7101,7 @@
       <c r="Q99" s="15"/>
       <c r="R99" s="14"/>
     </row>
-    <row r="100" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="10" t="n">
         <v>99</v>
       </c>
@@ -7102,10 +7109,10 @@
         <v>55</v>
       </c>
       <c r="C100" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D100" s="10" t="s">
         <v>240</v>
-      </c>
-      <c r="D100" s="10" t="s">
-        <v>65</v>
       </c>
       <c r="E100" s="10" t="s">
         <v>241</v>
@@ -7114,29 +7121,27 @@
         <v>242</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>46373</v>
+        <v>46346</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I100" s="10" t="n">
-        <v>5</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I100" s="10"/>
       <c r="J100" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K100" s="12" t="n">
-        <v>45192</v>
+        <v>46226</v>
       </c>
       <c r="L100" s="13" t="n">
         <f aca="false">IF(K100="","",K100-Resumo!$B$3)</f>
-        <v>-1126</v>
+        <v>-92</v>
       </c>
       <c r="M100" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N100" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O100" s="14"/>
       <c r="P100" s="14" t="s">
@@ -7153,10 +7158,10 @@
         <v>55</v>
       </c>
       <c r="C101" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D101" s="10" t="s">
         <v>240</v>
-      </c>
-      <c r="D101" s="10" t="s">
-        <v>65</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>241</v>
@@ -7165,26 +7170,24 @@
         <v>242</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>46373</v>
+        <v>46346</v>
       </c>
       <c r="H101" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I101" s="10" t="n">
-        <v>16</v>
-      </c>
+      <c r="I101" s="10"/>
       <c r="J101" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>45262</v>
+        <v>46282</v>
       </c>
       <c r="L101" s="13" t="n">
         <f aca="false">IF(K101="","",K101-Resumo!$B$3)</f>
-        <v>-1056</v>
+        <v>-36</v>
       </c>
       <c r="M101" s="10" t="s">
-        <v>245</v>
+        <v>74</v>
       </c>
       <c r="N101" s="10" t="s">
         <v>58</v>
@@ -7196,7 +7199,7 @@
       <c r="Q101" s="15"/>
       <c r="R101" s="14"/>
     </row>
-    <row r="102" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="10" t="n">
         <v>101</v>
       </c>
@@ -7204,41 +7207,41 @@
         <v>55</v>
       </c>
       <c r="C102" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D102" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="F102" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="D102" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="E102" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="F102" s="10" t="s">
-        <v>249</v>
-      </c>
       <c r="G102" s="12" t="n">
-        <v>48010</v>
+        <v>46373</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I102" s="10" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="J102" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K102" s="12" t="n">
-        <v>46127</v>
+        <v>46253</v>
       </c>
       <c r="L102" s="13" t="n">
         <f aca="false">IF(K102="","",K102-Resumo!$B$3)</f>
-        <v>-191</v>
+        <v>-65</v>
       </c>
       <c r="M102" s="10" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N102" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O102" s="14"/>
       <c r="P102" s="14" t="s">
@@ -7247,7 +7250,7 @@
       <c r="Q102" s="15"/>
       <c r="R102" s="14"/>
     </row>
-    <row r="103" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="10" t="n">
         <v>102</v>
       </c>
@@ -7255,41 +7258,41 @@
         <v>55</v>
       </c>
       <c r="C103" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D103" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="F103" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="D103" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="E103" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="F103" s="10" t="s">
-        <v>249</v>
-      </c>
       <c r="G103" s="12" t="n">
-        <v>48010</v>
+        <v>46373</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I103" s="10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J103" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>46280</v>
+        <v>45192</v>
       </c>
       <c r="L103" s="13" t="n">
         <f aca="false">IF(K103="","",K103-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>-1126</v>
       </c>
       <c r="M103" s="10" t="s">
-        <v>219</v>
+        <v>248</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O103" s="14"/>
       <c r="P103" s="14" t="s">
@@ -7306,41 +7309,41 @@
         <v>55</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>252</v>
+        <v>65</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>46043</v>
+        <v>46373</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I104" s="10" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J104" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K104" s="12" t="n">
-        <v>45923</v>
+        <v>45262</v>
       </c>
       <c r="L104" s="13" t="n">
         <f aca="false">IF(K104="","",K104-Resumo!$B$3)</f>
-        <v>-395</v>
+        <v>-1056</v>
       </c>
       <c r="M104" s="10" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="N104" s="10" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="O104" s="14"/>
       <c r="P104" s="14" t="s">
@@ -7357,19 +7360,19 @@
         <v>55</v>
       </c>
       <c r="C105" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="D105" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="D105" s="10" t="s">
+      <c r="E105" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="E105" s="10" t="s">
+      <c r="F105" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="F105" s="10" t="s">
-        <v>254</v>
-      </c>
       <c r="G105" s="12" t="n">
-        <v>46043</v>
+        <v>48010</v>
       </c>
       <c r="H105" s="10" t="s">
         <v>14</v>
@@ -7381,14 +7384,14 @@
         <v>56</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>46113</v>
+        <v>46127</v>
       </c>
       <c r="L105" s="13" t="n">
         <f aca="false">IF(K105="","",K105-Resumo!$B$3)</f>
-        <v>-205</v>
+        <v>-191</v>
       </c>
       <c r="M105" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="N105" s="10" t="s">
         <v>54</v>
@@ -7408,38 +7411,38 @@
         <v>55</v>
       </c>
       <c r="C106" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="D106" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="D106" s="10" t="s">
+      <c r="E106" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="E106" s="10" t="s">
+      <c r="F106" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="F106" s="10" t="s">
-        <v>254</v>
-      </c>
       <c r="G106" s="12" t="n">
-        <v>46043</v>
+        <v>48010</v>
       </c>
       <c r="H106" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J106" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K106" s="12" t="n">
-        <v>45351</v>
+        <v>46280</v>
       </c>
       <c r="L106" s="13" t="n">
         <f aca="false">IF(K106="","",K106-Resumo!$B$3)</f>
-        <v>-967</v>
+        <v>-38</v>
       </c>
       <c r="M106" s="10" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="N106" s="10" t="s">
         <v>58</v>
@@ -7459,38 +7462,38 @@
         <v>55</v>
       </c>
       <c r="C107" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="F107" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="D107" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="F107" s="10" t="s">
-        <v>260</v>
-      </c>
       <c r="G107" s="12" t="n">
-        <v>46408</v>
+        <v>46043</v>
       </c>
       <c r="H107" s="10" t="s">
         <v>9</v>
       </c>
       <c r="I107" s="10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J107" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>46288</v>
+        <v>45923</v>
       </c>
       <c r="L107" s="13" t="n">
         <f aca="false">IF(K107="","",K107-Resumo!$B$3)</f>
-        <v>-30</v>
+        <v>-395</v>
       </c>
       <c r="M107" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="N107" s="10" t="s">
         <v>99</v>
@@ -7510,19 +7513,19 @@
         <v>55</v>
       </c>
       <c r="C108" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="D108" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="F108" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="D108" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="E108" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="F108" s="10" t="s">
-        <v>260</v>
-      </c>
       <c r="G108" s="12" t="n">
-        <v>46408</v>
+        <v>46043</v>
       </c>
       <c r="H108" s="10" t="s">
         <v>14</v>
@@ -7541,7 +7544,7 @@
         <v>-205</v>
       </c>
       <c r="M108" s="10" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="N108" s="10" t="s">
         <v>54</v>
@@ -7561,38 +7564,38 @@
         <v>55</v>
       </c>
       <c r="C109" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="D109" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="F109" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="D109" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="E109" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="F109" s="10" t="s">
-        <v>260</v>
-      </c>
       <c r="G109" s="12" t="n">
-        <v>46408</v>
+        <v>46043</v>
       </c>
       <c r="H109" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J109" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>46282</v>
+        <v>45351</v>
       </c>
       <c r="L109" s="13" t="n">
         <f aca="false">IF(K109="","",K109-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-967</v>
       </c>
       <c r="M109" s="10" t="s">
-        <v>74</v>
+        <v>261</v>
       </c>
       <c r="N109" s="10" t="s">
         <v>58</v>
@@ -7609,13 +7612,13 @@
         <v>109</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C110" s="10" t="s">
         <v>262</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="E110" s="10" t="s">
         <v>263</v>
@@ -7624,27 +7627,29 @@
         <v>264</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>47310</v>
+        <v>46408</v>
       </c>
       <c r="H110" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I110" s="10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K110" s="12"/>
-      <c r="L110" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K110" s="12" t="n">
+        <v>46288</v>
+      </c>
+      <c r="L110" s="13" t="n">
         <f aca="false">IF(K110="","",K110-Resumo!$B$3)</f>
-        <v/>
+        <v>-30</v>
       </c>
       <c r="M110" s="10" t="s">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="N110" s="10" t="s">
-        <v>191</v>
+        <v>99</v>
       </c>
       <c r="O110" s="14"/>
       <c r="P110" s="14" t="s">
@@ -7658,13 +7663,13 @@
         <v>110</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C111" s="10" t="s">
         <v>262</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>263</v>
@@ -7673,7 +7678,7 @@
         <v>264</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>47310</v>
+        <v>46408</v>
       </c>
       <c r="H111" s="10" t="s">
         <v>14</v>
@@ -7682,15 +7687,17 @@
         <v>5</v>
       </c>
       <c r="J111" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K111" s="12"/>
-      <c r="L111" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K111" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="L111" s="13" t="n">
         <f aca="false">IF(K111="","",K111-Resumo!$B$3)</f>
-        <v/>
+        <v>-205</v>
       </c>
       <c r="M111" s="10" t="s">
-        <v>79</v>
+        <v>260</v>
       </c>
       <c r="N111" s="10" t="s">
         <v>54</v>
@@ -7713,7 +7720,7 @@
         <v>262</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>263</v>
@@ -7722,26 +7729,26 @@
         <v>264</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>47310</v>
+        <v>46408</v>
       </c>
       <c r="H112" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J112" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K112" s="12" t="n">
-        <v>46043</v>
+        <v>46282</v>
       </c>
       <c r="L112" s="13" t="n">
         <f aca="false">IF(K112="","",K112-Resumo!$B$3)</f>
-        <v>-275</v>
+        <v>-36</v>
       </c>
       <c r="M112" s="10" t="s">
-        <v>265</v>
+        <v>74</v>
       </c>
       <c r="N112" s="10" t="s">
         <v>58</v>
@@ -7753,18 +7760,18 @@
       <c r="Q112" s="15"/>
       <c r="R112" s="14"/>
     </row>
-    <row r="113" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="10" t="n">
         <v>112</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C113" s="10" t="s">
         <v>266</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>267</v>
@@ -7773,29 +7780,27 @@
         <v>268</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>46658</v>
+        <v>47310</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I113" s="10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K113" s="12" t="n">
-        <v>46107</v>
-      </c>
-      <c r="L113" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K113" s="12"/>
+      <c r="L113" s="13" t="str">
         <f aca="false">IF(K113="","",K113-Resumo!$B$3)</f>
-        <v>-211</v>
+        <v/>
       </c>
       <c r="M113" s="10" t="s">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>54</v>
+        <v>195</v>
       </c>
       <c r="O113" s="14"/>
       <c r="P113" s="14" t="s">
@@ -7804,18 +7809,18 @@
       <c r="Q113" s="15"/>
       <c r="R113" s="14"/>
     </row>
-    <row r="114" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="10" t="n">
         <v>113</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C114" s="10" t="s">
         <v>266</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>267</v>
@@ -7824,29 +7829,27 @@
         <v>268</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>46658</v>
+        <v>47310</v>
       </c>
       <c r="H114" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I114" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K114" s="12" t="n">
-        <v>46280</v>
-      </c>
-      <c r="L114" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K114" s="12"/>
+      <c r="L114" s="13" t="str">
         <f aca="false">IF(K114="","",K114-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v/>
       </c>
       <c r="M114" s="10" t="s">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="N114" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O114" s="14"/>
       <c r="P114" s="14" t="s">
@@ -7860,13 +7863,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C115" s="10" t="s">
         <v>266</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>267</v>
@@ -7875,27 +7878,29 @@
         <v>268</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>46658</v>
+        <v>47310</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I115" s="10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K115" s="12"/>
-      <c r="L115" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K115" s="12" t="n">
+        <v>46043</v>
+      </c>
+      <c r="L115" s="13" t="n">
         <f aca="false">IF(K115="","",K115-Resumo!$B$3)</f>
-        <v/>
+        <v>-275</v>
       </c>
       <c r="M115" s="10" t="s">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="O115" s="14"/>
       <c r="P115" s="14" t="s">
@@ -7915,16 +7920,16 @@
         <v>270</v>
       </c>
       <c r="D116" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E116" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="E116" s="10" t="s">
+      <c r="F116" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="F116" s="10" t="s">
-        <v>273</v>
-      </c>
       <c r="G116" s="12" t="n">
-        <v>47016</v>
+        <v>46658</v>
       </c>
       <c r="H116" s="10" t="s">
         <v>14</v>
@@ -7936,14 +7941,14 @@
         <v>56</v>
       </c>
       <c r="K116" s="12" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="L116" s="13" t="n">
         <f aca="false">IF(K116="","",K116-Resumo!$B$3)</f>
-        <v>-205</v>
+        <v>-211</v>
       </c>
       <c r="M116" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N116" s="10" t="s">
         <v>54</v>
@@ -7966,35 +7971,35 @@
         <v>270</v>
       </c>
       <c r="D117" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E117" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="E117" s="10" t="s">
+      <c r="F117" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="F117" s="10" t="s">
-        <v>273</v>
-      </c>
       <c r="G117" s="12" t="n">
-        <v>47016</v>
+        <v>46658</v>
       </c>
       <c r="H117" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J117" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>45519</v>
+        <v>46280</v>
       </c>
       <c r="L117" s="13" t="n">
         <f aca="false">IF(K117="","",K117-Resumo!$B$3)</f>
-        <v>-799</v>
+        <v>-38</v>
       </c>
       <c r="M117" s="10" t="s">
-        <v>275</v>
+        <v>223</v>
       </c>
       <c r="N117" s="10" t="s">
         <v>58</v>
@@ -8017,38 +8022,36 @@
         <v>270</v>
       </c>
       <c r="D118" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E118" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="E118" s="10" t="s">
+      <c r="F118" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="F118" s="10" t="s">
-        <v>273</v>
-      </c>
       <c r="G118" s="12" t="n">
-        <v>47016</v>
+        <v>46658</v>
       </c>
       <c r="H118" s="10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I118" s="10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J118" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K118" s="12" t="n">
-        <v>46339</v>
-      </c>
-      <c r="L118" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K118" s="12"/>
+      <c r="L118" s="13" t="str">
         <f aca="false">IF(K118="","",K118-Resumo!$B$3)</f>
-        <v>21</v>
+        <v/>
       </c>
       <c r="M118" s="10" t="s">
-        <v>276</v>
+        <v>79</v>
       </c>
       <c r="N118" s="10" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="O118" s="14"/>
       <c r="P118" s="14" t="s">
@@ -8057,7 +8060,7 @@
       <c r="Q118" s="15"/>
       <c r="R118" s="14"/>
     </row>
-    <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="10" t="n">
         <v>118</v>
       </c>
@@ -8065,41 +8068,41 @@
         <v>55</v>
       </c>
       <c r="C119" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="D119" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="E119" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="F119" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="D119" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="E119" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="F119" s="10" t="s">
-        <v>280</v>
-      </c>
       <c r="G119" s="12" t="n">
-        <v>46332</v>
+        <v>47016</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I119" s="10" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J119" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>46212</v>
+        <v>46113</v>
       </c>
       <c r="L119" s="13" t="n">
         <f aca="false">IF(K119="","",K119-Resumo!$B$3)</f>
-        <v>-106</v>
+        <v>-205</v>
       </c>
       <c r="M119" s="10" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="O119" s="14"/>
       <c r="P119" s="14" t="s">
@@ -8113,44 +8116,44 @@
         <v>119</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C120" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="D120" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="F120" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="D120" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="E120" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="F120" s="10" t="s">
-        <v>280</v>
-      </c>
       <c r="G120" s="12" t="n">
-        <v>46332</v>
+        <v>47016</v>
       </c>
       <c r="H120" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I120" s="10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J120" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K120" s="12" t="n">
-        <v>46248</v>
+        <v>45519</v>
       </c>
       <c r="L120" s="13" t="n">
         <f aca="false">IF(K120="","",K120-Resumo!$B$3)</f>
-        <v>-70</v>
+        <v>-799</v>
       </c>
       <c r="M120" s="10" t="s">
-        <v>85</v>
+        <v>279</v>
       </c>
       <c r="N120" s="10" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="O120" s="14"/>
       <c r="P120" s="14" t="s">
@@ -8159,49 +8162,49 @@
       <c r="Q120" s="15"/>
       <c r="R120" s="14"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="10" t="n">
         <v>120</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C121" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="D121" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="E121" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="F121" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="D121" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="E121" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="F121" s="10" t="s">
-        <v>280</v>
-      </c>
       <c r="G121" s="12" t="n">
-        <v>46332</v>
+        <v>47016</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I121" s="10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J121" s="10" t="s">
         <v>50</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>46328</v>
+        <v>46339</v>
       </c>
       <c r="L121" s="13" t="n">
         <f aca="false">IF(K121="","",K121-Resumo!$B$3)</f>
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="M121" s="10" t="s">
-        <v>87</v>
+        <v>280</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O121" s="14"/>
       <c r="P121" s="14" t="s">
@@ -8210,7 +8213,7 @@
       <c r="Q121" s="15"/>
       <c r="R121" s="14"/>
     </row>
-    <row r="122" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="10" t="n">
         <v>121</v>
       </c>
@@ -8218,41 +8221,41 @@
         <v>55</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G122" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H122" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I122" s="10" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J122" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K122" s="12" t="n">
-        <v>46259</v>
+        <v>46212</v>
       </c>
       <c r="L122" s="13" t="n">
         <f aca="false">IF(K122="","",K122-Resumo!$B$3)</f>
-        <v>-59</v>
+        <v>-106</v>
       </c>
       <c r="M122" s="10" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="N122" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O122" s="14"/>
       <c r="P122" s="14" t="s">
@@ -8266,44 +8269,44 @@
         <v>122</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G123" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I123" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J123" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>46280</v>
+        <v>46248</v>
       </c>
       <c r="L123" s="13" t="n">
         <f aca="false">IF(K123="","",K123-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>-70</v>
       </c>
       <c r="M123" s="10" t="s">
-        <v>219</v>
+        <v>85</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="O123" s="14"/>
       <c r="P123" s="14" t="s">
@@ -8312,47 +8315,49 @@
       <c r="Q123" s="15"/>
       <c r="R123" s="14"/>
     </row>
-    <row r="124" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="10" t="n">
         <v>123</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F124" s="10" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G124" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H124" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I124" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="I124" s="10" t="n">
-        <v>13</v>
-      </c>
       <c r="J124" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K124" s="12"/>
-      <c r="L124" s="13" t="str">
+        <v>50</v>
+      </c>
+      <c r="K124" s="12" t="n">
+        <v>46328</v>
+      </c>
+      <c r="L124" s="13" t="n">
         <f aca="false">IF(K124="","",K124-Resumo!$B$3)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="M124" s="10" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="N124" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O124" s="14"/>
       <c r="P124" s="14" t="s">
@@ -8361,49 +8366,49 @@
       <c r="Q124" s="15"/>
       <c r="R124" s="14"/>
     </row>
-    <row r="125" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="10" t="n">
         <v>124</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C125" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D125" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="E125" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="D125" s="10" t="s">
+      <c r="F125" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="E125" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="F125" s="10" t="s">
-        <v>286</v>
-      </c>
       <c r="G125" s="12" t="n">
-        <v>48215</v>
+        <v>46332</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I125" s="10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J125" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>46034</v>
+        <v>46259</v>
       </c>
       <c r="L125" s="13" t="n">
         <f aca="false">IF(K125="","",K125-Resumo!$B$3)</f>
-        <v>-284</v>
+        <v>-59</v>
       </c>
       <c r="M125" s="10" t="s">
-        <v>85</v>
+        <v>286</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="O125" s="14"/>
       <c r="P125" s="14" t="s">
@@ -8412,49 +8417,49 @@
       <c r="Q125" s="15"/>
       <c r="R125" s="14"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="10" t="n">
         <v>125</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C126" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D126" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="E126" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="D126" s="10" t="s">
+      <c r="F126" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="E126" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="F126" s="10" t="s">
-        <v>286</v>
-      </c>
       <c r="G126" s="12" t="n">
-        <v>48215</v>
+        <v>46332</v>
       </c>
       <c r="H126" s="10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I126" s="10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J126" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K126" s="12" t="n">
-        <v>46114</v>
+        <v>46280</v>
       </c>
       <c r="L126" s="13" t="n">
         <f aca="false">IF(K126="","",K126-Resumo!$B$3)</f>
-        <v>-204</v>
+        <v>-38</v>
       </c>
       <c r="M126" s="10" t="s">
-        <v>87</v>
+        <v>223</v>
       </c>
       <c r="N126" s="10" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="O126" s="14"/>
       <c r="P126" s="14" t="s">
@@ -8463,49 +8468,47 @@
       <c r="Q126" s="15"/>
       <c r="R126" s="14"/>
     </row>
-    <row r="127" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="10" t="n">
         <v>126</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C127" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D127" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="E127" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="D127" s="10" t="s">
+      <c r="F127" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="E127" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="F127" s="10" t="s">
-        <v>286</v>
-      </c>
       <c r="G127" s="12" t="n">
-        <v>48215</v>
+        <v>46332</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I127" s="10" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K127" s="12" t="n">
-        <v>46276</v>
-      </c>
-      <c r="L127" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K127" s="12"/>
+      <c r="L127" s="13" t="str">
         <f aca="false">IF(K127="","",K127-Resumo!$B$3)</f>
-        <v>-42</v>
+        <v/>
       </c>
       <c r="M127" s="10" t="s">
-        <v>287</v>
+        <v>79</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="O127" s="14"/>
       <c r="P127" s="14" t="s">
@@ -8519,42 +8522,44 @@
         <v>127</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E128" s="10" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="G128" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H128" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I128" s="10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J128" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K128" s="12"/>
-      <c r="L128" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K128" s="12" t="n">
+        <v>46034</v>
+      </c>
+      <c r="L128" s="13" t="n">
         <f aca="false">IF(K128="","",K128-Resumo!$B$3)</f>
-        <v/>
+        <v>-284</v>
       </c>
       <c r="M128" s="10" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="N128" s="10" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="O128" s="14"/>
       <c r="P128" s="14" t="s">
@@ -8563,47 +8568,49 @@
       <c r="Q128" s="15"/>
       <c r="R128" s="14"/>
     </row>
-    <row r="129" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="10" t="n">
         <v>128</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="G129" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I129" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K129" s="12"/>
-      <c r="L129" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K129" s="12" t="n">
+        <v>46114</v>
+      </c>
+      <c r="L129" s="13" t="n">
         <f aca="false">IF(K129="","",K129-Resumo!$B$3)</f>
-        <v/>
+        <v>-204</v>
       </c>
       <c r="M129" s="10" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O129" s="14"/>
       <c r="P129" s="14" t="s">
@@ -8612,47 +8619,49 @@
       <c r="Q129" s="15"/>
       <c r="R129" s="14"/>
     </row>
-    <row r="130" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="10" t="n">
         <v>129</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F130" s="10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="G130" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H130" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I130" s="10" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K130" s="12"/>
-      <c r="L130" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K130" s="12" t="n">
+        <v>46276</v>
+      </c>
+      <c r="L130" s="13" t="n">
         <f aca="false">IF(K130="","",K130-Resumo!$B$3)</f>
-        <v/>
+        <v>-42</v>
       </c>
       <c r="M130" s="10" t="s">
-        <v>79</v>
+        <v>291</v>
       </c>
       <c r="N130" s="10" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="O130" s="14"/>
       <c r="P130" s="14" t="s">
@@ -8669,25 +8678,25 @@
         <v>45</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="G131" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I131" s="10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J131" s="10" t="s">
         <v>6</v>
@@ -8701,7 +8710,7 @@
         <v>79</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="O131" s="14"/>
       <c r="P131" s="14" t="s">
@@ -8718,10 +8727,10 @@
         <v>45</v>
       </c>
       <c r="C132" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="D132" s="10" t="s">
         <v>288</v>
-      </c>
-      <c r="D132" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="E132" s="10" t="s">
         <v>289</v>
@@ -8730,27 +8739,27 @@
         <v>290</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>47697</v>
+        <v>48215</v>
       </c>
       <c r="H132" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I132" s="10"/>
+        <v>16</v>
+      </c>
+      <c r="I132" s="10" t="n">
+        <v>14</v>
+      </c>
       <c r="J132" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K132" s="12" t="n">
-        <v>46344</v>
-      </c>
-      <c r="L132" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K132" s="12"/>
+      <c r="L132" s="13" t="str">
         <f aca="false">IF(K132="","",K132-Resumo!$B$3)</f>
-        <v>26</v>
+        <v/>
       </c>
       <c r="M132" s="10" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="N132" s="10" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="O132" s="14"/>
       <c r="P132" s="14" t="s">
@@ -8759,18 +8768,18 @@
       <c r="Q132" s="15"/>
       <c r="R132" s="14"/>
     </row>
-    <row r="133" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="10" t="n">
         <v>132</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C133" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="D133" s="10" t="s">
         <v>288</v>
-      </c>
-      <c r="D133" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>289</v>
@@ -8779,29 +8788,27 @@
         <v>290</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>47697</v>
+        <v>48215</v>
       </c>
       <c r="H133" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I133" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="I133" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="J133" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K133" s="12" t="n">
-        <v>46127</v>
-      </c>
-      <c r="L133" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K133" s="12"/>
+      <c r="L133" s="13" t="str">
         <f aca="false">IF(K133="","",K133-Resumo!$B$3)</f>
-        <v>-191</v>
+        <v/>
       </c>
       <c r="M133" s="10" t="s">
-        <v>250</v>
+        <v>79</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="O133" s="14"/>
       <c r="P133" s="14" t="s">
@@ -8815,13 +8822,13 @@
         <v>133</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C134" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="D134" s="10" t="s">
         <v>288</v>
-      </c>
-      <c r="D134" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="E134" s="10" t="s">
         <v>289</v>
@@ -8830,29 +8837,27 @@
         <v>290</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>47697</v>
+        <v>48215</v>
       </c>
       <c r="H134" s="10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I134" s="10" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J134" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K134" s="12" t="n">
-        <v>46282</v>
-      </c>
-      <c r="L134" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K134" s="12"/>
+      <c r="L134" s="13" t="str">
         <f aca="false">IF(K134="","",K134-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v/>
       </c>
       <c r="M134" s="10" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="N134" s="10" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="O134" s="14"/>
       <c r="P134" s="14" t="s">
@@ -8866,13 +8871,13 @@
         <v>134</v>
       </c>
       <c r="B135" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>292</v>
+        <v>189</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>293</v>
@@ -8881,29 +8886,27 @@
         <v>294</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>46244</v>
+        <v>47697</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="I135" s="10" t="n">
-        <v>21</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I135" s="10"/>
       <c r="J135" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>46124</v>
+        <v>46344</v>
       </c>
       <c r="L135" s="13" t="n">
         <f aca="false">IF(K135="","",K135-Resumo!$B$3)</f>
-        <v>-194</v>
+        <v>26</v>
       </c>
       <c r="M135" s="10" t="s">
-        <v>295</v>
+        <v>51</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="O135" s="14"/>
       <c r="P135" s="14" t="s">
@@ -8920,10 +8923,10 @@
         <v>55</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D136" s="10" t="s">
-        <v>292</v>
+        <v>189</v>
       </c>
       <c r="E136" s="10" t="s">
         <v>293</v>
@@ -8932,7 +8935,7 @@
         <v>294</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>46244</v>
+        <v>47697</v>
       </c>
       <c r="H136" s="10" t="s">
         <v>14</v>
@@ -8944,14 +8947,14 @@
         <v>56</v>
       </c>
       <c r="K136" s="12" t="n">
-        <v>46276</v>
+        <v>46127</v>
       </c>
       <c r="L136" s="13" t="n">
         <f aca="false">IF(K136="","",K136-Resumo!$B$3)</f>
-        <v>-42</v>
+        <v>-191</v>
       </c>
       <c r="M136" s="10" t="s">
-        <v>287</v>
+        <v>254</v>
       </c>
       <c r="N136" s="10" t="s">
         <v>54</v>
@@ -8968,13 +8971,13 @@
         <v>136</v>
       </c>
       <c r="B137" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>292</v>
+        <v>189</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>293</v>
@@ -8983,24 +8986,26 @@
         <v>294</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>46244</v>
+        <v>47697</v>
       </c>
       <c r="H137" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J137" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K137" s="12"/>
-      <c r="L137" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K137" s="12" t="n">
+        <v>46282</v>
+      </c>
+      <c r="L137" s="13" t="n">
         <f aca="false">IF(K137="","",K137-Resumo!$B$3)</f>
-        <v/>
+        <v>-36</v>
       </c>
       <c r="M137" s="10" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="N137" s="10" t="s">
         <v>58</v>
@@ -9012,9 +9017,160 @@
       <c r="Q137" s="15"/>
       <c r="R137" s="14"/>
     </row>
+    <row r="138" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="10" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D138" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="E138" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="F138" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H138" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I138" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="J138" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K138" s="12" t="n">
+        <v>46124</v>
+      </c>
+      <c r="L138" s="13" t="n">
+        <f aca="false">IF(K138="","",K138-Resumo!$B$3)</f>
+        <v>-194</v>
+      </c>
+      <c r="M138" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="N138" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="O138" s="14"/>
+      <c r="P138" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q138" s="15"/>
+      <c r="R138" s="14"/>
+    </row>
+    <row r="139" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="10" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C139" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D139" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="E139" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="F139" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H139" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I139" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J139" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K139" s="12" t="n">
+        <v>46276</v>
+      </c>
+      <c r="L139" s="13" t="n">
+        <f aca="false">IF(K139="","",K139-Resumo!$B$3)</f>
+        <v>-42</v>
+      </c>
+      <c r="M139" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="N139" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="O139" s="14"/>
+      <c r="P139" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q139" s="15"/>
+      <c r="R139" s="14"/>
+    </row>
+    <row r="140" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="10" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C140" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D140" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="E140" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="F140" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H140" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I140" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="J140" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K140" s="12"/>
+      <c r="L140" s="13" t="str">
+        <f aca="false">IF(K140="","",K140-Resumo!$B$3)</f>
+        <v/>
+      </c>
+      <c r="M140" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N140" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O140" s="14"/>
+      <c r="P140" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q140" s="15"/>
+      <c r="R140" s="14"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R137"/>
-  <conditionalFormatting sqref="J2:J137">
+  <autoFilter ref="A1:R140"/>
+  <conditionalFormatting sqref="J2:J140">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$J2="Vencida"</formula>
     </cfRule>
@@ -9025,12 +9181,12 @@
       <formula>$J2="Sem data"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B137">
+  <conditionalFormatting sqref="B2:B140">
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>$B2="Alta"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P137">
+  <conditionalFormatting sqref="P2:P140">
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>$P2="Resolvido"</formula>
     </cfRule>
@@ -9039,7 +9195,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P137" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P140" type="list">
       <formula1>"A fazer,Em andamento,Aguardando cliente,Resolvido,Já estava em dia"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9060,7 +9216,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -9084,7 +9240,7 @@
         <v>8</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9092,15 +9248,15 @@
         <v>46</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A2,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A2,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A2,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A2,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A2,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A2,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>2</v>
       </c>
       <c r="E2" s="7" t="n">
@@ -9108,7 +9264,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A2,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A2,Pendências!$B$2:$B$140,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9117,15 +9273,15 @@
         <v>59</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A3,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A3,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A3,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A3,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A3,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A3,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E3" s="7" t="n">
@@ -9133,7 +9289,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A3,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A3,Pendências!$B$2:$B$140,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9142,15 +9298,15 @@
         <v>64</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A4,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A4,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A4,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A4,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A4,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A4,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
@@ -9158,7 +9314,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A4,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A4,Pendências!$B$2:$B$140,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9167,15 +9323,15 @@
         <v>69</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A5,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A5,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A5,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A5,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A5,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A5,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
@@ -9183,7 +9339,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A5,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A5,Pendências!$B$2:$B$140,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9192,15 +9348,15 @@
         <v>75</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A6,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A6,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A6,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A6,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A6,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A6,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
@@ -9208,7 +9364,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A6,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A6,Pendências!$B$2:$B$140,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -9217,15 +9373,15 @@
         <v>81</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A7,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A7,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>5</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A7,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A7,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A7,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A7,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
@@ -9233,7 +9389,7 @@
         <v>7</v>
       </c>
       <c r="F7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A7,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A7,Pendências!$B$2:$B$140,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9242,15 +9398,15 @@
         <v>94</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A8,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A8,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A8,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A8,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A8,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A8,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
@@ -9258,7 +9414,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A8,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A8,Pendências!$B$2:$B$140,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9267,15 +9423,15 @@
         <v>101</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A9,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A9,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A9,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A9,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A9,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A9,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
@@ -9283,7 +9439,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A9,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A9,Pendências!$B$2:$B$140,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -9292,15 +9448,15 @@
         <v>105</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A10,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A10,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A10,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A10,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A10,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A10,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E10" s="7" t="n">
@@ -9308,7 +9464,7 @@
         <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A10,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A10,Pendências!$B$2:$B$140,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9317,15 +9473,15 @@
         <v>111</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A11,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A11,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A11,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A11,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A11,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A11,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E11" s="7" t="n">
@@ -9333,7 +9489,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A11,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A11,Pendências!$B$2:$B$140,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -9342,15 +9498,15 @@
         <v>115</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A12,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A12,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A12,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A12,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A12,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A12,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
@@ -9358,7 +9514,7 @@
         <v>6</v>
       </c>
       <c r="F12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A12,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A12,Pendências!$B$2:$B$140,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9367,15 +9523,15 @@
         <v>119</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A13,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A13,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A13,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A13,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A13,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A13,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
@@ -9383,7 +9539,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A13,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A13,Pendências!$B$2:$B$140,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9392,74 +9548,74 @@
         <v>123</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A14,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A14,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A14,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A14,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A14,Pendências!$J$2:$J$137,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A14,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
         <f aca="false">SUM(B14:D14)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A14,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A14,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A15,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A15,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A15,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A15,Pendências!$J$2:$J$140,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A15,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A15,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
         <f aca="false">SUM(B15:D15)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A15,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A15,Pendências!$B$2:$B$140,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A16,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A16,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>3</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A16,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>1</v>
       </c>
-      <c r="C16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A16,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>0</v>
-      </c>
       <c r="D16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A16,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A16,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
         <f aca="false">SUM(B16:D16)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A16,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A16,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9467,99 +9623,99 @@
         <v>139</v>
       </c>
       <c r="B17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A17,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A17,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A17,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A17,Pendências!$J$2:$J$140,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A17,Pendências!$J$2:$J$137,"Vence em breve")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A17,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
         <f aca="false">SUM(B17:D17)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A17,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A17,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A18,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A18,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>4</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A18,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>2</v>
       </c>
-      <c r="C18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A18,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A18,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A18,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
         <f aca="false">SUM(B18:D18)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A18,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A18,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A19,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A19,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>2</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A19,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>1</v>
       </c>
-      <c r="C19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A19,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>0</v>
-      </c>
       <c r="D19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A19,Pendências!$J$2:$J$137,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A19,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
         <f aca="false">SUM(B19:D19)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A19,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A19,Pendências!$B$2:$B$140,"Alta")</f>
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A20,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A20,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A20,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A20,Pendências!$J$2:$J$140,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A20,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A20,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E20" s="7" t="n">
         <f aca="false">SUM(B20:D20)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A20,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A20,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9567,24 +9723,24 @@
         <v>157</v>
       </c>
       <c r="B21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A21,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A21,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A21,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>1</v>
       </c>
-      <c r="C21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A21,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>0</v>
-      </c>
       <c r="D21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A21,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A21,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
         <f aca="false">SUM(B21:D21)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A21,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A21,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9592,23 +9748,23 @@
         <v>161</v>
       </c>
       <c r="B22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A22,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A22,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A22,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A22,Pendências!$J$2:$J$140,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A22,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A22,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E22" s="7" t="n">
         <f aca="false">SUM(B22:D22)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A22,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A22,Pendências!$B$2:$B$140,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9617,15 +9773,15 @@
         <v>165</v>
       </c>
       <c r="B23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A23,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A23,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A23,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A23,Pendências!$J$2:$J$140,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A23,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A23,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
@@ -9633,24 +9789,24 @@
         <v>2</v>
       </c>
       <c r="F23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A23,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A23,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A24,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A24,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A24,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A24,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A24,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A24,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E24" s="7" t="n">
@@ -9658,58 +9814,58 @@
         <v>2</v>
       </c>
       <c r="F24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A24,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A24,Pendências!$B$2:$B$140,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A25,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A25,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A25,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A25,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A25,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A25,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
         <f aca="false">SUM(B25:D25)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A25,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A25,Pendências!$B$2:$B$140,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A26,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A26,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A26,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A26,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A26,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A26,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E26" s="7" t="n">
         <f aca="false">SUM(B26:D26)</f>
+        <v>3</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A26,Pendências!$B$2:$B$140,"Alta")</f>
         <v>2</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A26,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9717,49 +9873,49 @@
         <v>184</v>
       </c>
       <c r="B27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A27,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A27,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A27,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A27,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A27,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A27,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
         <f aca="false">SUM(B27:D27)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A27,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A27,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A28,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A28,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>5</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A28,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
-      <c r="C28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A28,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A28,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A28,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E28" s="7" t="n">
         <f aca="false">SUM(B28:D28)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A28,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A28,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9767,290 +9923,290 @@
         <v>198</v>
       </c>
       <c r="B29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A29,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A29,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>0</v>
       </c>
       <c r="C29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A29,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A29,Pendências!$J$2:$J$140,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A29,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A29,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
         <f aca="false">SUM(B29:D29)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A29,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A29,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A30,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A30,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A30,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A30,Pendências!$J$2:$J$140,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A30,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A30,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E30" s="7" t="n">
         <f aca="false">SUM(B30:D30)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A30,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A30,Pendências!$B$2:$B$140,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A31,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A31,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>3</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A31,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>1</v>
       </c>
-      <c r="C31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A31,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A31,Pendências!$J$2:$J$137,"Vence em breve")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A31,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
         <f aca="false">SUM(B31:D31)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A31,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A31,Pendências!$B$2:$B$140,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A32,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A32,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A32,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A32,Pendências!$J$2:$J$140,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A32,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A32,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E32" s="7" t="n">
         <f aca="false">SUM(B32:D32)</f>
+        <v>3</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A32,Pendências!$B$2:$B$140,"Alta")</f>
         <v>2</v>
-      </c>
-      <c r="F32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A32,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A33,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A33,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A33,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A33,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A33,Pendências!$J$2:$J$137,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A33,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E33" s="7" t="n">
         <f aca="false">SUM(B33:D33)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A33,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A33,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A34,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A34,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>4</v>
       </c>
       <c r="C34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A34,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A34,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A34,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A34,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E34" s="7" t="n">
         <f aca="false">SUM(B34:D34)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A34,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A34,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A35,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A35,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A35,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A35,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A35,Pendências!$J$2:$J$137,"Vence em breve")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A35,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <v>0</v>
       </c>
       <c r="E35" s="7" t="n">
         <f aca="false">SUM(B35:D35)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A35,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A35,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A36,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A36,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A36,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A36,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A36,Pendências!$J$2:$J$137,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A36,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E36" s="7" t="n">
         <f aca="false">SUM(B36:D36)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A36,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A36,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A37,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A37,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A37,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A37,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A37,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A37,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E37" s="7" t="n">
         <f aca="false">SUM(B37:D37)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A37,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A37,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A38,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A38,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A38,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A38,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A38,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A38,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E38" s="7" t="n">
         <f aca="false">SUM(B38:D38)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A38,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A38,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A39,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A39,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A39,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A39,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A39,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A39,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
         <f aca="false">SUM(B39:D39)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A39,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A39,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A40,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A40,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A40,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A40,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A40,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A40,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E40" s="7" t="n">
@@ -10058,7 +10214,7 @@
         <v>3</v>
       </c>
       <c r="F40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A40,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A40,Pendências!$B$2:$B$140,"Alta")</f>
         <v>3</v>
       </c>
     </row>
@@ -10067,15 +10223,15 @@
         <v>262</v>
       </c>
       <c r="B41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A41,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A41,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A41,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A41,Pendências!$J$2:$J$140,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A41,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A41,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E41" s="7" t="n">
@@ -10083,8 +10239,8 @@
         <v>3</v>
       </c>
       <c r="F41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A41,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A41,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10092,15 +10248,15 @@
         <v>266</v>
       </c>
       <c r="B42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A42,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A42,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>1</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A42,Pendências!$J$2:$J$140,"Sem data")</f>
         <v>2</v>
       </c>
-      <c r="C42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A42,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A42,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A42,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E42" s="7" t="n">
@@ -10108,8 +10264,8 @@
         <v>3</v>
       </c>
       <c r="F42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A42,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A42,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10117,128 +10273,153 @@
         <v>270</v>
       </c>
       <c r="B43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A43,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A43,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A43,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A43,Pendências!$J$2:$J$140,"Sem data")</f>
+        <v>1</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A43,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
-      </c>
-      <c r="D43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A43,Pendências!$J$2:$J$137,"Vence em breve")</f>
-        <v>1</v>
       </c>
       <c r="E43" s="7" t="n">
         <f aca="false">SUM(B43:D43)</f>
         <v>3</v>
       </c>
       <c r="F43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A43,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A43,Pendências!$B$2:$B$140,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A44,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A44,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A44,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A44,Pendências!$J$2:$J$140,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A44,Pendências!$J$2:$J$137,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A44,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E44" s="7" t="n">
         <f aca="false">SUM(B44:D44)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A44,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A44,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A45,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A45,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>4</v>
       </c>
       <c r="C45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A45,Pendências!$J$2:$J$137,"Sem data")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A45,Pendências!$J$2:$J$140,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A45,Pendências!$J$2:$J$137,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A45,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E45" s="7" t="n">
         <f aca="false">SUM(B45:D45)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A45,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A45,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A46,Pendências!$J$2:$J$137,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A46,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A46,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A46,Pendências!$J$2:$J$140,"Sem data")</f>
+        <v>4</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A46,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>0</v>
-      </c>
-      <c r="D46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A46,Pendências!$J$2:$J$137,"Vence em breve")</f>
-        <v>1</v>
       </c>
       <c r="E46" s="7" t="n">
         <f aca="false">SUM(B46:D46)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A46,Pendências!$B$2:$B$137,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A46,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A47,Pendências!$J$2:$J$137,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A47,Pendências!$J$2:$J$140,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A47,Pendências!$J$2:$J$137,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A47,Pendências!$J$2:$J$140,"Sem data")</f>
+        <v>0</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A47,Pendências!$J$2:$J$140,"Vence em breve")</f>
         <v>1</v>
-      </c>
-      <c r="D47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A47,Pendências!$J$2:$J$137,"Vence em breve")</f>
-        <v>0</v>
       </c>
       <c r="E47" s="7" t="n">
         <f aca="false">SUM(B47:D47)</f>
         <v>3</v>
       </c>
       <c r="F47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$137,$A47,Pendências!$B$2:$B$137,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A47,Pendências!$B$2:$B$140,"Alta")</f>
         <v>2</v>
       </c>
     </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="B48" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A48,Pendências!$J$2:$J$140,"Vencida")</f>
+        <v>2</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A48,Pendências!$J$2:$J$140,"Sem data")</f>
+        <v>1</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A48,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <f aca="false">SUM(B48:D48)</f>
+        <v>3</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A48,Pendências!$B$2:$B$140,"Alta")</f>
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F47"/>
+  <autoFilter ref="A1:F48"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -10255,7 +10436,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -10283,200 +10464,189 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>339</v>
+        <v>107</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>107</v>
+        <v>317</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
-        <v>345</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>316</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>

--- a/pendencias-condicionantes-2026-10-23.xlsx
+++ b/pendencias-condicionantes-2026-10-23.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Licenças que faltam" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Pendências!$A$1:$R$140</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Por empresa'!$A$1:$F$48</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Pendências!$A$1:$R$142</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Por empresa'!$A$1:$F$49</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="349">
   <si>
     <t xml:space="preserve">Condicionantes ambientais – pendências</t>
   </si>
@@ -512,6 +512,18 @@
     <t xml:space="preserve">2020-152705/TEC/LO-0151</t>
   </si>
   <si>
+    <t xml:space="preserve">G J Santos De Oliveira - Areia Branca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Areia Branca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.156.112/0001-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-201889/TEC/LO-0305</t>
+  </si>
+  <si>
     <t xml:space="preserve">G J Santos De Oliveira Ltda - Macau</t>
   </si>
   <si>
@@ -930,15 +942,6 @@
   </si>
   <si>
     <t xml:space="preserve">Prioridade alta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G J Santos de Oliveira – Areia Branca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.156.112/0001-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pasta 29 tem ANP e TOG; falta a licença</t>
   </si>
   <si>
     <t xml:space="preserve">Posto Santa Rita I</t>
@@ -1779,15 +1782,15 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A6,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A6,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>12</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A6,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A6,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A6,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A6,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
@@ -1800,15 +1803,15 @@
         <v>10</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A7,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A7,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>8</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A7,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A7,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A7,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A7,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>4</v>
       </c>
       <c r="E7" s="7" t="n">
@@ -1821,15 +1824,15 @@
         <v>11</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A8,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A8,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>7</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A8,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A8,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A8,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A8,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
@@ -1842,15 +1845,15 @@
         <v>12</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A9,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A9,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>5</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A9,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A9,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A9,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A9,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
@@ -1863,15 +1866,15 @@
         <v>13</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A10,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A10,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A10,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A10,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A10,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A10,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E10" s="7" t="n">
@@ -1884,20 +1887,20 @@
         <v>14</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A11,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A11,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>24</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A11,Pendências!$J$2:$J$140,"Sem data")</f>
-        <v>8</v>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A11,Pendências!$J$2:$J$142,"Sem data")</f>
+        <v>9</v>
       </c>
       <c r="D11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A11,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A11,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>4</v>
       </c>
       <c r="E11" s="7" t="n">
         <f aca="false">SUM(B11:D11)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1905,20 +1908,20 @@
         <v>15</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A12,Pendências!$J$2:$J$140,"Vencida")</f>
-        <v>37</v>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A12,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>38</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A12,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A12,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>8</v>
       </c>
       <c r="D12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A12,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A12,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
         <f aca="false">SUM(B12:D12)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1926,15 +1929,15 @@
         <v>16</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A13,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A13,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A13,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A13,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>4</v>
       </c>
       <c r="D13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A13,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A13,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>3</v>
       </c>
       <c r="E13" s="7" t="n">
@@ -1947,15 +1950,15 @@
         <v>17</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A14,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A14,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A14,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A14,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A14,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A14,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
@@ -1968,15 +1971,15 @@
         <v>18</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A15,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A15,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A15,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A15,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>4</v>
       </c>
       <c r="D15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A15,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A15,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
@@ -1989,15 +1992,15 @@
         <v>19</v>
       </c>
       <c r="B16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A16,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A16,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A16,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A16,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>3</v>
       </c>
       <c r="D16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$140,$A16,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A16,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
@@ -2011,11 +2014,11 @@
       </c>
       <c r="B17" s="8" t="n">
         <f aca="false">SUM(B6:B16)</f>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C17" s="8" t="n">
         <f aca="false">SUM(C6:C16)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" s="8" t="n">
         <f aca="false">SUM(D6:D16)</f>
@@ -2023,7 +2026,7 @@
       </c>
       <c r="E17" s="8" t="n">
         <f aca="false">SUM(E6:E16)</f>
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2036,8 +2039,8 @@
         <v>22</v>
       </c>
       <c r="B20" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$140,A20)</f>
-        <v>139</v>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$142,A20)</f>
+        <v>141</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2045,7 +2048,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$140,A21)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$142,A21)</f>
         <v>0</v>
       </c>
     </row>
@@ -2054,7 +2057,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$140,A22)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$142,A22)</f>
         <v>0</v>
       </c>
     </row>
@@ -2063,7 +2066,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$140,A23)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$142,A23)</f>
         <v>0</v>
       </c>
     </row>
@@ -2072,7 +2075,7 @@
         <v>26</v>
       </c>
       <c r="B24" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$140,A24)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$142,A24)</f>
         <v>0</v>
       </c>
     </row>
@@ -2097,7 +2100,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R140"/>
+  <dimension ref="A1:R142"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -5189,12 +5192,12 @@
       <c r="Q61" s="15"/>
       <c r="R61" s="14"/>
     </row>
-    <row r="62" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>161</v>
@@ -5209,27 +5212,27 @@
         <v>164</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>46911</v>
+        <v>47547</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I62" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I62" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J62" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K62" s="12" t="n">
-        <v>46282</v>
-      </c>
-      <c r="L62" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K62" s="12"/>
+      <c r="L62" s="13" t="str">
         <f aca="false">IF(K62="","",K62-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v/>
       </c>
       <c r="M62" s="10" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="N62" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O62" s="14"/>
       <c r="P62" s="14" t="s">
@@ -5238,45 +5241,49 @@
       <c r="Q62" s="15"/>
       <c r="R62" s="14"/>
     </row>
-    <row r="63" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>46875</v>
+        <v>47547</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I63" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="I63" s="10" t="n">
+        <v>16</v>
+      </c>
       <c r="J63" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K63" s="12"/>
-      <c r="L63" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K63" s="12" t="n">
+        <v>46281</v>
+      </c>
+      <c r="L63" s="13" t="n">
         <f aca="false">IF(K63="","",K63-Resumo!$B$3)</f>
-        <v/>
+        <v>-37</v>
       </c>
       <c r="M63" s="10" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O63" s="14"/>
       <c r="P63" s="14" t="s">
@@ -5305,7 +5312,7 @@
         <v>168</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>46875</v>
+        <v>46911</v>
       </c>
       <c r="H64" s="10" t="s">
         <v>15</v>
@@ -5339,7 +5346,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>169</v>
@@ -5354,26 +5361,22 @@
         <v>172</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>47952</v>
+        <v>46875</v>
       </c>
       <c r="H65" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I65" s="10" t="n">
-        <v>5</v>
-      </c>
+      <c r="I65" s="10"/>
       <c r="J65" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K65" s="12" t="n">
-        <v>45898</v>
-      </c>
-      <c r="L65" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K65" s="12"/>
+      <c r="L65" s="13" t="str">
         <f aca="false">IF(K65="","",K65-Resumo!$B$3)</f>
-        <v>-420</v>
+        <v/>
       </c>
       <c r="M65" s="10" t="s">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="N65" s="10" t="s">
         <v>54</v>
@@ -5405,26 +5408,24 @@
         <v>172</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>47952</v>
+        <v>46875</v>
       </c>
       <c r="H66" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I66" s="10" t="n">
-        <v>17</v>
-      </c>
+      <c r="I66" s="10"/>
       <c r="J66" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="L66" s="13" t="n">
         <f aca="false">IF(K66="","",K66-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-36</v>
       </c>
       <c r="M66" s="10" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="N66" s="10" t="s">
         <v>58</v>
@@ -5444,19 +5445,19 @@
         <v>55</v>
       </c>
       <c r="C67" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="D67" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="D67" s="10" t="s">
+      <c r="E67" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="E67" s="10" t="s">
+      <c r="F67" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F67" s="10" t="s">
-        <v>177</v>
-      </c>
       <c r="G67" s="12" t="n">
-        <v>46990</v>
+        <v>47952</v>
       </c>
       <c r="H67" s="10" t="s">
         <v>14</v>
@@ -5468,14 +5469,14 @@
         <v>56</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>46163</v>
+        <v>45898</v>
       </c>
       <c r="L67" s="13" t="n">
         <f aca="false">IF(K67="","",K67-Resumo!$B$3)</f>
-        <v>-155</v>
+        <v>-420</v>
       </c>
       <c r="M67" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N67" s="10" t="s">
         <v>54</v>
@@ -5495,25 +5496,25 @@
         <v>55</v>
       </c>
       <c r="C68" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="D68" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="D68" s="10" t="s">
+      <c r="E68" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="E68" s="10" t="s">
+      <c r="F68" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F68" s="10" t="s">
-        <v>177</v>
-      </c>
       <c r="G68" s="12" t="n">
-        <v>46990</v>
+        <v>47952</v>
       </c>
       <c r="H68" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J68" s="10" t="s">
         <v>56</v>
@@ -5538,18 +5539,18 @@
       <c r="Q68" s="15"/>
       <c r="R68" s="14"/>
     </row>
-    <row r="69" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C69" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D69" s="10" t="s">
         <v>179</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>95</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>180</v>
@@ -5558,27 +5559,29 @@
         <v>181</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>47087</v>
+        <v>46990</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I69" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I69" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J69" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>46274</v>
+        <v>46163</v>
       </c>
       <c r="L69" s="13" t="n">
         <f aca="false">IF(K69="","",K69-Resumo!$B$3)</f>
-        <v>-44</v>
+        <v>-155</v>
       </c>
       <c r="M69" s="10" t="s">
         <v>182</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O69" s="14"/>
       <c r="P69" s="14" t="s">
@@ -5587,7 +5590,7 @@
       <c r="Q69" s="15"/>
       <c r="R69" s="14"/>
     </row>
-    <row r="70" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="n">
         <v>69</v>
       </c>
@@ -5595,10 +5598,10 @@
         <v>55</v>
       </c>
       <c r="C70" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D70" s="10" t="s">
         <v>179</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>95</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>180</v>
@@ -5607,29 +5610,29 @@
         <v>181</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>47087</v>
+        <v>46990</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I70" s="10" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J70" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>45997</v>
+        <v>46281</v>
       </c>
       <c r="L70" s="13" t="n">
         <f aca="false">IF(K70="","",K70-Resumo!$B$3)</f>
-        <v>-321</v>
+        <v>-37</v>
       </c>
       <c r="M70" s="10" t="s">
-        <v>183</v>
+        <v>57</v>
       </c>
       <c r="N70" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O70" s="14"/>
       <c r="P70" s="14" t="s">
@@ -5643,44 +5646,42 @@
         <v>70</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>95</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>47087</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I71" s="10" t="n">
-        <v>16</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I71" s="10"/>
       <c r="J71" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="L71" s="13" t="n">
         <f aca="false">IF(K71="","",K71-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-44</v>
       </c>
       <c r="M71" s="10" t="s">
-        <v>57</v>
+        <v>186</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O71" s="14"/>
       <c r="P71" s="14" t="s">
@@ -5689,47 +5690,49 @@
       <c r="Q71" s="15"/>
       <c r="R71" s="14"/>
     </row>
-    <row r="72" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>95</v>
       </c>
       <c r="E72" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F72" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="F72" s="10" t="s">
-        <v>186</v>
-      </c>
       <c r="G72" s="12" t="n">
-        <v>47854</v>
+        <v>47087</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I72" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I72" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J72" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>46316</v>
+        <v>45997</v>
       </c>
       <c r="L72" s="13" t="n">
         <f aca="false">IF(K72="","",K72-Resumo!$B$3)</f>
-        <v>-2</v>
+        <v>-321</v>
       </c>
       <c r="M72" s="10" t="s">
         <v>187</v>
       </c>
       <c r="N72" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O72" s="14"/>
       <c r="P72" s="14" t="s">
@@ -5746,25 +5749,25 @@
         <v>55</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>95</v>
       </c>
       <c r="E73" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F73" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="F73" s="10" t="s">
-        <v>186</v>
-      </c>
       <c r="G73" s="12" t="n">
-        <v>47854</v>
+        <v>47087</v>
       </c>
       <c r="H73" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J73" s="10" t="s">
         <v>56</v>
@@ -5794,44 +5797,42 @@
         <v>73</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C74" s="10" t="s">
         <v>188</v>
       </c>
       <c r="D74" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E74" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="E74" s="10" t="s">
+      <c r="F74" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="F74" s="10" t="s">
-        <v>191</v>
-      </c>
       <c r="G74" s="12" t="n">
-        <v>46031</v>
+        <v>47854</v>
       </c>
       <c r="H74" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="I74" s="10" t="n">
-        <v>19</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I74" s="10"/>
       <c r="J74" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>45911</v>
+        <v>46316</v>
       </c>
       <c r="L74" s="13" t="n">
         <f aca="false">IF(K74="","",K74-Resumo!$B$3)</f>
-        <v>-407</v>
+        <v>-2</v>
       </c>
       <c r="M74" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N74" s="10" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="O74" s="14"/>
       <c r="P74" s="14" t="s">
@@ -5840,47 +5841,49 @@
       <c r="Q74" s="15"/>
       <c r="R74" s="14"/>
     </row>
-    <row r="75" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>188</v>
       </c>
       <c r="D75" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E75" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="E75" s="10" t="s">
+      <c r="F75" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="F75" s="10" t="s">
-        <v>191</v>
-      </c>
       <c r="G75" s="12" t="n">
-        <v>46031</v>
+        <v>47854</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I75" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="I75" s="10" t="n">
+        <v>18</v>
+      </c>
       <c r="J75" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>45659</v>
+        <v>46281</v>
       </c>
       <c r="L75" s="13" t="n">
         <f aca="false">IF(K75="","",K75-Resumo!$B$3)</f>
-        <v>-659</v>
+        <v>-37</v>
       </c>
       <c r="M75" s="10" t="s">
-        <v>193</v>
+        <v>57</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O75" s="14"/>
       <c r="P75" s="14" t="s">
@@ -5894,44 +5897,44 @@
         <v>75</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G76" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I76" s="10" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J76" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>46083</v>
+        <v>45911</v>
       </c>
       <c r="L76" s="13" t="n">
         <f aca="false">IF(K76="","",K76-Resumo!$B$3)</f>
-        <v>-235</v>
+        <v>-407</v>
       </c>
       <c r="M76" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N76" s="10" t="s">
-        <v>195</v>
+        <v>99</v>
       </c>
       <c r="O76" s="14"/>
       <c r="P76" s="14" t="s">
@@ -5945,44 +5948,42 @@
         <v>76</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G77" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I77" s="10" t="n">
-        <v>5</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I77" s="10"/>
       <c r="J77" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>45514</v>
+        <v>45659</v>
       </c>
       <c r="L77" s="13" t="n">
         <f aca="false">IF(K77="","",K77-Resumo!$B$3)</f>
-        <v>-804</v>
+        <v>-659</v>
       </c>
       <c r="M77" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O77" s="14"/>
       <c r="P77" s="14" t="s">
@@ -5996,44 +5997,44 @@
         <v>77</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G78" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I78" s="10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J78" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>45356</v>
+        <v>46083</v>
       </c>
       <c r="L78" s="13" t="n">
         <f aca="false">IF(K78="","",K78-Resumo!$B$3)</f>
-        <v>-962</v>
+        <v>-235</v>
       </c>
       <c r="M78" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N78" s="10" t="s">
-        <v>58</v>
+        <v>199</v>
       </c>
       <c r="O78" s="14"/>
       <c r="P78" s="14" t="s">
@@ -6042,47 +6043,49 @@
       <c r="Q78" s="15"/>
       <c r="R78" s="14"/>
     </row>
-    <row r="79" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="n">
         <v>78</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="E79" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>46031</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I79" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J79" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K79" s="12" t="n">
+        <v>45514</v>
+      </c>
+      <c r="L79" s="13" t="n">
+        <f aca="false">IF(K79="","",K79-Resumo!$B$3)</f>
+        <v>-804</v>
+      </c>
+      <c r="M79" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F79" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="G79" s="12" t="n">
-        <v>46729</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I79" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="J79" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K79" s="12"/>
-      <c r="L79" s="13" t="str">
-        <f aca="false">IF(K79="","",K79-Resumo!$B$3)</f>
-        <v/>
-      </c>
-      <c r="M79" s="10" t="s">
-        <v>79</v>
-      </c>
       <c r="N79" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O79" s="14"/>
       <c r="P79" s="14" t="s">
@@ -6096,42 +6099,44 @@
         <v>79</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>65</v>
+        <v>193</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>48171</v>
+        <v>46031</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I80" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="I80" s="10" t="n">
+        <v>15</v>
+      </c>
       <c r="J80" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>46272</v>
+        <v>45356</v>
       </c>
       <c r="L80" s="13" t="n">
         <f aca="false">IF(K80="","",K80-Resumo!$B$3)</f>
-        <v>-46</v>
+        <v>-962</v>
       </c>
       <c r="M80" s="10" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="N80" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O80" s="14"/>
       <c r="P80" s="14" t="s">
@@ -6140,49 +6145,47 @@
       <c r="Q80" s="15"/>
       <c r="R80" s="14"/>
     </row>
-    <row r="81" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C81" s="10" t="s">
         <v>202</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>65</v>
+        <v>203</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>48171</v>
+        <v>46729</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I81" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J81" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K81" s="12" t="n">
-        <v>46309</v>
-      </c>
-      <c r="L81" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K81" s="12"/>
+      <c r="L81" s="13" t="str">
         <f aca="false">IF(K81="","",K81-Resumo!$B$3)</f>
-        <v>-9</v>
+        <v/>
       </c>
       <c r="M81" s="10" t="s">
-        <v>206</v>
+        <v>79</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O81" s="14"/>
       <c r="P81" s="14" t="s">
@@ -6196,44 +6199,42 @@
         <v>81</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>65</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G82" s="12" t="n">
         <v>48171</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I82" s="10" t="n">
-        <v>15</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I82" s="10"/>
       <c r="J82" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>46281</v>
+        <v>46272</v>
       </c>
       <c r="L82" s="13" t="n">
         <f aca="false">IF(K82="","",K82-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-46</v>
       </c>
       <c r="M82" s="10" t="s">
-        <v>57</v>
+        <v>209</v>
       </c>
       <c r="N82" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O82" s="14"/>
       <c r="P82" s="14" t="s">
@@ -6242,7 +6243,7 @@
       <c r="Q82" s="15"/>
       <c r="R82" s="14"/>
     </row>
-    <row r="83" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="n">
         <v>82</v>
       </c>
@@ -6250,41 +6251,41 @@
         <v>55</v>
       </c>
       <c r="C83" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E83" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="D83" s="10" t="s">
+      <c r="F83" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="E83" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F83" s="10" t="s">
-        <v>210</v>
-      </c>
       <c r="G83" s="12" t="n">
-        <v>46288</v>
+        <v>48171</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I83" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J83" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>46168</v>
+        <v>46309</v>
       </c>
       <c r="L83" s="13" t="n">
         <f aca="false">IF(K83="","",K83-Resumo!$B$3)</f>
-        <v>-150</v>
+        <v>-9</v>
       </c>
       <c r="M83" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="O83" s="14"/>
       <c r="P83" s="14" t="s">
@@ -6298,44 +6299,44 @@
         <v>83</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C84" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E84" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="D84" s="10" t="s">
+      <c r="F84" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="E84" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F84" s="10" t="s">
-        <v>212</v>
-      </c>
       <c r="G84" s="12" t="n">
-        <v>48005</v>
+        <v>48171</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I84" s="10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J84" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>46163</v>
+        <v>46281</v>
       </c>
       <c r="L84" s="13" t="n">
         <f aca="false">IF(K84="","",K84-Resumo!$B$3)</f>
-        <v>-155</v>
+        <v>-37</v>
       </c>
       <c r="M84" s="10" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="N84" s="10" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="O84" s="14"/>
       <c r="P84" s="14" t="s">
@@ -6344,47 +6345,49 @@
       <c r="Q84" s="15"/>
       <c r="R84" s="14"/>
     </row>
-    <row r="85" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G85" s="12" t="n">
         <v>46288</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I85" s="10" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K85" s="12"/>
-      <c r="L85" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K85" s="12" t="n">
+        <v>46168</v>
+      </c>
+      <c r="L85" s="13" t="n">
         <f aca="false">IF(K85="","",K85-Resumo!$B$3)</f>
-        <v/>
+        <v>-150</v>
       </c>
       <c r="M85" s="10" t="s">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O85" s="14"/>
       <c r="P85" s="14" t="s">
@@ -6398,44 +6401,44 @@
         <v>85</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>46288</v>
+        <v>48005</v>
       </c>
       <c r="H86" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I86" s="10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J86" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>46283</v>
+        <v>46163</v>
       </c>
       <c r="L86" s="13" t="n">
         <f aca="false">IF(K86="","",K86-Resumo!$B$3)</f>
-        <v>-35</v>
+        <v>-155</v>
       </c>
       <c r="M86" s="10" t="s">
-        <v>213</v>
+        <v>85</v>
       </c>
       <c r="N86" s="10" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="O86" s="14"/>
       <c r="P86" s="14" t="s">
@@ -6449,41 +6452,39 @@
         <v>86</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C87" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="F87" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="D87" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F87" s="10" t="s">
-        <v>217</v>
-      </c>
       <c r="G87" s="12" t="n">
-        <v>46798</v>
+        <v>46288</v>
       </c>
       <c r="H87" s="10" t="s">
         <v>14</v>
       </c>
       <c r="I87" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K87" s="12" t="n">
-        <v>46323</v>
-      </c>
-      <c r="L87" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K87" s="12"/>
+      <c r="L87" s="13" t="str">
         <f aca="false">IF(K87="","",K87-Resumo!$B$3)</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="M87" s="10" t="s">
-        <v>218</v>
+        <v>79</v>
       </c>
       <c r="N87" s="10" t="s">
         <v>54</v>
@@ -6503,38 +6504,38 @@
         <v>55</v>
       </c>
       <c r="C88" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="F88" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="D88" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F88" s="10" t="s">
-        <v>217</v>
-      </c>
       <c r="G88" s="12" t="n">
-        <v>46798</v>
+        <v>46288</v>
       </c>
       <c r="H88" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J88" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="L88" s="13" t="n">
         <f aca="false">IF(K88="","",K88-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-35</v>
       </c>
       <c r="M88" s="10" t="s">
-        <v>57</v>
+        <v>217</v>
       </c>
       <c r="N88" s="10" t="s">
         <v>58</v>
@@ -6546,47 +6547,49 @@
       <c r="Q88" s="15"/>
       <c r="R88" s="14"/>
     </row>
-    <row r="89" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G89" s="12" t="n">
         <v>46798</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I89" s="10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K89" s="12"/>
-      <c r="L89" s="13" t="str">
+        <v>50</v>
+      </c>
+      <c r="K89" s="12" t="n">
+        <v>46323</v>
+      </c>
+      <c r="L89" s="13" t="n">
         <f aca="false">IF(K89="","",K89-Resumo!$B$3)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M89" s="10" t="s">
-        <v>79</v>
+        <v>222</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="O89" s="14"/>
       <c r="P89" s="14" t="s">
@@ -6603,19 +6606,19 @@
         <v>55</v>
       </c>
       <c r="C90" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="D90" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="D90" s="10" t="s">
+      <c r="E90" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="E90" s="10" t="s">
+      <c r="F90" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="F90" s="10" t="s">
-        <v>222</v>
-      </c>
       <c r="G90" s="12" t="n">
-        <v>47004</v>
+        <v>46798</v>
       </c>
       <c r="H90" s="10" t="s">
         <v>15</v>
@@ -6627,14 +6630,14 @@
         <v>56</v>
       </c>
       <c r="K90" s="12" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="L90" s="13" t="n">
         <f aca="false">IF(K90="","",K90-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="M90" s="10" t="s">
-        <v>223</v>
+        <v>57</v>
       </c>
       <c r="N90" s="10" t="s">
         <v>58</v>
@@ -6654,41 +6657,39 @@
         <v>45</v>
       </c>
       <c r="C91" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="D91" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="D91" s="10" t="s">
+      <c r="E91" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="E91" s="10" t="s">
+      <c r="F91" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="F91" s="10" t="s">
-        <v>222</v>
-      </c>
       <c r="G91" s="12" t="n">
-        <v>47004</v>
+        <v>46798</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I91" s="10" t="n">
         <v>15</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K91" s="12" t="n">
-        <v>46344</v>
-      </c>
-      <c r="L91" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K91" s="12"/>
+      <c r="L91" s="13" t="str">
         <f aca="false">IF(K91="","",K91-Resumo!$B$3)</f>
-        <v>26</v>
+        <v/>
       </c>
       <c r="M91" s="10" t="s">
-        <v>224</v>
+        <v>79</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="O91" s="14"/>
       <c r="P91" s="14" t="s">
@@ -6705,41 +6706,41 @@
         <v>55</v>
       </c>
       <c r="C92" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="E92" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="D92" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E92" s="10" t="s">
+      <c r="F92" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="F92" s="10" t="s">
-        <v>227</v>
-      </c>
       <c r="G92" s="12" t="n">
-        <v>46046</v>
+        <v>47004</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I92" s="10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J92" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K92" s="12" t="n">
-        <v>45926</v>
+        <v>46280</v>
       </c>
       <c r="L92" s="13" t="n">
         <f aca="false">IF(K92="","",K92-Resumo!$B$3)</f>
-        <v>-392</v>
+        <v>-38</v>
       </c>
       <c r="M92" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N92" s="10" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="O92" s="14"/>
       <c r="P92" s="14" t="s">
@@ -6753,42 +6754,44 @@
         <v>92</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="C93" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="E93" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="D93" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E93" s="10" t="s">
+      <c r="F93" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="F93" s="10" t="s">
-        <v>227</v>
-      </c>
       <c r="G93" s="12" t="n">
-        <v>46046</v>
+        <v>47004</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I93" s="10"/>
+        <v>16</v>
+      </c>
+      <c r="I93" s="10" t="n">
+        <v>15</v>
+      </c>
       <c r="J93" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>45823</v>
+        <v>46344</v>
       </c>
       <c r="L93" s="13" t="n">
         <f aca="false">IF(K93="","",K93-Resumo!$B$3)</f>
-        <v>-495</v>
+        <v>26</v>
       </c>
       <c r="M93" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="O93" s="14"/>
       <c r="P93" s="14" t="s">
@@ -6797,7 +6800,7 @@
       <c r="Q93" s="15"/>
       <c r="R93" s="14"/>
     </row>
-    <row r="94" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="n">
         <v>93</v>
       </c>
@@ -6805,41 +6808,41 @@
         <v>55</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>47</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G94" s="12" t="n">
         <v>46046</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I94" s="10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J94" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K94" s="12" t="n">
-        <v>46058</v>
+        <v>45926</v>
       </c>
       <c r="L94" s="13" t="n">
         <f aca="false">IF(K94="","",K94-Resumo!$B$3)</f>
-        <v>-260</v>
+        <v>-392</v>
       </c>
       <c r="M94" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N94" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O94" s="14"/>
       <c r="P94" s="14" t="s">
@@ -6853,44 +6856,42 @@
         <v>94</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>47</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G95" s="12" t="n">
         <v>46046</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I95" s="10" t="n">
-        <v>15</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I95" s="10"/>
       <c r="J95" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>46281</v>
+        <v>45823</v>
       </c>
       <c r="L95" s="13" t="n">
         <f aca="false">IF(K95="","",K95-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-495</v>
       </c>
       <c r="M95" s="10" t="s">
-        <v>57</v>
+        <v>233</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O95" s="14"/>
       <c r="P95" s="14" t="s">
@@ -6899,7 +6900,7 @@
       <c r="Q95" s="15"/>
       <c r="R95" s="14"/>
     </row>
-    <row r="96" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="n">
         <v>95</v>
       </c>
@@ -6907,41 +6908,41 @@
         <v>55</v>
       </c>
       <c r="C96" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="F96" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="D96" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E96" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="F96" s="10" t="s">
-        <v>233</v>
-      </c>
       <c r="G96" s="12" t="n">
-        <v>46970</v>
+        <v>46046</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I96" s="10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J96" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K96" s="12" t="n">
-        <v>46281</v>
+        <v>46058</v>
       </c>
       <c r="L96" s="13" t="n">
         <f aca="false">IF(K96="","",K96-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-260</v>
       </c>
       <c r="M96" s="10" t="s">
-        <v>57</v>
+        <v>234</v>
       </c>
       <c r="N96" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O96" s="14"/>
       <c r="P96" s="14" t="s">
@@ -6958,39 +6959,41 @@
         <v>55</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>46505</v>
+        <v>46046</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I97" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="I97" s="10" t="n">
+        <v>15</v>
+      </c>
       <c r="J97" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>46319</v>
+        <v>46281</v>
       </c>
       <c r="L97" s="13" t="n">
         <f aca="false">IF(K97="","",K97-Resumo!$B$3)</f>
-        <v>1</v>
+        <v>-37</v>
       </c>
       <c r="M97" s="10" t="s">
-        <v>237</v>
+        <v>57</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O97" s="14"/>
       <c r="P97" s="14" t="s">
@@ -6999,7 +7002,7 @@
       <c r="Q97" s="15"/>
       <c r="R97" s="14"/>
     </row>
-    <row r="98" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="n">
         <v>97</v>
       </c>
@@ -7007,41 +7010,41 @@
         <v>55</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>46505</v>
+        <v>46970</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I98" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J98" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K98" s="12" t="n">
-        <v>45891</v>
+        <v>46281</v>
       </c>
       <c r="L98" s="13" t="n">
         <f aca="false">IF(K98="","",K98-Resumo!$B$3)</f>
-        <v>-427</v>
+        <v>-37</v>
       </c>
       <c r="M98" s="10" t="s">
-        <v>238</v>
+        <v>57</v>
       </c>
       <c r="N98" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O98" s="14"/>
       <c r="P98" s="14" t="s">
@@ -7058,41 +7061,39 @@
         <v>55</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>70</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G99" s="12" t="n">
         <v>46505</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I99" s="10" t="n">
-        <v>15</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I99" s="10"/>
       <c r="J99" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>46282</v>
+        <v>46319</v>
       </c>
       <c r="L99" s="13" t="n">
         <f aca="false">IF(K99="","",K99-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>1</v>
       </c>
       <c r="M99" s="10" t="s">
-        <v>74</v>
+        <v>241</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O99" s="14"/>
       <c r="P99" s="14" t="s">
@@ -7101,7 +7102,7 @@
       <c r="Q99" s="15"/>
       <c r="R99" s="14"/>
     </row>
-    <row r="100" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="10" t="n">
         <v>99</v>
       </c>
@@ -7109,39 +7110,41 @@
         <v>55</v>
       </c>
       <c r="C100" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="D100" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E100" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="D100" s="10" t="s">
+      <c r="F100" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="E100" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="F100" s="10" t="s">
-        <v>242</v>
-      </c>
       <c r="G100" s="12" t="n">
-        <v>46346</v>
+        <v>46505</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="I100" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I100" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J100" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K100" s="12" t="n">
-        <v>46226</v>
+        <v>45891</v>
       </c>
       <c r="L100" s="13" t="n">
         <f aca="false">IF(K100="","",K100-Resumo!$B$3)</f>
-        <v>-92</v>
+        <v>-427</v>
       </c>
       <c r="M100" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="N100" s="10" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="O100" s="14"/>
       <c r="P100" s="14" t="s">
@@ -7158,24 +7161,26 @@
         <v>55</v>
       </c>
       <c r="C101" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="D101" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E101" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="D101" s="10" t="s">
+      <c r="F101" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="E101" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="F101" s="10" t="s">
-        <v>242</v>
-      </c>
       <c r="G101" s="12" t="n">
-        <v>46346</v>
+        <v>46505</v>
       </c>
       <c r="H101" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I101" s="10"/>
+      <c r="I101" s="10" t="n">
+        <v>15</v>
+      </c>
       <c r="J101" s="10" t="s">
         <v>56</v>
       </c>
@@ -7207,10 +7212,10 @@
         <v>55</v>
       </c>
       <c r="C102" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="D102" s="10" t="s">
         <v>244</v>
-      </c>
-      <c r="D102" s="10" t="s">
-        <v>65</v>
       </c>
       <c r="E102" s="10" t="s">
         <v>245</v>
@@ -7219,23 +7224,21 @@
         <v>246</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>46373</v>
+        <v>46346</v>
       </c>
       <c r="H102" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I102" s="10" t="n">
-        <v>22</v>
-      </c>
+      <c r="I102" s="10"/>
       <c r="J102" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K102" s="12" t="n">
-        <v>46253</v>
+        <v>46226</v>
       </c>
       <c r="L102" s="13" t="n">
         <f aca="false">IF(K102="","",K102-Resumo!$B$3)</f>
-        <v>-65</v>
+        <v>-92</v>
       </c>
       <c r="M102" s="10" t="s">
         <v>247</v>
@@ -7250,7 +7253,7 @@
       <c r="Q102" s="15"/>
       <c r="R102" s="14"/>
     </row>
-    <row r="103" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="10" t="n">
         <v>102</v>
       </c>
@@ -7258,10 +7261,10 @@
         <v>55</v>
       </c>
       <c r="C103" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="D103" s="10" t="s">
         <v>244</v>
-      </c>
-      <c r="D103" s="10" t="s">
-        <v>65</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>245</v>
@@ -7270,29 +7273,27 @@
         <v>246</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>46373</v>
+        <v>46346</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I103" s="10" t="n">
-        <v>5</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I103" s="10"/>
       <c r="J103" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>45192</v>
+        <v>46282</v>
       </c>
       <c r="L103" s="13" t="n">
         <f aca="false">IF(K103="","",K103-Resumo!$B$3)</f>
-        <v>-1126</v>
+        <v>-36</v>
       </c>
       <c r="M103" s="10" t="s">
-        <v>248</v>
+        <v>74</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O103" s="14"/>
       <c r="P103" s="14" t="s">
@@ -7309,41 +7310,41 @@
         <v>55</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D104" s="10" t="s">
         <v>65</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="G104" s="12" t="n">
         <v>46373</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I104" s="10" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J104" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K104" s="12" t="n">
-        <v>45262</v>
+        <v>46253</v>
       </c>
       <c r="L104" s="13" t="n">
         <f aca="false">IF(K104="","",K104-Resumo!$B$3)</f>
-        <v>-1056</v>
+        <v>-65</v>
       </c>
       <c r="M104" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N104" s="10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O104" s="14"/>
       <c r="P104" s="14" t="s">
@@ -7360,19 +7361,19 @@
         <v>55</v>
       </c>
       <c r="C105" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D105" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="F105" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="D105" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="E105" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="F105" s="10" t="s">
-        <v>253</v>
-      </c>
       <c r="G105" s="12" t="n">
-        <v>48010</v>
+        <v>46373</v>
       </c>
       <c r="H105" s="10" t="s">
         <v>14</v>
@@ -7384,14 +7385,14 @@
         <v>56</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>46127</v>
+        <v>45192</v>
       </c>
       <c r="L105" s="13" t="n">
         <f aca="false">IF(K105="","",K105-Resumo!$B$3)</f>
-        <v>-191</v>
+        <v>-1126</v>
       </c>
       <c r="M105" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N105" s="10" t="s">
         <v>54</v>
@@ -7411,38 +7412,38 @@
         <v>55</v>
       </c>
       <c r="C106" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D106" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="F106" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="D106" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="E106" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="F106" s="10" t="s">
-        <v>253</v>
-      </c>
       <c r="G106" s="12" t="n">
-        <v>48010</v>
+        <v>46373</v>
       </c>
       <c r="H106" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J106" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K106" s="12" t="n">
-        <v>46280</v>
+        <v>45262</v>
       </c>
       <c r="L106" s="13" t="n">
         <f aca="false">IF(K106="","",K106-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>-1056</v>
       </c>
       <c r="M106" s="10" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="N106" s="10" t="s">
         <v>58</v>
@@ -7454,7 +7455,7 @@
       <c r="Q106" s="15"/>
       <c r="R106" s="14"/>
     </row>
-    <row r="107" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="10" t="n">
         <v>106</v>
       </c>
@@ -7462,41 +7463,41 @@
         <v>55</v>
       </c>
       <c r="C107" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D107" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="D107" s="10" t="s">
+      <c r="E107" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="E107" s="10" t="s">
+      <c r="F107" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="F107" s="10" t="s">
-        <v>258</v>
-      </c>
       <c r="G107" s="12" t="n">
-        <v>46043</v>
+        <v>48010</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I107" s="10" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="J107" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>45923</v>
+        <v>46127</v>
       </c>
       <c r="L107" s="13" t="n">
         <f aca="false">IF(K107="","",K107-Resumo!$B$3)</f>
-        <v>-395</v>
+        <v>-191</v>
       </c>
       <c r="M107" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="O107" s="14"/>
       <c r="P107" s="14" t="s">
@@ -7505,7 +7506,7 @@
       <c r="Q107" s="15"/>
       <c r="R107" s="14"/>
     </row>
-    <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="10" t="n">
         <v>107</v>
       </c>
@@ -7513,41 +7514,41 @@
         <v>55</v>
       </c>
       <c r="C108" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D108" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="D108" s="10" t="s">
+      <c r="E108" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="E108" s="10" t="s">
+      <c r="F108" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="F108" s="10" t="s">
-        <v>258</v>
-      </c>
       <c r="G108" s="12" t="n">
-        <v>46043</v>
+        <v>48010</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I108" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J108" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K108" s="12" t="n">
-        <v>46113</v>
+        <v>46280</v>
       </c>
       <c r="L108" s="13" t="n">
         <f aca="false">IF(K108="","",K108-Resumo!$B$3)</f>
-        <v>-205</v>
+        <v>-38</v>
       </c>
       <c r="M108" s="10" t="s">
-        <v>260</v>
+        <v>227</v>
       </c>
       <c r="N108" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O108" s="14"/>
       <c r="P108" s="14" t="s">
@@ -7564,41 +7565,41 @@
         <v>55</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G109" s="12" t="n">
         <v>46043</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I109" s="10" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J109" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>45351</v>
+        <v>45923</v>
       </c>
       <c r="L109" s="13" t="n">
         <f aca="false">IF(K109="","",K109-Resumo!$B$3)</f>
-        <v>-967</v>
+        <v>-395</v>
       </c>
       <c r="M109" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O109" s="14"/>
       <c r="P109" s="14" t="s">
@@ -7607,7 +7608,7 @@
       <c r="Q109" s="15"/>
       <c r="R109" s="14"/>
     </row>
-    <row r="110" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="n">
         <v>109</v>
       </c>
@@ -7615,41 +7616,41 @@
         <v>55</v>
       </c>
       <c r="C110" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="D110" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="F110" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="D110" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="F110" s="10" t="s">
-        <v>264</v>
-      </c>
       <c r="G110" s="12" t="n">
-        <v>46408</v>
+        <v>46043</v>
       </c>
       <c r="H110" s="10" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I110" s="10" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J110" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K110" s="12" t="n">
-        <v>46288</v>
+        <v>46113</v>
       </c>
       <c r="L110" s="13" t="n">
         <f aca="false">IF(K110="","",K110-Resumo!$B$3)</f>
-        <v>-30</v>
+        <v>-205</v>
       </c>
       <c r="M110" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N110" s="10" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="O110" s="14"/>
       <c r="P110" s="14" t="s">
@@ -7658,7 +7659,7 @@
       <c r="Q110" s="15"/>
       <c r="R110" s="14"/>
     </row>
-    <row r="111" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="10" t="n">
         <v>110</v>
       </c>
@@ -7666,41 +7667,41 @@
         <v>55</v>
       </c>
       <c r="C111" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="D111" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="F111" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="D111" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="E111" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="F111" s="10" t="s">
-        <v>264</v>
-      </c>
       <c r="G111" s="12" t="n">
-        <v>46408</v>
+        <v>46043</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I111" s="10" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J111" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>46113</v>
+        <v>45351</v>
       </c>
       <c r="L111" s="13" t="n">
         <f aca="false">IF(K111="","",K111-Resumo!$B$3)</f>
-        <v>-205</v>
+        <v>-967</v>
       </c>
       <c r="M111" s="10" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O111" s="14"/>
       <c r="P111" s="14" t="s">
@@ -7717,41 +7718,41 @@
         <v>55</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F112" s="10" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G112" s="12" t="n">
         <v>46408</v>
       </c>
       <c r="H112" s="10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I112" s="10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J112" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K112" s="12" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="L112" s="13" t="n">
         <f aca="false">IF(K112="","",K112-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-30</v>
       </c>
       <c r="M112" s="10" t="s">
-        <v>74</v>
+        <v>269</v>
       </c>
       <c r="N112" s="10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O112" s="14"/>
       <c r="P112" s="14" t="s">
@@ -7760,18 +7761,18 @@
       <c r="Q112" s="15"/>
       <c r="R112" s="14"/>
     </row>
-    <row r="113" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="10" t="n">
         <v>112</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C113" s="10" t="s">
         <v>266</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>95</v>
+        <v>203</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>267</v>
@@ -7780,27 +7781,29 @@
         <v>268</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>47310</v>
+        <v>46408</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I113" s="10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K113" s="12"/>
-      <c r="L113" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K113" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="L113" s="13" t="n">
         <f aca="false">IF(K113="","",K113-Resumo!$B$3)</f>
-        <v/>
+        <v>-205</v>
       </c>
       <c r="M113" s="10" t="s">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>195</v>
+        <v>54</v>
       </c>
       <c r="O113" s="14"/>
       <c r="P113" s="14" t="s">
@@ -7809,18 +7812,18 @@
       <c r="Q113" s="15"/>
       <c r="R113" s="14"/>
     </row>
-    <row r="114" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="10" t="n">
         <v>113</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C114" s="10" t="s">
         <v>266</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>95</v>
+        <v>203</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>267</v>
@@ -7829,27 +7832,29 @@
         <v>268</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>47310</v>
+        <v>46408</v>
       </c>
       <c r="H114" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I114" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K114" s="12"/>
-      <c r="L114" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K114" s="12" t="n">
+        <v>46282</v>
+      </c>
+      <c r="L114" s="13" t="n">
         <f aca="false">IF(K114="","",K114-Resumo!$B$3)</f>
-        <v/>
+        <v>-36</v>
       </c>
       <c r="M114" s="10" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="N114" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O114" s="14"/>
       <c r="P114" s="14" t="s">
@@ -7863,44 +7868,42 @@
         <v>114</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D115" s="10" t="s">
         <v>95</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="G115" s="12" t="n">
         <v>47310</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I115" s="10" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K115" s="12" t="n">
-        <v>46043</v>
-      </c>
-      <c r="L115" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K115" s="12"/>
+      <c r="L115" s="13" t="str">
         <f aca="false">IF(K115="","",K115-Resumo!$B$3)</f>
-        <v>-275</v>
+        <v/>
       </c>
       <c r="M115" s="10" t="s">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>58</v>
+        <v>199</v>
       </c>
       <c r="O115" s="14"/>
       <c r="P115" s="14" t="s">
@@ -7914,13 +7917,13 @@
         <v>115</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C116" s="10" t="s">
         <v>270</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>271</v>
@@ -7929,7 +7932,7 @@
         <v>272</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>46658</v>
+        <v>47310</v>
       </c>
       <c r="H116" s="10" t="s">
         <v>14</v>
@@ -7938,17 +7941,15 @@
         <v>5</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K116" s="12" t="n">
-        <v>46107</v>
-      </c>
-      <c r="L116" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K116" s="12"/>
+      <c r="L116" s="13" t="str">
         <f aca="false">IF(K116="","",K116-Resumo!$B$3)</f>
-        <v>-211</v>
+        <v/>
       </c>
       <c r="M116" s="10" t="s">
-        <v>273</v>
+        <v>79</v>
       </c>
       <c r="N116" s="10" t="s">
         <v>54</v>
@@ -7971,7 +7972,7 @@
         <v>270</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>271</v>
@@ -7980,26 +7981,26 @@
         <v>272</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>46658</v>
+        <v>47310</v>
       </c>
       <c r="H117" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J117" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>46280</v>
+        <v>46043</v>
       </c>
       <c r="L117" s="13" t="n">
         <f aca="false">IF(K117="","",K117-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>-275</v>
       </c>
       <c r="M117" s="10" t="s">
-        <v>223</v>
+        <v>273</v>
       </c>
       <c r="N117" s="10" t="s">
         <v>58</v>
@@ -8011,47 +8012,49 @@
       <c r="Q117" s="15"/>
       <c r="R117" s="14"/>
     </row>
-    <row r="118" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="10" t="n">
         <v>117</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D118" s="10" t="s">
         <v>158</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F118" s="10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="G118" s="12" t="n">
         <v>46658</v>
       </c>
       <c r="H118" s="10" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I118" s="10" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J118" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K118" s="12"/>
-      <c r="L118" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K118" s="12" t="n">
+        <v>46107</v>
+      </c>
+      <c r="L118" s="13" t="n">
         <f aca="false">IF(K118="","",K118-Resumo!$B$3)</f>
-        <v/>
+        <v>-211</v>
       </c>
       <c r="M118" s="10" t="s">
-        <v>79</v>
+        <v>277</v>
       </c>
       <c r="N118" s="10" t="s">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="O118" s="14"/>
       <c r="P118" s="14" t="s">
@@ -8060,7 +8063,7 @@
       <c r="Q118" s="15"/>
       <c r="R118" s="14"/>
     </row>
-    <row r="119" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="10" t="n">
         <v>118</v>
       </c>
@@ -8071,38 +8074,38 @@
         <v>274</v>
       </c>
       <c r="D119" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E119" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="E119" s="10" t="s">
+      <c r="F119" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="F119" s="10" t="s">
-        <v>277</v>
-      </c>
       <c r="G119" s="12" t="n">
-        <v>47016</v>
+        <v>46658</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I119" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J119" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>46113</v>
+        <v>46280</v>
       </c>
       <c r="L119" s="13" t="n">
         <f aca="false">IF(K119="","",K119-Resumo!$B$3)</f>
-        <v>-205</v>
+        <v>-38</v>
       </c>
       <c r="M119" s="10" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O119" s="14"/>
       <c r="P119" s="14" t="s">
@@ -8116,44 +8119,42 @@
         <v>119</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C120" s="10" t="s">
         <v>274</v>
       </c>
       <c r="D120" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E120" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="E120" s="10" t="s">
+      <c r="F120" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="F120" s="10" t="s">
-        <v>277</v>
-      </c>
       <c r="G120" s="12" t="n">
-        <v>47016</v>
+        <v>46658</v>
       </c>
       <c r="H120" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I120" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J120" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K120" s="12" t="n">
-        <v>45519</v>
-      </c>
-      <c r="L120" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K120" s="12"/>
+      <c r="L120" s="13" t="str">
         <f aca="false">IF(K120="","",K120-Resumo!$B$3)</f>
-        <v>-799</v>
+        <v/>
       </c>
       <c r="M120" s="10" t="s">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="N120" s="10" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="O120" s="14"/>
       <c r="P120" s="14" t="s">
@@ -8162,49 +8163,49 @@
       <c r="Q120" s="15"/>
       <c r="R120" s="14"/>
     </row>
-    <row r="121" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="10" t="n">
         <v>120</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="G121" s="12" t="n">
         <v>47016</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I121" s="10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J121" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>46339</v>
+        <v>46113</v>
       </c>
       <c r="L121" s="13" t="n">
         <f aca="false">IF(K121="","",K121-Resumo!$B$3)</f>
-        <v>21</v>
+        <v>-205</v>
       </c>
       <c r="M121" s="10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="O121" s="14"/>
       <c r="P121" s="14" t="s">
@@ -8221,41 +8222,41 @@
         <v>55</v>
       </c>
       <c r="C122" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="D122" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="F122" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D122" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="E122" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="F122" s="10" t="s">
-        <v>284</v>
-      </c>
       <c r="G122" s="12" t="n">
-        <v>46332</v>
+        <v>47016</v>
       </c>
       <c r="H122" s="10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I122" s="10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J122" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K122" s="12" t="n">
-        <v>46212</v>
+        <v>45519</v>
       </c>
       <c r="L122" s="13" t="n">
         <f aca="false">IF(K122="","",K122-Resumo!$B$3)</f>
-        <v>-106</v>
+        <v>-799</v>
       </c>
       <c r="M122" s="10" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="N122" s="10" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="O122" s="14"/>
       <c r="P122" s="14" t="s">
@@ -8269,44 +8270,44 @@
         <v>122</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="C123" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="D123" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="E123" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="F123" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D123" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="E123" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="F123" s="10" t="s">
-        <v>284</v>
-      </c>
       <c r="G123" s="12" t="n">
-        <v>46332</v>
+        <v>47016</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I123" s="10" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>46248</v>
+        <v>46339</v>
       </c>
       <c r="L123" s="13" t="n">
         <f aca="false">IF(K123="","",K123-Resumo!$B$3)</f>
-        <v>-70</v>
+        <v>21</v>
       </c>
       <c r="M123" s="10" t="s">
-        <v>85</v>
+        <v>284</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="O123" s="14"/>
       <c r="P123" s="14" t="s">
@@ -8315,7 +8316,7 @@
       <c r="Q123" s="15"/>
       <c r="R123" s="14"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="10" t="n">
         <v>123</v>
       </c>
@@ -8323,41 +8324,41 @@
         <v>55</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F124" s="10" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G124" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H124" s="10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I124" s="10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K124" s="12" t="n">
-        <v>46328</v>
+        <v>46212</v>
       </c>
       <c r="L124" s="13" t="n">
         <f aca="false">IF(K124="","",K124-Resumo!$B$3)</f>
-        <v>10</v>
+        <v>-106</v>
       </c>
       <c r="M124" s="10" t="s">
-        <v>87</v>
+        <v>289</v>
       </c>
       <c r="N124" s="10" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O124" s="14"/>
       <c r="P124" s="14" t="s">
@@ -8366,49 +8367,49 @@
       <c r="Q124" s="15"/>
       <c r="R124" s="14"/>
     </row>
-    <row r="125" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="10" t="n">
         <v>124</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G125" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I125" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J125" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>46259</v>
+        <v>46248</v>
       </c>
       <c r="L125" s="13" t="n">
         <f aca="false">IF(K125="","",K125-Resumo!$B$3)</f>
-        <v>-59</v>
+        <v>-70</v>
       </c>
       <c r="M125" s="10" t="s">
-        <v>286</v>
+        <v>85</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="O125" s="14"/>
       <c r="P125" s="14" t="s">
@@ -8417,7 +8418,7 @@
       <c r="Q125" s="15"/>
       <c r="R125" s="14"/>
     </row>
-    <row r="126" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="10" t="n">
         <v>125</v>
       </c>
@@ -8425,41 +8426,41 @@
         <v>55</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F126" s="10" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G126" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H126" s="10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I126" s="10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J126" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K126" s="12" t="n">
-        <v>46280</v>
+        <v>46328</v>
       </c>
       <c r="L126" s="13" t="n">
         <f aca="false">IF(K126="","",K126-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>10</v>
       </c>
       <c r="M126" s="10" t="s">
-        <v>223</v>
+        <v>87</v>
       </c>
       <c r="N126" s="10" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="O126" s="14"/>
       <c r="P126" s="14" t="s">
@@ -8468,47 +8469,49 @@
       <c r="Q126" s="15"/>
       <c r="R126" s="14"/>
     </row>
-    <row r="127" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="10" t="n">
         <v>126</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G127" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I127" s="10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K127" s="12"/>
-      <c r="L127" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K127" s="12" t="n">
+        <v>46259</v>
+      </c>
+      <c r="L127" s="13" t="n">
         <f aca="false">IF(K127="","",K127-Resumo!$B$3)</f>
-        <v/>
+        <v>-59</v>
       </c>
       <c r="M127" s="10" t="s">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="O127" s="14"/>
       <c r="P127" s="14" t="s">
@@ -8522,44 +8525,44 @@
         <v>127</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C128" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="D128" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="E128" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="D128" s="10" t="s">
+      <c r="F128" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="E128" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="F128" s="10" t="s">
-        <v>290</v>
-      </c>
       <c r="G128" s="12" t="n">
-        <v>48215</v>
+        <v>46332</v>
       </c>
       <c r="H128" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I128" s="10" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J128" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K128" s="12" t="n">
-        <v>46034</v>
+        <v>46280</v>
       </c>
       <c r="L128" s="13" t="n">
         <f aca="false">IF(K128="","",K128-Resumo!$B$3)</f>
-        <v>-284</v>
+        <v>-38</v>
       </c>
       <c r="M128" s="10" t="s">
-        <v>85</v>
+        <v>227</v>
       </c>
       <c r="N128" s="10" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="O128" s="14"/>
       <c r="P128" s="14" t="s">
@@ -8568,49 +8571,47 @@
       <c r="Q128" s="15"/>
       <c r="R128" s="14"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="10" t="n">
         <v>128</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="C129" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="D129" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="E129" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="D129" s="10" t="s">
+      <c r="F129" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="E129" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="F129" s="10" t="s">
-        <v>290</v>
-      </c>
       <c r="G129" s="12" t="n">
-        <v>48215</v>
+        <v>46332</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I129" s="10" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K129" s="12" t="n">
-        <v>46114</v>
-      </c>
-      <c r="L129" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K129" s="12"/>
+      <c r="L129" s="13" t="str">
         <f aca="false">IF(K129="","",K129-Resumo!$B$3)</f>
-        <v>-204</v>
+        <v/>
       </c>
       <c r="M129" s="10" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O129" s="14"/>
       <c r="P129" s="14" t="s">
@@ -8619,49 +8620,49 @@
       <c r="Q129" s="15"/>
       <c r="R129" s="14"/>
     </row>
-    <row r="130" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="10" t="n">
         <v>129</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F130" s="10" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G130" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H130" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I130" s="10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J130" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K130" s="12" t="n">
-        <v>46276</v>
+        <v>46034</v>
       </c>
       <c r="L130" s="13" t="n">
         <f aca="false">IF(K130="","",K130-Resumo!$B$3)</f>
-        <v>-42</v>
+        <v>-284</v>
       </c>
       <c r="M130" s="10" t="s">
-        <v>291</v>
+        <v>85</v>
       </c>
       <c r="N130" s="10" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="O130" s="14"/>
       <c r="P130" s="14" t="s">
@@ -8670,47 +8671,49 @@
       <c r="Q130" s="15"/>
       <c r="R130" s="14"/>
     </row>
-    <row r="131" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="10" t="n">
         <v>130</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G131" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I131" s="10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K131" s="12"/>
-      <c r="L131" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K131" s="12" t="n">
+        <v>46114</v>
+      </c>
+      <c r="L131" s="13" t="n">
         <f aca="false">IF(K131="","",K131-Resumo!$B$3)</f>
-        <v/>
+        <v>-204</v>
       </c>
       <c r="M131" s="10" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="O131" s="14"/>
       <c r="P131" s="14" t="s">
@@ -8719,47 +8722,49 @@
       <c r="Q131" s="15"/>
       <c r="R131" s="14"/>
     </row>
-    <row r="132" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="10" t="n">
         <v>131</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G132" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H132" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I132" s="10" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J132" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K132" s="12"/>
-      <c r="L132" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K132" s="12" t="n">
+        <v>46276</v>
+      </c>
+      <c r="L132" s="13" t="n">
         <f aca="false">IF(K132="","",K132-Resumo!$B$3)</f>
-        <v/>
+        <v>-42</v>
       </c>
       <c r="M132" s="10" t="s">
-        <v>79</v>
+        <v>295</v>
       </c>
       <c r="N132" s="10" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="O132" s="14"/>
       <c r="P132" s="14" t="s">
@@ -8776,25 +8781,25 @@
         <v>45</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G133" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I133" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J133" s="10" t="s">
         <v>6</v>
@@ -8808,7 +8813,7 @@
         <v>79</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="O133" s="14"/>
       <c r="P133" s="14" t="s">
@@ -8825,25 +8830,25 @@
         <v>45</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G134" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H134" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I134" s="10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J134" s="10" t="s">
         <v>6</v>
@@ -8857,7 +8862,7 @@
         <v>79</v>
       </c>
       <c r="N134" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O134" s="14"/>
       <c r="P134" s="14" t="s">
@@ -8874,10 +8879,10 @@
         <v>45</v>
       </c>
       <c r="C135" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="D135" s="10" t="s">
         <v>292</v>
-      </c>
-      <c r="D135" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>293</v>
@@ -8886,27 +8891,27 @@
         <v>294</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>47697</v>
+        <v>48215</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I135" s="10"/>
+        <v>17</v>
+      </c>
+      <c r="I135" s="10" t="n">
+        <v>14</v>
+      </c>
       <c r="J135" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K135" s="12" t="n">
-        <v>46344</v>
-      </c>
-      <c r="L135" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K135" s="12"/>
+      <c r="L135" s="13" t="str">
         <f aca="false">IF(K135="","",K135-Resumo!$B$3)</f>
-        <v>26</v>
+        <v/>
       </c>
       <c r="M135" s="10" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="O135" s="14"/>
       <c r="P135" s="14" t="s">
@@ -8915,18 +8920,18 @@
       <c r="Q135" s="15"/>
       <c r="R135" s="14"/>
     </row>
-    <row r="136" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="10" t="n">
         <v>135</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C136" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="D136" s="10" t="s">
         <v>292</v>
-      </c>
-      <c r="D136" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="E136" s="10" t="s">
         <v>293</v>
@@ -8935,29 +8940,27 @@
         <v>294</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>47697</v>
+        <v>48215</v>
       </c>
       <c r="H136" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I136" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J136" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K136" s="12" t="n">
-        <v>46127</v>
-      </c>
-      <c r="L136" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K136" s="12"/>
+      <c r="L136" s="13" t="str">
         <f aca="false">IF(K136="","",K136-Resumo!$B$3)</f>
-        <v>-191</v>
+        <v/>
       </c>
       <c r="M136" s="10" t="s">
-        <v>254</v>
+        <v>79</v>
       </c>
       <c r="N136" s="10" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="O136" s="14"/>
       <c r="P136" s="14" t="s">
@@ -8971,44 +8974,42 @@
         <v>136</v>
       </c>
       <c r="B137" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G137" s="12" t="n">
         <v>47697</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I137" s="10" t="n">
-        <v>17</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I137" s="10"/>
       <c r="J137" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>46282</v>
+        <v>46344</v>
       </c>
       <c r="L137" s="13" t="n">
         <f aca="false">IF(K137="","",K137-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>26</v>
       </c>
       <c r="M137" s="10" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O137" s="14"/>
       <c r="P137" s="14" t="s">
@@ -9017,7 +9018,7 @@
       <c r="Q137" s="15"/>
       <c r="R137" s="14"/>
     </row>
-    <row r="138" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="10" t="n">
         <v>137</v>
       </c>
@@ -9025,10 +9026,10 @@
         <v>55</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D138" s="10" t="s">
-        <v>296</v>
+        <v>193</v>
       </c>
       <c r="E138" s="10" t="s">
         <v>297</v>
@@ -9037,29 +9038,29 @@
         <v>298</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>46244</v>
+        <v>47697</v>
       </c>
       <c r="H138" s="10" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I138" s="10" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="J138" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K138" s="12" t="n">
-        <v>46124</v>
+        <v>46127</v>
       </c>
       <c r="L138" s="13" t="n">
         <f aca="false">IF(K138="","",K138-Resumo!$B$3)</f>
-        <v>-194</v>
+        <v>-191</v>
       </c>
       <c r="M138" s="10" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="N138" s="10" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="O138" s="14"/>
       <c r="P138" s="14" t="s">
@@ -9068,7 +9069,7 @@
       <c r="Q138" s="15"/>
       <c r="R138" s="14"/>
     </row>
-    <row r="139" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="10" t="n">
         <v>138</v>
       </c>
@@ -9076,10 +9077,10 @@
         <v>55</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D139" s="10" t="s">
-        <v>296</v>
+        <v>193</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>297</v>
@@ -9088,29 +9089,29 @@
         <v>298</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>46244</v>
+        <v>47697</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I139" s="10" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J139" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="L139" s="13" t="n">
         <f aca="false">IF(K139="","",K139-Resumo!$B$3)</f>
-        <v>-42</v>
+        <v>-36</v>
       </c>
       <c r="M139" s="10" t="s">
-        <v>291</v>
+        <v>74</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O139" s="14"/>
       <c r="P139" s="14" t="s">
@@ -9124,42 +9125,44 @@
         <v>139</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F140" s="10" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G140" s="12" t="n">
         <v>46244</v>
       </c>
       <c r="H140" s="10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I140" s="10" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J140" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K140" s="12"/>
-      <c r="L140" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K140" s="12" t="n">
+        <v>46124</v>
+      </c>
+      <c r="L140" s="13" t="n">
         <f aca="false">IF(K140="","",K140-Resumo!$B$3)</f>
-        <v/>
+        <v>-194</v>
       </c>
       <c r="M140" s="10" t="s">
-        <v>79</v>
+        <v>303</v>
       </c>
       <c r="N140" s="10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O140" s="14"/>
       <c r="P140" s="14" t="s">
@@ -9168,9 +9171,109 @@
       <c r="Q140" s="15"/>
       <c r="R140" s="14"/>
     </row>
+    <row r="141" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="D141" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="E141" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="F141" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H141" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I141" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J141" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K141" s="12" t="n">
+        <v>46276</v>
+      </c>
+      <c r="L141" s="13" t="n">
+        <f aca="false">IF(K141="","",K141-Resumo!$B$3)</f>
+        <v>-42</v>
+      </c>
+      <c r="M141" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="N141" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="O141" s="14"/>
+      <c r="P141" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q141" s="15"/>
+      <c r="R141" s="14"/>
+    </row>
+    <row r="142" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="10" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="D142" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="E142" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="F142" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H142" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I142" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="J142" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K142" s="12"/>
+      <c r="L142" s="13" t="str">
+        <f aca="false">IF(K142="","",K142-Resumo!$B$3)</f>
+        <v/>
+      </c>
+      <c r="M142" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N142" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O142" s="14"/>
+      <c r="P142" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q142" s="15"/>
+      <c r="R142" s="14"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R140"/>
-  <conditionalFormatting sqref="J2:J140">
+  <autoFilter ref="A1:R142"/>
+  <conditionalFormatting sqref="J2:J142">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$J2="Vencida"</formula>
     </cfRule>
@@ -9181,12 +9284,12 @@
       <formula>$J2="Sem data"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B140">
+  <conditionalFormatting sqref="B2:B142">
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>$B2="Alta"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P140">
+  <conditionalFormatting sqref="P2:P142">
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>$P2="Resolvido"</formula>
     </cfRule>
@@ -9195,7 +9298,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P140" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P142" type="list">
       <formula1>"A fazer,Em andamento,Aguardando cliente,Resolvido,Já estava em dia"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9216,7 +9319,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -9240,7 +9343,7 @@
         <v>8</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9248,15 +9351,15 @@
         <v>46</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A2,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A2,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A2,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A2,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A2,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A2,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>2</v>
       </c>
       <c r="E2" s="7" t="n">
@@ -9264,7 +9367,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A2,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A2,Pendências!$B$2:$B$142,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9273,15 +9376,15 @@
         <v>59</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A3,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A3,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A3,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A3,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A3,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A3,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E3" s="7" t="n">
@@ -9289,7 +9392,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A3,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A3,Pendências!$B$2:$B$142,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9298,15 +9401,15 @@
         <v>64</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A4,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A4,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A4,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A4,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A4,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A4,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
@@ -9314,7 +9417,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A4,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A4,Pendências!$B$2:$B$142,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9323,15 +9426,15 @@
         <v>69</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A5,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A5,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A5,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A5,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A5,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A5,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
@@ -9339,7 +9442,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A5,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A5,Pendências!$B$2:$B$142,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9348,15 +9451,15 @@
         <v>75</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A6,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A6,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A6,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A6,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A6,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A6,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
@@ -9364,7 +9467,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A6,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A6,Pendências!$B$2:$B$142,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -9373,15 +9476,15 @@
         <v>81</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A7,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A7,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>5</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A7,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A7,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A7,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A7,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
@@ -9389,7 +9492,7 @@
         <v>7</v>
       </c>
       <c r="F7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A7,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A7,Pendências!$B$2:$B$142,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9398,15 +9501,15 @@
         <v>94</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A8,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A8,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A8,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A8,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A8,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A8,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
@@ -9414,7 +9517,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A8,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A8,Pendências!$B$2:$B$142,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9423,15 +9526,15 @@
         <v>101</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A9,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A9,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A9,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A9,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A9,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A9,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
@@ -9439,7 +9542,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A9,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A9,Pendências!$B$2:$B$142,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -9448,15 +9551,15 @@
         <v>105</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A10,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A10,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A10,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A10,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A10,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A10,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E10" s="7" t="n">
@@ -9464,7 +9567,7 @@
         <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A10,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A10,Pendências!$B$2:$B$142,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9473,15 +9576,15 @@
         <v>111</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A11,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A11,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A11,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A11,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A11,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A11,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E11" s="7" t="n">
@@ -9489,7 +9592,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A11,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A11,Pendências!$B$2:$B$142,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -9498,15 +9601,15 @@
         <v>115</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A12,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A12,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A12,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A12,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A12,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A12,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
@@ -9514,7 +9617,7 @@
         <v>6</v>
       </c>
       <c r="F12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A12,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A12,Pendências!$B$2:$B$142,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9523,15 +9626,15 @@
         <v>119</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A13,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A13,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A13,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A13,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A13,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A13,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
@@ -9539,7 +9642,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A13,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A13,Pendências!$B$2:$B$142,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9548,15 +9651,15 @@
         <v>123</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A14,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A14,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A14,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A14,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A14,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A14,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
@@ -9564,7 +9667,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A14,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A14,Pendências!$B$2:$B$142,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9573,15 +9676,15 @@
         <v>127</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A15,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A15,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A15,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A15,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A15,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A15,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
@@ -9589,7 +9692,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A15,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A15,Pendências!$B$2:$B$142,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9598,15 +9701,15 @@
         <v>132</v>
       </c>
       <c r="B16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A16,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A16,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A16,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A16,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A16,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A16,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
@@ -9614,7 +9717,7 @@
         <v>4</v>
       </c>
       <c r="F16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A16,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A16,Pendências!$B$2:$B$142,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9623,15 +9726,15 @@
         <v>139</v>
       </c>
       <c r="B17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A17,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A17,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A17,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A17,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A17,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A17,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
@@ -9639,7 +9742,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A17,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A17,Pendências!$B$2:$B$142,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9648,15 +9751,15 @@
         <v>143</v>
       </c>
       <c r="B18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A18,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A18,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>4</v>
       </c>
       <c r="C18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A18,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A18,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A18,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A18,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
@@ -9664,7 +9767,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A18,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A18,Pendências!$B$2:$B$142,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9673,15 +9776,15 @@
         <v>148</v>
       </c>
       <c r="B19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A19,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A19,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A19,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A19,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A19,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A19,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
@@ -9689,7 +9792,7 @@
         <v>4</v>
       </c>
       <c r="F19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A19,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A19,Pendências!$B$2:$B$142,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9698,15 +9801,15 @@
         <v>154</v>
       </c>
       <c r="B20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A20,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A20,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A20,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A20,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A20,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A20,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E20" s="7" t="n">
@@ -9714,7 +9817,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A20,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A20,Pendências!$B$2:$B$142,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9723,15 +9826,15 @@
         <v>157</v>
       </c>
       <c r="B21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A21,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A21,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A21,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A21,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A21,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A21,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
@@ -9739,7 +9842,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A21,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A21,Pendências!$B$2:$B$142,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9748,23 +9851,23 @@
         <v>161</v>
       </c>
       <c r="B22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A22,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A22,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A22,Pendências!$J$2:$J$140,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A22,Pendências!$J$2:$J$142,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A22,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A22,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E22" s="7" t="n">
         <f aca="false">SUM(B22:D22)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A22,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A22,Pendências!$B$2:$B$142,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9773,23 +9876,23 @@
         <v>165</v>
       </c>
       <c r="B23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A23,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A23,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A23,Pendências!$J$2:$J$140,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A23,Pendências!$J$2:$J$142,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A23,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A23,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
         <f aca="false">SUM(B23:D23)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A23,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A23,Pendências!$B$2:$B$142,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9798,15 +9901,15 @@
         <v>169</v>
       </c>
       <c r="B24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A24,Pendências!$J$2:$J$140,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A24,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A24,Pendências!$J$2:$J$140,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A24,Pendências!$J$2:$J$142,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A24,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A24,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E24" s="7" t="n">
@@ -9814,24 +9917,24 @@
         <v>2</v>
       </c>
       <c r="F24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A24,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A24,Pendências!$B$2:$B$142,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A25,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A25,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A25,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A25,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A25,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A25,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
@@ -9839,58 +9942,58 @@
         <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A25,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A25,Pendências!$B$2:$B$142,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A26,Pendências!$J$2:$J$140,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A26,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A26,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A26,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A26,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A26,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E26" s="7" t="n">
         <f aca="false">SUM(B26:D26)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A26,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A26,Pendências!$B$2:$B$142,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A27,Pendências!$J$2:$J$140,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A27,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A27,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A27,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A27,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A27,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
         <f aca="false">SUM(B27:D27)</f>
+        <v>3</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A27,Pendências!$B$2:$B$142,"Alta")</f>
         <v>2</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A27,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9898,49 +10001,49 @@
         <v>188</v>
       </c>
       <c r="B28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A28,Pendências!$J$2:$J$140,"Vencida")</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A28,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A28,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A28,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A28,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A28,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E28" s="7" t="n">
         <f aca="false">SUM(B28:D28)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A28,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A28,Pendências!$B$2:$B$142,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A29,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A29,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>5</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A29,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
-      <c r="C29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A29,Pendências!$J$2:$J$140,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A29,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A29,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
         <f aca="false">SUM(B29:D29)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A29,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A29,Pendências!$B$2:$B$142,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9948,290 +10051,290 @@
         <v>202</v>
       </c>
       <c r="B30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A30,Pendências!$J$2:$J$140,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A30,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>0</v>
       </c>
       <c r="C30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A30,Pendências!$J$2:$J$140,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A30,Pendências!$J$2:$J$142,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A30,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A30,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E30" s="7" t="n">
         <f aca="false">SUM(B30:D30)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A30,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A30,Pendências!$B$2:$B$142,"Alta")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A31,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A31,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A31,Pendências!$J$2:$J$140,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A31,Pendências!$J$2:$J$142,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A31,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A31,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
         <f aca="false">SUM(B31:D31)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A31,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A31,Pendências!$B$2:$B$142,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A32,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A32,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>3</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A32,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>1</v>
       </c>
-      <c r="C32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A32,Pendências!$J$2:$J$140,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A32,Pendências!$J$2:$J$140,"Vence em breve")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A32,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <v>0</v>
       </c>
       <c r="E32" s="7" t="n">
         <f aca="false">SUM(B32:D32)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A32,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A32,Pendências!$B$2:$B$142,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A33,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A33,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A33,Pendências!$J$2:$J$140,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A33,Pendências!$J$2:$J$142,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A33,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A33,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E33" s="7" t="n">
         <f aca="false">SUM(B33:D33)</f>
+        <v>3</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A33,Pendências!$B$2:$B$142,"Alta")</f>
         <v>2</v>
-      </c>
-      <c r="F33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A33,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>1</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A34,Pendências!$J$2:$J$140,"Vencida")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A34,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A34,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A34,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A34,Pendências!$J$2:$J$140,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A34,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E34" s="7" t="n">
         <f aca="false">SUM(B34:D34)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A34,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A34,Pendências!$B$2:$B$142,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A35,Pendências!$J$2:$J$140,"Vencida")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A35,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>4</v>
       </c>
       <c r="C35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A35,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A35,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A35,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A35,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E35" s="7" t="n">
         <f aca="false">SUM(B35:D35)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A35,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A35,Pendências!$B$2:$B$142,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A36,Pendências!$J$2:$J$140,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A36,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A36,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A36,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A36,Pendências!$J$2:$J$140,"Vence em breve")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A36,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <v>0</v>
       </c>
       <c r="E36" s="7" t="n">
         <f aca="false">SUM(B36:D36)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A36,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A36,Pendências!$B$2:$B$142,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A37,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A37,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A37,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A37,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A37,Pendências!$J$2:$J$140,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A37,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E37" s="7" t="n">
         <f aca="false">SUM(B37:D37)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A37,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A37,Pendências!$B$2:$B$142,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A38,Pendências!$J$2:$J$140,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A38,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A38,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A38,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A38,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A38,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E38" s="7" t="n">
         <f aca="false">SUM(B38:D38)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A38,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A38,Pendências!$B$2:$B$142,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A39,Pendências!$J$2:$J$140,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A39,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A39,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A39,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A39,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A39,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
         <f aca="false">SUM(B39:D39)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A39,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A39,Pendências!$B$2:$B$142,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A40,Pendências!$J$2:$J$140,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A40,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A40,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A40,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A40,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A40,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E40" s="7" t="n">
         <f aca="false">SUM(B40:D40)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A40,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A40,Pendências!$B$2:$B$142,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A41,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A41,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A41,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A41,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A41,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A41,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E41" s="7" t="n">
@@ -10239,7 +10342,7 @@
         <v>3</v>
       </c>
       <c r="F41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A41,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A41,Pendências!$B$2:$B$142,"Alta")</f>
         <v>3</v>
       </c>
     </row>
@@ -10248,15 +10351,15 @@
         <v>266</v>
       </c>
       <c r="B42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A42,Pendências!$J$2:$J$140,"Vencida")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A42,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A42,Pendências!$J$2:$J$140,"Sem data")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A42,Pendências!$J$2:$J$142,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A42,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A42,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E42" s="7" t="n">
@@ -10264,8 +10367,8 @@
         <v>3</v>
       </c>
       <c r="F42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A42,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A42,Pendências!$B$2:$B$142,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10273,15 +10376,15 @@
         <v>270</v>
       </c>
       <c r="B43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A43,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A43,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>1</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A43,Pendências!$J$2:$J$142,"Sem data")</f>
         <v>2</v>
       </c>
-      <c r="C43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A43,Pendências!$J$2:$J$140,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A43,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A43,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
@@ -10289,8 +10392,8 @@
         <v>3</v>
       </c>
       <c r="F43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A43,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A43,Pendências!$B$2:$B$142,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10298,128 +10401,153 @@
         <v>274</v>
       </c>
       <c r="B44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A44,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A44,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A44,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A44,Pendências!$J$2:$J$142,"Sem data")</f>
+        <v>1</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A44,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
-      </c>
-      <c r="D44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A44,Pendências!$J$2:$J$140,"Vence em breve")</f>
-        <v>1</v>
       </c>
       <c r="E44" s="7" t="n">
         <f aca="false">SUM(B44:D44)</f>
         <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A44,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A44,Pendências!$B$2:$B$142,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A45,Pendências!$J$2:$J$140,"Vencida")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A45,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A45,Pendências!$J$2:$J$140,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A45,Pendências!$J$2:$J$142,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A45,Pendências!$J$2:$J$140,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A45,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E45" s="7" t="n">
         <f aca="false">SUM(B45:D45)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A45,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A45,Pendências!$B$2:$B$142,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A46,Pendências!$J$2:$J$140,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A46,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>4</v>
       </c>
       <c r="C46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A46,Pendências!$J$2:$J$140,"Sem data")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A46,Pendências!$J$2:$J$142,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A46,Pendências!$J$2:$J$140,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A46,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E46" s="7" t="n">
         <f aca="false">SUM(B46:D46)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A46,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A46,Pendências!$B$2:$B$142,"Alta")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A47,Pendências!$J$2:$J$140,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A47,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A47,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A47,Pendências!$J$2:$J$142,"Sem data")</f>
+        <v>4</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A47,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>0</v>
-      </c>
-      <c r="D47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A47,Pendências!$J$2:$J$140,"Vence em breve")</f>
-        <v>1</v>
       </c>
       <c r="E47" s="7" t="n">
         <f aca="false">SUM(B47:D47)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A47,Pendências!$B$2:$B$140,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A47,Pendências!$B$2:$B$142,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B48" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A48,Pendências!$J$2:$J$140,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A48,Pendências!$J$2:$J$142,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C48" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A48,Pendências!$J$2:$J$140,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A48,Pendências!$J$2:$J$142,"Sem data")</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A48,Pendências!$J$2:$J$142,"Vence em breve")</f>
         <v>1</v>
-      </c>
-      <c r="D48" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A48,Pendências!$J$2:$J$140,"Vence em breve")</f>
-        <v>0</v>
       </c>
       <c r="E48" s="7" t="n">
         <f aca="false">SUM(B48:D48)</f>
         <v>3</v>
       </c>
       <c r="F48" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$140,$A48,Pendências!$B$2:$B$140,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A48,Pendências!$B$2:$B$142,"Alta")</f>
         <v>2</v>
       </c>
     </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="B49" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A49,Pendências!$J$2:$J$142,"Vencida")</f>
+        <v>2</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A49,Pendências!$J$2:$J$142,"Sem data")</f>
+        <v>1</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A49,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <f aca="false">SUM(B49:D49)</f>
+        <v>3</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A49,Pendências!$B$2:$B$142,"Alta")</f>
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F48"/>
+  <autoFilter ref="A1:F49"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -10436,7 +10564,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -10464,189 +10592,178 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>340</v>
+        <v>107</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>107</v>
+        <v>318</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="s">
-        <v>346</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>

--- a/pendencias-condicionantes-2026-10-23.xlsx
+++ b/pendencias-condicionantes-2026-10-23.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Licenças que faltam" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Pendências!$A$1:$R$142</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Por empresa'!$A$1:$F$49</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Pendências!$A$1:$R$145</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Por empresa'!$A$1:$F$50</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="350">
   <si>
     <t xml:space="preserve">Condicionantes ambientais – pendências</t>
   </si>
@@ -500,12 +500,27 @@
     <t xml:space="preserve">2021-170886/TEC/RLO-1166</t>
   </si>
   <si>
+    <t xml:space="preserve">Francisco Glauber Sousa Bessa (Posto Bessa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">São Miguel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">032.078.574-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-191538/TEC/LO-0048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documento na pasta: Certificado da empresa Posto Bessa Ltda emitido em 10/06/2026, válido por 3 meses (o único da pasta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emitir novo certificado no site da ANP (vale 3 meses) e protocolar no Comunic@.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Francisco Valentim Goncalves</t>
   </si>
   <si>
-    <t xml:space="preserve">São Miguel</t>
-  </si>
-  <si>
     <t xml:space="preserve">07.951.495/0001-83</t>
   </si>
   <si>
@@ -626,9 +641,6 @@
     <t xml:space="preserve">Documento na pasta: Certificado emitido em 02/12/2025, válido por 3 meses (o mais recente da pasta)</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitir novo certificado no site da ANP (vale 3 meses) e protocolar no Comunic@.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Documento na pasta: AVCB emitido em 10/08/2023</t>
   </si>
   <si>
@@ -1020,15 +1032,6 @@
   </si>
   <si>
     <t xml:space="preserve">Pasta 51 tem TOG e ANP; falta a licença</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Posto Bessa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.327.357/0001-42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pasta 53 sem licença</t>
   </si>
   <si>
     <t xml:space="preserve">Posto União Nunes (Patu)</t>
@@ -1782,15 +1785,15 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A6,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A6,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>12</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A6,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A6,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A6,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A6,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
@@ -1803,15 +1806,15 @@
         <v>10</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A7,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A7,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>8</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A7,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A7,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A7,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A7,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>4</v>
       </c>
       <c r="E7" s="7" t="n">
@@ -1824,15 +1827,15 @@
         <v>11</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A8,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A8,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>7</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A8,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A8,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A8,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A8,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
@@ -1845,15 +1848,15 @@
         <v>12</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A9,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A9,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>5</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A9,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A9,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A9,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A9,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
@@ -1866,20 +1869,20 @@
         <v>13</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A10,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A10,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>2</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A10,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>1</v>
       </c>
-      <c r="C10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A10,Pendências!$J$2:$J$142,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A10,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A10,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E10" s="7" t="n">
         <f aca="false">SUM(B10:D10)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1887,20 +1890,20 @@
         <v>14</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A11,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A11,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>24</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A11,Pendências!$J$2:$J$142,"Sem data")</f>
-        <v>9</v>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A11,Pendências!$J$2:$J$145,"Sem data")</f>
+        <v>10</v>
       </c>
       <c r="D11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A11,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A11,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>4</v>
       </c>
       <c r="E11" s="7" t="n">
         <f aca="false">SUM(B11:D11)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1908,20 +1911,20 @@
         <v>15</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A12,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A12,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>38</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A12,Pendências!$J$2:$J$142,"Sem data")</f>
-        <v>8</v>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A12,Pendências!$J$2:$J$145,"Sem data")</f>
+        <v>9</v>
       </c>
       <c r="D12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A12,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A12,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
         <f aca="false">SUM(B12:D12)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1929,15 +1932,15 @@
         <v>16</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A13,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A13,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A13,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A13,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>4</v>
       </c>
       <c r="D13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A13,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A13,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>3</v>
       </c>
       <c r="E13" s="7" t="n">
@@ -1950,15 +1953,15 @@
         <v>17</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A14,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A14,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A14,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A14,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A14,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A14,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
@@ -1971,15 +1974,15 @@
         <v>18</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A15,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A15,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A15,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A15,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>4</v>
       </c>
       <c r="D15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A15,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A15,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
@@ -1992,15 +1995,15 @@
         <v>19</v>
       </c>
       <c r="B16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A16,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A16,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A16,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A16,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>3</v>
       </c>
       <c r="D16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$142,$A16,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A16,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
@@ -2014,11 +2017,11 @@
       </c>
       <c r="B17" s="8" t="n">
         <f aca="false">SUM(B6:B16)</f>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C17" s="8" t="n">
         <f aca="false">SUM(C6:C16)</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D17" s="8" t="n">
         <f aca="false">SUM(D6:D16)</f>
@@ -2026,7 +2029,7 @@
       </c>
       <c r="E17" s="8" t="n">
         <f aca="false">SUM(E6:E16)</f>
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2039,8 +2042,8 @@
         <v>22</v>
       </c>
       <c r="B20" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$142,A20)</f>
-        <v>141</v>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$145,A20)</f>
+        <v>144</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2048,7 +2051,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$142,A21)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$145,A21)</f>
         <v>0</v>
       </c>
     </row>
@@ -2057,7 +2060,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$142,A22)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$145,A22)</f>
         <v>0</v>
       </c>
     </row>
@@ -2066,7 +2069,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$142,A23)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$145,A23)</f>
         <v>0</v>
       </c>
     </row>
@@ -2075,7 +2078,7 @@
         <v>26</v>
       </c>
       <c r="B24" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$142,A24)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$145,A24)</f>
         <v>0</v>
       </c>
     </row>
@@ -2100,7 +2103,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R142"/>
+  <dimension ref="A1:R145"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -5041,12 +5044,12 @@
       <c r="Q58" s="15"/>
       <c r="R58" s="14"/>
     </row>
-    <row r="59" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>157</v>
@@ -5061,29 +5064,29 @@
         <v>160</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>46374</v>
+        <v>47190</v>
       </c>
       <c r="H59" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I59" s="10" t="n">
         <v>9</v>
-      </c>
-      <c r="I59" s="10" t="n">
-        <v>20</v>
       </c>
       <c r="J59" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>46254</v>
+        <v>46275</v>
       </c>
       <c r="L59" s="13" t="n">
         <f aca="false">IF(K59="","",K59-Resumo!$B$3)</f>
-        <v>-64</v>
+        <v>-43</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>98</v>
+        <v>161</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>99</v>
+        <v>162</v>
       </c>
       <c r="O59" s="14"/>
       <c r="P59" s="14" t="s">
@@ -5112,7 +5115,7 @@
         <v>160</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>46374</v>
+        <v>47190</v>
       </c>
       <c r="H60" s="10" t="s">
         <v>14</v>
@@ -5146,7 +5149,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>157</v>
@@ -5161,26 +5164,24 @@
         <v>160</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>46374</v>
+        <v>47190</v>
       </c>
       <c r="H61" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K61" s="12" t="n">
-        <v>46282</v>
-      </c>
-      <c r="L61" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K61" s="12"/>
+      <c r="L61" s="13" t="str">
         <f aca="false">IF(K61="","",K61-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v/>
       </c>
       <c r="M61" s="10" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="N61" s="10" t="s">
         <v>58</v>
@@ -5192,47 +5193,49 @@
       <c r="Q61" s="15"/>
       <c r="R61" s="14"/>
     </row>
-    <row r="62" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>47547</v>
+        <v>46374</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I62" s="10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K62" s="12"/>
-      <c r="L62" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K62" s="12" t="n">
+        <v>46254</v>
+      </c>
+      <c r="L62" s="13" t="n">
         <f aca="false">IF(K62="","",K62-Resumo!$B$3)</f>
-        <v/>
+        <v>-64</v>
       </c>
       <c r="M62" s="10" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="N62" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O62" s="14"/>
       <c r="P62" s="14" t="s">
@@ -5241,49 +5244,47 @@
       <c r="Q62" s="15"/>
       <c r="R62" s="14"/>
     </row>
-    <row r="63" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>47547</v>
+        <v>46374</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I63" s="10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K63" s="12" t="n">
-        <v>46281</v>
-      </c>
-      <c r="L63" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K63" s="12"/>
+      <c r="L63" s="13" t="str">
         <f aca="false">IF(K63="","",K63-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v/>
       </c>
       <c r="M63" s="10" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O63" s="14"/>
       <c r="P63" s="14" t="s">
@@ -5300,24 +5301,26 @@
         <v>55</v>
       </c>
       <c r="C64" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F64" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="D64" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="F64" s="10" t="s">
-        <v>168</v>
-      </c>
       <c r="G64" s="12" t="n">
-        <v>46911</v>
+        <v>46374</v>
       </c>
       <c r="H64" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I64" s="10"/>
+      <c r="I64" s="10" t="n">
+        <v>15</v>
+      </c>
       <c r="J64" s="10" t="s">
         <v>56</v>
       </c>
@@ -5349,24 +5352,26 @@
         <v>45</v>
       </c>
       <c r="C65" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F65" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="D65" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F65" s="10" t="s">
-        <v>172</v>
-      </c>
       <c r="G65" s="12" t="n">
-        <v>46875</v>
+        <v>47547</v>
       </c>
       <c r="H65" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I65" s="10"/>
+      <c r="I65" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J65" s="10" t="s">
         <v>6</v>
       </c>
@@ -5396,36 +5401,38 @@
         <v>55</v>
       </c>
       <c r="C66" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F66" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="D66" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F66" s="10" t="s">
-        <v>172</v>
-      </c>
       <c r="G66" s="12" t="n">
-        <v>46875</v>
+        <v>47547</v>
       </c>
       <c r="H66" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I66" s="10"/>
+      <c r="I66" s="10" t="n">
+        <v>16</v>
+      </c>
       <c r="J66" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="L66" s="13" t="n">
         <f aca="false">IF(K66="","",K66-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="M66" s="10" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="N66" s="10" t="s">
         <v>58</v>
@@ -5437,7 +5444,7 @@
       <c r="Q66" s="15"/>
       <c r="R66" s="14"/>
     </row>
-    <row r="67" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="n">
         <v>66</v>
       </c>
@@ -5445,41 +5452,39 @@
         <v>55</v>
       </c>
       <c r="C67" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F67" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="D67" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="E67" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F67" s="10" t="s">
-        <v>176</v>
-      </c>
       <c r="G67" s="12" t="n">
-        <v>47952</v>
+        <v>46911</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I67" s="10" t="n">
-        <v>5</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I67" s="10"/>
       <c r="J67" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>45898</v>
+        <v>46282</v>
       </c>
       <c r="L67" s="13" t="n">
         <f aca="false">IF(K67="","",K67-Resumo!$B$3)</f>
-        <v>-420</v>
+        <v>-36</v>
       </c>
       <c r="M67" s="10" t="s">
-        <v>177</v>
+        <v>74</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O67" s="14"/>
       <c r="P67" s="14" t="s">
@@ -5488,49 +5493,45 @@
       <c r="Q67" s="15"/>
       <c r="R67" s="14"/>
     </row>
-    <row r="68" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="n">
         <v>67</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>47952</v>
+        <v>46875</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I68" s="10" t="n">
-        <v>17</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I68" s="10"/>
       <c r="J68" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K68" s="12" t="n">
-        <v>46281</v>
-      </c>
-      <c r="L68" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K68" s="12"/>
+      <c r="L68" s="13" t="str">
         <f aca="false">IF(K68="","",K68-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v/>
       </c>
       <c r="M68" s="10" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="N68" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O68" s="14"/>
       <c r="P68" s="14" t="s">
@@ -5539,7 +5540,7 @@
       <c r="Q68" s="15"/>
       <c r="R68" s="14"/>
     </row>
-    <row r="69" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="n">
         <v>68</v>
       </c>
@@ -5547,41 +5548,39 @@
         <v>55</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>46990</v>
+        <v>46875</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I69" s="10" t="n">
-        <v>5</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I69" s="10"/>
       <c r="J69" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>46163</v>
+        <v>46282</v>
       </c>
       <c r="L69" s="13" t="n">
         <f aca="false">IF(K69="","",K69-Resumo!$B$3)</f>
-        <v>-155</v>
+        <v>-36</v>
       </c>
       <c r="M69" s="10" t="s">
-        <v>182</v>
+        <v>74</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O69" s="14"/>
       <c r="P69" s="14" t="s">
@@ -5590,7 +5589,7 @@
       <c r="Q69" s="15"/>
       <c r="R69" s="14"/>
     </row>
-    <row r="70" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="n">
         <v>69</v>
       </c>
@@ -5610,29 +5609,29 @@
         <v>181</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>46990</v>
+        <v>47952</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I70" s="10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J70" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>46281</v>
+        <v>45898</v>
       </c>
       <c r="L70" s="13" t="n">
         <f aca="false">IF(K70="","",K70-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-420</v>
       </c>
       <c r="M70" s="10" t="s">
-        <v>57</v>
+        <v>182</v>
       </c>
       <c r="N70" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O70" s="14"/>
       <c r="P70" s="14" t="s">
@@ -5646,42 +5645,44 @@
         <v>70</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>47087</v>
+        <v>47952</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I71" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="I71" s="10" t="n">
+        <v>17</v>
+      </c>
       <c r="J71" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="L71" s="13" t="n">
         <f aca="false">IF(K71="","",K71-Resumo!$B$3)</f>
-        <v>-44</v>
+        <v>-37</v>
       </c>
       <c r="M71" s="10" t="s">
-        <v>186</v>
+        <v>57</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O71" s="14"/>
       <c r="P71" s="14" t="s">
@@ -5701,16 +5702,16 @@
         <v>183</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>95</v>
+        <v>184</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>47087</v>
+        <v>46990</v>
       </c>
       <c r="H72" s="10" t="s">
         <v>14</v>
@@ -5722,11 +5723,11 @@
         <v>56</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>45997</v>
+        <v>46163</v>
       </c>
       <c r="L72" s="13" t="n">
         <f aca="false">IF(K72="","",K72-Resumo!$B$3)</f>
-        <v>-321</v>
+        <v>-155</v>
       </c>
       <c r="M72" s="10" t="s">
         <v>187</v>
@@ -5752,16 +5753,16 @@
         <v>183</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>95</v>
+        <v>184</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>47087</v>
+        <v>46990</v>
       </c>
       <c r="H73" s="10" t="s">
         <v>15</v>
@@ -5812,7 +5813,7 @@
         <v>190</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>47854</v>
+        <v>47087</v>
       </c>
       <c r="H74" s="10" t="s">
         <v>10</v>
@@ -5822,11 +5823,11 @@
         <v>56</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>46316</v>
+        <v>46274</v>
       </c>
       <c r="L74" s="13" t="n">
         <f aca="false">IF(K74="","",K74-Resumo!$B$3)</f>
-        <v>-2</v>
+        <v>-44</v>
       </c>
       <c r="M74" s="10" t="s">
         <v>191</v>
@@ -5841,7 +5842,7 @@
       <c r="Q74" s="15"/>
       <c r="R74" s="14"/>
     </row>
-    <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="n">
         <v>74</v>
       </c>
@@ -5861,29 +5862,29 @@
         <v>190</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>47854</v>
+        <v>47087</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I75" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J75" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>46281</v>
+        <v>45997</v>
       </c>
       <c r="L75" s="13" t="n">
         <f aca="false">IF(K75="","",K75-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-321</v>
       </c>
       <c r="M75" s="10" t="s">
-        <v>57</v>
+        <v>192</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O75" s="14"/>
       <c r="P75" s="14" t="s">
@@ -5900,41 +5901,41 @@
         <v>55</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>193</v>
+        <v>95</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>46031</v>
+        <v>47087</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I76" s="10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J76" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>45911</v>
+        <v>46281</v>
       </c>
       <c r="L76" s="13" t="n">
         <f aca="false">IF(K76="","",K76-Resumo!$B$3)</f>
-        <v>-407</v>
+        <v>-37</v>
       </c>
       <c r="M76" s="10" t="s">
-        <v>196</v>
+        <v>57</v>
       </c>
       <c r="N76" s="10" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="O76" s="14"/>
       <c r="P76" s="14" t="s">
@@ -5943,7 +5944,7 @@
       <c r="Q76" s="15"/>
       <c r="R76" s="14"/>
     </row>
-    <row r="77" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="n">
         <v>76</v>
       </c>
@@ -5951,10 +5952,10 @@
         <v>80</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>193</v>
+        <v>95</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>194</v>
@@ -5963,7 +5964,7 @@
         <v>195</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>46031</v>
+        <v>47854</v>
       </c>
       <c r="H77" s="10" t="s">
         <v>10</v>
@@ -5973,14 +5974,14 @@
         <v>56</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>45659</v>
+        <v>46316</v>
       </c>
       <c r="L77" s="13" t="n">
         <f aca="false">IF(K77="","",K77-Resumo!$B$3)</f>
-        <v>-659</v>
+        <v>-2</v>
       </c>
       <c r="M77" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N77" s="10" t="s">
         <v>52</v>
@@ -5997,13 +5998,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>193</v>
+        <v>95</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>194</v>
@@ -6012,29 +6013,29 @@
         <v>195</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>46031</v>
+        <v>47854</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I78" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J78" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>46083</v>
+        <v>46281</v>
       </c>
       <c r="L78" s="13" t="n">
         <f aca="false">IF(K78="","",K78-Resumo!$B$3)</f>
-        <v>-235</v>
+        <v>-37</v>
       </c>
       <c r="M78" s="10" t="s">
-        <v>198</v>
+        <v>57</v>
       </c>
       <c r="N78" s="10" t="s">
-        <v>199</v>
+        <v>58</v>
       </c>
       <c r="O78" s="14"/>
       <c r="P78" s="14" t="s">
@@ -6043,7 +6044,7 @@
       <c r="Q78" s="15"/>
       <c r="R78" s="14"/>
     </row>
-    <row r="79" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="n">
         <v>78</v>
       </c>
@@ -6051,41 +6052,41 @@
         <v>55</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G79" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I79" s="10" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J79" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>45514</v>
+        <v>45911</v>
       </c>
       <c r="L79" s="13" t="n">
         <f aca="false">IF(K79="","",K79-Resumo!$B$3)</f>
-        <v>-804</v>
+        <v>-407</v>
       </c>
       <c r="M79" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O79" s="14"/>
       <c r="P79" s="14" t="s">
@@ -6094,49 +6095,47 @@
       <c r="Q79" s="15"/>
       <c r="R79" s="14"/>
     </row>
-    <row r="80" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="10" t="n">
         <v>79</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G80" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I80" s="10" t="n">
-        <v>15</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I80" s="10"/>
       <c r="J80" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>45356</v>
+        <v>45659</v>
       </c>
       <c r="L80" s="13" t="n">
         <f aca="false">IF(K80="","",K80-Resumo!$B$3)</f>
-        <v>-962</v>
+        <v>-659</v>
       </c>
       <c r="M80" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N80" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O80" s="14"/>
       <c r="P80" s="14" t="s">
@@ -6150,42 +6149,44 @@
         <v>80</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D81" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>46031</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I81" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="J81" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K81" s="12" t="n">
+        <v>46083</v>
+      </c>
+      <c r="L81" s="13" t="n">
+        <f aca="false">IF(K81="","",K81-Resumo!$B$3)</f>
+        <v>-235</v>
+      </c>
+      <c r="M81" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="E81" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F81" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="G81" s="12" t="n">
-        <v>46729</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I81" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="J81" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K81" s="12"/>
-      <c r="L81" s="13" t="str">
-        <f aca="false">IF(K81="","",K81-Resumo!$B$3)</f>
-        <v/>
-      </c>
-      <c r="M81" s="10" t="s">
-        <v>79</v>
-      </c>
       <c r="N81" s="10" t="s">
-        <v>58</v>
+        <v>162</v>
       </c>
       <c r="O81" s="14"/>
       <c r="P81" s="14" t="s">
@@ -6194,47 +6195,49 @@
       <c r="Q81" s="15"/>
       <c r="R81" s="14"/>
     </row>
-    <row r="82" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>65</v>
+        <v>198</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>48171</v>
+        <v>46031</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I82" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I82" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J82" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>46272</v>
+        <v>45514</v>
       </c>
       <c r="L82" s="13" t="n">
         <f aca="false">IF(K82="","",K82-Resumo!$B$3)</f>
-        <v>-46</v>
+        <v>-804</v>
       </c>
       <c r="M82" s="10" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="N82" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O82" s="14"/>
       <c r="P82" s="14" t="s">
@@ -6243,7 +6246,7 @@
       <c r="Q82" s="15"/>
       <c r="R82" s="14"/>
     </row>
-    <row r="83" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="n">
         <v>82</v>
       </c>
@@ -6251,41 +6254,41 @@
         <v>55</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>65</v>
+        <v>198</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>48171</v>
+        <v>46031</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I83" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J83" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>46309</v>
+        <v>45356</v>
       </c>
       <c r="L83" s="13" t="n">
         <f aca="false">IF(K83="","",K83-Resumo!$B$3)</f>
-        <v>-9</v>
+        <v>-962</v>
       </c>
       <c r="M83" s="10" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O83" s="14"/>
       <c r="P83" s="14" t="s">
@@ -6299,22 +6302,22 @@
         <v>83</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C84" s="10" t="s">
         <v>206</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>65</v>
+        <v>207</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>48171</v>
+        <v>46729</v>
       </c>
       <c r="H84" s="10" t="s">
         <v>15</v>
@@ -6323,17 +6326,15 @@
         <v>15</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K84" s="12" t="n">
-        <v>46281</v>
-      </c>
-      <c r="L84" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K84" s="12"/>
+      <c r="L84" s="13" t="str">
         <f aca="false">IF(K84="","",K84-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v/>
       </c>
       <c r="M84" s="10" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="N84" s="10" t="s">
         <v>58</v>
@@ -6350,44 +6351,42 @@
         <v>84</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C85" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E85" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="D85" s="10" t="s">
+      <c r="F85" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="E85" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F85" s="10" t="s">
-        <v>214</v>
-      </c>
       <c r="G85" s="12" t="n">
-        <v>46288</v>
+        <v>48171</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="I85" s="10" t="n">
-        <v>18</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I85" s="10"/>
       <c r="J85" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>46168</v>
+        <v>46272</v>
       </c>
       <c r="L85" s="13" t="n">
         <f aca="false">IF(K85="","",K85-Resumo!$B$3)</f>
-        <v>-150</v>
+        <v>-46</v>
       </c>
       <c r="M85" s="10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="O85" s="14"/>
       <c r="P85" s="14" t="s">
@@ -6396,49 +6395,49 @@
       <c r="Q85" s="15"/>
       <c r="R85" s="14"/>
     </row>
-    <row r="86" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="n">
         <v>85</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C86" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E86" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="D86" s="10" t="s">
+      <c r="F86" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="E86" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F86" s="10" t="s">
-        <v>216</v>
-      </c>
       <c r="G86" s="12" t="n">
-        <v>48005</v>
+        <v>48171</v>
       </c>
       <c r="H86" s="10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I86" s="10" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J86" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>46163</v>
+        <v>46309</v>
       </c>
       <c r="L86" s="13" t="n">
         <f aca="false">IF(K86="","",K86-Resumo!$B$3)</f>
-        <v>-155</v>
+        <v>-9</v>
       </c>
       <c r="M86" s="10" t="s">
-        <v>85</v>
+        <v>214</v>
       </c>
       <c r="N86" s="10" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="O86" s="14"/>
       <c r="P86" s="14" t="s">
@@ -6447,47 +6446,49 @@
       <c r="Q86" s="15"/>
       <c r="R86" s="14"/>
     </row>
-    <row r="87" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="n">
         <v>86</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C87" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E87" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="D87" s="10" t="s">
+      <c r="F87" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="E87" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F87" s="10" t="s">
-        <v>214</v>
-      </c>
       <c r="G87" s="12" t="n">
-        <v>46288</v>
+        <v>48171</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I87" s="10" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K87" s="12"/>
-      <c r="L87" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K87" s="12" t="n">
+        <v>46281</v>
+      </c>
+      <c r="L87" s="13" t="n">
         <f aca="false">IF(K87="","",K87-Resumo!$B$3)</f>
-        <v/>
+        <v>-37</v>
       </c>
       <c r="M87" s="10" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O87" s="14"/>
       <c r="P87" s="14" t="s">
@@ -6504,41 +6505,41 @@
         <v>55</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F88" s="10" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G88" s="12" t="n">
         <v>46288</v>
       </c>
       <c r="H88" s="10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I88" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J88" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>46283</v>
+        <v>46168</v>
       </c>
       <c r="L88" s="13" t="n">
         <f aca="false">IF(K88="","",K88-Resumo!$B$3)</f>
-        <v>-35</v>
+        <v>-150</v>
       </c>
       <c r="M88" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N88" s="10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O88" s="14"/>
       <c r="P88" s="14" t="s">
@@ -6547,49 +6548,49 @@
       <c r="Q88" s="15"/>
       <c r="R88" s="14"/>
     </row>
-    <row r="89" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E89" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="F89" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="F89" s="10" t="s">
-        <v>221</v>
-      </c>
       <c r="G89" s="12" t="n">
-        <v>46798</v>
+        <v>48005</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I89" s="10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>46323</v>
+        <v>46163</v>
       </c>
       <c r="L89" s="13" t="n">
         <f aca="false">IF(K89="","",K89-Resumo!$B$3)</f>
-        <v>5</v>
+        <v>-155</v>
       </c>
       <c r="M89" s="10" t="s">
-        <v>222</v>
+        <v>85</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="O89" s="14"/>
       <c r="P89" s="14" t="s">
@@ -6598,49 +6599,47 @@
       <c r="Q89" s="15"/>
       <c r="R89" s="14"/>
     </row>
-    <row r="90" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="10" t="n">
         <v>89</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C90" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="F90" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="D90" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="F90" s="10" t="s">
-        <v>221</v>
-      </c>
       <c r="G90" s="12" t="n">
-        <v>46798</v>
+        <v>46288</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I90" s="10" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J90" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K90" s="12" t="n">
-        <v>46281</v>
-      </c>
-      <c r="L90" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K90" s="12"/>
+      <c r="L90" s="13" t="str">
         <f aca="false">IF(K90="","",K90-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v/>
       </c>
       <c r="M90" s="10" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="N90" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O90" s="14"/>
       <c r="P90" s="14" t="s">
@@ -6654,42 +6653,44 @@
         <v>90</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C91" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="F91" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="D91" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="E91" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="F91" s="10" t="s">
+      <c r="G91" s="12" t="n">
+        <v>46288</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I91" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="J91" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K91" s="12" t="n">
+        <v>46283</v>
+      </c>
+      <c r="L91" s="13" t="n">
+        <f aca="false">IF(K91="","",K91-Resumo!$B$3)</f>
+        <v>-35</v>
+      </c>
+      <c r="M91" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="G91" s="12" t="n">
-        <v>46798</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="I91" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="J91" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K91" s="12"/>
-      <c r="L91" s="13" t="str">
-        <f aca="false">IF(K91="","",K91-Resumo!$B$3)</f>
-        <v/>
-      </c>
-      <c r="M91" s="10" t="s">
-        <v>79</v>
-      </c>
       <c r="N91" s="10" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="O91" s="14"/>
       <c r="P91" s="14" t="s">
@@ -6698,7 +6699,7 @@
       <c r="Q91" s="15"/>
       <c r="R91" s="14"/>
     </row>
-    <row r="92" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="n">
         <v>91</v>
       </c>
@@ -6706,41 +6707,41 @@
         <v>55</v>
       </c>
       <c r="C92" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="D92" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="D92" s="10" t="s">
+      <c r="E92" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="E92" s="10" t="s">
+      <c r="F92" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="F92" s="10" t="s">
-        <v>226</v>
-      </c>
       <c r="G92" s="12" t="n">
-        <v>47004</v>
+        <v>46798</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I92" s="10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J92" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K92" s="12" t="n">
-        <v>46280</v>
+        <v>46323</v>
       </c>
       <c r="L92" s="13" t="n">
         <f aca="false">IF(K92="","",K92-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>5</v>
       </c>
       <c r="M92" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N92" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O92" s="14"/>
       <c r="P92" s="14" t="s">
@@ -6754,44 +6755,44 @@
         <v>92</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C93" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="D93" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="D93" s="10" t="s">
+      <c r="E93" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="E93" s="10" t="s">
+      <c r="F93" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="F93" s="10" t="s">
-        <v>226</v>
-      </c>
       <c r="G93" s="12" t="n">
-        <v>47004</v>
+        <v>46798</v>
       </c>
       <c r="H93" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I93" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="I93" s="10" t="n">
-        <v>15</v>
-      </c>
       <c r="J93" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>46344</v>
+        <v>46281</v>
       </c>
       <c r="L93" s="13" t="n">
         <f aca="false">IF(K93="","",K93-Resumo!$B$3)</f>
-        <v>26</v>
+        <v>-37</v>
       </c>
       <c r="M93" s="10" t="s">
-        <v>228</v>
+        <v>57</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="O93" s="14"/>
       <c r="P93" s="14" t="s">
@@ -6805,44 +6806,42 @@
         <v>93</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>47</v>
+        <v>223</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>46046</v>
+        <v>46798</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I94" s="10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K94" s="12" t="n">
-        <v>45926</v>
-      </c>
-      <c r="L94" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K94" s="12"/>
+      <c r="L94" s="13" t="str">
         <f aca="false">IF(K94="","",K94-Resumo!$B$3)</f>
-        <v>-392</v>
+        <v/>
       </c>
       <c r="M94" s="10" t="s">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="N94" s="10" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="O94" s="14"/>
       <c r="P94" s="14" t="s">
@@ -6856,42 +6855,44 @@
         <v>94</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C95" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="E95" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="D95" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E95" s="10" t="s">
+      <c r="F95" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="F95" s="10" t="s">
-        <v>231</v>
-      </c>
       <c r="G95" s="12" t="n">
-        <v>46046</v>
+        <v>47004</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I95" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="I95" s="10" t="n">
+        <v>16</v>
+      </c>
       <c r="J95" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>45823</v>
+        <v>46280</v>
       </c>
       <c r="L95" s="13" t="n">
         <f aca="false">IF(K95="","",K95-Resumo!$B$3)</f>
-        <v>-495</v>
+        <v>-38</v>
       </c>
       <c r="M95" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O95" s="14"/>
       <c r="P95" s="14" t="s">
@@ -6900,49 +6901,49 @@
       <c r="Q95" s="15"/>
       <c r="R95" s="14"/>
     </row>
-    <row r="96" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="n">
         <v>95</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C96" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="E96" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="D96" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E96" s="10" t="s">
+      <c r="F96" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="F96" s="10" t="s">
-        <v>231</v>
-      </c>
       <c r="G96" s="12" t="n">
-        <v>46046</v>
+        <v>47004</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I96" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J96" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K96" s="12" t="n">
-        <v>46058</v>
+        <v>46344</v>
       </c>
       <c r="L96" s="13" t="n">
         <f aca="false">IF(K96="","",K96-Resumo!$B$3)</f>
-        <v>-260</v>
+        <v>26</v>
       </c>
       <c r="M96" s="10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="N96" s="10" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="O96" s="14"/>
       <c r="P96" s="14" t="s">
@@ -6959,41 +6960,41 @@
         <v>55</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>47</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="G97" s="12" t="n">
         <v>46046</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I97" s="10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J97" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>46281</v>
+        <v>45926</v>
       </c>
       <c r="L97" s="13" t="n">
         <f aca="false">IF(K97="","",K97-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-392</v>
       </c>
       <c r="M97" s="10" t="s">
-        <v>57</v>
+        <v>236</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O97" s="14"/>
       <c r="P97" s="14" t="s">
@@ -7007,44 +7008,42 @@
         <v>97</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C98" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D98" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="F98" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="D98" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="F98" s="10" t="s">
-        <v>237</v>
-      </c>
       <c r="G98" s="12" t="n">
-        <v>46970</v>
+        <v>46046</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I98" s="10" t="n">
-        <v>15</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I98" s="10"/>
       <c r="J98" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K98" s="12" t="n">
-        <v>46281</v>
+        <v>45823</v>
       </c>
       <c r="L98" s="13" t="n">
         <f aca="false">IF(K98="","",K98-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-495</v>
       </c>
       <c r="M98" s="10" t="s">
-        <v>57</v>
+        <v>237</v>
       </c>
       <c r="N98" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O98" s="14"/>
       <c r="P98" s="14" t="s">
@@ -7053,7 +7052,7 @@
       <c r="Q98" s="15"/>
       <c r="R98" s="14"/>
     </row>
-    <row r="99" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="n">
         <v>98</v>
       </c>
@@ -7061,39 +7060,41 @@
         <v>55</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>46505</v>
+        <v>46046</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I99" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I99" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J99" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>46319</v>
+        <v>46058</v>
       </c>
       <c r="L99" s="13" t="n">
         <f aca="false">IF(K99="","",K99-Resumo!$B$3)</f>
-        <v>1</v>
+        <v>-260</v>
       </c>
       <c r="M99" s="10" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O99" s="14"/>
       <c r="P99" s="14" t="s">
@@ -7102,7 +7103,7 @@
       <c r="Q99" s="15"/>
       <c r="R99" s="14"/>
     </row>
-    <row r="100" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="10" t="n">
         <v>99</v>
       </c>
@@ -7110,41 +7111,41 @@
         <v>55</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>46505</v>
+        <v>46046</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I100" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J100" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K100" s="12" t="n">
-        <v>45891</v>
+        <v>46281</v>
       </c>
       <c r="L100" s="13" t="n">
         <f aca="false">IF(K100="","",K100-Resumo!$B$3)</f>
-        <v>-427</v>
+        <v>-37</v>
       </c>
       <c r="M100" s="10" t="s">
-        <v>242</v>
+        <v>57</v>
       </c>
       <c r="N100" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O100" s="14"/>
       <c r="P100" s="14" t="s">
@@ -7161,19 +7162,19 @@
         <v>55</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>46505</v>
+        <v>46970</v>
       </c>
       <c r="H101" s="10" t="s">
         <v>15</v>
@@ -7185,14 +7186,14 @@
         <v>56</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="L101" s="13" t="n">
         <f aca="false">IF(K101="","",K101-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="M101" s="10" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="N101" s="10" t="s">
         <v>58</v>
@@ -7212,39 +7213,39 @@
         <v>55</v>
       </c>
       <c r="C102" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="D102" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E102" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="D102" s="10" t="s">
+      <c r="F102" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="E102" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="F102" s="10" t="s">
-        <v>246</v>
-      </c>
       <c r="G102" s="12" t="n">
-        <v>46346</v>
+        <v>46505</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I102" s="10"/>
       <c r="J102" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K102" s="12" t="n">
-        <v>46226</v>
+        <v>46319</v>
       </c>
       <c r="L102" s="13" t="n">
         <f aca="false">IF(K102="","",K102-Resumo!$B$3)</f>
-        <v>-92</v>
+        <v>1</v>
       </c>
       <c r="M102" s="10" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="N102" s="10" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="O102" s="14"/>
       <c r="P102" s="14" t="s">
@@ -7253,7 +7254,7 @@
       <c r="Q102" s="15"/>
       <c r="R102" s="14"/>
     </row>
-    <row r="103" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="10" t="n">
         <v>102</v>
       </c>
@@ -7261,39 +7262,41 @@
         <v>55</v>
       </c>
       <c r="C103" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="D103" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E103" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="D103" s="10" t="s">
+      <c r="F103" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="E103" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="F103" s="10" t="s">
-        <v>246</v>
-      </c>
       <c r="G103" s="12" t="n">
-        <v>46346</v>
+        <v>46505</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I103" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I103" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J103" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>46282</v>
+        <v>45891</v>
       </c>
       <c r="L103" s="13" t="n">
         <f aca="false">IF(K103="","",K103-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-427</v>
       </c>
       <c r="M103" s="10" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O103" s="14"/>
       <c r="P103" s="14" t="s">
@@ -7310,41 +7313,41 @@
         <v>55</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>46373</v>
+        <v>46505</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I104" s="10" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J104" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K104" s="12" t="n">
-        <v>46253</v>
+        <v>46282</v>
       </c>
       <c r="L104" s="13" t="n">
         <f aca="false">IF(K104="","",K104-Resumo!$B$3)</f>
-        <v>-65</v>
+        <v>-36</v>
       </c>
       <c r="M104" s="10" t="s">
-        <v>251</v>
+        <v>74</v>
       </c>
       <c r="N104" s="10" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="O104" s="14"/>
       <c r="P104" s="14" t="s">
@@ -7353,7 +7356,7 @@
       <c r="Q104" s="15"/>
       <c r="R104" s="14"/>
     </row>
-    <row r="105" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="10" t="n">
         <v>104</v>
       </c>
@@ -7361,10 +7364,10 @@
         <v>55</v>
       </c>
       <c r="C105" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="D105" s="10" t="s">
         <v>248</v>
-      </c>
-      <c r="D105" s="10" t="s">
-        <v>65</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>249</v>
@@ -7373,29 +7376,27 @@
         <v>250</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>46373</v>
+        <v>46346</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I105" s="10" t="n">
-        <v>5</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I105" s="10"/>
       <c r="J105" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>45192</v>
+        <v>46226</v>
       </c>
       <c r="L105" s="13" t="n">
         <f aca="false">IF(K105="","",K105-Resumo!$B$3)</f>
-        <v>-1126</v>
+        <v>-92</v>
       </c>
       <c r="M105" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O105" s="14"/>
       <c r="P105" s="14" t="s">
@@ -7412,10 +7413,10 @@
         <v>55</v>
       </c>
       <c r="C106" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="D106" s="10" t="s">
         <v>248</v>
-      </c>
-      <c r="D106" s="10" t="s">
-        <v>65</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>249</v>
@@ -7424,26 +7425,24 @@
         <v>250</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>46373</v>
+        <v>46346</v>
       </c>
       <c r="H106" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I106" s="10" t="n">
-        <v>16</v>
-      </c>
+      <c r="I106" s="10"/>
       <c r="J106" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K106" s="12" t="n">
-        <v>45262</v>
+        <v>46282</v>
       </c>
       <c r="L106" s="13" t="n">
         <f aca="false">IF(K106="","",K106-Resumo!$B$3)</f>
-        <v>-1056</v>
+        <v>-36</v>
       </c>
       <c r="M106" s="10" t="s">
-        <v>253</v>
+        <v>74</v>
       </c>
       <c r="N106" s="10" t="s">
         <v>58</v>
@@ -7455,7 +7454,7 @@
       <c r="Q106" s="15"/>
       <c r="R106" s="14"/>
     </row>
-    <row r="107" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="10" t="n">
         <v>106</v>
       </c>
@@ -7463,41 +7462,41 @@
         <v>55</v>
       </c>
       <c r="C107" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F107" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="D107" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="F107" s="10" t="s">
-        <v>257</v>
-      </c>
       <c r="G107" s="12" t="n">
-        <v>48010</v>
+        <v>46373</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I107" s="10" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="J107" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>46127</v>
+        <v>46253</v>
       </c>
       <c r="L107" s="13" t="n">
         <f aca="false">IF(K107="","",K107-Resumo!$B$3)</f>
-        <v>-191</v>
+        <v>-65</v>
       </c>
       <c r="M107" s="10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O107" s="14"/>
       <c r="P107" s="14" t="s">
@@ -7506,7 +7505,7 @@
       <c r="Q107" s="15"/>
       <c r="R107" s="14"/>
     </row>
-    <row r="108" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="10" t="n">
         <v>107</v>
       </c>
@@ -7514,41 +7513,41 @@
         <v>55</v>
       </c>
       <c r="C108" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="D108" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F108" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="D108" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="E108" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="F108" s="10" t="s">
-        <v>257</v>
-      </c>
       <c r="G108" s="12" t="n">
-        <v>48010</v>
+        <v>46373</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I108" s="10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J108" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K108" s="12" t="n">
-        <v>46280</v>
+        <v>45192</v>
       </c>
       <c r="L108" s="13" t="n">
         <f aca="false">IF(K108="","",K108-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>-1126</v>
       </c>
       <c r="M108" s="10" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="N108" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O108" s="14"/>
       <c r="P108" s="14" t="s">
@@ -7565,41 +7564,41 @@
         <v>55</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>260</v>
+        <v>65</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>46043</v>
+        <v>46373</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I109" s="10" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J109" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>45923</v>
+        <v>45262</v>
       </c>
       <c r="L109" s="13" t="n">
         <f aca="false">IF(K109="","",K109-Resumo!$B$3)</f>
-        <v>-395</v>
+        <v>-1056</v>
       </c>
       <c r="M109" s="10" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="O109" s="14"/>
       <c r="P109" s="14" t="s">
@@ -7616,19 +7615,19 @@
         <v>55</v>
       </c>
       <c r="C110" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="D110" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="D110" s="10" t="s">
+      <c r="E110" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="E110" s="10" t="s">
+      <c r="F110" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="F110" s="10" t="s">
-        <v>262</v>
-      </c>
       <c r="G110" s="12" t="n">
-        <v>46043</v>
+        <v>48010</v>
       </c>
       <c r="H110" s="10" t="s">
         <v>14</v>
@@ -7640,14 +7639,14 @@
         <v>56</v>
       </c>
       <c r="K110" s="12" t="n">
-        <v>46113</v>
+        <v>46127</v>
       </c>
       <c r="L110" s="13" t="n">
         <f aca="false">IF(K110="","",K110-Resumo!$B$3)</f>
-        <v>-205</v>
+        <v>-191</v>
       </c>
       <c r="M110" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="N110" s="10" t="s">
         <v>54</v>
@@ -7667,38 +7666,38 @@
         <v>55</v>
       </c>
       <c r="C111" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="D111" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="D111" s="10" t="s">
+      <c r="E111" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="E111" s="10" t="s">
+      <c r="F111" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="F111" s="10" t="s">
-        <v>262</v>
-      </c>
       <c r="G111" s="12" t="n">
-        <v>46043</v>
+        <v>48010</v>
       </c>
       <c r="H111" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J111" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>45351</v>
+        <v>46280</v>
       </c>
       <c r="L111" s="13" t="n">
         <f aca="false">IF(K111="","",K111-Resumo!$B$3)</f>
-        <v>-967</v>
+        <v>-38</v>
       </c>
       <c r="M111" s="10" t="s">
-        <v>265</v>
+        <v>231</v>
       </c>
       <c r="N111" s="10" t="s">
         <v>58</v>
@@ -7718,38 +7717,38 @@
         <v>55</v>
       </c>
       <c r="C112" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="D112" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="F112" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="D112" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="E112" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="F112" s="10" t="s">
-        <v>268</v>
-      </c>
       <c r="G112" s="12" t="n">
-        <v>46408</v>
+        <v>46043</v>
       </c>
       <c r="H112" s="10" t="s">
         <v>9</v>
       </c>
       <c r="I112" s="10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J112" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K112" s="12" t="n">
-        <v>46288</v>
+        <v>45923</v>
       </c>
       <c r="L112" s="13" t="n">
         <f aca="false">IF(K112="","",K112-Resumo!$B$3)</f>
-        <v>-30</v>
+        <v>-395</v>
       </c>
       <c r="M112" s="10" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N112" s="10" t="s">
         <v>99</v>
@@ -7769,19 +7768,19 @@
         <v>55</v>
       </c>
       <c r="C113" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="D113" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="E113" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="F113" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="D113" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="E113" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="F113" s="10" t="s">
-        <v>268</v>
-      </c>
       <c r="G113" s="12" t="n">
-        <v>46408</v>
+        <v>46043</v>
       </c>
       <c r="H113" s="10" t="s">
         <v>14</v>
@@ -7800,7 +7799,7 @@
         <v>-205</v>
       </c>
       <c r="M113" s="10" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="N113" s="10" t="s">
         <v>54</v>
@@ -7820,38 +7819,38 @@
         <v>55</v>
       </c>
       <c r="C114" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="D114" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="F114" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="D114" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="E114" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="F114" s="10" t="s">
-        <v>268</v>
-      </c>
       <c r="G114" s="12" t="n">
-        <v>46408</v>
+        <v>46043</v>
       </c>
       <c r="H114" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J114" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K114" s="12" t="n">
-        <v>46282</v>
+        <v>45351</v>
       </c>
       <c r="L114" s="13" t="n">
         <f aca="false">IF(K114="","",K114-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-967</v>
       </c>
       <c r="M114" s="10" t="s">
-        <v>74</v>
+        <v>269</v>
       </c>
       <c r="N114" s="10" t="s">
         <v>58</v>
@@ -7868,13 +7867,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C115" s="10" t="s">
         <v>270</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>95</v>
+        <v>207</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>271</v>
@@ -7883,27 +7882,29 @@
         <v>272</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>47310</v>
+        <v>46408</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I115" s="10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K115" s="12"/>
-      <c r="L115" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K115" s="12" t="n">
+        <v>46288</v>
+      </c>
+      <c r="L115" s="13" t="n">
         <f aca="false">IF(K115="","",K115-Resumo!$B$3)</f>
-        <v/>
+        <v>-30</v>
       </c>
       <c r="M115" s="10" t="s">
-        <v>79</v>
+        <v>273</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="O115" s="14"/>
       <c r="P115" s="14" t="s">
@@ -7917,13 +7918,13 @@
         <v>115</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C116" s="10" t="s">
         <v>270</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>95</v>
+        <v>207</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>271</v>
@@ -7932,7 +7933,7 @@
         <v>272</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>47310</v>
+        <v>46408</v>
       </c>
       <c r="H116" s="10" t="s">
         <v>14</v>
@@ -7941,15 +7942,17 @@
         <v>5</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K116" s="12"/>
-      <c r="L116" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K116" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="L116" s="13" t="n">
         <f aca="false">IF(K116="","",K116-Resumo!$B$3)</f>
-        <v/>
+        <v>-205</v>
       </c>
       <c r="M116" s="10" t="s">
-        <v>79</v>
+        <v>268</v>
       </c>
       <c r="N116" s="10" t="s">
         <v>54</v>
@@ -7972,7 +7975,7 @@
         <v>270</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>95</v>
+        <v>207</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>271</v>
@@ -7981,26 +7984,26 @@
         <v>272</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>47310</v>
+        <v>46408</v>
       </c>
       <c r="H117" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J117" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>46043</v>
+        <v>46282</v>
       </c>
       <c r="L117" s="13" t="n">
         <f aca="false">IF(K117="","",K117-Resumo!$B$3)</f>
-        <v>-275</v>
+        <v>-36</v>
       </c>
       <c r="M117" s="10" t="s">
-        <v>273</v>
+        <v>74</v>
       </c>
       <c r="N117" s="10" t="s">
         <v>58</v>
@@ -8012,18 +8015,18 @@
       <c r="Q117" s="15"/>
       <c r="R117" s="14"/>
     </row>
-    <row r="118" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="10" t="n">
         <v>117</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C118" s="10" t="s">
         <v>274</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>275</v>
@@ -8032,29 +8035,27 @@
         <v>276</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>46658</v>
+        <v>47310</v>
       </c>
       <c r="H118" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I118" s="10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J118" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K118" s="12" t="n">
-        <v>46107</v>
-      </c>
-      <c r="L118" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K118" s="12"/>
+      <c r="L118" s="13" t="str">
         <f aca="false">IF(K118="","",K118-Resumo!$B$3)</f>
-        <v>-211</v>
+        <v/>
       </c>
       <c r="M118" s="10" t="s">
-        <v>277</v>
+        <v>79</v>
       </c>
       <c r="N118" s="10" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="O118" s="14"/>
       <c r="P118" s="14" t="s">
@@ -8063,18 +8064,18 @@
       <c r="Q118" s="15"/>
       <c r="R118" s="14"/>
     </row>
-    <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="10" t="n">
         <v>118</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C119" s="10" t="s">
         <v>274</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>275</v>
@@ -8083,29 +8084,27 @@
         <v>276</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>46658</v>
+        <v>47310</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I119" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K119" s="12" t="n">
-        <v>46280</v>
-      </c>
-      <c r="L119" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K119" s="12"/>
+      <c r="L119" s="13" t="str">
         <f aca="false">IF(K119="","",K119-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v/>
       </c>
       <c r="M119" s="10" t="s">
-        <v>227</v>
+        <v>79</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O119" s="14"/>
       <c r="P119" s="14" t="s">
@@ -8119,13 +8118,13 @@
         <v>119</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C120" s="10" t="s">
         <v>274</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>275</v>
@@ -8134,27 +8133,29 @@
         <v>276</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>46658</v>
+        <v>47310</v>
       </c>
       <c r="H120" s="10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I120" s="10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J120" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K120" s="12"/>
-      <c r="L120" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K120" s="12" t="n">
+        <v>46043</v>
+      </c>
+      <c r="L120" s="13" t="n">
         <f aca="false">IF(K120="","",K120-Resumo!$B$3)</f>
-        <v/>
+        <v>-275</v>
       </c>
       <c r="M120" s="10" t="s">
-        <v>79</v>
+        <v>277</v>
       </c>
       <c r="N120" s="10" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="O120" s="14"/>
       <c r="P120" s="14" t="s">
@@ -8174,16 +8175,16 @@
         <v>278</v>
       </c>
       <c r="D121" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E121" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="E121" s="10" t="s">
+      <c r="F121" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="F121" s="10" t="s">
-        <v>281</v>
-      </c>
       <c r="G121" s="12" t="n">
-        <v>47016</v>
+        <v>46658</v>
       </c>
       <c r="H121" s="10" t="s">
         <v>14</v>
@@ -8195,14 +8196,14 @@
         <v>56</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="L121" s="13" t="n">
         <f aca="false">IF(K121="","",K121-Resumo!$B$3)</f>
-        <v>-205</v>
+        <v>-211</v>
       </c>
       <c r="M121" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N121" s="10" t="s">
         <v>54</v>
@@ -8225,35 +8226,35 @@
         <v>278</v>
       </c>
       <c r="D122" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E122" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="E122" s="10" t="s">
+      <c r="F122" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="F122" s="10" t="s">
-        <v>281</v>
-      </c>
       <c r="G122" s="12" t="n">
-        <v>47016</v>
+        <v>46658</v>
       </c>
       <c r="H122" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J122" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K122" s="12" t="n">
-        <v>45519</v>
+        <v>46280</v>
       </c>
       <c r="L122" s="13" t="n">
         <f aca="false">IF(K122="","",K122-Resumo!$B$3)</f>
-        <v>-799</v>
+        <v>-38</v>
       </c>
       <c r="M122" s="10" t="s">
-        <v>283</v>
+        <v>231</v>
       </c>
       <c r="N122" s="10" t="s">
         <v>58</v>
@@ -8276,38 +8277,36 @@
         <v>278</v>
       </c>
       <c r="D123" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E123" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="E123" s="10" t="s">
+      <c r="F123" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="F123" s="10" t="s">
-        <v>281</v>
-      </c>
       <c r="G123" s="12" t="n">
-        <v>47016</v>
+        <v>46658</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I123" s="10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K123" s="12" t="n">
-        <v>46339</v>
-      </c>
-      <c r="L123" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K123" s="12"/>
+      <c r="L123" s="13" t="str">
         <f aca="false">IF(K123="","",K123-Resumo!$B$3)</f>
-        <v>21</v>
+        <v/>
       </c>
       <c r="M123" s="10" t="s">
-        <v>284</v>
+        <v>79</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="O123" s="14"/>
       <c r="P123" s="14" t="s">
@@ -8316,7 +8315,7 @@
       <c r="Q123" s="15"/>
       <c r="R123" s="14"/>
     </row>
-    <row r="124" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="10" t="n">
         <v>123</v>
       </c>
@@ -8324,41 +8323,41 @@
         <v>55</v>
       </c>
       <c r="C124" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="D124" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="F124" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="D124" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="E124" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="F124" s="10" t="s">
-        <v>288</v>
-      </c>
       <c r="G124" s="12" t="n">
-        <v>46332</v>
+        <v>47016</v>
       </c>
       <c r="H124" s="10" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I124" s="10" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J124" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K124" s="12" t="n">
-        <v>46212</v>
+        <v>46113</v>
       </c>
       <c r="L124" s="13" t="n">
         <f aca="false">IF(K124="","",K124-Resumo!$B$3)</f>
-        <v>-106</v>
+        <v>-205</v>
       </c>
       <c r="M124" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="N124" s="10" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="O124" s="14"/>
       <c r="P124" s="14" t="s">
@@ -8372,44 +8371,44 @@
         <v>124</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C125" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="D125" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="E125" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="F125" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="D125" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="E125" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="F125" s="10" t="s">
-        <v>288</v>
-      </c>
       <c r="G125" s="12" t="n">
-        <v>46332</v>
+        <v>47016</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I125" s="10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J125" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>46248</v>
+        <v>45519</v>
       </c>
       <c r="L125" s="13" t="n">
         <f aca="false">IF(K125="","",K125-Resumo!$B$3)</f>
-        <v>-70</v>
+        <v>-799</v>
       </c>
       <c r="M125" s="10" t="s">
-        <v>85</v>
+        <v>287</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="O125" s="14"/>
       <c r="P125" s="14" t="s">
@@ -8418,49 +8417,49 @@
       <c r="Q125" s="15"/>
       <c r="R125" s="14"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="10" t="n">
         <v>125</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C126" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="D126" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="F126" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="D126" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="E126" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="F126" s="10" t="s">
-        <v>288</v>
-      </c>
       <c r="G126" s="12" t="n">
-        <v>46332</v>
+        <v>47016</v>
       </c>
       <c r="H126" s="10" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I126" s="10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J126" s="10" t="s">
         <v>50</v>
       </c>
       <c r="K126" s="12" t="n">
-        <v>46328</v>
+        <v>46339</v>
       </c>
       <c r="L126" s="13" t="n">
         <f aca="false">IF(K126="","",K126-Resumo!$B$3)</f>
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="M126" s="10" t="s">
-        <v>87</v>
+        <v>288</v>
       </c>
       <c r="N126" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O126" s="14"/>
       <c r="P126" s="14" t="s">
@@ -8469,7 +8468,7 @@
       <c r="Q126" s="15"/>
       <c r="R126" s="14"/>
     </row>
-    <row r="127" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="10" t="n">
         <v>126</v>
       </c>
@@ -8477,41 +8476,41 @@
         <v>55</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G127" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I127" s="10" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J127" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>46259</v>
+        <v>46212</v>
       </c>
       <c r="L127" s="13" t="n">
         <f aca="false">IF(K127="","",K127-Resumo!$B$3)</f>
-        <v>-59</v>
+        <v>-106</v>
       </c>
       <c r="M127" s="10" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O127" s="14"/>
       <c r="P127" s="14" t="s">
@@ -8525,44 +8524,44 @@
         <v>127</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E128" s="10" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G128" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H128" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I128" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J128" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K128" s="12" t="n">
-        <v>46280</v>
+        <v>46248</v>
       </c>
       <c r="L128" s="13" t="n">
         <f aca="false">IF(K128="","",K128-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>-70</v>
       </c>
       <c r="M128" s="10" t="s">
-        <v>227</v>
+        <v>85</v>
       </c>
       <c r="N128" s="10" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="O128" s="14"/>
       <c r="P128" s="14" t="s">
@@ -8571,47 +8570,49 @@
       <c r="Q128" s="15"/>
       <c r="R128" s="14"/>
     </row>
-    <row r="129" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="10" t="n">
         <v>128</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G129" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H129" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I129" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="I129" s="10" t="n">
-        <v>13</v>
-      </c>
       <c r="J129" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K129" s="12"/>
-      <c r="L129" s="13" t="str">
+        <v>50</v>
+      </c>
+      <c r="K129" s="12" t="n">
+        <v>46328</v>
+      </c>
+      <c r="L129" s="13" t="n">
         <f aca="false">IF(K129="","",K129-Resumo!$B$3)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="M129" s="10" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O129" s="14"/>
       <c r="P129" s="14" t="s">
@@ -8620,49 +8621,49 @@
       <c r="Q129" s="15"/>
       <c r="R129" s="14"/>
     </row>
-    <row r="130" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="10" t="n">
         <v>129</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C130" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D130" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="E130" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="D130" s="10" t="s">
+      <c r="F130" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="E130" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="F130" s="10" t="s">
-        <v>294</v>
-      </c>
       <c r="G130" s="12" t="n">
-        <v>48215</v>
+        <v>46332</v>
       </c>
       <c r="H130" s="10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I130" s="10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J130" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K130" s="12" t="n">
-        <v>46034</v>
+        <v>46259</v>
       </c>
       <c r="L130" s="13" t="n">
         <f aca="false">IF(K130="","",K130-Resumo!$B$3)</f>
-        <v>-284</v>
+        <v>-59</v>
       </c>
       <c r="M130" s="10" t="s">
-        <v>85</v>
+        <v>294</v>
       </c>
       <c r="N130" s="10" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="O130" s="14"/>
       <c r="P130" s="14" t="s">
@@ -8671,49 +8672,49 @@
       <c r="Q130" s="15"/>
       <c r="R130" s="14"/>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="10" t="n">
         <v>130</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C131" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D131" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="E131" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="D131" s="10" t="s">
+      <c r="F131" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="E131" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="F131" s="10" t="s">
-        <v>294</v>
-      </c>
       <c r="G131" s="12" t="n">
-        <v>48215</v>
+        <v>46332</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I131" s="10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J131" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>46114</v>
+        <v>46280</v>
       </c>
       <c r="L131" s="13" t="n">
         <f aca="false">IF(K131="","",K131-Resumo!$B$3)</f>
-        <v>-204</v>
+        <v>-38</v>
       </c>
       <c r="M131" s="10" t="s">
-        <v>87</v>
+        <v>231</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="O131" s="14"/>
       <c r="P131" s="14" t="s">
@@ -8722,49 +8723,47 @@
       <c r="Q131" s="15"/>
       <c r="R131" s="14"/>
     </row>
-    <row r="132" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="10" t="n">
         <v>131</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C132" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D132" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="E132" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="D132" s="10" t="s">
+      <c r="F132" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="E132" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="F132" s="10" t="s">
-        <v>294</v>
-      </c>
       <c r="G132" s="12" t="n">
-        <v>48215</v>
+        <v>46332</v>
       </c>
       <c r="H132" s="10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I132" s="10" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J132" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K132" s="12" t="n">
-        <v>46276</v>
-      </c>
-      <c r="L132" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K132" s="12"/>
+      <c r="L132" s="13" t="str">
         <f aca="false">IF(K132="","",K132-Resumo!$B$3)</f>
-        <v>-42</v>
+        <v/>
       </c>
       <c r="M132" s="10" t="s">
-        <v>295</v>
+        <v>79</v>
       </c>
       <c r="N132" s="10" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="O132" s="14"/>
       <c r="P132" s="14" t="s">
@@ -8778,42 +8777,44 @@
         <v>132</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G133" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I133" s="10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J133" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K133" s="12"/>
-      <c r="L133" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K133" s="12" t="n">
+        <v>46034</v>
+      </c>
+      <c r="L133" s="13" t="n">
         <f aca="false">IF(K133="","",K133-Resumo!$B$3)</f>
-        <v/>
+        <v>-284</v>
       </c>
       <c r="M133" s="10" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="O133" s="14"/>
       <c r="P133" s="14" t="s">
@@ -8822,47 +8823,49 @@
       <c r="Q133" s="15"/>
       <c r="R133" s="14"/>
     </row>
-    <row r="134" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="10" t="n">
         <v>133</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G134" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H134" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I134" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J134" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K134" s="12"/>
-      <c r="L134" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K134" s="12" t="n">
+        <v>46114</v>
+      </c>
+      <c r="L134" s="13" t="n">
         <f aca="false">IF(K134="","",K134-Resumo!$B$3)</f>
-        <v/>
+        <v>-204</v>
       </c>
       <c r="M134" s="10" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="N134" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O134" s="14"/>
       <c r="P134" s="14" t="s">
@@ -8871,47 +8874,49 @@
       <c r="Q134" s="15"/>
       <c r="R134" s="14"/>
     </row>
-    <row r="135" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="10" t="n">
         <v>134</v>
       </c>
       <c r="B135" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G135" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I135" s="10" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J135" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K135" s="12"/>
-      <c r="L135" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K135" s="12" t="n">
+        <v>46276</v>
+      </c>
+      <c r="L135" s="13" t="n">
         <f aca="false">IF(K135="","",K135-Resumo!$B$3)</f>
-        <v/>
+        <v>-42</v>
       </c>
       <c r="M135" s="10" t="s">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="O135" s="14"/>
       <c r="P135" s="14" t="s">
@@ -8928,25 +8933,25 @@
         <v>45</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D136" s="10" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="F136" s="10" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G136" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H136" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I136" s="10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J136" s="10" t="s">
         <v>6</v>
@@ -8960,7 +8965,7 @@
         <v>79</v>
       </c>
       <c r="N136" s="10" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="O136" s="14"/>
       <c r="P136" s="14" t="s">
@@ -8977,10 +8982,10 @@
         <v>45</v>
       </c>
       <c r="C137" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D137" s="10" t="s">
         <v>296</v>
-      </c>
-      <c r="D137" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>297</v>
@@ -8989,27 +8994,27 @@
         <v>298</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>47697</v>
+        <v>48215</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I137" s="10"/>
+        <v>16</v>
+      </c>
+      <c r="I137" s="10" t="n">
+        <v>14</v>
+      </c>
       <c r="J137" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K137" s="12" t="n">
-        <v>46344</v>
-      </c>
-      <c r="L137" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K137" s="12"/>
+      <c r="L137" s="13" t="str">
         <f aca="false">IF(K137="","",K137-Resumo!$B$3)</f>
-        <v>26</v>
+        <v/>
       </c>
       <c r="M137" s="10" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="O137" s="14"/>
       <c r="P137" s="14" t="s">
@@ -9018,18 +9023,18 @@
       <c r="Q137" s="15"/>
       <c r="R137" s="14"/>
     </row>
-    <row r="138" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="10" t="n">
         <v>137</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C138" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D138" s="10" t="s">
         <v>296</v>
-      </c>
-      <c r="D138" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="E138" s="10" t="s">
         <v>297</v>
@@ -9038,29 +9043,27 @@
         <v>298</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>47697</v>
+        <v>48215</v>
       </c>
       <c r="H138" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I138" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="I138" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="J138" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K138" s="12" t="n">
-        <v>46127</v>
-      </c>
-      <c r="L138" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K138" s="12"/>
+      <c r="L138" s="13" t="str">
         <f aca="false">IF(K138="","",K138-Resumo!$B$3)</f>
-        <v>-191</v>
+        <v/>
       </c>
       <c r="M138" s="10" t="s">
-        <v>258</v>
+        <v>79</v>
       </c>
       <c r="N138" s="10" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="O138" s="14"/>
       <c r="P138" s="14" t="s">
@@ -9074,13 +9077,13 @@
         <v>138</v>
       </c>
       <c r="B139" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C139" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D139" s="10" t="s">
         <v>296</v>
-      </c>
-      <c r="D139" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>297</v>
@@ -9089,29 +9092,27 @@
         <v>298</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>47697</v>
+        <v>48215</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I139" s="10" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J139" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K139" s="12" t="n">
-        <v>46282</v>
-      </c>
-      <c r="L139" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K139" s="12"/>
+      <c r="L139" s="13" t="str">
         <f aca="false">IF(K139="","",K139-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v/>
       </c>
       <c r="M139" s="10" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="O139" s="14"/>
       <c r="P139" s="14" t="s">
@@ -9125,13 +9126,13 @@
         <v>139</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>300</v>
+        <v>198</v>
       </c>
       <c r="E140" s="10" t="s">
         <v>301</v>
@@ -9140,29 +9141,27 @@
         <v>302</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>46244</v>
+        <v>47697</v>
       </c>
       <c r="H140" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="I140" s="10" t="n">
-        <v>21</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I140" s="10"/>
       <c r="J140" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K140" s="12" t="n">
-        <v>46124</v>
+        <v>46344</v>
       </c>
       <c r="L140" s="13" t="n">
         <f aca="false">IF(K140="","",K140-Resumo!$B$3)</f>
-        <v>-194</v>
+        <v>26</v>
       </c>
       <c r="M140" s="10" t="s">
-        <v>303</v>
+        <v>51</v>
       </c>
       <c r="N140" s="10" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="O140" s="14"/>
       <c r="P140" s="14" t="s">
@@ -9179,10 +9178,10 @@
         <v>55</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>300</v>
+        <v>198</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>301</v>
@@ -9191,7 +9190,7 @@
         <v>302</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>46244</v>
+        <v>47697</v>
       </c>
       <c r="H141" s="10" t="s">
         <v>14</v>
@@ -9203,14 +9202,14 @@
         <v>56</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>46276</v>
+        <v>46127</v>
       </c>
       <c r="L141" s="13" t="n">
         <f aca="false">IF(K141="","",K141-Resumo!$B$3)</f>
-        <v>-42</v>
+        <v>-191</v>
       </c>
       <c r="M141" s="10" t="s">
-        <v>295</v>
+        <v>262</v>
       </c>
       <c r="N141" s="10" t="s">
         <v>54</v>
@@ -9227,13 +9226,13 @@
         <v>141</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>300</v>
+        <v>198</v>
       </c>
       <c r="E142" s="10" t="s">
         <v>301</v>
@@ -9242,24 +9241,26 @@
         <v>302</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>46244</v>
+        <v>47697</v>
       </c>
       <c r="H142" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I142" s="10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K142" s="12"/>
-      <c r="L142" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K142" s="12" t="n">
+        <v>46282</v>
+      </c>
+      <c r="L142" s="13" t="n">
         <f aca="false">IF(K142="","",K142-Resumo!$B$3)</f>
-        <v/>
+        <v>-36</v>
       </c>
       <c r="M142" s="10" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="N142" s="10" t="s">
         <v>58</v>
@@ -9271,9 +9272,160 @@
       <c r="Q142" s="15"/>
       <c r="R142" s="14"/>
     </row>
+    <row r="143" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="10" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C143" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="D143" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E143" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="F143" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H143" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I143" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="J143" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K143" s="12" t="n">
+        <v>46124</v>
+      </c>
+      <c r="L143" s="13" t="n">
+        <f aca="false">IF(K143="","",K143-Resumo!$B$3)</f>
+        <v>-194</v>
+      </c>
+      <c r="M143" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="N143" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="O143" s="14"/>
+      <c r="P143" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q143" s="15"/>
+      <c r="R143" s="14"/>
+    </row>
+    <row r="144" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="10" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="D144" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E144" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="F144" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H144" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I144" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J144" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K144" s="12" t="n">
+        <v>46276</v>
+      </c>
+      <c r="L144" s="13" t="n">
+        <f aca="false">IF(K144="","",K144-Resumo!$B$3)</f>
+        <v>-42</v>
+      </c>
+      <c r="M144" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="N144" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="O144" s="14"/>
+      <c r="P144" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q144" s="15"/>
+      <c r="R144" s="14"/>
+    </row>
+    <row r="145" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="10" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="D145" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E145" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="F145" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H145" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I145" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="J145" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K145" s="12"/>
+      <c r="L145" s="13" t="str">
+        <f aca="false">IF(K145="","",K145-Resumo!$B$3)</f>
+        <v/>
+      </c>
+      <c r="M145" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N145" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O145" s="14"/>
+      <c r="P145" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q145" s="15"/>
+      <c r="R145" s="14"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R142"/>
-  <conditionalFormatting sqref="J2:J142">
+  <autoFilter ref="A1:R145"/>
+  <conditionalFormatting sqref="J2:J145">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$J2="Vencida"</formula>
     </cfRule>
@@ -9284,12 +9436,12 @@
       <formula>$J2="Sem data"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B142">
+  <conditionalFormatting sqref="B2:B145">
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>$B2="Alta"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P142">
+  <conditionalFormatting sqref="P2:P145">
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>$P2="Resolvido"</formula>
     </cfRule>
@@ -9298,7 +9450,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P142" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P145" type="list">
       <formula1>"A fazer,Em andamento,Aguardando cliente,Resolvido,Já estava em dia"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9319,7 +9471,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -9343,7 +9495,7 @@
         <v>8</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9351,15 +9503,15 @@
         <v>46</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A2,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A2,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A2,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A2,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A2,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A2,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>2</v>
       </c>
       <c r="E2" s="7" t="n">
@@ -9367,7 +9519,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A2,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A2,Pendências!$B$2:$B$145,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9376,15 +9528,15 @@
         <v>59</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A3,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A3,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A3,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A3,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A3,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A3,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E3" s="7" t="n">
@@ -9392,7 +9544,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A3,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A3,Pendências!$B$2:$B$145,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9401,15 +9553,15 @@
         <v>64</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A4,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A4,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A4,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A4,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A4,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A4,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
@@ -9417,7 +9569,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A4,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A4,Pendências!$B$2:$B$145,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9426,15 +9578,15 @@
         <v>69</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A5,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A5,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A5,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A5,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A5,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A5,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
@@ -9442,7 +9594,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A5,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A5,Pendências!$B$2:$B$145,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9451,15 +9603,15 @@
         <v>75</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A6,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A6,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A6,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A6,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A6,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A6,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
@@ -9467,7 +9619,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A6,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A6,Pendências!$B$2:$B$145,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -9476,15 +9628,15 @@
         <v>81</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A7,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A7,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>5</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A7,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A7,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A7,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A7,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
@@ -9492,7 +9644,7 @@
         <v>7</v>
       </c>
       <c r="F7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A7,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A7,Pendências!$B$2:$B$145,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9501,15 +9653,15 @@
         <v>94</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A8,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A8,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A8,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A8,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A8,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A8,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
@@ -9517,7 +9669,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A8,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A8,Pendências!$B$2:$B$145,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9526,15 +9678,15 @@
         <v>101</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A9,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A9,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A9,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A9,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A9,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A9,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
@@ -9542,7 +9694,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A9,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A9,Pendências!$B$2:$B$145,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -9551,15 +9703,15 @@
         <v>105</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A10,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A10,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A10,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A10,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A10,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A10,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E10" s="7" t="n">
@@ -9567,7 +9719,7 @@
         <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A10,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A10,Pendências!$B$2:$B$145,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9576,15 +9728,15 @@
         <v>111</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A11,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A11,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A11,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A11,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A11,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A11,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E11" s="7" t="n">
@@ -9592,7 +9744,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A11,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A11,Pendências!$B$2:$B$145,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -9601,15 +9753,15 @@
         <v>115</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A12,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A12,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A12,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A12,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A12,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A12,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
@@ -9617,7 +9769,7 @@
         <v>6</v>
       </c>
       <c r="F12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A12,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A12,Pendências!$B$2:$B$145,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9626,15 +9778,15 @@
         <v>119</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A13,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A13,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A13,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A13,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A13,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A13,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
@@ -9642,7 +9794,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A13,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A13,Pendências!$B$2:$B$145,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9651,15 +9803,15 @@
         <v>123</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A14,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A14,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A14,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A14,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A14,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A14,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
@@ -9667,7 +9819,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A14,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A14,Pendências!$B$2:$B$145,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9676,15 +9828,15 @@
         <v>127</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A15,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A15,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A15,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A15,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A15,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A15,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
@@ -9692,7 +9844,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A15,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A15,Pendências!$B$2:$B$145,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9701,15 +9853,15 @@
         <v>132</v>
       </c>
       <c r="B16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A16,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A16,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A16,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A16,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A16,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A16,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
@@ -9717,7 +9869,7 @@
         <v>4</v>
       </c>
       <c r="F16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A16,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A16,Pendências!$B$2:$B$145,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9726,15 +9878,15 @@
         <v>139</v>
       </c>
       <c r="B17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A17,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A17,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A17,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A17,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A17,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A17,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
@@ -9742,7 +9894,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A17,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A17,Pendências!$B$2:$B$145,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9751,15 +9903,15 @@
         <v>143</v>
       </c>
       <c r="B18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A18,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A18,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>4</v>
       </c>
       <c r="C18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A18,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A18,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A18,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A18,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
@@ -9767,7 +9919,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A18,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A18,Pendências!$B$2:$B$145,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9776,15 +9928,15 @@
         <v>148</v>
       </c>
       <c r="B19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A19,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A19,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A19,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A19,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A19,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A19,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
@@ -9792,7 +9944,7 @@
         <v>4</v>
       </c>
       <c r="F19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A19,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A19,Pendências!$B$2:$B$145,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9801,15 +9953,15 @@
         <v>154</v>
       </c>
       <c r="B20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A20,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A20,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A20,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A20,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A20,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A20,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E20" s="7" t="n">
@@ -9817,7 +9969,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A20,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A20,Pendências!$B$2:$B$145,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9826,15 +9978,15 @@
         <v>157</v>
       </c>
       <c r="B21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A21,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A21,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>1</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A21,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>2</v>
       </c>
-      <c r="C21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A21,Pendências!$J$2:$J$142,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A21,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A21,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
@@ -9842,99 +9994,99 @@
         <v>3</v>
       </c>
       <c r="F21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A21,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A21,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A22,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A22,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>2</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A22,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>1</v>
       </c>
-      <c r="C22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A22,Pendências!$J$2:$J$142,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A22,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A22,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E22" s="7" t="n">
         <f aca="false">SUM(B22:D22)</f>
+        <v>3</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A22,Pendências!$B$2:$B$145,"Alta")</f>
         <v>2</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A22,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A23,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A23,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A23,Pendências!$J$2:$J$142,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A23,Pendências!$J$2:$J$145,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A23,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A23,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
         <f aca="false">SUM(B23:D23)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A23,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A23,Pendências!$B$2:$B$145,"Alta")</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A24,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A24,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A24,Pendências!$J$2:$J$142,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A24,Pendências!$J$2:$J$145,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A24,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A24,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E24" s="7" t="n">
         <f aca="false">SUM(B24:D24)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A24,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A24,Pendências!$B$2:$B$145,"Alta")</f>
         <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A25,Pendências!$J$2:$J$142,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A25,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A25,Pendências!$J$2:$J$142,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A25,Pendências!$J$2:$J$145,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A25,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A25,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
@@ -9942,8 +10094,8 @@
         <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A25,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A25,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9951,15 +10103,15 @@
         <v>178</v>
       </c>
       <c r="B26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A26,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A26,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A26,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A26,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A26,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A26,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E26" s="7" t="n">
@@ -9967,7 +10119,7 @@
         <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A26,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A26,Pendências!$B$2:$B$145,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9976,23 +10128,23 @@
         <v>183</v>
       </c>
       <c r="B27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A27,Pendências!$J$2:$J$142,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A27,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A27,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A27,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A27,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A27,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
         <f aca="false">SUM(B27:D27)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A27,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A27,Pendências!$B$2:$B$145,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -10001,74 +10153,74 @@
         <v>188</v>
       </c>
       <c r="B28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A28,Pendências!$J$2:$J$142,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A28,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A28,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A28,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A28,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A28,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E28" s="7" t="n">
         <f aca="false">SUM(B28:D28)</f>
+        <v>3</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A28,Pendências!$B$2:$B$145,"Alta")</f>
         <v>2</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A28,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A29,Pendências!$J$2:$J$142,"Vencida")</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A29,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A29,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A29,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A29,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A29,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
         <f aca="false">SUM(B29:D29)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A29,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A29,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A30,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A30,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>5</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A30,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
-      <c r="C30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A30,Pendências!$J$2:$J$142,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A30,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A30,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E30" s="7" t="n">
         <f aca="false">SUM(B30:D30)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A30,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A30,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10076,290 +10228,290 @@
         <v>206</v>
       </c>
       <c r="B31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A31,Pendências!$J$2:$J$142,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A31,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>0</v>
       </c>
       <c r="C31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A31,Pendências!$J$2:$J$142,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A31,Pendências!$J$2:$J$145,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A31,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A31,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
         <f aca="false">SUM(B31:D31)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A31,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A31,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A32,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A32,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A32,Pendências!$J$2:$J$142,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A32,Pendências!$J$2:$J$145,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A32,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A32,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E32" s="7" t="n">
         <f aca="false">SUM(B32:D32)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A32,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A32,Pendências!$B$2:$B$145,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A33,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A33,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>3</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A33,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>1</v>
       </c>
-      <c r="C33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A33,Pendências!$J$2:$J$142,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A33,Pendências!$J$2:$J$142,"Vence em breve")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A33,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
         <f aca="false">SUM(B33:D33)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A33,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A33,Pendências!$B$2:$B$145,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A34,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A34,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A34,Pendências!$J$2:$J$142,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A34,Pendências!$J$2:$J$145,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A34,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A34,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E34" s="7" t="n">
         <f aca="false">SUM(B34:D34)</f>
+        <v>3</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A34,Pendências!$B$2:$B$145,"Alta")</f>
         <v>2</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A34,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>1</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A35,Pendências!$J$2:$J$142,"Vencida")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A35,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A35,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A35,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A35,Pendências!$J$2:$J$142,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A35,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E35" s="7" t="n">
         <f aca="false">SUM(B35:D35)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A35,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A35,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A36,Pendências!$J$2:$J$142,"Vencida")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A36,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>4</v>
       </c>
       <c r="C36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A36,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A36,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A36,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A36,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E36" s="7" t="n">
         <f aca="false">SUM(B36:D36)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A36,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A36,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A37,Pendências!$J$2:$J$142,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A37,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A37,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A37,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A37,Pendências!$J$2:$J$142,"Vence em breve")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A37,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <v>0</v>
       </c>
       <c r="E37" s="7" t="n">
         <f aca="false">SUM(B37:D37)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A37,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A37,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A38,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A38,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A38,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A38,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A38,Pendências!$J$2:$J$142,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A38,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E38" s="7" t="n">
         <f aca="false">SUM(B38:D38)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A38,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A38,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A39,Pendências!$J$2:$J$142,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A39,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A39,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A39,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A39,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A39,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
         <f aca="false">SUM(B39:D39)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A39,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A39,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A40,Pendências!$J$2:$J$142,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A40,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A40,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A40,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A40,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A40,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E40" s="7" t="n">
         <f aca="false">SUM(B40:D40)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A40,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A40,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A41,Pendências!$J$2:$J$142,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A41,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A41,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A41,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A41,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A41,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E41" s="7" t="n">
         <f aca="false">SUM(B41:D41)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A41,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A41,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A42,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A42,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A42,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A42,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A42,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A42,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E42" s="7" t="n">
@@ -10367,7 +10519,7 @@
         <v>3</v>
       </c>
       <c r="F42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A42,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A42,Pendências!$B$2:$B$145,"Alta")</f>
         <v>3</v>
       </c>
     </row>
@@ -10376,15 +10528,15 @@
         <v>270</v>
       </c>
       <c r="B43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A43,Pendências!$J$2:$J$142,"Vencida")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A43,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A43,Pendências!$J$2:$J$142,"Sem data")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A43,Pendências!$J$2:$J$145,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A43,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A43,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
@@ -10392,8 +10544,8 @@
         <v>3</v>
       </c>
       <c r="F43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A43,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A43,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10401,15 +10553,15 @@
         <v>274</v>
       </c>
       <c r="B44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A44,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A44,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>1</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A44,Pendências!$J$2:$J$145,"Sem data")</f>
         <v>2</v>
       </c>
-      <c r="C44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A44,Pendências!$J$2:$J$142,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A44,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A44,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E44" s="7" t="n">
@@ -10417,8 +10569,8 @@
         <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A44,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A44,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10426,128 +10578,153 @@
         <v>278</v>
       </c>
       <c r="B45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A45,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A45,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A45,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A45,Pendências!$J$2:$J$145,"Sem data")</f>
+        <v>1</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A45,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
-      </c>
-      <c r="D45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A45,Pendências!$J$2:$J$142,"Vence em breve")</f>
-        <v>1</v>
       </c>
       <c r="E45" s="7" t="n">
         <f aca="false">SUM(B45:D45)</f>
         <v>3</v>
       </c>
       <c r="F45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A45,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A45,Pendências!$B$2:$B$145,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A46,Pendências!$J$2:$J$142,"Vencida")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A46,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A46,Pendências!$J$2:$J$142,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A46,Pendências!$J$2:$J$145,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A46,Pendências!$J$2:$J$142,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A46,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E46" s="7" t="n">
         <f aca="false">SUM(B46:D46)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A46,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A46,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A47,Pendências!$J$2:$J$142,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A47,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>4</v>
       </c>
       <c r="C47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A47,Pendências!$J$2:$J$142,"Sem data")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A47,Pendências!$J$2:$J$145,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A47,Pendências!$J$2:$J$142,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A47,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E47" s="7" t="n">
         <f aca="false">SUM(B47:D47)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A47,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A47,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B48" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A48,Pendências!$J$2:$J$142,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A48,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C48" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A48,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A48,Pendências!$J$2:$J$145,"Sem data")</f>
+        <v>4</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A48,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>0</v>
-      </c>
-      <c r="D48" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A48,Pendências!$J$2:$J$142,"Vence em breve")</f>
-        <v>1</v>
       </c>
       <c r="E48" s="7" t="n">
         <f aca="false">SUM(B48:D48)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F48" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A48,Pendências!$B$2:$B$142,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A48,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B49" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A49,Pendências!$J$2:$J$142,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A49,Pendências!$J$2:$J$145,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C49" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A49,Pendências!$J$2:$J$142,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A49,Pendências!$J$2:$J$145,"Sem data")</f>
+        <v>0</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A49,Pendências!$J$2:$J$145,"Vence em breve")</f>
         <v>1</v>
-      </c>
-      <c r="D49" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A49,Pendências!$J$2:$J$142,"Vence em breve")</f>
-        <v>0</v>
       </c>
       <c r="E49" s="7" t="n">
         <f aca="false">SUM(B49:D49)</f>
         <v>3</v>
       </c>
       <c r="F49" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$142,$A49,Pendências!$B$2:$B$142,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A49,Pendências!$B$2:$B$145,"Alta")</f>
         <v>2</v>
       </c>
     </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="B50" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A50,Pendências!$J$2:$J$145,"Vencida")</f>
+        <v>2</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A50,Pendências!$J$2:$J$145,"Sem data")</f>
+        <v>1</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A50,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <f aca="false">SUM(B50:D50)</f>
+        <v>3</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A50,Pendências!$B$2:$B$145,"Alta")</f>
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F49"/>
+  <autoFilter ref="A1:F50"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -10564,7 +10741,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -10592,178 +10769,167 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>341</v>
+        <v>107</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>107</v>
+        <v>322</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="s">
-        <v>347</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>318</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>

--- a/pendencias-condicionantes-2026-10-23.xlsx
+++ b/pendencias-condicionantes-2026-10-23.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Licenças que faltam" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Pendências!$A$1:$R$145</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Por empresa'!$A$1:$F$50</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Pendências!$A$1:$R$149</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Por empresa'!$A$1:$F$51</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="357">
   <si>
     <t xml:space="preserve">Condicionantes ambientais – pendências</t>
   </si>
@@ -818,6 +818,27 @@
     <t xml:space="preserve">Documento na pasta: AVCB emitido em 15/04/2025</t>
   </si>
   <si>
+    <t xml:space="preserve">Posto Gangorra Ltda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafael Fernandes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03.365.159/0001-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-150998/TEC/RLO-0422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licença vale até 04/08/2026 (pedido ≥120 dias antes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documento na pasta: Coleta em 15/06/2026 (pasta 57, CNPJ 19.688.384/0001-05: confirmar se é a mesma empresa) → +3 meses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documento na pasta: Verificação de 14/11/2025 (pasta 57); renovação anual</t>
+  </si>
+  <si>
     <t xml:space="preserve">Posto Ln Ltda</t>
   </si>
   <si>
@@ -1043,13 +1064,13 @@
     <t xml:space="preserve">Pasta 55 só tem ANP; falta a licença</t>
   </si>
   <si>
-    <t xml:space="preserve">Alexandre's Combustíveis (Posto Gangorra)</t>
+    <t xml:space="preserve">Alexandre's Combustíveis (pasta 57)</t>
   </si>
   <si>
     <t xml:space="preserve">19.688.384/0001-05</t>
   </si>
   <si>
-    <t xml:space="preserve">Pasta 57 tem TOG, ANP, INMETRO e laudo; falta a licença</t>
+    <t xml:space="preserve">Os documentos da pasta 57 foram associados à licença do Posto Gangorra (CNPJ 03.365.159/0001-06). Confirmar se são a mesma empresa e, se não, enviar a licença do Alexandre's</t>
   </si>
   <si>
     <t xml:space="preserve">Gildo Alves de Carvalho (Posto Boa Vista)</t>
@@ -1785,20 +1806,20 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A6,Pendências!$J$2:$J$145,"Vencida")</f>
-        <v>12</v>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A6,Pendências!$J$2:$J$149,"Vencida")</f>
+        <v>13</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A6,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A6,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A6,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A6,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
         <f aca="false">SUM(B6:D6)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1806,15 +1827,15 @@
         <v>10</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A7,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A7,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>8</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A7,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A7,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A7,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A7,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>4</v>
       </c>
       <c r="E7" s="7" t="n">
@@ -1827,15 +1848,15 @@
         <v>11</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A8,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A8,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>7</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A8,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A8,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A8,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A8,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
@@ -1848,15 +1869,15 @@
         <v>12</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A9,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A9,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>5</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A9,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A9,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A9,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A9,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
@@ -1869,15 +1890,15 @@
         <v>13</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A10,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A10,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A10,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A10,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A10,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A10,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E10" s="7" t="n">
@@ -1890,20 +1911,20 @@
         <v>14</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A11,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A11,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>24</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A11,Pendências!$J$2:$J$145,"Sem data")</f>
-        <v>10</v>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A11,Pendências!$J$2:$J$149,"Sem data")</f>
+        <v>11</v>
       </c>
       <c r="D11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A11,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A11,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>4</v>
       </c>
       <c r="E11" s="7" t="n">
         <f aca="false">SUM(B11:D11)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1911,20 +1932,20 @@
         <v>15</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A12,Pendências!$J$2:$J$145,"Vencida")</f>
-        <v>38</v>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A12,Pendências!$J$2:$J$149,"Vencida")</f>
+        <v>39</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A12,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A12,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>9</v>
       </c>
       <c r="D12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A12,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A12,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
         <f aca="false">SUM(B12:D12)</f>
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1932,20 +1953,20 @@
         <v>16</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A13,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A13,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A13,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A13,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>4</v>
       </c>
       <c r="D13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A13,Pendências!$J$2:$J$145,"Vence em breve")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A13,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <v>4</v>
       </c>
       <c r="E13" s="7" t="n">
         <f aca="false">SUM(B13:D13)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1953,15 +1974,15 @@
         <v>17</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A14,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A14,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A14,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A14,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A14,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A14,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
@@ -1974,15 +1995,15 @@
         <v>18</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A15,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A15,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A15,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A15,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>4</v>
       </c>
       <c r="D15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A15,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A15,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
@@ -1995,15 +2016,15 @@
         <v>19</v>
       </c>
       <c r="B16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A16,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A16,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A16,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A16,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>3</v>
       </c>
       <c r="D16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$145,$A16,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A16,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
@@ -2017,19 +2038,19 @@
       </c>
       <c r="B17" s="8" t="n">
         <f aca="false">SUM(B6:B16)</f>
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C17" s="8" t="n">
         <f aca="false">SUM(C6:C16)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" s="8" t="n">
         <f aca="false">SUM(D6:D16)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" s="8" t="n">
         <f aca="false">SUM(E6:E16)</f>
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2042,8 +2063,8 @@
         <v>22</v>
       </c>
       <c r="B20" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$145,A20)</f>
-        <v>144</v>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$149,A20)</f>
+        <v>148</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2051,7 +2072,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$145,A21)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$149,A21)</f>
         <v>0</v>
       </c>
     </row>
@@ -2060,7 +2081,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$145,A22)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$149,A22)</f>
         <v>0</v>
       </c>
     </row>
@@ -2069,7 +2090,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$145,A23)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$149,A23)</f>
         <v>0</v>
       </c>
     </row>
@@ -2078,7 +2099,7 @@
         <v>26</v>
       </c>
       <c r="B24" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$145,A24)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$149,A24)</f>
         <v>0</v>
       </c>
     </row>
@@ -2103,7 +2124,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R145"/>
+  <dimension ref="A1:R149"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -7729,23 +7750,23 @@
         <v>266</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>46043</v>
+        <v>46238</v>
       </c>
       <c r="H112" s="10" t="s">
         <v>9</v>
       </c>
       <c r="I112" s="10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J112" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K112" s="12" t="n">
-        <v>45923</v>
+        <v>46118</v>
       </c>
       <c r="L112" s="13" t="n">
         <f aca="false">IF(K112="","",K112-Resumo!$B$3)</f>
-        <v>-395</v>
+        <v>-200</v>
       </c>
       <c r="M112" s="10" t="s">
         <v>267</v>
@@ -7765,7 +7786,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C113" s="10" t="s">
         <v>263</v>
@@ -7780,26 +7801,24 @@
         <v>266</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>46043</v>
+        <v>46238</v>
       </c>
       <c r="H113" s="10" t="s">
         <v>14</v>
       </c>
       <c r="I113" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K113" s="12" t="n">
-        <v>46113</v>
-      </c>
-      <c r="L113" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K113" s="12"/>
+      <c r="L113" s="13" t="str">
         <f aca="false">IF(K113="","",K113-Resumo!$B$3)</f>
-        <v>-205</v>
+        <v/>
       </c>
       <c r="M113" s="10" t="s">
-        <v>268</v>
+        <v>79</v>
       </c>
       <c r="N113" s="10" t="s">
         <v>54</v>
@@ -7811,7 +7830,7 @@
       <c r="Q113" s="15"/>
       <c r="R113" s="14"/>
     </row>
-    <row r="114" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="10" t="n">
         <v>113</v>
       </c>
@@ -7831,26 +7850,26 @@
         <v>266</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>46043</v>
+        <v>46238</v>
       </c>
       <c r="H114" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J114" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K114" s="12" t="n">
-        <v>45351</v>
+        <v>46280</v>
       </c>
       <c r="L114" s="13" t="n">
         <f aca="false">IF(K114="","",K114-Resumo!$B$3)</f>
-        <v>-967</v>
+        <v>-38</v>
       </c>
       <c r="M114" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N114" s="10" t="s">
         <v>58</v>
@@ -7867,44 +7886,44 @@
         <v>114</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>207</v>
+        <v>264</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>46408</v>
+        <v>46238</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I115" s="10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>46288</v>
+        <v>46340</v>
       </c>
       <c r="L115" s="13" t="n">
         <f aca="false">IF(K115="","",K115-Resumo!$B$3)</f>
-        <v>-30</v>
+        <v>22</v>
       </c>
       <c r="M115" s="10" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="O115" s="14"/>
       <c r="P115" s="14" t="s">
@@ -7913,7 +7932,7 @@
       <c r="Q115" s="15"/>
       <c r="R115" s="14"/>
     </row>
-    <row r="116" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="10" t="n">
         <v>115</v>
       </c>
@@ -7924,38 +7943,38 @@
         <v>270</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>207</v>
+        <v>271</v>
       </c>
       <c r="E116" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F116" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>46408</v>
+        <v>46043</v>
       </c>
       <c r="H116" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I116" s="10" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J116" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K116" s="12" t="n">
-        <v>46113</v>
+        <v>45923</v>
       </c>
       <c r="L116" s="13" t="n">
         <f aca="false">IF(K116="","",K116-Resumo!$B$3)</f>
-        <v>-205</v>
+        <v>-395</v>
       </c>
       <c r="M116" s="10" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="N116" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O116" s="14"/>
       <c r="P116" s="14" t="s">
@@ -7964,7 +7983,7 @@
       <c r="Q116" s="15"/>
       <c r="R116" s="14"/>
     </row>
-    <row r="117" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="10" t="n">
         <v>116</v>
       </c>
@@ -7975,38 +7994,38 @@
         <v>270</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>207</v>
+        <v>271</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>46408</v>
+        <v>46043</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I117" s="10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J117" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>46282</v>
+        <v>46113</v>
       </c>
       <c r="L117" s="13" t="n">
         <f aca="false">IF(K117="","",K117-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-205</v>
       </c>
       <c r="M117" s="10" t="s">
-        <v>74</v>
+        <v>275</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O117" s="14"/>
       <c r="P117" s="14" t="s">
@@ -8020,42 +8039,44 @@
         <v>117</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>95</v>
+        <v>271</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F118" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>46043</v>
+      </c>
+      <c r="H118" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I118" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="J118" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K118" s="12" t="n">
+        <v>45351</v>
+      </c>
+      <c r="L118" s="13" t="n">
+        <f aca="false">IF(K118="","",K118-Resumo!$B$3)</f>
+        <v>-967</v>
+      </c>
+      <c r="M118" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="G118" s="12" t="n">
-        <v>47310</v>
-      </c>
-      <c r="H118" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I118" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="J118" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K118" s="12"/>
-      <c r="L118" s="13" t="str">
-        <f aca="false">IF(K118="","",K118-Resumo!$B$3)</f>
-        <v/>
-      </c>
-      <c r="M118" s="10" t="s">
-        <v>79</v>
-      </c>
       <c r="N118" s="10" t="s">
-        <v>162</v>
+        <v>58</v>
       </c>
       <c r="O118" s="14"/>
       <c r="P118" s="14" t="s">
@@ -8064,47 +8085,49 @@
       <c r="Q118" s="15"/>
       <c r="R118" s="14"/>
     </row>
-    <row r="119" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="10" t="n">
         <v>118</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>95</v>
+        <v>207</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>47310</v>
+        <v>46408</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I119" s="10" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K119" s="12"/>
-      <c r="L119" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K119" s="12" t="n">
+        <v>46288</v>
+      </c>
+      <c r="L119" s="13" t="n">
         <f aca="false">IF(K119="","",K119-Resumo!$B$3)</f>
-        <v/>
+        <v>-30</v>
       </c>
       <c r="M119" s="10" t="s">
-        <v>79</v>
+        <v>280</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O119" s="14"/>
       <c r="P119" s="14" t="s">
@@ -8113,7 +8136,7 @@
       <c r="Q119" s="15"/>
       <c r="R119" s="14"/>
     </row>
-    <row r="120" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="10" t="n">
         <v>119</v>
       </c>
@@ -8121,41 +8144,41 @@
         <v>55</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>95</v>
+        <v>207</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F120" s="10" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>47310</v>
+        <v>46408</v>
       </c>
       <c r="H120" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I120" s="10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J120" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K120" s="12" t="n">
-        <v>46043</v>
+        <v>46113</v>
       </c>
       <c r="L120" s="13" t="n">
         <f aca="false">IF(K120="","",K120-Resumo!$B$3)</f>
-        <v>-275</v>
+        <v>-205</v>
       </c>
       <c r="M120" s="10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="N120" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O120" s="14"/>
       <c r="P120" s="14" t="s">
@@ -8164,7 +8187,7 @@
       <c r="Q120" s="15"/>
       <c r="R120" s="14"/>
     </row>
-    <row r="121" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="10" t="n">
         <v>120</v>
       </c>
@@ -8172,41 +8195,41 @@
         <v>55</v>
       </c>
       <c r="C121" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D121" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="E121" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="D121" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="E121" s="10" t="s">
+      <c r="F121" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="F121" s="10" t="s">
-        <v>280</v>
-      </c>
       <c r="G121" s="12" t="n">
-        <v>46658</v>
+        <v>46408</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I121" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J121" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>46107</v>
+        <v>46282</v>
       </c>
       <c r="L121" s="13" t="n">
         <f aca="false">IF(K121="","",K121-Resumo!$B$3)</f>
-        <v>-211</v>
+        <v>-36</v>
       </c>
       <c r="M121" s="10" t="s">
-        <v>281</v>
+        <v>74</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O121" s="14"/>
       <c r="P121" s="14" t="s">
@@ -8220,44 +8243,42 @@
         <v>121</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>46658</v>
+        <v>47310</v>
       </c>
       <c r="H122" s="10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I122" s="10" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J122" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K122" s="12" t="n">
-        <v>46280</v>
-      </c>
-      <c r="L122" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K122" s="12"/>
+      <c r="L122" s="13" t="str">
         <f aca="false">IF(K122="","",K122-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v/>
       </c>
       <c r="M122" s="10" t="s">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="N122" s="10" t="s">
-        <v>58</v>
+        <v>162</v>
       </c>
       <c r="O122" s="14"/>
       <c r="P122" s="14" t="s">
@@ -8266,7 +8287,7 @@
       <c r="Q122" s="15"/>
       <c r="R122" s="14"/>
     </row>
-    <row r="123" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="10" t="n">
         <v>122</v>
       </c>
@@ -8274,25 +8295,25 @@
         <v>45</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>46658</v>
+        <v>47310</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I123" s="10" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J123" s="10" t="s">
         <v>6</v>
@@ -8306,7 +8327,7 @@
         <v>79</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="O123" s="14"/>
       <c r="P123" s="14" t="s">
@@ -8315,7 +8336,7 @@
       <c r="Q123" s="15"/>
       <c r="R123" s="14"/>
     </row>
-    <row r="124" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="10" t="n">
         <v>123</v>
       </c>
@@ -8323,41 +8344,41 @@
         <v>55</v>
       </c>
       <c r="C124" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D124" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E124" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="D124" s="10" t="s">
+      <c r="F124" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="E124" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="F124" s="10" t="s">
-        <v>285</v>
-      </c>
       <c r="G124" s="12" t="n">
-        <v>47016</v>
+        <v>47310</v>
       </c>
       <c r="H124" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I124" s="10" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J124" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K124" s="12" t="n">
-        <v>46113</v>
+        <v>46043</v>
       </c>
       <c r="L124" s="13" t="n">
         <f aca="false">IF(K124="","",K124-Resumo!$B$3)</f>
-        <v>-205</v>
+        <v>-275</v>
       </c>
       <c r="M124" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="N124" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O124" s="14"/>
       <c r="P124" s="14" t="s">
@@ -8366,7 +8387,7 @@
       <c r="Q124" s="15"/>
       <c r="R124" s="14"/>
     </row>
-    <row r="125" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="10" t="n">
         <v>124</v>
       </c>
@@ -8374,41 +8395,41 @@
         <v>55</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>283</v>
+        <v>158</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>47016</v>
+        <v>46658</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I125" s="10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J125" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>45519</v>
+        <v>46107</v>
       </c>
       <c r="L125" s="13" t="n">
         <f aca="false">IF(K125="","",K125-Resumo!$B$3)</f>
-        <v>-799</v>
+        <v>-211</v>
       </c>
       <c r="M125" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O125" s="14"/>
       <c r="P125" s="14" t="s">
@@ -8422,44 +8443,44 @@
         <v>125</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>283</v>
+        <v>158</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F126" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>47016</v>
+        <v>46658</v>
       </c>
       <c r="H126" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I126" s="10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J126" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K126" s="12" t="n">
-        <v>46339</v>
+        <v>46280</v>
       </c>
       <c r="L126" s="13" t="n">
         <f aca="false">IF(K126="","",K126-Resumo!$B$3)</f>
-        <v>21</v>
+        <v>-38</v>
       </c>
       <c r="M126" s="10" t="s">
-        <v>288</v>
+        <v>231</v>
       </c>
       <c r="N126" s="10" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="O126" s="14"/>
       <c r="P126" s="14" t="s">
@@ -8473,44 +8494,42 @@
         <v>126</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>290</v>
+        <v>158</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>46332</v>
+        <v>46658</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I127" s="10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K127" s="12" t="n">
-        <v>46212</v>
-      </c>
-      <c r="L127" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K127" s="12"/>
+      <c r="L127" s="13" t="str">
         <f aca="false">IF(K127="","",K127-Resumo!$B$3)</f>
-        <v>-106</v>
+        <v/>
       </c>
       <c r="M127" s="10" t="s">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="O127" s="14"/>
       <c r="P127" s="14" t="s">
@@ -8519,12 +8538,12 @@
       <c r="Q127" s="15"/>
       <c r="R127" s="14"/>
     </row>
-    <row r="128" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="10" t="n">
         <v>127</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>289</v>
@@ -8539,29 +8558,29 @@
         <v>292</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>46332</v>
+        <v>47016</v>
       </c>
       <c r="H128" s="10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I128" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J128" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K128" s="12" t="n">
-        <v>46248</v>
+        <v>46113</v>
       </c>
       <c r="L128" s="13" t="n">
         <f aca="false">IF(K128="","",K128-Resumo!$B$3)</f>
-        <v>-70</v>
+        <v>-205</v>
       </c>
       <c r="M128" s="10" t="s">
-        <v>85</v>
+        <v>293</v>
       </c>
       <c r="N128" s="10" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="O128" s="14"/>
       <c r="P128" s="14" t="s">
@@ -8570,7 +8589,7 @@
       <c r="Q128" s="15"/>
       <c r="R128" s="14"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="10" t="n">
         <v>128</v>
       </c>
@@ -8590,29 +8609,29 @@
         <v>292</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>46332</v>
+        <v>47016</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I129" s="10" t="n">
         <v>16</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>46328</v>
+        <v>45519</v>
       </c>
       <c r="L129" s="13" t="n">
         <f aca="false">IF(K129="","",K129-Resumo!$B$3)</f>
-        <v>10</v>
+        <v>-799</v>
       </c>
       <c r="M129" s="10" t="s">
-        <v>87</v>
+        <v>294</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="O129" s="14"/>
       <c r="P129" s="14" t="s">
@@ -8621,12 +8640,12 @@
       <c r="Q129" s="15"/>
       <c r="R129" s="14"/>
     </row>
-    <row r="130" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="10" t="n">
         <v>129</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>289</v>
@@ -8641,29 +8660,29 @@
         <v>292</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>46332</v>
+        <v>47016</v>
       </c>
       <c r="H130" s="10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I130" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K130" s="12" t="n">
-        <v>46259</v>
+        <v>46339</v>
       </c>
       <c r="L130" s="13" t="n">
         <f aca="false">IF(K130="","",K130-Resumo!$B$3)</f>
-        <v>-59</v>
+        <v>21</v>
       </c>
       <c r="M130" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N130" s="10" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="O130" s="14"/>
       <c r="P130" s="14" t="s">
@@ -8680,41 +8699,41 @@
         <v>55</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="G131" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I131" s="10" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J131" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>46280</v>
+        <v>46212</v>
       </c>
       <c r="L131" s="13" t="n">
         <f aca="false">IF(K131="","",K131-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>-106</v>
       </c>
       <c r="M131" s="10" t="s">
-        <v>231</v>
+        <v>300</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O131" s="14"/>
       <c r="P131" s="14" t="s">
@@ -8728,42 +8747,44 @@
         <v>131</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="G132" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H132" s="10" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I132" s="10" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J132" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K132" s="12"/>
-      <c r="L132" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K132" s="12" t="n">
+        <v>46248</v>
+      </c>
+      <c r="L132" s="13" t="n">
         <f aca="false">IF(K132="","",K132-Resumo!$B$3)</f>
-        <v/>
+        <v>-70</v>
       </c>
       <c r="M132" s="10" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="N132" s="10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="O132" s="14"/>
       <c r="P132" s="14" t="s">
@@ -8772,49 +8793,49 @@
       <c r="Q132" s="15"/>
       <c r="R132" s="14"/>
     </row>
-    <row r="133" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="10" t="n">
         <v>132</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>48215</v>
+        <v>46332</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I133" s="10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J133" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>46034</v>
+        <v>46328</v>
       </c>
       <c r="L133" s="13" t="n">
         <f aca="false">IF(K133="","",K133-Resumo!$B$3)</f>
-        <v>-284</v>
+        <v>10</v>
       </c>
       <c r="M133" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="O133" s="14"/>
       <c r="P133" s="14" t="s">
@@ -8823,49 +8844,49 @@
       <c r="Q133" s="15"/>
       <c r="R133" s="14"/>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="10" t="n">
         <v>133</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>48215</v>
+        <v>46332</v>
       </c>
       <c r="H134" s="10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I134" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J134" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K134" s="12" t="n">
-        <v>46114</v>
+        <v>46259</v>
       </c>
       <c r="L134" s="13" t="n">
         <f aca="false">IF(K134="","",K134-Resumo!$B$3)</f>
-        <v>-204</v>
+        <v>-59</v>
       </c>
       <c r="M134" s="10" t="s">
-        <v>87</v>
+        <v>301</v>
       </c>
       <c r="N134" s="10" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="O134" s="14"/>
       <c r="P134" s="14" t="s">
@@ -8874,7 +8895,7 @@
       <c r="Q134" s="15"/>
       <c r="R134" s="14"/>
     </row>
-    <row r="135" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="10" t="n">
         <v>134</v>
       </c>
@@ -8882,41 +8903,41 @@
         <v>55</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>48215</v>
+        <v>46332</v>
       </c>
       <c r="H135" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I135" s="10" t="n">
         <v>14</v>
-      </c>
-      <c r="I135" s="10" t="n">
-        <v>5</v>
       </c>
       <c r="J135" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="L135" s="13" t="n">
         <f aca="false">IF(K135="","",K135-Resumo!$B$3)</f>
-        <v>-42</v>
+        <v>-38</v>
       </c>
       <c r="M135" s="10" t="s">
-        <v>299</v>
+        <v>231</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O135" s="14"/>
       <c r="P135" s="14" t="s">
@@ -8933,25 +8954,25 @@
         <v>45</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D136" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F136" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>48215</v>
+        <v>46332</v>
       </c>
       <c r="H136" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I136" s="10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J136" s="10" t="s">
         <v>6</v>
@@ -8965,7 +8986,7 @@
         <v>79</v>
       </c>
       <c r="N136" s="10" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="O136" s="14"/>
       <c r="P136" s="14" t="s">
@@ -8979,42 +9000,44 @@
         <v>136</v>
       </c>
       <c r="B137" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="G137" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I137" s="10" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J137" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K137" s="12"/>
-      <c r="L137" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K137" s="12" t="n">
+        <v>46034</v>
+      </c>
+      <c r="L137" s="13" t="n">
         <f aca="false">IF(K137="","",K137-Resumo!$B$3)</f>
-        <v/>
+        <v>-284</v>
       </c>
       <c r="M137" s="10" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="O137" s="14"/>
       <c r="P137" s="14" t="s">
@@ -9023,47 +9046,49 @@
       <c r="Q137" s="15"/>
       <c r="R137" s="14"/>
     </row>
-    <row r="138" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="10" t="n">
         <v>137</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="D138" s="10" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E138" s="10" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F138" s="10" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="G138" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H138" s="10" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I138" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J138" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K138" s="12"/>
-      <c r="L138" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K138" s="12" t="n">
+        <v>46114</v>
+      </c>
+      <c r="L138" s="13" t="n">
         <f aca="false">IF(K138="","",K138-Resumo!$B$3)</f>
-        <v/>
+        <v>-204</v>
       </c>
       <c r="M138" s="10" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="N138" s="10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O138" s="14"/>
       <c r="P138" s="14" t="s">
@@ -9072,47 +9097,49 @@
       <c r="Q138" s="15"/>
       <c r="R138" s="14"/>
     </row>
-    <row r="139" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="10" t="n">
         <v>138</v>
       </c>
       <c r="B139" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="D139" s="10" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F139" s="10" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="G139" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I139" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J139" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K139" s="12"/>
-      <c r="L139" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K139" s="12" t="n">
+        <v>46276</v>
+      </c>
+      <c r="L139" s="13" t="n">
         <f aca="false">IF(K139="","",K139-Resumo!$B$3)</f>
-        <v/>
+        <v>-42</v>
       </c>
       <c r="M139" s="10" t="s">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="O139" s="14"/>
       <c r="P139" s="14" t="s">
@@ -9129,39 +9156,39 @@
         <v>45</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>198</v>
+        <v>303</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F140" s="10" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>47697</v>
+        <v>48215</v>
       </c>
       <c r="H140" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I140" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="I140" s="10" t="n">
+        <v>15</v>
+      </c>
       <c r="J140" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K140" s="12" t="n">
-        <v>46344</v>
-      </c>
-      <c r="L140" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K140" s="12"/>
+      <c r="L140" s="13" t="str">
         <f aca="false">IF(K140="","",K140-Resumo!$B$3)</f>
-        <v>26</v>
+        <v/>
       </c>
       <c r="M140" s="10" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="N140" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O140" s="14"/>
       <c r="P140" s="14" t="s">
@@ -9170,49 +9197,47 @@
       <c r="Q140" s="15"/>
       <c r="R140" s="14"/>
     </row>
-    <row r="141" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="10" t="n">
         <v>140</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>198</v>
+        <v>303</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>47697</v>
+        <v>48215</v>
       </c>
       <c r="H141" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I141" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="I141" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="J141" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K141" s="12" t="n">
-        <v>46127</v>
-      </c>
-      <c r="L141" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K141" s="12"/>
+      <c r="L141" s="13" t="str">
         <f aca="false">IF(K141="","",K141-Resumo!$B$3)</f>
-        <v>-191</v>
+        <v/>
       </c>
       <c r="M141" s="10" t="s">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="O141" s="14"/>
       <c r="P141" s="14" t="s">
@@ -9226,44 +9251,42 @@
         <v>141</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>198</v>
+        <v>303</v>
       </c>
       <c r="E142" s="10" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F142" s="10" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>47697</v>
+        <v>48215</v>
       </c>
       <c r="H142" s="10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I142" s="10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K142" s="12" t="n">
-        <v>46282</v>
-      </c>
-      <c r="L142" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K142" s="12"/>
+      <c r="L142" s="13" t="str">
         <f aca="false">IF(K142="","",K142-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v/>
       </c>
       <c r="M142" s="10" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="N142" s="10" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="O142" s="14"/>
       <c r="P142" s="14" t="s">
@@ -9277,44 +9300,42 @@
         <v>142</v>
       </c>
       <c r="B143" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C143" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="D143" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="D143" s="10" t="s">
+      <c r="E143" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="E143" s="10" t="s">
+      <c r="F143" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="F143" s="10" t="s">
-        <v>306</v>
-      </c>
       <c r="G143" s="12" t="n">
-        <v>46244</v>
+        <v>48215</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I143" s="10" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J143" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K143" s="12" t="n">
-        <v>46124</v>
-      </c>
-      <c r="L143" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K143" s="12"/>
+      <c r="L143" s="13" t="str">
         <f aca="false">IF(K143="","",K143-Resumo!$B$3)</f>
-        <v>-194</v>
+        <v/>
       </c>
       <c r="M143" s="10" t="s">
-        <v>307</v>
+        <v>79</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="O143" s="14"/>
       <c r="P143" s="14" t="s">
@@ -9323,49 +9344,47 @@
       <c r="Q143" s="15"/>
       <c r="R143" s="14"/>
     </row>
-    <row r="144" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="10" t="n">
         <v>143</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>304</v>
+        <v>198</v>
       </c>
       <c r="E144" s="10" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F144" s="10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>46244</v>
+        <v>47697</v>
       </c>
       <c r="H144" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I144" s="10" t="n">
-        <v>5</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I144" s="10"/>
       <c r="J144" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K144" s="12" t="n">
-        <v>46276</v>
+        <v>46344</v>
       </c>
       <c r="L144" s="13" t="n">
         <f aca="false">IF(K144="","",K144-Resumo!$B$3)</f>
-        <v>-42</v>
+        <v>26</v>
       </c>
       <c r="M144" s="10" t="s">
-        <v>299</v>
+        <v>51</v>
       </c>
       <c r="N144" s="10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O144" s="14"/>
       <c r="P144" s="14" t="s">
@@ -9374,47 +9393,49 @@
       <c r="Q144" s="15"/>
       <c r="R144" s="14"/>
     </row>
-    <row r="145" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="10" t="n">
         <v>144</v>
       </c>
       <c r="B145" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>304</v>
+        <v>198</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F145" s="10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>46244</v>
+        <v>47697</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I145" s="10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J145" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K145" s="12"/>
-      <c r="L145" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K145" s="12" t="n">
+        <v>46127</v>
+      </c>
+      <c r="L145" s="13" t="n">
         <f aca="false">IF(K145="","",K145-Resumo!$B$3)</f>
-        <v/>
+        <v>-191</v>
       </c>
       <c r="M145" s="10" t="s">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O145" s="14"/>
       <c r="P145" s="14" t="s">
@@ -9423,9 +9444,211 @@
       <c r="Q145" s="15"/>
       <c r="R145" s="14"/>
     </row>
+    <row r="146" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="10" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C146" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="D146" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="E146" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="F146" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>47697</v>
+      </c>
+      <c r="H146" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I146" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="J146" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K146" s="12" t="n">
+        <v>46282</v>
+      </c>
+      <c r="L146" s="13" t="n">
+        <f aca="false">IF(K146="","",K146-Resumo!$B$3)</f>
+        <v>-36</v>
+      </c>
+      <c r="M146" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="N146" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O146" s="14"/>
+      <c r="P146" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q146" s="15"/>
+      <c r="R146" s="14"/>
+    </row>
+    <row r="147" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="10" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C147" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="D147" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="E147" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="F147" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H147" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I147" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="J147" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K147" s="12" t="n">
+        <v>46124</v>
+      </c>
+      <c r="L147" s="13" t="n">
+        <f aca="false">IF(K147="","",K147-Resumo!$B$3)</f>
+        <v>-194</v>
+      </c>
+      <c r="M147" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="N147" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="O147" s="14"/>
+      <c r="P147" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q147" s="15"/>
+      <c r="R147" s="14"/>
+    </row>
+    <row r="148" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="10" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="D148" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="E148" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="F148" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H148" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I148" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J148" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K148" s="12" t="n">
+        <v>46276</v>
+      </c>
+      <c r="L148" s="13" t="n">
+        <f aca="false">IF(K148="","",K148-Resumo!$B$3)</f>
+        <v>-42</v>
+      </c>
+      <c r="M148" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="N148" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="O148" s="14"/>
+      <c r="P148" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q148" s="15"/>
+      <c r="R148" s="14"/>
+    </row>
+    <row r="149" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="10" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C149" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="D149" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="E149" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="F149" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H149" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I149" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="J149" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K149" s="12"/>
+      <c r="L149" s="13" t="str">
+        <f aca="false">IF(K149="","",K149-Resumo!$B$3)</f>
+        <v/>
+      </c>
+      <c r="M149" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N149" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O149" s="14"/>
+      <c r="P149" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q149" s="15"/>
+      <c r="R149" s="14"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R145"/>
-  <conditionalFormatting sqref="J2:J145">
+  <autoFilter ref="A1:R149"/>
+  <conditionalFormatting sqref="J2:J149">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$J2="Vencida"</formula>
     </cfRule>
@@ -9436,12 +9659,12 @@
       <formula>$J2="Sem data"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B145">
+  <conditionalFormatting sqref="B2:B149">
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>$B2="Alta"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P145">
+  <conditionalFormatting sqref="P2:P149">
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>$P2="Resolvido"</formula>
     </cfRule>
@@ -9450,7 +9673,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P145" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P149" type="list">
       <formula1>"A fazer,Em andamento,Aguardando cliente,Resolvido,Já estava em dia"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9471,7 +9694,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -9495,7 +9718,7 @@
         <v>8</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9503,15 +9726,15 @@
         <v>46</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A2,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A2,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A2,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A2,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A2,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A2,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>2</v>
       </c>
       <c r="E2" s="7" t="n">
@@ -9519,7 +9742,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A2,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A2,Pendências!$B$2:$B$149,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9528,15 +9751,15 @@
         <v>59</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A3,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A3,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A3,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A3,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A3,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A3,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E3" s="7" t="n">
@@ -9544,7 +9767,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A3,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A3,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9553,15 +9776,15 @@
         <v>64</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A4,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A4,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A4,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A4,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A4,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A4,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
@@ -9569,7 +9792,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A4,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A4,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9578,15 +9801,15 @@
         <v>69</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A5,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A5,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A5,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A5,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A5,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A5,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
@@ -9594,7 +9817,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A5,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A5,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9603,15 +9826,15 @@
         <v>75</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A6,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A6,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A6,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A6,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A6,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A6,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
@@ -9619,7 +9842,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A6,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A6,Pendências!$B$2:$B$149,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -9628,15 +9851,15 @@
         <v>81</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A7,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A7,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>5</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A7,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A7,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A7,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A7,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
@@ -9644,7 +9867,7 @@
         <v>7</v>
       </c>
       <c r="F7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A7,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A7,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9653,15 +9876,15 @@
         <v>94</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A8,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A8,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A8,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A8,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A8,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A8,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
@@ -9669,7 +9892,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A8,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A8,Pendências!$B$2:$B$149,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9678,15 +9901,15 @@
         <v>101</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A9,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A9,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A9,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A9,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A9,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A9,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
@@ -9694,7 +9917,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A9,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A9,Pendências!$B$2:$B$149,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -9703,15 +9926,15 @@
         <v>105</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A10,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A10,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A10,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A10,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A10,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A10,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E10" s="7" t="n">
@@ -9719,7 +9942,7 @@
         <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A10,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A10,Pendências!$B$2:$B$149,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9728,15 +9951,15 @@
         <v>111</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A11,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A11,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A11,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A11,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A11,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A11,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E11" s="7" t="n">
@@ -9744,7 +9967,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A11,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A11,Pendências!$B$2:$B$149,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -9753,15 +9976,15 @@
         <v>115</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A12,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A12,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A12,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A12,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A12,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A12,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
@@ -9769,7 +9992,7 @@
         <v>6</v>
       </c>
       <c r="F12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A12,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A12,Pendências!$B$2:$B$149,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9778,15 +10001,15 @@
         <v>119</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A13,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A13,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A13,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A13,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A13,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A13,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
@@ -9794,7 +10017,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A13,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A13,Pendências!$B$2:$B$149,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9803,15 +10026,15 @@
         <v>123</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A14,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A14,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A14,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A14,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A14,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A14,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
@@ -9819,7 +10042,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A14,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A14,Pendências!$B$2:$B$149,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9828,15 +10051,15 @@
         <v>127</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A15,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A15,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A15,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A15,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A15,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A15,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
@@ -9844,7 +10067,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A15,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A15,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9853,15 +10076,15 @@
         <v>132</v>
       </c>
       <c r="B16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A16,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A16,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A16,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A16,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A16,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A16,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
@@ -9869,7 +10092,7 @@
         <v>4</v>
       </c>
       <c r="F16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A16,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A16,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9878,15 +10101,15 @@
         <v>139</v>
       </c>
       <c r="B17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A17,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A17,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A17,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A17,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A17,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A17,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
@@ -9894,7 +10117,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A17,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A17,Pendências!$B$2:$B$149,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9903,15 +10126,15 @@
         <v>143</v>
       </c>
       <c r="B18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A18,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A18,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>4</v>
       </c>
       <c r="C18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A18,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A18,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A18,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A18,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
@@ -9919,7 +10142,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A18,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A18,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9928,15 +10151,15 @@
         <v>148</v>
       </c>
       <c r="B19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A19,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A19,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A19,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A19,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A19,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A19,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
@@ -9944,7 +10167,7 @@
         <v>4</v>
       </c>
       <c r="F19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A19,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A19,Pendências!$B$2:$B$149,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9953,15 +10176,15 @@
         <v>154</v>
       </c>
       <c r="B20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A20,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A20,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A20,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A20,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A20,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A20,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E20" s="7" t="n">
@@ -9969,7 +10192,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A20,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A20,Pendências!$B$2:$B$149,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9978,15 +10201,15 @@
         <v>157</v>
       </c>
       <c r="B21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A21,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A21,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A21,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A21,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A21,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A21,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
@@ -9994,7 +10217,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A21,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A21,Pendências!$B$2:$B$149,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -10003,15 +10226,15 @@
         <v>163</v>
       </c>
       <c r="B22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A22,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A22,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A22,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A22,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A22,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A22,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E22" s="7" t="n">
@@ -10019,7 +10242,7 @@
         <v>3</v>
       </c>
       <c r="F22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A22,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A22,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -10028,15 +10251,15 @@
         <v>166</v>
       </c>
       <c r="B23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A23,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A23,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A23,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A23,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A23,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A23,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
@@ -10044,7 +10267,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A23,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A23,Pendências!$B$2:$B$149,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -10053,15 +10276,15 @@
         <v>170</v>
       </c>
       <c r="B24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A24,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A24,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A24,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A24,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A24,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A24,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E24" s="7" t="n">
@@ -10069,7 +10292,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A24,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A24,Pendências!$B$2:$B$149,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -10078,15 +10301,15 @@
         <v>174</v>
       </c>
       <c r="B25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A25,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A25,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A25,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A25,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A25,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A25,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
@@ -10094,7 +10317,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A25,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A25,Pendências!$B$2:$B$149,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -10103,15 +10326,15 @@
         <v>178</v>
       </c>
       <c r="B26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A26,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A26,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A26,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A26,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A26,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A26,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E26" s="7" t="n">
@@ -10119,7 +10342,7 @@
         <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A26,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A26,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -10128,15 +10351,15 @@
         <v>183</v>
       </c>
       <c r="B27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A27,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A27,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A27,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A27,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A27,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A27,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
@@ -10144,7 +10367,7 @@
         <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A27,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A27,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -10153,15 +10376,15 @@
         <v>188</v>
       </c>
       <c r="B28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A28,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A28,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A28,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A28,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A28,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A28,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E28" s="7" t="n">
@@ -10169,7 +10392,7 @@
         <v>3</v>
       </c>
       <c r="F28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A28,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A28,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -10178,15 +10401,15 @@
         <v>193</v>
       </c>
       <c r="B29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A29,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A29,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A29,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A29,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A29,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A29,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
@@ -10194,7 +10417,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A29,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A29,Pendências!$B$2:$B$149,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -10203,15 +10426,15 @@
         <v>197</v>
       </c>
       <c r="B30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A30,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A30,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>5</v>
       </c>
       <c r="C30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A30,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A30,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A30,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A30,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E30" s="7" t="n">
@@ -10219,7 +10442,7 @@
         <v>5</v>
       </c>
       <c r="F30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A30,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A30,Pendências!$B$2:$B$149,"Alta")</f>
         <v>3</v>
       </c>
     </row>
@@ -10228,15 +10451,15 @@
         <v>206</v>
       </c>
       <c r="B31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A31,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A31,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A31,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A31,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A31,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A31,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
@@ -10244,7 +10467,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A31,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A31,Pendências!$B$2:$B$149,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -10253,15 +10476,15 @@
         <v>210</v>
       </c>
       <c r="B32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A32,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A32,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A32,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A32,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A32,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A32,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E32" s="7" t="n">
@@ -10269,7 +10492,7 @@
         <v>3</v>
       </c>
       <c r="F32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A32,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A32,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -10278,15 +10501,15 @@
         <v>215</v>
       </c>
       <c r="B33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A33,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A33,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A33,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A33,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A33,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A33,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
@@ -10294,7 +10517,7 @@
         <v>4</v>
       </c>
       <c r="F33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A33,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A33,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -10303,15 +10526,15 @@
         <v>222</v>
       </c>
       <c r="B34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A34,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A34,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A34,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A34,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A34,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A34,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E34" s="7" t="n">
@@ -10319,7 +10542,7 @@
         <v>3</v>
       </c>
       <c r="F34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A34,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A34,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -10328,15 +10551,15 @@
         <v>227</v>
       </c>
       <c r="B35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A35,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A35,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A35,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A35,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A35,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A35,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E35" s="7" t="n">
@@ -10344,7 +10567,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A35,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A35,Pendências!$B$2:$B$149,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -10353,15 +10576,15 @@
         <v>233</v>
       </c>
       <c r="B36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A36,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A36,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>4</v>
       </c>
       <c r="C36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A36,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A36,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A36,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A36,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E36" s="7" t="n">
@@ -10369,7 +10592,7 @@
         <v>4</v>
       </c>
       <c r="F36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A36,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A36,Pendências!$B$2:$B$149,"Alta")</f>
         <v>3</v>
       </c>
     </row>
@@ -10378,15 +10601,15 @@
         <v>239</v>
       </c>
       <c r="B37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A37,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A37,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A37,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A37,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A37,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A37,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E37" s="7" t="n">
@@ -10394,7 +10617,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A37,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A37,Pendências!$B$2:$B$149,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -10403,15 +10626,15 @@
         <v>242</v>
       </c>
       <c r="B38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A38,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A38,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A38,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A38,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A38,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A38,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E38" s="7" t="n">
@@ -10419,7 +10642,7 @@
         <v>3</v>
       </c>
       <c r="F38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A38,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A38,Pendências!$B$2:$B$149,"Alta")</f>
         <v>3</v>
       </c>
     </row>
@@ -10428,15 +10651,15 @@
         <v>247</v>
       </c>
       <c r="B39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A39,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A39,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A39,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A39,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A39,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A39,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
@@ -10444,7 +10667,7 @@
         <v>2</v>
       </c>
       <c r="F39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A39,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A39,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -10453,15 +10676,15 @@
         <v>252</v>
       </c>
       <c r="B40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A40,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A40,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A40,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A40,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A40,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A40,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E40" s="7" t="n">
@@ -10469,7 +10692,7 @@
         <v>3</v>
       </c>
       <c r="F40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A40,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A40,Pendências!$B$2:$B$149,"Alta")</f>
         <v>3</v>
       </c>
     </row>
@@ -10478,15 +10701,15 @@
         <v>258</v>
       </c>
       <c r="B41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A41,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A41,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A41,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A41,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A41,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A41,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E41" s="7" t="n">
@@ -10494,7 +10717,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A41,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A41,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -10503,24 +10726,24 @@
         <v>263</v>
       </c>
       <c r="B42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A42,Pendências!$J$2:$J$145,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A42,Pendências!$J$2:$J$149,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A42,Pendências!$J$2:$J$145,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A42,Pendências!$J$2:$J$149,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A42,Pendências!$J$2:$J$145,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A42,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E42" s="7" t="n">
         <f aca="false">SUM(B42:D42)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A42,Pendências!$B$2:$B$145,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A42,Pendências!$B$2:$B$149,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10528,15 +10751,15 @@
         <v>270</v>
       </c>
       <c r="B43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A43,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A43,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A43,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A43,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A43,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A43,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
@@ -10544,24 +10767,24 @@
         <v>3</v>
       </c>
       <c r="F43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A43,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A43,Pendências!$B$2:$B$149,"Alta")</f>
         <v>3</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A44,Pendências!$J$2:$J$145,"Vencida")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A44,Pendências!$J$2:$J$149,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A44,Pendências!$J$2:$J$145,"Sem data")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A44,Pendências!$J$2:$J$149,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A44,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A44,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E44" s="7" t="n">
@@ -10569,24 +10792,24 @@
         <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A44,Pendências!$B$2:$B$145,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A44,Pendências!$B$2:$B$149,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A45,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A45,Pendências!$J$2:$J$149,"Vencida")</f>
+        <v>1</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A45,Pendências!$J$2:$J$149,"Sem data")</f>
         <v>2</v>
       </c>
-      <c r="C45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A45,Pendências!$J$2:$J$145,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A45,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A45,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E45" s="7" t="n">
@@ -10594,32 +10817,32 @@
         <v>3</v>
       </c>
       <c r="F45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A45,Pendências!$B$2:$B$145,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A45,Pendências!$B$2:$B$149,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A46,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A46,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A46,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A46,Pendências!$J$2:$J$149,"Sem data")</f>
+        <v>1</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A46,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
-      </c>
-      <c r="D46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A46,Pendências!$J$2:$J$145,"Vence em breve")</f>
-        <v>1</v>
       </c>
       <c r="E46" s="7" t="n">
         <f aca="false">SUM(B46:D46)</f>
         <v>3</v>
       </c>
       <c r="F46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A46,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A46,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -10628,103 +10851,128 @@
         <v>289</v>
       </c>
       <c r="B47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A47,Pendências!$J$2:$J$145,"Vencida")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A47,Pendências!$J$2:$J$149,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A47,Pendências!$J$2:$J$145,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A47,Pendências!$J$2:$J$149,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A47,Pendências!$J$2:$J$145,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A47,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E47" s="7" t="n">
         <f aca="false">SUM(B47:D47)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A47,Pendências!$B$2:$B$145,"Alta")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A47,Pendências!$B$2:$B$149,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B48" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A48,Pendências!$J$2:$J$145,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A48,Pendências!$J$2:$J$149,"Vencida")</f>
+        <v>4</v>
       </c>
       <c r="C48" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A48,Pendências!$J$2:$J$145,"Sem data")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A48,Pendências!$J$2:$J$149,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D48" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A48,Pendências!$J$2:$J$145,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A48,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E48" s="7" t="n">
         <f aca="false">SUM(B48:D48)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F48" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A48,Pendências!$B$2:$B$145,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A48,Pendências!$B$2:$B$149,"Alta")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B49" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A49,Pendências!$J$2:$J$145,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A49,Pendências!$J$2:$J$149,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C49" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A49,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A49,Pendências!$J$2:$J$149,"Sem data")</f>
+        <v>4</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A49,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>0</v>
-      </c>
-      <c r="D49" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A49,Pendências!$J$2:$J$145,"Vence em breve")</f>
-        <v>1</v>
       </c>
       <c r="E49" s="7" t="n">
         <f aca="false">SUM(B49:D49)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F49" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A49,Pendências!$B$2:$B$145,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A49,Pendências!$B$2:$B$149,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B50" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A50,Pendências!$J$2:$J$145,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A50,Pendências!$J$2:$J$149,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C50" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A50,Pendências!$J$2:$J$145,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A50,Pendências!$J$2:$J$149,"Sem data")</f>
+        <v>0</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A50,Pendências!$J$2:$J$149,"Vence em breve")</f>
         <v>1</v>
-      </c>
-      <c r="D50" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A50,Pendências!$J$2:$J$145,"Vence em breve")</f>
-        <v>0</v>
       </c>
       <c r="E50" s="7" t="n">
         <f aca="false">SUM(B50:D50)</f>
         <v>3</v>
       </c>
       <c r="F50" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$145,$A50,Pendências!$B$2:$B$145,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A50,Pendências!$B$2:$B$149,"Alta")</f>
         <v>2</v>
       </c>
     </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="B51" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A51,Pendências!$J$2:$J$149,"Vencida")</f>
+        <v>2</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A51,Pendências!$J$2:$J$149,"Sem data")</f>
+        <v>1</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A51,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <v>0</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <f aca="false">SUM(B51:D51)</f>
+        <v>3</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A51,Pendências!$B$2:$B$149,"Alta")</f>
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F50"/>
+  <autoFilter ref="A1:F51"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -10769,167 +11017,167 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>107</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>

--- a/pendencias-condicionantes-2026-10-23.xlsx
+++ b/pendencias-condicionantes-2026-10-23.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Licenças que faltam" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Pendências!$A$1:$R$149</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Por empresa'!$A$1:$F$51</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Pendências!$A$1:$R$152</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Por empresa'!$A$1:$F$52</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="360">
   <si>
     <t xml:space="preserve">Condicionantes ambientais – pendências</t>
   </si>
@@ -578,6 +578,24 @@
     <t xml:space="preserve">Documento na pasta: AVCB nº 55769 emitido em 29/08/2024</t>
   </si>
   <si>
+    <t xml:space="preserve">Gildo Alves De Carvalho — Posto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEVERIANO MELO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04.993.854/0001-77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-156929/TEC/LO-0268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licença vale até 08/02/2027 (pedido ≥120 dias antes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documento na pasta: AVCB nº 60927 emitido em 22/04/2025</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gomes Comercio De Combustiveis Ltda</t>
   </si>
   <si>
@@ -1071,15 +1089,6 @@
   </si>
   <si>
     <t xml:space="preserve">Os documentos da pasta 57 foram associados à licença do Posto Gangorra (CNPJ 03.365.159/0001-06). Confirmar se são a mesma empresa e, se não, enviar a licença do Alexandre's</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gildo Alves de Carvalho (Posto Boa Vista)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04.993.854/0001-77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temos só a licença de transporte; falta a licença do posto</t>
   </si>
   <si>
     <t xml:space="preserve">Comercial Freitas (Posto Esperança, Almino Afonso)</t>
@@ -1806,20 +1815,20 @@
         <v>9</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A6,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>13</v>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A6,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>14</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A6,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A6,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A6,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A6,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
         <f aca="false">SUM(B6:D6)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1827,15 +1836,15 @@
         <v>10</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A7,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A7,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>8</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A7,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A7,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A7,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A7,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>4</v>
       </c>
       <c r="E7" s="7" t="n">
@@ -1848,15 +1857,15 @@
         <v>11</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A8,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A8,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>7</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A8,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A8,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A8,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A8,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
@@ -1869,15 +1878,15 @@
         <v>12</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A9,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A9,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>5</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A9,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A9,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A9,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A9,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
@@ -1890,15 +1899,15 @@
         <v>13</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A10,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A10,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A10,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A10,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A10,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A10,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E10" s="7" t="n">
@@ -1911,20 +1920,20 @@
         <v>14</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A11,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>24</v>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A11,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>25</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A11,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A11,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>11</v>
       </c>
       <c r="D11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A11,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A11,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>4</v>
       </c>
       <c r="E11" s="7" t="n">
         <f aca="false">SUM(B11:D11)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1932,20 +1941,20 @@
         <v>15</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A12,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>39</v>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A12,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>40</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A12,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A12,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>9</v>
       </c>
       <c r="D12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A12,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A12,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
         <f aca="false">SUM(B12:D12)</f>
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1953,15 +1962,15 @@
         <v>16</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A13,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A13,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A13,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A13,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>4</v>
       </c>
       <c r="D13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A13,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A13,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>4</v>
       </c>
       <c r="E13" s="7" t="n">
@@ -1974,15 +1983,15 @@
         <v>17</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A14,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A14,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A14,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A14,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A14,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A14,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
@@ -1995,15 +2004,15 @@
         <v>18</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A15,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A15,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A15,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A15,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>4</v>
       </c>
       <c r="D15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A15,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A15,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
@@ -2016,15 +2025,15 @@
         <v>19</v>
       </c>
       <c r="B16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A16,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A16,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A16,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A16,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>3</v>
       </c>
       <c r="D16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$H$2:$H$149,$A16,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$H$2:$H$152,$A16,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
@@ -2038,7 +2047,7 @@
       </c>
       <c r="B17" s="8" t="n">
         <f aca="false">SUM(B6:B16)</f>
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C17" s="8" t="n">
         <f aca="false">SUM(C6:C16)</f>
@@ -2050,7 +2059,7 @@
       </c>
       <c r="E17" s="8" t="n">
         <f aca="false">SUM(E6:E16)</f>
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2063,8 +2072,8 @@
         <v>22</v>
       </c>
       <c r="B20" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$149,A20)</f>
-        <v>148</v>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$152,A20)</f>
+        <v>151</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2072,7 +2081,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$149,A21)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$152,A21)</f>
         <v>0</v>
       </c>
     </row>
@@ -2081,7 +2090,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$149,A22)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$152,A22)</f>
         <v>0</v>
       </c>
     </row>
@@ -2090,7 +2099,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$149,A23)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$152,A23)</f>
         <v>0</v>
       </c>
     </row>
@@ -2099,7 +2108,7 @@
         <v>26</v>
       </c>
       <c r="B24" s="6" t="n">
-        <f aca="false">COUNTIF(Pendências!$P$2:$P$149,A24)</f>
+        <f aca="false">COUNTIF(Pendências!$P$2:$P$152,A24)</f>
         <v>0</v>
       </c>
     </row>
@@ -2124,7 +2133,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R149"/>
+  <dimension ref="A1:R152"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -5712,7 +5721,7 @@
       <c r="Q71" s="15"/>
       <c r="R71" s="14"/>
     </row>
-    <row r="72" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="n">
         <v>71</v>
       </c>
@@ -5732,29 +5741,29 @@
         <v>186</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>46990</v>
+        <v>46426</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I72" s="10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J72" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>46163</v>
+        <v>46306</v>
       </c>
       <c r="L72" s="13" t="n">
         <f aca="false">IF(K72="","",K72-Resumo!$B$3)</f>
-        <v>-155</v>
+        <v>-12</v>
       </c>
       <c r="M72" s="10" t="s">
         <v>187</v>
       </c>
       <c r="N72" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O72" s="14"/>
       <c r="P72" s="14" t="s">
@@ -5763,7 +5772,7 @@
       <c r="Q72" s="15"/>
       <c r="R72" s="14"/>
     </row>
-    <row r="73" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="n">
         <v>72</v>
       </c>
@@ -5783,29 +5792,29 @@
         <v>186</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>46990</v>
+        <v>46426</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I73" s="10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J73" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>46281</v>
+        <v>46134</v>
       </c>
       <c r="L73" s="13" t="n">
         <f aca="false">IF(K73="","",K73-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-184</v>
       </c>
       <c r="M73" s="10" t="s">
-        <v>57</v>
+        <v>188</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O73" s="14"/>
       <c r="P73" s="14" t="s">
@@ -5819,42 +5828,44 @@
         <v>73</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>95</v>
+        <v>184</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>47087</v>
+        <v>46426</v>
       </c>
       <c r="H74" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I74" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="I74" s="10" t="n">
+        <v>15</v>
+      </c>
       <c r="J74" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="L74" s="13" t="n">
         <f aca="false">IF(K74="","",K74-Resumo!$B$3)</f>
-        <v>-44</v>
+        <v>-37</v>
       </c>
       <c r="M74" s="10" t="s">
-        <v>191</v>
+        <v>57</v>
       </c>
       <c r="N74" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O74" s="14"/>
       <c r="P74" s="14" t="s">
@@ -5871,19 +5882,19 @@
         <v>55</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>47087</v>
+        <v>46990</v>
       </c>
       <c r="H75" s="10" t="s">
         <v>14</v>
@@ -5895,14 +5906,14 @@
         <v>56</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>45997</v>
+        <v>46163</v>
       </c>
       <c r="L75" s="13" t="n">
         <f aca="false">IF(K75="","",K75-Resumo!$B$3)</f>
-        <v>-321</v>
+        <v>-155</v>
       </c>
       <c r="M75" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N75" s="10" t="s">
         <v>54</v>
@@ -5922,19 +5933,19 @@
         <v>55</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>47087</v>
+        <v>46990</v>
       </c>
       <c r="H76" s="10" t="s">
         <v>15</v>
@@ -5973,19 +5984,19 @@
         <v>80</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>95</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>47854</v>
+        <v>47087</v>
       </c>
       <c r="H77" s="10" t="s">
         <v>10</v>
@@ -5995,14 +6006,14 @@
         <v>56</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>46316</v>
+        <v>46274</v>
       </c>
       <c r="L77" s="13" t="n">
         <f aca="false">IF(K77="","",K77-Resumo!$B$3)</f>
-        <v>-2</v>
+        <v>-44</v>
       </c>
       <c r="M77" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N77" s="10" t="s">
         <v>52</v>
@@ -6014,7 +6025,7 @@
       <c r="Q77" s="15"/>
       <c r="R77" s="14"/>
     </row>
-    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="n">
         <v>77</v>
       </c>
@@ -6022,41 +6033,41 @@
         <v>55</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>95</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>47854</v>
+        <v>47087</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I78" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J78" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>46281</v>
+        <v>45997</v>
       </c>
       <c r="L78" s="13" t="n">
         <f aca="false">IF(K78="","",K78-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-321</v>
       </c>
       <c r="M78" s="10" t="s">
-        <v>57</v>
+        <v>198</v>
       </c>
       <c r="N78" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O78" s="14"/>
       <c r="P78" s="14" t="s">
@@ -6073,41 +6084,41 @@
         <v>55</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>198</v>
+        <v>95</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>46031</v>
+        <v>47087</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I79" s="10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J79" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>45911</v>
+        <v>46281</v>
       </c>
       <c r="L79" s="13" t="n">
         <f aca="false">IF(K79="","",K79-Resumo!$B$3)</f>
-        <v>-407</v>
+        <v>-37</v>
       </c>
       <c r="M79" s="10" t="s">
-        <v>201</v>
+        <v>57</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="O79" s="14"/>
       <c r="P79" s="14" t="s">
@@ -6116,7 +6127,7 @@
       <c r="Q79" s="15"/>
       <c r="R79" s="14"/>
     </row>
-    <row r="80" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="10" t="n">
         <v>79</v>
       </c>
@@ -6124,19 +6135,19 @@
         <v>80</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>198</v>
+        <v>95</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>46031</v>
+        <v>47854</v>
       </c>
       <c r="H80" s="10" t="s">
         <v>10</v>
@@ -6146,11 +6157,11 @@
         <v>56</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>45659</v>
+        <v>46316</v>
       </c>
       <c r="L80" s="13" t="n">
         <f aca="false">IF(K80="","",K80-Resumo!$B$3)</f>
-        <v>-659</v>
+        <v>-2</v>
       </c>
       <c r="M80" s="10" t="s">
         <v>202</v>
@@ -6170,44 +6181,44 @@
         <v>80</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>198</v>
+        <v>95</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>46031</v>
+        <v>47854</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I81" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J81" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>46083</v>
+        <v>46281</v>
       </c>
       <c r="L81" s="13" t="n">
         <f aca="false">IF(K81="","",K81-Resumo!$B$3)</f>
-        <v>-235</v>
+        <v>-37</v>
       </c>
       <c r="M81" s="10" t="s">
-        <v>203</v>
+        <v>57</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>162</v>
+        <v>58</v>
       </c>
       <c r="O81" s="14"/>
       <c r="P81" s="14" t="s">
@@ -6216,7 +6227,7 @@
       <c r="Q81" s="15"/>
       <c r="R81" s="14"/>
     </row>
-    <row r="82" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="n">
         <v>81</v>
       </c>
@@ -6224,41 +6235,41 @@
         <v>55</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="G82" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I82" s="10" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J82" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>45514</v>
+        <v>45911</v>
       </c>
       <c r="L82" s="13" t="n">
         <f aca="false">IF(K82="","",K82-Resumo!$B$3)</f>
-        <v>-804</v>
+        <v>-407</v>
       </c>
       <c r="M82" s="10" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="N82" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O82" s="14"/>
       <c r="P82" s="14" t="s">
@@ -6267,49 +6278,47 @@
       <c r="Q82" s="15"/>
       <c r="R82" s="14"/>
     </row>
-    <row r="83" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I83" s="10" t="n">
-        <v>15</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I83" s="10"/>
       <c r="J83" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>45356</v>
+        <v>45659</v>
       </c>
       <c r="L83" s="13" t="n">
         <f aca="false">IF(K83="","",K83-Resumo!$B$3)</f>
-        <v>-962</v>
+        <v>-659</v>
       </c>
       <c r="M83" s="10" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O83" s="14"/>
       <c r="P83" s="14" t="s">
@@ -6323,42 +6332,44 @@
         <v>83</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C84" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="F84" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="D84" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="F84" s="10" t="s">
+      <c r="G84" s="12" t="n">
+        <v>46031</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I84" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="J84" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>46083</v>
+      </c>
+      <c r="L84" s="13" t="n">
+        <f aca="false">IF(K84="","",K84-Resumo!$B$3)</f>
+        <v>-235</v>
+      </c>
+      <c r="M84" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="G84" s="12" t="n">
-        <v>46729</v>
-      </c>
-      <c r="H84" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I84" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="J84" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K84" s="12"/>
-      <c r="L84" s="13" t="str">
-        <f aca="false">IF(K84="","",K84-Resumo!$B$3)</f>
-        <v/>
-      </c>
-      <c r="M84" s="10" t="s">
-        <v>79</v>
-      </c>
       <c r="N84" s="10" t="s">
-        <v>58</v>
+        <v>162</v>
       </c>
       <c r="O84" s="14"/>
       <c r="P84" s="14" t="s">
@@ -6367,47 +6378,49 @@
       <c r="Q84" s="15"/>
       <c r="R84" s="14"/>
     </row>
-    <row r="85" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>65</v>
+        <v>204</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>48171</v>
+        <v>46031</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I85" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I85" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J85" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>46272</v>
+        <v>45514</v>
       </c>
       <c r="L85" s="13" t="n">
         <f aca="false">IF(K85="","",K85-Resumo!$B$3)</f>
-        <v>-46</v>
+        <v>-804</v>
       </c>
       <c r="M85" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O85" s="14"/>
       <c r="P85" s="14" t="s">
@@ -6416,7 +6429,7 @@
       <c r="Q85" s="15"/>
       <c r="R85" s="14"/>
     </row>
-    <row r="86" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="n">
         <v>85</v>
       </c>
@@ -6424,41 +6437,41 @@
         <v>55</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>65</v>
+        <v>204</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>48171</v>
+        <v>46031</v>
       </c>
       <c r="H86" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I86" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J86" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>46309</v>
+        <v>45356</v>
       </c>
       <c r="L86" s="13" t="n">
         <f aca="false">IF(K86="","",K86-Resumo!$B$3)</f>
-        <v>-9</v>
+        <v>-962</v>
       </c>
       <c r="M86" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="N86" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O86" s="14"/>
       <c r="P86" s="14" t="s">
@@ -6472,22 +6485,22 @@
         <v>86</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>65</v>
+        <v>213</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>48171</v>
+        <v>46729</v>
       </c>
       <c r="H87" s="10" t="s">
         <v>15</v>
@@ -6496,17 +6509,15 @@
         <v>15</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K87" s="12" t="n">
-        <v>46281</v>
-      </c>
-      <c r="L87" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K87" s="12"/>
+      <c r="L87" s="13" t="str">
         <f aca="false">IF(K87="","",K87-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v/>
       </c>
       <c r="M87" s="10" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="N87" s="10" t="s">
         <v>58</v>
@@ -6523,13 +6534,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>217</v>
@@ -6538,29 +6549,27 @@
         <v>218</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>46288</v>
+        <v>48171</v>
       </c>
       <c r="H88" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="I88" s="10" t="n">
-        <v>18</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I88" s="10"/>
       <c r="J88" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>46168</v>
+        <v>46272</v>
       </c>
       <c r="L88" s="13" t="n">
         <f aca="false">IF(K88="","",K88-Resumo!$B$3)</f>
-        <v>-150</v>
+        <v>-46</v>
       </c>
       <c r="M88" s="10" t="s">
         <v>219</v>
       </c>
       <c r="N88" s="10" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="O88" s="14"/>
       <c r="P88" s="14" t="s">
@@ -6569,49 +6578,49 @@
       <c r="Q88" s="15"/>
       <c r="R88" s="14"/>
     </row>
-    <row r="89" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>217</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>48005</v>
+        <v>48171</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I89" s="10" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J89" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>46163</v>
+        <v>46309</v>
       </c>
       <c r="L89" s="13" t="n">
         <f aca="false">IF(K89="","",K89-Resumo!$B$3)</f>
-        <v>-155</v>
+        <v>-9</v>
       </c>
       <c r="M89" s="10" t="s">
-        <v>85</v>
+        <v>220</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="O89" s="14"/>
       <c r="P89" s="14" t="s">
@@ -6620,18 +6629,18 @@
       <c r="Q89" s="15"/>
       <c r="R89" s="14"/>
     </row>
-    <row r="90" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="10" t="n">
         <v>89</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>217</v>
@@ -6640,27 +6649,29 @@
         <v>218</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>46288</v>
+        <v>48171</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I90" s="10" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J90" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K90" s="12"/>
-      <c r="L90" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K90" s="12" t="n">
+        <v>46281</v>
+      </c>
+      <c r="L90" s="13" t="n">
         <f aca="false">IF(K90="","",K90-Resumo!$B$3)</f>
-        <v/>
+        <v>-37</v>
       </c>
       <c r="M90" s="10" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="N90" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O90" s="14"/>
       <c r="P90" s="14" t="s">
@@ -6677,41 +6688,41 @@
         <v>55</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="G91" s="12" t="n">
         <v>46288</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I91" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J91" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>46283</v>
+        <v>46168</v>
       </c>
       <c r="L91" s="13" t="n">
         <f aca="false">IF(K91="","",K91-Resumo!$B$3)</f>
-        <v>-35</v>
+        <v>-150</v>
       </c>
       <c r="M91" s="10" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O91" s="14"/>
       <c r="P91" s="14" t="s">
@@ -6720,49 +6731,49 @@
       <c r="Q91" s="15"/>
       <c r="R91" s="14"/>
     </row>
-    <row r="92" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="n">
         <v>91</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C92" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="D92" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="D92" s="10" t="s">
+      <c r="E92" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="E92" s="10" t="s">
-        <v>224</v>
-      </c>
       <c r="F92" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>46798</v>
+        <v>48005</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I92" s="10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J92" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K92" s="12" t="n">
-        <v>46323</v>
+        <v>46163</v>
       </c>
       <c r="L92" s="13" t="n">
         <f aca="false">IF(K92="","",K92-Resumo!$B$3)</f>
-        <v>5</v>
+        <v>-155</v>
       </c>
       <c r="M92" s="10" t="s">
-        <v>226</v>
+        <v>85</v>
       </c>
       <c r="N92" s="10" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="O92" s="14"/>
       <c r="P92" s="14" t="s">
@@ -6771,49 +6782,47 @@
       <c r="Q92" s="15"/>
       <c r="R92" s="14"/>
     </row>
-    <row r="93" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="n">
         <v>92</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C93" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="D93" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="D93" s="10" t="s">
+      <c r="E93" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="E93" s="10" t="s">
+      <c r="F93" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="F93" s="10" t="s">
-        <v>225</v>
-      </c>
       <c r="G93" s="12" t="n">
-        <v>46798</v>
+        <v>46288</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I93" s="10" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K93" s="12" t="n">
-        <v>46281</v>
-      </c>
-      <c r="L93" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K93" s="12"/>
+      <c r="L93" s="13" t="str">
         <f aca="false">IF(K93="","",K93-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v/>
       </c>
       <c r="M93" s="10" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O93" s="14"/>
       <c r="P93" s="14" t="s">
@@ -6827,42 +6836,44 @@
         <v>93</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C94" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="D94" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="D94" s="10" t="s">
+      <c r="E94" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="E94" s="10" t="s">
+      <c r="F94" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="F94" s="10" t="s">
-        <v>225</v>
-      </c>
       <c r="G94" s="12" t="n">
-        <v>46798</v>
+        <v>46288</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I94" s="10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K94" s="12"/>
-      <c r="L94" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K94" s="12" t="n">
+        <v>46283</v>
+      </c>
+      <c r="L94" s="13" t="n">
         <f aca="false">IF(K94="","",K94-Resumo!$B$3)</f>
-        <v/>
+        <v>-35</v>
       </c>
       <c r="M94" s="10" t="s">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="N94" s="10" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="O94" s="14"/>
       <c r="P94" s="14" t="s">
@@ -6871,7 +6882,7 @@
       <c r="Q94" s="15"/>
       <c r="R94" s="14"/>
     </row>
-    <row r="95" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="10" t="n">
         <v>94</v>
       </c>
@@ -6879,41 +6890,41 @@
         <v>55</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>47004</v>
+        <v>46798</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I95" s="10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J95" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>46280</v>
+        <v>46323</v>
       </c>
       <c r="L95" s="13" t="n">
         <f aca="false">IF(K95="","",K95-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>5</v>
       </c>
       <c r="M95" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O95" s="14"/>
       <c r="P95" s="14" t="s">
@@ -6927,44 +6938,44 @@
         <v>95</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>47004</v>
+        <v>46798</v>
       </c>
       <c r="H96" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I96" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="I96" s="10" t="n">
-        <v>15</v>
-      </c>
       <c r="J96" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K96" s="12" t="n">
-        <v>46344</v>
+        <v>46281</v>
       </c>
       <c r="L96" s="13" t="n">
         <f aca="false">IF(K96="","",K96-Resumo!$B$3)</f>
-        <v>26</v>
+        <v>-37</v>
       </c>
       <c r="M96" s="10" t="s">
-        <v>232</v>
+        <v>57</v>
       </c>
       <c r="N96" s="10" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="O96" s="14"/>
       <c r="P96" s="14" t="s">
@@ -6978,44 +6989,42 @@
         <v>96</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>47</v>
+        <v>229</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>46046</v>
+        <v>46798</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I97" s="10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J97" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K97" s="12" t="n">
-        <v>45926</v>
-      </c>
-      <c r="L97" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K97" s="12"/>
+      <c r="L97" s="13" t="str">
         <f aca="false">IF(K97="","",K97-Resumo!$B$3)</f>
-        <v>-392</v>
+        <v/>
       </c>
       <c r="M97" s="10" t="s">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="O97" s="14"/>
       <c r="P97" s="14" t="s">
@@ -7029,42 +7038,44 @@
         <v>97</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C98" s="10" t="s">
         <v>233</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>47</v>
+        <v>234</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>46046</v>
+        <v>47004</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I98" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="I98" s="10" t="n">
+        <v>16</v>
+      </c>
       <c r="J98" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K98" s="12" t="n">
-        <v>45823</v>
+        <v>46280</v>
       </c>
       <c r="L98" s="13" t="n">
         <f aca="false">IF(K98="","",K98-Resumo!$B$3)</f>
-        <v>-495</v>
+        <v>-38</v>
       </c>
       <c r="M98" s="10" t="s">
         <v>237</v>
       </c>
       <c r="N98" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O98" s="14"/>
       <c r="P98" s="14" t="s">
@@ -7073,49 +7084,49 @@
       <c r="Q98" s="15"/>
       <c r="R98" s="14"/>
     </row>
-    <row r="99" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="n">
         <v>98</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C99" s="10" t="s">
         <v>233</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>47</v>
+        <v>234</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>46046</v>
+        <v>47004</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I99" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J99" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>46058</v>
+        <v>46344</v>
       </c>
       <c r="L99" s="13" t="n">
         <f aca="false">IF(K99="","",K99-Resumo!$B$3)</f>
-        <v>-260</v>
+        <v>26</v>
       </c>
       <c r="M99" s="10" t="s">
         <v>238</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="O99" s="14"/>
       <c r="P99" s="14" t="s">
@@ -7132,41 +7143,41 @@
         <v>55</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="D100" s="10" t="s">
         <v>47</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="G100" s="12" t="n">
         <v>46046</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I100" s="10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J100" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K100" s="12" t="n">
-        <v>46281</v>
+        <v>45926</v>
       </c>
       <c r="L100" s="13" t="n">
         <f aca="false">IF(K100="","",K100-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-392</v>
       </c>
       <c r="M100" s="10" t="s">
-        <v>57</v>
+        <v>242</v>
       </c>
       <c r="N100" s="10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O100" s="14"/>
       <c r="P100" s="14" t="s">
@@ -7180,13 +7191,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C101" s="10" t="s">
         <v>239</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>240</v>
@@ -7195,29 +7206,27 @@
         <v>241</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>46970</v>
+        <v>46046</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I101" s="10" t="n">
-        <v>15</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I101" s="10"/>
       <c r="J101" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>46281</v>
+        <v>45823</v>
       </c>
       <c r="L101" s="13" t="n">
         <f aca="false">IF(K101="","",K101-Resumo!$B$3)</f>
-        <v>-37</v>
+        <v>-495</v>
       </c>
       <c r="M101" s="10" t="s">
-        <v>57</v>
+        <v>243</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O101" s="14"/>
       <c r="P101" s="14" t="s">
@@ -7226,7 +7235,7 @@
       <c r="Q101" s="15"/>
       <c r="R101" s="14"/>
     </row>
-    <row r="102" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="10" t="n">
         <v>101</v>
       </c>
@@ -7234,39 +7243,41 @@
         <v>55</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>46505</v>
+        <v>46046</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I102" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I102" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J102" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K102" s="12" t="n">
-        <v>46319</v>
+        <v>46058</v>
       </c>
       <c r="L102" s="13" t="n">
         <f aca="false">IF(K102="","",K102-Resumo!$B$3)</f>
-        <v>1</v>
+        <v>-260</v>
       </c>
       <c r="M102" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N102" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O102" s="14"/>
       <c r="P102" s="14" t="s">
@@ -7275,7 +7286,7 @@
       <c r="Q102" s="15"/>
       <c r="R102" s="14"/>
     </row>
-    <row r="103" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="10" t="n">
         <v>102</v>
       </c>
@@ -7283,41 +7294,41 @@
         <v>55</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>46505</v>
+        <v>46046</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I103" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J103" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>45891</v>
+        <v>46281</v>
       </c>
       <c r="L103" s="13" t="n">
         <f aca="false">IF(K103="","",K103-Resumo!$B$3)</f>
-        <v>-427</v>
+        <v>-37</v>
       </c>
       <c r="M103" s="10" t="s">
-        <v>246</v>
+        <v>57</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O103" s="14"/>
       <c r="P103" s="14" t="s">
@@ -7334,19 +7345,19 @@
         <v>55</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>46505</v>
+        <v>46970</v>
       </c>
       <c r="H104" s="10" t="s">
         <v>15</v>
@@ -7358,14 +7369,14 @@
         <v>56</v>
       </c>
       <c r="K104" s="12" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="L104" s="13" t="n">
         <f aca="false">IF(K104="","",K104-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="M104" s="10" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="N104" s="10" t="s">
         <v>58</v>
@@ -7385,10 +7396,10 @@
         <v>55</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>248</v>
+        <v>70</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>249</v>
@@ -7397,27 +7408,27 @@
         <v>250</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>46346</v>
+        <v>46505</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>46226</v>
+        <v>46319</v>
       </c>
       <c r="L105" s="13" t="n">
         <f aca="false">IF(K105="","",K105-Resumo!$B$3)</f>
-        <v>-92</v>
+        <v>1</v>
       </c>
       <c r="M105" s="10" t="s">
         <v>251</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="O105" s="14"/>
       <c r="P105" s="14" t="s">
@@ -7426,7 +7437,7 @@
       <c r="Q105" s="15"/>
       <c r="R105" s="14"/>
     </row>
-    <row r="106" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="10" t="n">
         <v>105</v>
       </c>
@@ -7434,10 +7445,10 @@
         <v>55</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>248</v>
+        <v>70</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>249</v>
@@ -7446,27 +7457,29 @@
         <v>250</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>46346</v>
+        <v>46505</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I106" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="I106" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="J106" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K106" s="12" t="n">
-        <v>46282</v>
+        <v>45891</v>
       </c>
       <c r="L106" s="13" t="n">
         <f aca="false">IF(K106="","",K106-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-427</v>
       </c>
       <c r="M106" s="10" t="s">
-        <v>74</v>
+        <v>252</v>
       </c>
       <c r="N106" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O106" s="14"/>
       <c r="P106" s="14" t="s">
@@ -7483,41 +7496,41 @@
         <v>55</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>46373</v>
+        <v>46505</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I107" s="10" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J107" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>46253</v>
+        <v>46282</v>
       </c>
       <c r="L107" s="13" t="n">
         <f aca="false">IF(K107="","",K107-Resumo!$B$3)</f>
-        <v>-65</v>
+        <v>-36</v>
       </c>
       <c r="M107" s="10" t="s">
-        <v>255</v>
+        <v>74</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="O107" s="14"/>
       <c r="P107" s="14" t="s">
@@ -7526,7 +7539,7 @@
       <c r="Q107" s="15"/>
       <c r="R107" s="14"/>
     </row>
-    <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="10" t="n">
         <v>107</v>
       </c>
@@ -7534,41 +7547,39 @@
         <v>55</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>65</v>
+        <v>254</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F108" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>46373</v>
+        <v>46346</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I108" s="10" t="n">
-        <v>5</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I108" s="10"/>
       <c r="J108" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K108" s="12" t="n">
-        <v>45192</v>
+        <v>46226</v>
       </c>
       <c r="L108" s="13" t="n">
         <f aca="false">IF(K108="","",K108-Resumo!$B$3)</f>
-        <v>-1126</v>
+        <v>-92</v>
       </c>
       <c r="M108" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N108" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O108" s="14"/>
       <c r="P108" s="14" t="s">
@@ -7585,38 +7596,36 @@
         <v>55</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>65</v>
+        <v>254</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>46373</v>
+        <v>46346</v>
       </c>
       <c r="H109" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I109" s="10" t="n">
-        <v>16</v>
-      </c>
+      <c r="I109" s="10"/>
       <c r="J109" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>45262</v>
+        <v>46282</v>
       </c>
       <c r="L109" s="13" t="n">
         <f aca="false">IF(K109="","",K109-Resumo!$B$3)</f>
-        <v>-1056</v>
+        <v>-36</v>
       </c>
       <c r="M109" s="10" t="s">
-        <v>257</v>
+        <v>74</v>
       </c>
       <c r="N109" s="10" t="s">
         <v>58</v>
@@ -7628,7 +7637,7 @@
       <c r="Q109" s="15"/>
       <c r="R109" s="14"/>
     </row>
-    <row r="110" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="n">
         <v>109</v>
       </c>
@@ -7639,38 +7648,38 @@
         <v>258</v>
       </c>
       <c r="D110" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E110" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="E110" s="10" t="s">
+      <c r="F110" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="F110" s="10" t="s">
-        <v>261</v>
-      </c>
       <c r="G110" s="12" t="n">
-        <v>48010</v>
+        <v>46373</v>
       </c>
       <c r="H110" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I110" s="10" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="J110" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K110" s="12" t="n">
-        <v>46127</v>
+        <v>46253</v>
       </c>
       <c r="L110" s="13" t="n">
         <f aca="false">IF(K110="","",K110-Resumo!$B$3)</f>
-        <v>-191</v>
+        <v>-65</v>
       </c>
       <c r="M110" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N110" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O110" s="14"/>
       <c r="P110" s="14" t="s">
@@ -7679,7 +7688,7 @@
       <c r="Q110" s="15"/>
       <c r="R110" s="14"/>
     </row>
-    <row r="111" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="10" t="n">
         <v>110</v>
       </c>
@@ -7690,38 +7699,38 @@
         <v>258</v>
       </c>
       <c r="D111" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E111" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="E111" s="10" t="s">
+      <c r="F111" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="F111" s="10" t="s">
-        <v>261</v>
-      </c>
       <c r="G111" s="12" t="n">
-        <v>48010</v>
+        <v>46373</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I111" s="10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J111" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>46280</v>
+        <v>45192</v>
       </c>
       <c r="L111" s="13" t="n">
         <f aca="false">IF(K111="","",K111-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>-1126</v>
       </c>
       <c r="M111" s="10" t="s">
-        <v>231</v>
+        <v>262</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O111" s="14"/>
       <c r="P111" s="14" t="s">
@@ -7738,41 +7747,41 @@
         <v>55</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>264</v>
+        <v>65</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="F112" s="10" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>46238</v>
+        <v>46373</v>
       </c>
       <c r="H112" s="10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I112" s="10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J112" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K112" s="12" t="n">
-        <v>46118</v>
+        <v>45262</v>
       </c>
       <c r="L112" s="13" t="n">
         <f aca="false">IF(K112="","",K112-Resumo!$B$3)</f>
-        <v>-200</v>
+        <v>-1056</v>
       </c>
       <c r="M112" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="N112" s="10" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="O112" s="14"/>
       <c r="P112" s="14" t="s">
@@ -7786,39 +7795,41 @@
         <v>112</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>46238</v>
+        <v>48010</v>
       </c>
       <c r="H113" s="10" t="s">
         <v>14</v>
       </c>
       <c r="I113" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K113" s="12"/>
-      <c r="L113" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K113" s="12" t="n">
+        <v>46127</v>
+      </c>
+      <c r="L113" s="13" t="n">
         <f aca="false">IF(K113="","",K113-Resumo!$B$3)</f>
-        <v/>
+        <v>-191</v>
       </c>
       <c r="M113" s="10" t="s">
-        <v>79</v>
+        <v>268</v>
       </c>
       <c r="N113" s="10" t="s">
         <v>54</v>
@@ -7830,7 +7841,7 @@
       <c r="Q113" s="15"/>
       <c r="R113" s="14"/>
     </row>
-    <row r="114" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="10" t="n">
         <v>113</v>
       </c>
@@ -7838,25 +7849,25 @@
         <v>55</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F114" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>46238</v>
+        <v>48010</v>
       </c>
       <c r="H114" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J114" s="10" t="s">
         <v>56</v>
@@ -7869,7 +7880,7 @@
         <v>-38</v>
       </c>
       <c r="M114" s="10" t="s">
-        <v>268</v>
+        <v>237</v>
       </c>
       <c r="N114" s="10" t="s">
         <v>58</v>
@@ -7886,44 +7897,44 @@
         <v>114</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="G115" s="12" t="n">
         <v>46238</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I115" s="10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>46340</v>
+        <v>46118</v>
       </c>
       <c r="L115" s="13" t="n">
         <f aca="false">IF(K115="","",K115-Resumo!$B$3)</f>
-        <v>22</v>
+        <v>-200</v>
       </c>
       <c r="M115" s="10" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="O115" s="14"/>
       <c r="P115" s="14" t="s">
@@ -7932,49 +7943,47 @@
       <c r="Q115" s="15"/>
       <c r="R115" s="14"/>
     </row>
-    <row r="116" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="10" t="n">
         <v>115</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C116" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D116" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="D116" s="10" t="s">
+      <c r="E116" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="E116" s="10" t="s">
+      <c r="F116" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="F116" s="10" t="s">
-        <v>273</v>
-      </c>
       <c r="G116" s="12" t="n">
-        <v>46043</v>
+        <v>46238</v>
       </c>
       <c r="H116" s="10" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I116" s="10" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K116" s="12" t="n">
-        <v>45923</v>
-      </c>
-      <c r="L116" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K116" s="12"/>
+      <c r="L116" s="13" t="str">
         <f aca="false">IF(K116="","",K116-Resumo!$B$3)</f>
-        <v>-395</v>
+        <v/>
       </c>
       <c r="M116" s="10" t="s">
-        <v>274</v>
+        <v>79</v>
       </c>
       <c r="N116" s="10" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="O116" s="14"/>
       <c r="P116" s="14" t="s">
@@ -7991,41 +8000,41 @@
         <v>55</v>
       </c>
       <c r="C117" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D117" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="D117" s="10" t="s">
+      <c r="E117" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="E117" s="10" t="s">
+      <c r="F117" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="F117" s="10" t="s">
-        <v>273</v>
-      </c>
       <c r="G117" s="12" t="n">
-        <v>46043</v>
+        <v>46238</v>
       </c>
       <c r="H117" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I117" s="10" t="n">
         <v>14</v>
-      </c>
-      <c r="I117" s="10" t="n">
-        <v>5</v>
       </c>
       <c r="J117" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>46113</v>
+        <v>46280</v>
       </c>
       <c r="L117" s="13" t="n">
         <f aca="false">IF(K117="","",K117-Resumo!$B$3)</f>
-        <v>-205</v>
+        <v>-38</v>
       </c>
       <c r="M117" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O117" s="14"/>
       <c r="P117" s="14" t="s">
@@ -8039,44 +8048,44 @@
         <v>117</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C118" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D118" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="D118" s="10" t="s">
+      <c r="E118" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="E118" s="10" t="s">
+      <c r="F118" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="F118" s="10" t="s">
-        <v>273</v>
-      </c>
       <c r="G118" s="12" t="n">
-        <v>46043</v>
+        <v>46238</v>
       </c>
       <c r="H118" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I118" s="10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J118" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K118" s="12" t="n">
-        <v>45351</v>
+        <v>46340</v>
       </c>
       <c r="L118" s="13" t="n">
         <f aca="false">IF(K118="","",K118-Resumo!$B$3)</f>
-        <v>-967</v>
+        <v>22</v>
       </c>
       <c r="M118" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N118" s="10" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="O118" s="14"/>
       <c r="P118" s="14" t="s">
@@ -8093,10 +8102,10 @@
         <v>55</v>
       </c>
       <c r="C119" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="D119" s="10" t="s">
         <v>277</v>
-      </c>
-      <c r="D119" s="10" t="s">
-        <v>207</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>278</v>
@@ -8105,23 +8114,23 @@
         <v>279</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>46408</v>
+        <v>46043</v>
       </c>
       <c r="H119" s="10" t="s">
         <v>9</v>
       </c>
       <c r="I119" s="10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J119" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>46288</v>
+        <v>45923</v>
       </c>
       <c r="L119" s="13" t="n">
         <f aca="false">IF(K119="","",K119-Resumo!$B$3)</f>
-        <v>-30</v>
+        <v>-395</v>
       </c>
       <c r="M119" s="10" t="s">
         <v>280</v>
@@ -8144,10 +8153,10 @@
         <v>55</v>
       </c>
       <c r="C120" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="D120" s="10" t="s">
         <v>277</v>
-      </c>
-      <c r="D120" s="10" t="s">
-        <v>207</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>278</v>
@@ -8156,7 +8165,7 @@
         <v>279</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>46408</v>
+        <v>46043</v>
       </c>
       <c r="H120" s="10" t="s">
         <v>14</v>
@@ -8175,7 +8184,7 @@
         <v>-205</v>
       </c>
       <c r="M120" s="10" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="N120" s="10" t="s">
         <v>54</v>
@@ -8195,10 +8204,10 @@
         <v>55</v>
       </c>
       <c r="C121" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="D121" s="10" t="s">
         <v>277</v>
-      </c>
-      <c r="D121" s="10" t="s">
-        <v>207</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>278</v>
@@ -8207,26 +8216,26 @@
         <v>279</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>46408</v>
+        <v>46043</v>
       </c>
       <c r="H121" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J121" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>46282</v>
+        <v>45351</v>
       </c>
       <c r="L121" s="13" t="n">
         <f aca="false">IF(K121="","",K121-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v>-967</v>
       </c>
       <c r="M121" s="10" t="s">
-        <v>74</v>
+        <v>282</v>
       </c>
       <c r="N121" s="10" t="s">
         <v>58</v>
@@ -8243,42 +8252,44 @@
         <v>121</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>47310</v>
+        <v>46408</v>
       </c>
       <c r="H122" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I122" s="10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J122" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K122" s="12"/>
-      <c r="L122" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K122" s="12" t="n">
+        <v>46288</v>
+      </c>
+      <c r="L122" s="13" t="n">
         <f aca="false">IF(K122="","",K122-Resumo!$B$3)</f>
-        <v/>
+        <v>-30</v>
       </c>
       <c r="M122" s="10" t="s">
-        <v>79</v>
+        <v>286</v>
       </c>
       <c r="N122" s="10" t="s">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="O122" s="14"/>
       <c r="P122" s="14" t="s">
@@ -8292,22 +8303,22 @@
         <v>122</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>47310</v>
+        <v>46408</v>
       </c>
       <c r="H123" s="10" t="s">
         <v>14</v>
@@ -8316,15 +8327,17 @@
         <v>5</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K123" s="12"/>
-      <c r="L123" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K123" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="L123" s="13" t="n">
         <f aca="false">IF(K123="","",K123-Resumo!$B$3)</f>
-        <v/>
+        <v>-205</v>
       </c>
       <c r="M123" s="10" t="s">
-        <v>79</v>
+        <v>281</v>
       </c>
       <c r="N123" s="10" t="s">
         <v>54</v>
@@ -8344,38 +8357,38 @@
         <v>55</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F124" s="10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>47310</v>
+        <v>46408</v>
       </c>
       <c r="H124" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J124" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K124" s="12" t="n">
-        <v>46043</v>
+        <v>46282</v>
       </c>
       <c r="L124" s="13" t="n">
         <f aca="false">IF(K124="","",K124-Resumo!$B$3)</f>
-        <v>-275</v>
+        <v>-36</v>
       </c>
       <c r="M124" s="10" t="s">
-        <v>284</v>
+        <v>74</v>
       </c>
       <c r="N124" s="10" t="s">
         <v>58</v>
@@ -8387,49 +8400,47 @@
       <c r="Q124" s="15"/>
       <c r="R124" s="14"/>
     </row>
-    <row r="125" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="10" t="n">
         <v>124</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>46658</v>
+        <v>47310</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I125" s="10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K125" s="12" t="n">
-        <v>46107</v>
-      </c>
-      <c r="L125" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K125" s="12"/>
+      <c r="L125" s="13" t="str">
         <f aca="false">IF(K125="","",K125-Resumo!$B$3)</f>
-        <v>-211</v>
+        <v/>
       </c>
       <c r="M125" s="10" t="s">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="O125" s="14"/>
       <c r="P125" s="14" t="s">
@@ -8438,49 +8449,47 @@
       <c r="Q125" s="15"/>
       <c r="R125" s="14"/>
     </row>
-    <row r="126" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="10" t="n">
         <v>125</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F126" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>46658</v>
+        <v>47310</v>
       </c>
       <c r="H126" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I126" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J126" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K126" s="12" t="n">
-        <v>46280</v>
-      </c>
-      <c r="L126" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K126" s="12"/>
+      <c r="L126" s="13" t="str">
         <f aca="false">IF(K126="","",K126-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v/>
       </c>
       <c r="M126" s="10" t="s">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="N126" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O126" s="14"/>
       <c r="P126" s="14" t="s">
@@ -8494,42 +8503,44 @@
         <v>126</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>46658</v>
+        <v>47310</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I127" s="10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K127" s="12"/>
-      <c r="L127" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K127" s="12" t="n">
+        <v>46043</v>
+      </c>
+      <c r="L127" s="13" t="n">
         <f aca="false">IF(K127="","",K127-Resumo!$B$3)</f>
-        <v/>
+        <v>-275</v>
       </c>
       <c r="M127" s="10" t="s">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="O127" s="14"/>
       <c r="P127" s="14" t="s">
@@ -8546,19 +8557,19 @@
         <v>55</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>290</v>
+        <v>158</v>
       </c>
       <c r="E128" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>47016</v>
+        <v>46658</v>
       </c>
       <c r="H128" s="10" t="s">
         <v>14</v>
@@ -8570,14 +8581,14 @@
         <v>56</v>
       </c>
       <c r="K128" s="12" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="L128" s="13" t="n">
         <f aca="false">IF(K128="","",K128-Resumo!$B$3)</f>
-        <v>-205</v>
+        <v>-211</v>
       </c>
       <c r="M128" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N128" s="10" t="s">
         <v>54</v>
@@ -8597,38 +8608,38 @@
         <v>55</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>290</v>
+        <v>158</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>47016</v>
+        <v>46658</v>
       </c>
       <c r="H129" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J129" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>45519</v>
+        <v>46280</v>
       </c>
       <c r="L129" s="13" t="n">
         <f aca="false">IF(K129="","",K129-Resumo!$B$3)</f>
-        <v>-799</v>
+        <v>-38</v>
       </c>
       <c r="M129" s="10" t="s">
-        <v>294</v>
+        <v>237</v>
       </c>
       <c r="N129" s="10" t="s">
         <v>58</v>
@@ -8648,41 +8659,39 @@
         <v>45</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>290</v>
+        <v>158</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F130" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>47016</v>
+        <v>46658</v>
       </c>
       <c r="H130" s="10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I130" s="10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K130" s="12" t="n">
-        <v>46339</v>
-      </c>
-      <c r="L130" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K130" s="12"/>
+      <c r="L130" s="13" t="str">
         <f aca="false">IF(K130="","",K130-Resumo!$B$3)</f>
-        <v>21</v>
+        <v/>
       </c>
       <c r="M130" s="10" t="s">
-        <v>295</v>
+        <v>79</v>
       </c>
       <c r="N130" s="10" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="O130" s="14"/>
       <c r="P130" s="14" t="s">
@@ -8691,7 +8700,7 @@
       <c r="Q130" s="15"/>
       <c r="R130" s="14"/>
     </row>
-    <row r="131" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="10" t="n">
         <v>130</v>
       </c>
@@ -8699,41 +8708,41 @@
         <v>55</v>
       </c>
       <c r="C131" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D131" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="D131" s="10" t="s">
+      <c r="E131" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="E131" s="10" t="s">
+      <c r="F131" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="F131" s="10" t="s">
-        <v>299</v>
-      </c>
       <c r="G131" s="12" t="n">
-        <v>46332</v>
+        <v>47016</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I131" s="10" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J131" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>46212</v>
+        <v>46113</v>
       </c>
       <c r="L131" s="13" t="n">
         <f aca="false">IF(K131="","",K131-Resumo!$B$3)</f>
-        <v>-106</v>
+        <v>-205</v>
       </c>
       <c r="M131" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="O131" s="14"/>
       <c r="P131" s="14" t="s">
@@ -8747,44 +8756,44 @@
         <v>131</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C132" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D132" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="D132" s="10" t="s">
+      <c r="E132" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="E132" s="10" t="s">
+      <c r="F132" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="F132" s="10" t="s">
-        <v>299</v>
-      </c>
       <c r="G132" s="12" t="n">
-        <v>46332</v>
+        <v>47016</v>
       </c>
       <c r="H132" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I132" s="10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J132" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K132" s="12" t="n">
-        <v>46248</v>
+        <v>45519</v>
       </c>
       <c r="L132" s="13" t="n">
         <f aca="false">IF(K132="","",K132-Resumo!$B$3)</f>
-        <v>-70</v>
+        <v>-799</v>
       </c>
       <c r="M132" s="10" t="s">
-        <v>85</v>
+        <v>300</v>
       </c>
       <c r="N132" s="10" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="O132" s="14"/>
       <c r="P132" s="14" t="s">
@@ -8793,49 +8802,49 @@
       <c r="Q132" s="15"/>
       <c r="R132" s="14"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="10" t="n">
         <v>132</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C133" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D133" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="D133" s="10" t="s">
+      <c r="E133" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="E133" s="10" t="s">
+      <c r="F133" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="F133" s="10" t="s">
-        <v>299</v>
-      </c>
       <c r="G133" s="12" t="n">
-        <v>46332</v>
+        <v>47016</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I133" s="10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J133" s="10" t="s">
         <v>50</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>46328</v>
+        <v>46339</v>
       </c>
       <c r="L133" s="13" t="n">
         <f aca="false">IF(K133="","",K133-Resumo!$B$3)</f>
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="M133" s="10" t="s">
-        <v>87</v>
+        <v>301</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O133" s="14"/>
       <c r="P133" s="14" t="s">
@@ -8844,7 +8853,7 @@
       <c r="Q133" s="15"/>
       <c r="R133" s="14"/>
     </row>
-    <row r="134" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="10" t="n">
         <v>133</v>
       </c>
@@ -8852,41 +8861,41 @@
         <v>55</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="G134" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H134" s="10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I134" s="10" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J134" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K134" s="12" t="n">
-        <v>46259</v>
+        <v>46212</v>
       </c>
       <c r="L134" s="13" t="n">
         <f aca="false">IF(K134="","",K134-Resumo!$B$3)</f>
-        <v>-59</v>
+        <v>-106</v>
       </c>
       <c r="M134" s="10" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="N134" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O134" s="14"/>
       <c r="P134" s="14" t="s">
@@ -8900,44 +8909,44 @@
         <v>134</v>
       </c>
       <c r="B135" s="11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="G135" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I135" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J135" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>46280</v>
+        <v>46248</v>
       </c>
       <c r="L135" s="13" t="n">
         <f aca="false">IF(K135="","",K135-Resumo!$B$3)</f>
-        <v>-38</v>
+        <v>-70</v>
       </c>
       <c r="M135" s="10" t="s">
-        <v>231</v>
+        <v>85</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="O135" s="14"/>
       <c r="P135" s="14" t="s">
@@ -8946,47 +8955,49 @@
       <c r="Q135" s="15"/>
       <c r="R135" s="14"/>
     </row>
-    <row r="136" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="10" t="n">
         <v>135</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D136" s="10" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F136" s="10" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="G136" s="12" t="n">
         <v>46332</v>
       </c>
       <c r="H136" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I136" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="I136" s="10" t="n">
-        <v>13</v>
-      </c>
       <c r="J136" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K136" s="12"/>
-      <c r="L136" s="13" t="str">
+        <v>50</v>
+      </c>
+      <c r="K136" s="12" t="n">
+        <v>46328</v>
+      </c>
+      <c r="L136" s="13" t="n">
         <f aca="false">IF(K136="","",K136-Resumo!$B$3)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="M136" s="10" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="N136" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O136" s="14"/>
       <c r="P136" s="14" t="s">
@@ -8995,12 +9006,12 @@
       <c r="Q136" s="15"/>
       <c r="R136" s="14"/>
     </row>
-    <row r="137" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="10" t="n">
         <v>136</v>
       </c>
       <c r="B137" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>302</v>
@@ -9015,29 +9026,29 @@
         <v>305</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>48215</v>
+        <v>46332</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I137" s="10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J137" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>46034</v>
+        <v>46259</v>
       </c>
       <c r="L137" s="13" t="n">
         <f aca="false">IF(K137="","",K137-Resumo!$B$3)</f>
-        <v>-284</v>
+        <v>-59</v>
       </c>
       <c r="M137" s="10" t="s">
-        <v>85</v>
+        <v>307</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="O137" s="14"/>
       <c r="P137" s="14" t="s">
@@ -9046,12 +9057,12 @@
       <c r="Q137" s="15"/>
       <c r="R137" s="14"/>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="10" t="n">
         <v>137</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>302</v>
@@ -9066,29 +9077,29 @@
         <v>305</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>48215</v>
+        <v>46332</v>
       </c>
       <c r="H138" s="10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I138" s="10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J138" s="10" t="s">
         <v>56</v>
       </c>
       <c r="K138" s="12" t="n">
-        <v>46114</v>
+        <v>46280</v>
       </c>
       <c r="L138" s="13" t="n">
         <f aca="false">IF(K138="","",K138-Resumo!$B$3)</f>
-        <v>-204</v>
+        <v>-38</v>
       </c>
       <c r="M138" s="10" t="s">
-        <v>87</v>
+        <v>237</v>
       </c>
       <c r="N138" s="10" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="O138" s="14"/>
       <c r="P138" s="14" t="s">
@@ -9097,12 +9108,12 @@
       <c r="Q138" s="15"/>
       <c r="R138" s="14"/>
     </row>
-    <row r="139" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="10" t="n">
         <v>138</v>
       </c>
       <c r="B139" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C139" s="10" t="s">
         <v>302</v>
@@ -9117,29 +9128,27 @@
         <v>305</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>48215</v>
+        <v>46332</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I139" s="10" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J139" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K139" s="12" t="n">
-        <v>46276</v>
-      </c>
-      <c r="L139" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K139" s="12"/>
+      <c r="L139" s="13" t="str">
         <f aca="false">IF(K139="","",K139-Resumo!$B$3)</f>
-        <v>-42</v>
+        <v/>
       </c>
       <c r="M139" s="10" t="s">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="O139" s="14"/>
       <c r="P139" s="14" t="s">
@@ -9153,42 +9162,44 @@
         <v>139</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="F140" s="10" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="G140" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H140" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I140" s="10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J140" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K140" s="12"/>
-      <c r="L140" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K140" s="12" t="n">
+        <v>46034</v>
+      </c>
+      <c r="L140" s="13" t="n">
         <f aca="false">IF(K140="","",K140-Resumo!$B$3)</f>
-        <v/>
+        <v>-284</v>
       </c>
       <c r="M140" s="10" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="N140" s="10" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="O140" s="14"/>
       <c r="P140" s="14" t="s">
@@ -9197,47 +9208,49 @@
       <c r="Q140" s="15"/>
       <c r="R140" s="14"/>
     </row>
-    <row r="141" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="10" t="n">
         <v>140</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="G141" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I141" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J141" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K141" s="12"/>
-      <c r="L141" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K141" s="12" t="n">
+        <v>46114</v>
+      </c>
+      <c r="L141" s="13" t="n">
         <f aca="false">IF(K141="","",K141-Resumo!$B$3)</f>
-        <v/>
+        <v>-204</v>
       </c>
       <c r="M141" s="10" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O141" s="14"/>
       <c r="P141" s="14" t="s">
@@ -9246,47 +9259,49 @@
       <c r="Q141" s="15"/>
       <c r="R141" s="14"/>
     </row>
-    <row r="142" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="10" t="n">
         <v>141</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E142" s="10" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="F142" s="10" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="G142" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H142" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I142" s="10" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K142" s="12"/>
-      <c r="L142" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K142" s="12" t="n">
+        <v>46276</v>
+      </c>
+      <c r="L142" s="13" t="n">
         <f aca="false">IF(K142="","",K142-Resumo!$B$3)</f>
-        <v/>
+        <v>-42</v>
       </c>
       <c r="M142" s="10" t="s">
-        <v>79</v>
+        <v>312</v>
       </c>
       <c r="N142" s="10" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="O142" s="14"/>
       <c r="P142" s="14" t="s">
@@ -9303,25 +9318,25 @@
         <v>45</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="F143" s="10" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="G143" s="12" t="n">
         <v>48215</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I143" s="10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J143" s="10" t="s">
         <v>6</v>
@@ -9335,7 +9350,7 @@
         <v>79</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="O143" s="14"/>
       <c r="P143" s="14" t="s">
@@ -9352,39 +9367,39 @@
         <v>45</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>198</v>
+        <v>309</v>
       </c>
       <c r="E144" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F144" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>47697</v>
+        <v>48215</v>
       </c>
       <c r="H144" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I144" s="10"/>
+        <v>16</v>
+      </c>
+      <c r="I144" s="10" t="n">
+        <v>14</v>
+      </c>
       <c r="J144" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K144" s="12" t="n">
-        <v>46344</v>
-      </c>
-      <c r="L144" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K144" s="12"/>
+      <c r="L144" s="13" t="str">
         <f aca="false">IF(K144="","",K144-Resumo!$B$3)</f>
-        <v>26</v>
+        <v/>
       </c>
       <c r="M144" s="10" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="N144" s="10" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="O144" s="14"/>
       <c r="P144" s="14" t="s">
@@ -9393,49 +9408,47 @@
       <c r="Q144" s="15"/>
       <c r="R144" s="14"/>
     </row>
-    <row r="145" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="10" t="n">
         <v>144</v>
       </c>
       <c r="B145" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>198</v>
+        <v>309</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F145" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>47697</v>
+        <v>48215</v>
       </c>
       <c r="H145" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I145" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="I145" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="J145" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K145" s="12" t="n">
-        <v>46127</v>
-      </c>
-      <c r="L145" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K145" s="12"/>
+      <c r="L145" s="13" t="str">
         <f aca="false">IF(K145="","",K145-Resumo!$B$3)</f>
-        <v>-191</v>
+        <v/>
       </c>
       <c r="M145" s="10" t="s">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="O145" s="14"/>
       <c r="P145" s="14" t="s">
@@ -9449,44 +9462,42 @@
         <v>145</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>198</v>
+        <v>309</v>
       </c>
       <c r="E146" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F146" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>47697</v>
+        <v>48215</v>
       </c>
       <c r="H146" s="10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I146" s="10" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J146" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K146" s="12" t="n">
-        <v>46282</v>
-      </c>
-      <c r="L146" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K146" s="12"/>
+      <c r="L146" s="13" t="str">
         <f aca="false">IF(K146="","",K146-Resumo!$B$3)</f>
-        <v>-36</v>
+        <v/>
       </c>
       <c r="M146" s="10" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="N146" s="10" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="O146" s="14"/>
       <c r="P146" s="14" t="s">
@@ -9500,44 +9511,42 @@
         <v>146</v>
       </c>
       <c r="B147" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>311</v>
+        <v>204</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F147" s="10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>46244</v>
+        <v>47697</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="I147" s="10" t="n">
-        <v>21</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I147" s="10"/>
       <c r="J147" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>46124</v>
+        <v>46344</v>
       </c>
       <c r="L147" s="13" t="n">
         <f aca="false">IF(K147="","",K147-Resumo!$B$3)</f>
-        <v>-194</v>
+        <v>26</v>
       </c>
       <c r="M147" s="10" t="s">
-        <v>314</v>
+        <v>51</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="O147" s="14"/>
       <c r="P147" s="14" t="s">
@@ -9554,19 +9563,19 @@
         <v>55</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D148" s="10" t="s">
-        <v>311</v>
+        <v>204</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F148" s="10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>46244</v>
+        <v>47697</v>
       </c>
       <c r="H148" s="10" t="s">
         <v>14</v>
@@ -9578,14 +9587,14 @@
         <v>56</v>
       </c>
       <c r="K148" s="12" t="n">
-        <v>46276</v>
+        <v>46127</v>
       </c>
       <c r="L148" s="13" t="n">
         <f aca="false">IF(K148="","",K148-Resumo!$B$3)</f>
-        <v>-42</v>
+        <v>-191</v>
       </c>
       <c r="M148" s="10" t="s">
-        <v>306</v>
+        <v>268</v>
       </c>
       <c r="N148" s="10" t="s">
         <v>54</v>
@@ -9602,39 +9611,41 @@
         <v>148</v>
       </c>
       <c r="B149" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D149" s="10" t="s">
-        <v>311</v>
+        <v>204</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F149" s="10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>46244</v>
+        <v>47697</v>
       </c>
       <c r="H149" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J149" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K149" s="12"/>
-      <c r="L149" s="13" t="str">
+        <v>56</v>
+      </c>
+      <c r="K149" s="12" t="n">
+        <v>46282</v>
+      </c>
+      <c r="L149" s="13" t="n">
         <f aca="false">IF(K149="","",K149-Resumo!$B$3)</f>
-        <v/>
+        <v>-36</v>
       </c>
       <c r="M149" s="10" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="N149" s="10" t="s">
         <v>58</v>
@@ -9646,9 +9657,160 @@
       <c r="Q149" s="15"/>
       <c r="R149" s="14"/>
     </row>
+    <row r="150" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="10" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C150" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="D150" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="E150" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="F150" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H150" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I150" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="J150" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K150" s="12" t="n">
+        <v>46124</v>
+      </c>
+      <c r="L150" s="13" t="n">
+        <f aca="false">IF(K150="","",K150-Resumo!$B$3)</f>
+        <v>-194</v>
+      </c>
+      <c r="M150" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="N150" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="O150" s="14"/>
+      <c r="P150" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q150" s="15"/>
+      <c r="R150" s="14"/>
+    </row>
+    <row r="151" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="D151" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="E151" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="F151" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H151" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I151" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J151" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K151" s="12" t="n">
+        <v>46276</v>
+      </c>
+      <c r="L151" s="13" t="n">
+        <f aca="false">IF(K151="","",K151-Resumo!$B$3)</f>
+        <v>-42</v>
+      </c>
+      <c r="M151" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="N151" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="O151" s="14"/>
+      <c r="P151" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q151" s="15"/>
+      <c r="R151" s="14"/>
+    </row>
+    <row r="152" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="10" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C152" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="D152" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="E152" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="F152" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H152" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I152" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="J152" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K152" s="12"/>
+      <c r="L152" s="13" t="str">
+        <f aca="false">IF(K152="","",K152-Resumo!$B$3)</f>
+        <v/>
+      </c>
+      <c r="M152" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N152" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O152" s="14"/>
+      <c r="P152" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q152" s="15"/>
+      <c r="R152" s="14"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R149"/>
-  <conditionalFormatting sqref="J2:J149">
+  <autoFilter ref="A1:R152"/>
+  <conditionalFormatting sqref="J2:J152">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$J2="Vencida"</formula>
     </cfRule>
@@ -9659,12 +9821,12 @@
       <formula>$J2="Sem data"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B149">
+  <conditionalFormatting sqref="B2:B152">
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>$B2="Alta"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P149">
+  <conditionalFormatting sqref="P2:P152">
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>$P2="Resolvido"</formula>
     </cfRule>
@@ -9673,7 +9835,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P149" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P152" type="list">
       <formula1>"A fazer,Em andamento,Aguardando cliente,Resolvido,Já estava em dia"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9694,7 +9856,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -9718,7 +9880,7 @@
         <v>8</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9726,15 +9888,15 @@
         <v>46</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A2,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A2,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A2,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A2,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A2,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A2,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>2</v>
       </c>
       <c r="E2" s="7" t="n">
@@ -9742,7 +9904,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A2,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A2,Pendências!$B$2:$B$152,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9751,15 +9913,15 @@
         <v>59</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A3,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A3,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A3,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A3,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A3,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A3,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E3" s="7" t="n">
@@ -9767,7 +9929,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A3,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A3,Pendências!$B$2:$B$152,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9776,15 +9938,15 @@
         <v>64</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A4,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A4,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A4,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A4,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A4,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A4,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
@@ -9792,7 +9954,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A4,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A4,Pendências!$B$2:$B$152,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9801,15 +9963,15 @@
         <v>69</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A5,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A5,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A5,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A5,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A5,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A5,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
@@ -9817,7 +9979,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A5,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A5,Pendências!$B$2:$B$152,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9826,15 +9988,15 @@
         <v>75</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A6,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A6,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A6,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A6,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A6,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A6,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
@@ -9842,7 +10004,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A6,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A6,Pendências!$B$2:$B$152,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -9851,15 +10013,15 @@
         <v>81</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A7,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A7,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>5</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A7,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A7,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A7,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A7,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
@@ -9867,7 +10029,7 @@
         <v>7</v>
       </c>
       <c r="F7" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A7,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A7,Pendências!$B$2:$B$152,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -9876,15 +10038,15 @@
         <v>94</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A8,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A8,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A8,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A8,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A8,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A8,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
@@ -9892,7 +10054,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A8,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A8,Pendências!$B$2:$B$152,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9901,15 +10063,15 @@
         <v>101</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A9,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A9,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A9,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A9,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A9,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A9,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
@@ -9917,7 +10079,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A9,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A9,Pendências!$B$2:$B$152,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -9926,15 +10088,15 @@
         <v>105</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A10,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A10,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A10,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A10,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A10,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A10,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E10" s="7" t="n">
@@ -9942,7 +10104,7 @@
         <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A10,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A10,Pendências!$B$2:$B$152,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -9951,15 +10113,15 @@
         <v>111</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A11,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A11,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>0</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A11,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A11,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A11,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A11,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E11" s="7" t="n">
@@ -9967,7 +10129,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A11,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A11,Pendências!$B$2:$B$152,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -9976,15 +10138,15 @@
         <v>115</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A12,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A12,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A12,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A12,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A12,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A12,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
@@ -9992,7 +10154,7 @@
         <v>6</v>
       </c>
       <c r="F12" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A12,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A12,Pendências!$B$2:$B$152,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -10001,15 +10163,15 @@
         <v>119</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A13,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A13,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A13,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A13,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A13,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A13,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
@@ -10017,7 +10179,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A13,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A13,Pendências!$B$2:$B$152,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -10026,15 +10188,15 @@
         <v>123</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A14,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A14,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A14,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A14,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A14,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A14,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
@@ -10042,7 +10204,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A14,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A14,Pendências!$B$2:$B$152,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -10051,15 +10213,15 @@
         <v>127</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A15,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A15,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A15,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A15,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A15,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A15,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
@@ -10067,7 +10229,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A15,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A15,Pendências!$B$2:$B$152,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -10076,15 +10238,15 @@
         <v>132</v>
       </c>
       <c r="B16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A16,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A16,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A16,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A16,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A16,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A16,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
@@ -10092,7 +10254,7 @@
         <v>4</v>
       </c>
       <c r="F16" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A16,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A16,Pendências!$B$2:$B$152,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -10101,15 +10263,15 @@
         <v>139</v>
       </c>
       <c r="B17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A17,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A17,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A17,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A17,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A17,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A17,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
@@ -10117,7 +10279,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A17,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A17,Pendências!$B$2:$B$152,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -10126,15 +10288,15 @@
         <v>143</v>
       </c>
       <c r="B18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A18,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A18,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>4</v>
       </c>
       <c r="C18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A18,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A18,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A18,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A18,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
@@ -10142,7 +10304,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A18,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A18,Pendências!$B$2:$B$152,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -10151,15 +10313,15 @@
         <v>148</v>
       </c>
       <c r="B19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A19,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A19,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A19,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A19,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A19,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A19,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
@@ -10167,7 +10329,7 @@
         <v>4</v>
       </c>
       <c r="F19" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A19,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A19,Pendências!$B$2:$B$152,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -10176,15 +10338,15 @@
         <v>154</v>
       </c>
       <c r="B20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A20,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A20,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A20,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A20,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A20,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A20,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E20" s="7" t="n">
@@ -10192,7 +10354,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A20,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A20,Pendências!$B$2:$B$152,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -10201,15 +10363,15 @@
         <v>157</v>
       </c>
       <c r="B21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A21,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A21,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A21,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A21,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>2</v>
       </c>
       <c r="D21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A21,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A21,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
@@ -10217,7 +10379,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A21,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A21,Pendências!$B$2:$B$152,"Alta")</f>
         <v>0</v>
       </c>
     </row>
@@ -10226,15 +10388,15 @@
         <v>163</v>
       </c>
       <c r="B22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A22,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A22,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A22,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A22,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A22,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A22,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E22" s="7" t="n">
@@ -10242,7 +10404,7 @@
         <v>3</v>
       </c>
       <c r="F22" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A22,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A22,Pendências!$B$2:$B$152,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -10251,15 +10413,15 @@
         <v>166</v>
       </c>
       <c r="B23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A23,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A23,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A23,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A23,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A23,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A23,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
@@ -10267,7 +10429,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A23,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A23,Pendências!$B$2:$B$152,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -10276,15 +10438,15 @@
         <v>170</v>
       </c>
       <c r="B24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A24,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A24,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A24,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A24,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A24,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A24,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E24" s="7" t="n">
@@ -10292,7 +10454,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A24,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A24,Pendências!$B$2:$B$152,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -10301,15 +10463,15 @@
         <v>174</v>
       </c>
       <c r="B25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A25,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A25,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A25,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A25,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>1</v>
       </c>
       <c r="D25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A25,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A25,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
@@ -10317,7 +10479,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A25,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A25,Pendências!$B$2:$B$152,"Alta")</f>
         <v>1</v>
       </c>
     </row>
@@ -10326,15 +10488,15 @@
         <v>178</v>
       </c>
       <c r="B26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A26,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A26,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A26,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A26,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A26,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A26,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E26" s="7" t="n">
@@ -10342,7 +10504,7 @@
         <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A26,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A26,Pendências!$B$2:$B$152,"Alta")</f>
         <v>2</v>
       </c>
     </row>
@@ -10351,224 +10513,224 @@
         <v>183</v>
       </c>
       <c r="B27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A27,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A27,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A27,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A27,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A27,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A27,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
         <f aca="false">SUM(B27:D27)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A27,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A27,Pendências!$B$2:$B$152,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A28,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A28,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A28,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A28,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A28,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A28,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E28" s="7" t="n">
         <f aca="false">SUM(B28:D28)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A28,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A28,Pendências!$B$2:$B$152,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A29,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A29,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A29,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A29,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A29,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A29,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
         <f aca="false">SUM(B29:D29)</f>
+        <v>3</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A29,Pendências!$B$2:$B$152,"Alta")</f>
         <v>2</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A29,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A30,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A30,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A30,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A30,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A30,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A30,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E30" s="7" t="n">
         <f aca="false">SUM(B30:D30)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F30" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A30,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A30,Pendências!$B$2:$B$152,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A31,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A31,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>5</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A31,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
-      <c r="C31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A31,Pendências!$J$2:$J$149,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A31,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A31,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
         <f aca="false">SUM(B31:D31)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F31" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A31,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A31,Pendências!$B$2:$B$152,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A32,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A32,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>0</v>
       </c>
       <c r="C32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A32,Pendências!$J$2:$J$149,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A32,Pendências!$J$2:$J$152,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A32,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A32,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E32" s="7" t="n">
         <f aca="false">SUM(B32:D32)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A32,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A32,Pendências!$B$2:$B$152,"Alta")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A33,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A33,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A33,Pendências!$J$2:$J$149,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A33,Pendências!$J$2:$J$152,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A33,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A33,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
         <f aca="false">SUM(B33:D33)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F33" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A33,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A33,Pendências!$B$2:$B$152,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A34,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A34,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>3</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A34,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>1</v>
       </c>
-      <c r="C34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A34,Pendências!$J$2:$J$149,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A34,Pendências!$J$2:$J$149,"Vence em breve")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A34,Pendências!$J$2:$J$152,"Vence em breve")</f>
+        <v>0</v>
       </c>
       <c r="E34" s="7" t="n">
         <f aca="false">SUM(B34:D34)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A34,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A34,Pendências!$B$2:$B$152,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A35,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A35,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>1</v>
       </c>
       <c r="C35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A35,Pendências!$J$2:$J$149,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A35,Pendências!$J$2:$J$152,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A35,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A35,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E35" s="7" t="n">
         <f aca="false">SUM(B35:D35)</f>
+        <v>3</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A35,Pendências!$B$2:$B$152,"Alta")</f>
         <v>2</v>
-      </c>
-      <c r="F35" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A35,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10576,24 +10738,24 @@
         <v>233</v>
       </c>
       <c r="B36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A36,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A36,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A36,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A36,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A36,Pendências!$J$2:$J$149,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A36,Pendências!$J$2:$J$152,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E36" s="7" t="n">
         <f aca="false">SUM(B36:D36)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F36" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A36,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A36,Pendências!$B$2:$B$152,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10601,99 +10763,99 @@
         <v>239</v>
       </c>
       <c r="B37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A37,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A37,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>4</v>
       </c>
       <c r="C37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A37,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A37,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A37,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A37,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E37" s="7" t="n">
         <f aca="false">SUM(B37:D37)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F37" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A37,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A37,Pendências!$B$2:$B$152,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A38,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A38,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>1</v>
       </c>
       <c r="C38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A38,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A38,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A38,Pendências!$J$2:$J$149,"Vence em breve")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A38,Pendências!$J$2:$J$152,"Vence em breve")</f>
+        <v>0</v>
       </c>
       <c r="E38" s="7" t="n">
         <f aca="false">SUM(B38:D38)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A38,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A38,Pendências!$B$2:$B$152,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A39,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A39,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A39,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A39,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A39,Pendências!$J$2:$J$149,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A39,Pendências!$J$2:$J$152,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E39" s="7" t="n">
         <f aca="false">SUM(B39:D39)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A39,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A39,Pendências!$B$2:$B$152,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A40,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A40,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A40,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A40,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A40,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A40,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E40" s="7" t="n">
         <f aca="false">SUM(B40:D40)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A40,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A40,Pendências!$B$2:$B$152,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10701,90 +10863,90 @@
         <v>258</v>
       </c>
       <c r="B41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A41,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A41,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A41,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A41,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A41,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A41,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E41" s="7" t="n">
         <f aca="false">SUM(B41:D41)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A41,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A41,Pendências!$B$2:$B$152,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A42,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A42,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A42,Pendências!$J$2:$J$149,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A42,Pendências!$J$2:$J$152,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A42,Pendências!$J$2:$J$149,"Vence em breve")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A42,Pendências!$J$2:$J$152,"Vence em breve")</f>
+        <v>0</v>
       </c>
       <c r="E42" s="7" t="n">
         <f aca="false">SUM(B42:D42)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A42,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A42,Pendências!$B$2:$B$152,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A43,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A43,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A43,Pendências!$J$2:$J$149,"Sem data")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A43,Pendências!$J$2:$J$152,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A43,Pendências!$J$2:$J$149,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A43,Pendências!$J$2:$J$152,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E43" s="7" t="n">
         <f aca="false">SUM(B43:D43)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A43,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A43,Pendências!$B$2:$B$152,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A44,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A44,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>3</v>
       </c>
       <c r="C44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A44,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A44,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>0</v>
       </c>
       <c r="D44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A44,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A44,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E44" s="7" t="n">
@@ -10792,24 +10954,24 @@
         <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A44,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A44,Pendências!$B$2:$B$152,"Alta")</f>
         <v>3</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A45,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A45,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A45,Pendências!$J$2:$J$149,"Sem data")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A45,Pendências!$J$2:$J$152,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A45,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A45,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E45" s="7" t="n">
@@ -10817,24 +10979,24 @@
         <v>3</v>
       </c>
       <c r="F45" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A45,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A45,Pendências!$B$2:$B$152,"Alta")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A46,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A46,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>1</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A46,Pendências!$J$2:$J$152,"Sem data")</f>
         <v>2</v>
       </c>
-      <c r="C46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A46,Pendências!$J$2:$J$149,"Sem data")</f>
-        <v>1</v>
-      </c>
       <c r="D46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A46,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A46,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
       </c>
       <c r="E46" s="7" t="n">
@@ -10842,58 +11004,58 @@
         <v>3</v>
       </c>
       <c r="F46" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A46,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A46,Pendências!$B$2:$B$152,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A47,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A47,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A47,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A47,Pendências!$J$2:$J$152,"Sem data")</f>
+        <v>1</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A47,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
-      </c>
-      <c r="D47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A47,Pendências!$J$2:$J$149,"Vence em breve")</f>
-        <v>1</v>
       </c>
       <c r="E47" s="7" t="n">
         <f aca="false">SUM(B47:D47)</f>
         <v>3</v>
       </c>
       <c r="F47" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A47,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A47,Pendências!$B$2:$B$152,"Alta")</f>
         <v>2</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B48" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A48,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A48,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>2</v>
       </c>
       <c r="C48" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A48,Pendências!$J$2:$J$149,"Sem data")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A48,Pendências!$J$2:$J$152,"Sem data")</f>
+        <v>0</v>
       </c>
       <c r="D48" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A48,Pendências!$J$2:$J$149,"Vence em breve")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A48,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>1</v>
       </c>
       <c r="E48" s="7" t="n">
         <f aca="false">SUM(B48:D48)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F48" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A48,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A48,Pendências!$B$2:$B$152,"Alta")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10901,78 +11063,103 @@
         <v>302</v>
       </c>
       <c r="B49" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A49,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A49,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>4</v>
       </c>
       <c r="C49" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A49,Pendências!$J$2:$J$149,"Sem data")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A49,Pendências!$J$2:$J$152,"Sem data")</f>
+        <v>1</v>
       </c>
       <c r="D49" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A49,Pendências!$J$2:$J$149,"Vence em breve")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A49,Pendências!$J$2:$J$152,"Vence em breve")</f>
+        <v>1</v>
       </c>
       <c r="E49" s="7" t="n">
         <f aca="false">SUM(B49:D49)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F49" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A49,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A49,Pendências!$B$2:$B$152,"Alta")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B50" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A50,Pendências!$J$2:$J$149,"Vencida")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A50,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>3</v>
       </c>
       <c r="C50" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A50,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A50,Pendências!$J$2:$J$152,"Sem data")</f>
+        <v>4</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A50,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>0</v>
-      </c>
-      <c r="D50" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A50,Pendências!$J$2:$J$149,"Vence em breve")</f>
-        <v>1</v>
       </c>
       <c r="E50" s="7" t="n">
         <f aca="false">SUM(B50:D50)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F50" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A50,Pendências!$B$2:$B$149,"Alta")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A50,Pendências!$B$2:$B$152,"Alta")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B51" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A51,Pendências!$J$2:$J$149,"Vencida")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A51,Pendências!$J$2:$J$152,"Vencida")</f>
         <v>2</v>
       </c>
       <c r="C51" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A51,Pendências!$J$2:$J$149,"Sem data")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A51,Pendências!$J$2:$J$152,"Sem data")</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A51,Pendências!$J$2:$J$152,"Vence em breve")</f>
         <v>1</v>
-      </c>
-      <c r="D51" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A51,Pendências!$J$2:$J$149,"Vence em breve")</f>
-        <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
         <f aca="false">SUM(B51:D51)</f>
         <v>3</v>
       </c>
       <c r="F51" s="6" t="n">
-        <f aca="false">COUNTIFS(Pendências!$C$2:$C$149,$A51,Pendências!$B$2:$B$149,"Alta")</f>
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A51,Pendências!$B$2:$B$152,"Alta")</f>
         <v>2</v>
       </c>
     </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="B52" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A52,Pendências!$J$2:$J$152,"Vencida")</f>
+        <v>2</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A52,Pendências!$J$2:$J$152,"Sem data")</f>
+        <v>1</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A52,Pendências!$J$2:$J$152,"Vence em breve")</f>
+        <v>0</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <f aca="false">SUM(B52:D52)</f>
+        <v>3</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <f aca="false">COUNTIFS(Pendências!$C$2:$C$152,$A52,Pendências!$B$2:$B$152,"Alta")</f>
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F51"/>
+  <autoFilter ref="A1:F52"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -10989,7 +11176,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -11017,167 +11204,156 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>349</v>
+        <v>107</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>107</v>
+        <v>335</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
-        <v>355</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
